--- a/eval/results/statistical_tests_full150.xlsx
+++ b/eval/results/statistical_tests_full150.xlsx
@@ -675,7 +675,7 @@
         <v>0.111</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0698</v>
+        <v>0.0693</v>
       </c>
       <c r="J2" t="n">
         <v>0.853</v>
@@ -690,7 +690,7 @@
         <v>0.9330000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>0.793</v>
+        <v>0.8</v>
       </c>
       <c r="O2" t="n">
         <v>0.767</v>
@@ -738,7 +738,7 @@
         <v>0.96</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="AE2" t="n">
         <v>0.887</v>
@@ -811,7 +811,7 @@
         <v>0.111</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0698</v>
+        <v>0.0693</v>
       </c>
       <c r="J3" t="n">
         <v>0.853</v>
@@ -826,7 +826,7 @@
         <v>0.9330000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>0.793</v>
+        <v>0.8</v>
       </c>
       <c r="O3" t="n">
         <v>0.767</v>
@@ -874,7 +874,7 @@
         <v>0.96</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="AE3" t="n">
         <v>0.887</v>
@@ -947,7 +947,7 @@
         <v>0.111</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0959</v>
+        <v>0.0958</v>
       </c>
       <c r="J4" t="n">
         <v>0.853</v>
@@ -962,7 +962,7 @@
         <v>0.9330000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>0.793</v>
+        <v>0.8</v>
       </c>
       <c r="O4" t="n">
         <v>0.767</v>
@@ -1010,7 +1010,7 @@
         <v>0.987</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="AE4" t="n">
         <v>0.84</v>
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.0825</v>
+        <v>0.0934</v>
       </c>
       <c r="F5" t="n">
         <v>0.823</v>
@@ -1083,7 +1083,7 @@
         <v>0.111</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0959</v>
+        <v>0.0958</v>
       </c>
       <c r="J5" t="n">
         <v>0.853</v>
@@ -1098,7 +1098,7 @@
         <v>0.9330000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>0.793</v>
+        <v>0.8</v>
       </c>
       <c r="O5" t="n">
         <v>0.767</v>
@@ -1146,7 +1146,7 @@
         <v>0.987</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="AE5" t="n">
         <v>0.84</v>
@@ -1182,7 +1182,7 @@
         <v>0.633</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.124</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="6">
@@ -1207,19 +1207,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.015</v>
+        <v>0.014</v>
       </c>
       <c r="F6" t="n">
         <v>0.796</v>
       </c>
       <c r="G6" t="n">
-        <v>0.849</v>
+        <v>0.85</v>
       </c>
       <c r="H6" t="n">
         <v>0.152</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0914</v>
+        <v>0.0911</v>
       </c>
       <c r="J6" t="n">
         <v>0.773</v>
@@ -1282,7 +1282,7 @@
         <v>0.98</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.78</v>
+        <v>0.787</v>
       </c>
       <c r="AE6" t="n">
         <v>0.853</v>
@@ -1318,7 +1318,7 @@
         <v>0.7</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.03</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="7">
@@ -1343,19 +1343,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.00257</v>
+        <v>0.00232</v>
       </c>
       <c r="F7" t="n">
         <v>0.796</v>
       </c>
       <c r="G7" t="n">
-        <v>0.849</v>
+        <v>0.85</v>
       </c>
       <c r="H7" t="n">
         <v>0.152</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0914</v>
+        <v>0.0911</v>
       </c>
       <c r="J7" t="n">
         <v>0.773</v>
@@ -1418,7 +1418,7 @@
         <v>0.98</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.78</v>
+        <v>0.787</v>
       </c>
       <c r="AE7" t="n">
         <v>0.853</v>
@@ -1454,7 +1454,7 @@
         <v>0.7</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.00771</v>
+        <v>0.00696</v>
       </c>
     </row>
     <row r="8">
@@ -1479,19 +1479,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.0103</v>
+        <v>0.009889999999999999</v>
       </c>
       <c r="F8" t="n">
         <v>0.796</v>
       </c>
       <c r="G8" t="n">
-        <v>0.869</v>
+        <v>0.87</v>
       </c>
       <c r="H8" t="n">
         <v>0.152</v>
       </c>
       <c r="I8" t="n">
-        <v>0.074</v>
+        <v>0.0738</v>
       </c>
       <c r="J8" t="n">
         <v>0.773</v>
@@ -1554,7 +1554,7 @@
         <v>0.993</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.833</v>
+        <v>0.84</v>
       </c>
       <c r="AE8" t="n">
         <v>0.9</v>
@@ -1590,7 +1590,7 @@
         <v>0.72</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.03</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="9">
@@ -1621,13 +1621,13 @@
         <v>0.796</v>
       </c>
       <c r="G9" t="n">
-        <v>0.869</v>
+        <v>0.87</v>
       </c>
       <c r="H9" t="n">
         <v>0.152</v>
       </c>
       <c r="I9" t="n">
-        <v>0.074</v>
+        <v>0.0738</v>
       </c>
       <c r="J9" t="n">
         <v>0.773</v>
@@ -1690,7 +1690,7 @@
         <v>0.993</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.833</v>
+        <v>0.84</v>
       </c>
       <c r="AE9" t="n">
         <v>0.9</v>
@@ -1751,7 +1751,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.575</v>
+        <v>0.555</v>
       </c>
       <c r="F10" t="n">
         <v>0.777</v>
@@ -1826,7 +1826,7 @@
         <v>0.953</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.713</v>
+        <v>0.72</v>
       </c>
       <c r="AE10" t="n">
         <v>0.733</v>
@@ -1862,7 +1862,7 @@
         <v>0.667</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.666</v>
       </c>
     </row>
     <row r="11">
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.776</v>
+        <v>0.73</v>
       </c>
       <c r="F11" t="n">
         <v>0.777</v>
@@ -1962,7 +1962,7 @@
         <v>0.953</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.713</v>
+        <v>0.72</v>
       </c>
       <c r="AE11" t="n">
         <v>0.733</v>
@@ -2370,7 +2370,7 @@
         <v>0.833</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.95</v>
+        <v>0.951</v>
       </c>
       <c r="AE14" t="n">
         <v>0.921</v>
@@ -2506,7 +2506,7 @@
         <v>0.833</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.95</v>
+        <v>0.951</v>
       </c>
       <c r="AE15" t="n">
         <v>0.921</v>
@@ -2642,7 +2642,7 @@
         <v>0.955</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.929</v>
+        <v>0.93</v>
       </c>
       <c r="AE16" t="n">
         <v>0.833</v>
@@ -2778,7 +2778,7 @@
         <v>0.955</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.929</v>
+        <v>0.93</v>
       </c>
       <c r="AE17" t="n">
         <v>0.833</v>
@@ -3186,7 +3186,7 @@
         <v>1</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.963</v>
+        <v>0.964</v>
       </c>
       <c r="AE20" t="n">
         <v>0.975</v>
@@ -3322,7 +3322,7 @@
         <v>1</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.963</v>
+        <v>0.964</v>
       </c>
       <c r="AE21" t="n">
         <v>0.975</v>
@@ -3383,7 +3383,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.0248</v>
+        <v>0.0247</v>
       </c>
       <c r="F22" t="n">
         <v>0.78</v>
@@ -3458,7 +3458,7 @@
         <v>1</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.953</v>
+        <v>0.954</v>
       </c>
       <c r="AE22" t="n">
         <v>0.9330000000000001</v>
@@ -3494,7 +3494,7 @@
         <v>0.576</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.0496</v>
+        <v>0.0494</v>
       </c>
     </row>
     <row r="23">
@@ -3594,7 +3594,7 @@
         <v>1</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.953</v>
+        <v>0.954</v>
       </c>
       <c r="AE23" t="n">
         <v>0.9330000000000001</v>
@@ -3930,10 +3930,10 @@
         <v>0.00988</v>
       </c>
       <c r="F26" t="n">
-        <v>0.762</v>
+        <v>0.763</v>
       </c>
       <c r="G26" t="n">
-        <v>0.841</v>
+        <v>0.842</v>
       </c>
       <c r="H26" t="n">
         <v>0.152</v>
@@ -3954,7 +3954,7 @@
         <v>0.955</v>
       </c>
       <c r="N26" t="n">
-        <v>0.743</v>
+        <v>0.752</v>
       </c>
       <c r="O26" t="n">
         <v>0.674</v>
@@ -4002,7 +4002,7 @@
         <v>0.909</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.752</v>
+        <v>0.762</v>
       </c>
       <c r="AE26" t="n">
         <v>0.891</v>
@@ -4066,10 +4066,10 @@
         <v>0.0132</v>
       </c>
       <c r="F27" t="n">
-        <v>0.762</v>
+        <v>0.763</v>
       </c>
       <c r="G27" t="n">
-        <v>0.841</v>
+        <v>0.842</v>
       </c>
       <c r="H27" t="n">
         <v>0.152</v>
@@ -4090,7 +4090,7 @@
         <v>0.955</v>
       </c>
       <c r="N27" t="n">
-        <v>0.743</v>
+        <v>0.752</v>
       </c>
       <c r="O27" t="n">
         <v>0.674</v>
@@ -4138,7 +4138,7 @@
         <v>0.909</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.752</v>
+        <v>0.762</v>
       </c>
       <c r="AE27" t="n">
         <v>0.891</v>
@@ -4202,7 +4202,7 @@
         <v>0.342</v>
       </c>
       <c r="F28" t="n">
-        <v>0.762</v>
+        <v>0.763</v>
       </c>
       <c r="G28" t="n">
         <v>0.794</v>
@@ -4226,7 +4226,7 @@
         <v>0.955</v>
       </c>
       <c r="N28" t="n">
-        <v>0.743</v>
+        <v>0.752</v>
       </c>
       <c r="O28" t="n">
         <v>0.674</v>
@@ -4274,7 +4274,7 @@
         <v>0.955</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.782</v>
+        <v>0.792</v>
       </c>
       <c r="AE28" t="n">
         <v>0.924</v>
@@ -4338,7 +4338,7 @@
         <v>0.345</v>
       </c>
       <c r="F29" t="n">
-        <v>0.762</v>
+        <v>0.763</v>
       </c>
       <c r="G29" t="n">
         <v>0.794</v>
@@ -4362,7 +4362,7 @@
         <v>0.955</v>
       </c>
       <c r="N29" t="n">
-        <v>0.743</v>
+        <v>0.752</v>
       </c>
       <c r="O29" t="n">
         <v>0.674</v>
@@ -4410,7 +4410,7 @@
         <v>0.955</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.782</v>
+        <v>0.792</v>
       </c>
       <c r="AE29" t="n">
         <v>0.924</v>
@@ -4471,7 +4471,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.092</v>
+        <v>0.0951</v>
       </c>
       <c r="F30" t="n">
         <v>0.756</v>
@@ -4546,7 +4546,7 @@
         <v>0.864</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.673</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="AE30" t="n">
         <v>0.793</v>
@@ -4582,7 +4582,7 @@
         <v>0.4</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.138</v>
+        <v>0.142</v>
       </c>
     </row>
     <row r="31">
@@ -4682,7 +4682,7 @@
         <v>0.864</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.673</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="AE31" t="n">
         <v>0.793</v>
@@ -4743,7 +4743,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.122</v>
+        <v>0.118</v>
       </c>
       <c r="F32" t="n">
         <v>0.756</v>
@@ -4818,7 +4818,7 @@
         <v>0.955</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.782</v>
+        <v>0.792</v>
       </c>
       <c r="AE32" t="n">
         <v>0.859</v>
@@ -4854,7 +4854,7 @@
         <v>0.491</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.146</v>
+        <v>0.142</v>
       </c>
     </row>
     <row r="33">
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.124</v>
+        <v>0.109</v>
       </c>
       <c r="F33" t="n">
         <v>0.756</v>
@@ -4954,7 +4954,7 @@
         <v>0.955</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.782</v>
+        <v>0.792</v>
       </c>
       <c r="AE33" t="n">
         <v>0.859</v>
@@ -4990,7 +4990,7 @@
         <v>0.491</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.186</v>
+        <v>0.164</v>
       </c>
     </row>
     <row r="34">
@@ -5015,13 +5015,13 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.000735</v>
+        <v>0.000816</v>
       </c>
       <c r="F34" t="n">
         <v>0.679</v>
       </c>
       <c r="G34" t="n">
-        <v>0.578</v>
+        <v>0.579</v>
       </c>
       <c r="H34" t="n">
         <v>0.168</v>
@@ -5090,7 +5090,7 @@
         <v>0.6820000000000001</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.604</v>
+        <v>0.614</v>
       </c>
       <c r="AE34" t="n">
         <v>0.609</v>
@@ -5126,7 +5126,7 @@
         <v>0.345</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.0022</v>
+        <v>0.00245</v>
       </c>
     </row>
     <row r="35">
@@ -5157,7 +5157,7 @@
         <v>0.679</v>
       </c>
       <c r="G35" t="n">
-        <v>0.578</v>
+        <v>0.579</v>
       </c>
       <c r="H35" t="n">
         <v>0.168</v>
@@ -5226,7 +5226,7 @@
         <v>0.6820000000000001</v>
       </c>
       <c r="AD35" t="n">
-        <v>0.604</v>
+        <v>0.614</v>
       </c>
       <c r="AE35" t="n">
         <v>0.609</v>
@@ -5963,13 +5963,13 @@
         <v>0.67</v>
       </c>
       <c r="U2" t="n">
-        <v>0.793</v>
+        <v>0.8</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="W2" t="n">
-        <v>0.885</v>
+        <v>0.884</v>
       </c>
       <c r="X2" t="n">
         <v>1</v>
@@ -6180,7 +6180,7 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>0.95</v>
+        <v>0.951</v>
       </c>
       <c r="W3" t="n">
         <v>1</v>
@@ -6391,10 +6391,10 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0.743</v>
+        <v>0.752</v>
       </c>
       <c r="V4" t="n">
-        <v>0.752</v>
+        <v>0.762</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
@@ -6605,16 +6605,16 @@
         <v>0.5580000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>0.793</v>
+        <v>0.8</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="W5" t="n">
-        <v>0.772</v>
+        <v>0.769</v>
       </c>
       <c r="X5" t="n">
-        <v>0.95</v>
+        <v>0.946</v>
       </c>
       <c r="Y5" t="n">
         <v>0.767</v>
@@ -6638,7 +6638,7 @@
         <v>0.755</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.95</v>
+        <v>0.946</v>
       </c>
       <c r="AG5" t="n">
         <v>0.967</v>
@@ -6822,7 +6822,7 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>0.929</v>
+        <v>0.93</v>
       </c>
       <c r="W6" t="n">
         <v>1</v>
@@ -7033,13 +7033,13 @@
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0.743</v>
+        <v>0.752</v>
       </c>
       <c r="V7" t="n">
-        <v>0.782</v>
+        <v>0.792</v>
       </c>
       <c r="W7" t="n">
-        <v>0.62</v>
+        <v>0.615</v>
       </c>
       <c r="X7" t="n">
         <v>0.784</v>
@@ -7250,10 +7250,10 @@
         <v>0.8</v>
       </c>
       <c r="V8" t="n">
-        <v>0.78</v>
+        <v>0.787</v>
       </c>
       <c r="W8" t="n">
-        <v>0.777</v>
+        <v>0.887</v>
       </c>
       <c r="X8" t="n">
         <v>1</v>
@@ -7467,7 +7467,7 @@
         <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>0.124</v>
+        <v>0.123</v>
       </c>
       <c r="X9" t="n">
         <v>0.248</v>
@@ -7678,13 +7678,13 @@
         <v>0.743</v>
       </c>
       <c r="V10" t="n">
-        <v>0.673</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="W10" t="n">
-        <v>0.353</v>
+        <v>0.437</v>
       </c>
       <c r="X10" t="n">
-        <v>0.707</v>
+        <v>0.794</v>
       </c>
       <c r="Y10" t="n">
         <v>0.761</v>
@@ -7756,7 +7756,7 @@
         <v>0.318</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.707</v>
+        <v>0.727</v>
       </c>
       <c r="AW10" t="n">
         <v>0.6889999999999999</v>
@@ -7892,13 +7892,13 @@
         <v>0.8</v>
       </c>
       <c r="V11" t="n">
-        <v>0.833</v>
+        <v>0.84</v>
       </c>
       <c r="W11" t="n">
-        <v>0.551</v>
+        <v>0.453</v>
       </c>
       <c r="X11" t="n">
-        <v>0.735</v>
+        <v>0.604</v>
       </c>
       <c r="Y11" t="n">
         <v>0.787</v>
@@ -8106,10 +8106,10 @@
         <v>0.949</v>
       </c>
       <c r="V12" t="n">
-        <v>0.963</v>
+        <v>0.964</v>
       </c>
       <c r="W12" t="n">
-        <v>0.716</v>
+        <v>0.715</v>
       </c>
       <c r="X12" t="n">
         <v>1</v>
@@ -8320,13 +8320,13 @@
         <v>0.743</v>
       </c>
       <c r="V13" t="n">
-        <v>0.782</v>
+        <v>0.792</v>
       </c>
       <c r="W13" t="n">
-        <v>0.62</v>
+        <v>0.506</v>
       </c>
       <c r="X13" t="n">
-        <v>0.827</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="Y13" t="n">
         <v>0.761</v>
@@ -8534,7 +8534,7 @@
         <v>0.72</v>
       </c>
       <c r="V14" t="n">
-        <v>0.713</v>
+        <v>0.72</v>
       </c>
       <c r="W14" t="n">
         <v>1</v>
@@ -8748,7 +8748,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="V15" t="n">
-        <v>0.953</v>
+        <v>0.954</v>
       </c>
       <c r="W15" t="n">
         <v>1</v>
@@ -8962,10 +8962,10 @@
         <v>0.624</v>
       </c>
       <c r="V16" t="n">
-        <v>0.604</v>
+        <v>0.614</v>
       </c>
       <c r="W16" t="n">
-        <v>0.885</v>
+        <v>1</v>
       </c>
       <c r="X16" t="n">
         <v>1</v>

--- a/eval/results/statistical_tests_full150.xlsx
+++ b/eval/results/statistical_tests_full150.xlsx
@@ -503,22 +503,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.00037</v>
+        <v>0.000781</v>
       </c>
       <c r="F2" t="n">
-        <v>0.823</v>
+        <v>0.831</v>
       </c>
       <c r="G2" t="n">
-        <v>0.893</v>
+        <v>0.898</v>
       </c>
       <c r="H2" t="n">
-        <v>0.111</v>
+        <v>0.109</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0687</v>
+        <v>0.0654</v>
       </c>
       <c r="J2" t="n">
-        <v>0.00222</v>
+        <v>0.00469</v>
       </c>
     </row>
     <row r="3">
@@ -543,22 +543,22 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.000973</v>
+        <v>0.0009790000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>0.823</v>
+        <v>0.831</v>
       </c>
       <c r="G3" t="n">
-        <v>0.893</v>
+        <v>0.898</v>
       </c>
       <c r="H3" t="n">
-        <v>0.111</v>
+        <v>0.109</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0687</v>
+        <v>0.0654</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00561</v>
+        <v>0.00587</v>
       </c>
     </row>
     <row r="4">
@@ -583,22 +583,22 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.0684</v>
+        <v>0.139</v>
       </c>
       <c r="F4" t="n">
-        <v>0.823</v>
+        <v>0.831</v>
       </c>
       <c r="G4" t="n">
-        <v>0.844</v>
+        <v>0.846</v>
       </c>
       <c r="H4" t="n">
-        <v>0.111</v>
+        <v>0.109</v>
       </c>
       <c r="I4" t="n">
-        <v>0.09619999999999999</v>
+        <v>0.097</v>
       </c>
       <c r="J4" t="n">
-        <v>0.103</v>
+        <v>0.209</v>
       </c>
     </row>
     <row r="5">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.0934</v>
+        <v>0.155</v>
       </c>
       <c r="F5" t="n">
-        <v>0.823</v>
+        <v>0.831</v>
       </c>
       <c r="G5" t="n">
-        <v>0.844</v>
+        <v>0.846</v>
       </c>
       <c r="H5" t="n">
-        <v>0.111</v>
+        <v>0.109</v>
       </c>
       <c r="I5" t="n">
-        <v>0.09619999999999999</v>
+        <v>0.097</v>
       </c>
       <c r="J5" t="n">
-        <v>0.14</v>
+        <v>0.232</v>
       </c>
     </row>
     <row r="6">
@@ -663,22 +663,22 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.0145</v>
+        <v>0.0137</v>
       </c>
       <c r="F6" t="n">
-        <v>0.796</v>
+        <v>0.801</v>
       </c>
       <c r="G6" t="n">
-        <v>0.849</v>
+        <v>0.851</v>
       </c>
       <c r="H6" t="n">
-        <v>0.152</v>
+        <v>0.148</v>
       </c>
       <c r="I6" t="n">
         <v>0.0917</v>
       </c>
       <c r="J6" t="n">
-        <v>0.029</v>
+        <v>0.0274</v>
       </c>
     </row>
     <row r="7">
@@ -703,22 +703,22 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.00187</v>
+        <v>0.0023</v>
       </c>
       <c r="F7" t="n">
-        <v>0.796</v>
+        <v>0.801</v>
       </c>
       <c r="G7" t="n">
-        <v>0.849</v>
+        <v>0.851</v>
       </c>
       <c r="H7" t="n">
-        <v>0.152</v>
+        <v>0.148</v>
       </c>
       <c r="I7" t="n">
         <v>0.0917</v>
       </c>
       <c r="J7" t="n">
-        <v>0.00561</v>
+        <v>0.0069</v>
       </c>
     </row>
     <row r="8">
@@ -743,22 +743,22 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.00929</v>
+        <v>0.0092</v>
       </c>
       <c r="F8" t="n">
-        <v>0.796</v>
+        <v>0.801</v>
       </c>
       <c r="G8" t="n">
-        <v>0.87</v>
+        <v>0.871</v>
       </c>
       <c r="H8" t="n">
-        <v>0.152</v>
+        <v>0.148</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0738</v>
+        <v>0.0737</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0279</v>
+        <v>0.0274</v>
       </c>
     </row>
     <row r="9">
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.00898</v>
+        <v>0.008970000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>0.796</v>
+        <v>0.801</v>
       </c>
       <c r="G9" t="n">
-        <v>0.87</v>
+        <v>0.871</v>
       </c>
       <c r="H9" t="n">
-        <v>0.152</v>
+        <v>0.148</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0738</v>
+        <v>0.0737</v>
       </c>
       <c r="J9" t="n">
-        <v>0.018</v>
+        <v>0.0179</v>
       </c>
     </row>
     <row r="10">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.51</v>
+        <v>0.543</v>
       </c>
       <c r="F10" t="n">
-        <v>0.776</v>
+        <v>0.78</v>
       </c>
       <c r="G10" t="n">
-        <v>0.785</v>
+        <v>0.788</v>
       </c>
       <c r="H10" t="n">
-        <v>0.124</v>
+        <v>0.125</v>
       </c>
       <c r="I10" t="n">
-        <v>0.115</v>
+        <v>0.113</v>
       </c>
       <c r="J10" t="n">
-        <v>0.612</v>
+        <v>0.652</v>
       </c>
     </row>
     <row r="11">
@@ -863,22 +863,22 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.706</v>
       </c>
       <c r="F11" t="n">
-        <v>0.776</v>
+        <v>0.78</v>
       </c>
       <c r="G11" t="n">
-        <v>0.785</v>
+        <v>0.788</v>
       </c>
       <c r="H11" t="n">
-        <v>0.124</v>
+        <v>0.125</v>
       </c>
       <c r="I11" t="n">
-        <v>0.115</v>
+        <v>0.113</v>
       </c>
       <c r="J11" t="n">
-        <v>0.776</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="12">
@@ -903,22 +903,22 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.848</v>
+        <v>0.882</v>
       </c>
       <c r="F12" t="n">
-        <v>0.776</v>
+        <v>0.78</v>
       </c>
       <c r="G12" t="n">
-        <v>0.78</v>
+        <v>0.782</v>
       </c>
       <c r="H12" t="n">
-        <v>0.124</v>
+        <v>0.125</v>
       </c>
       <c r="I12" t="n">
-        <v>0.103</v>
+        <v>0.104</v>
       </c>
       <c r="J12" t="n">
-        <v>0.848</v>
+        <v>0.882</v>
       </c>
     </row>
     <row r="13">
@@ -943,22 +943,22 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.776</v>
+        <v>0.82</v>
       </c>
       <c r="F13" t="n">
-        <v>0.776</v>
+        <v>0.78</v>
       </c>
       <c r="G13" t="n">
-        <v>0.78</v>
+        <v>0.782</v>
       </c>
       <c r="H13" t="n">
-        <v>0.124</v>
+        <v>0.125</v>
       </c>
       <c r="I13" t="n">
-        <v>0.103</v>
+        <v>0.104</v>
       </c>
       <c r="J13" t="n">
-        <v>0.776</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="14">
@@ -983,22 +983,22 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.0401</v>
+        <v>0.0588</v>
       </c>
       <c r="F14" t="n">
-        <v>0.833</v>
+        <v>0.843</v>
       </c>
       <c r="G14" t="n">
-        <v>0.902</v>
+        <v>0.907</v>
       </c>
       <c r="H14" t="n">
-        <v>0.161</v>
+        <v>0.16</v>
       </c>
       <c r="I14" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0601</v>
+        <v>0.0882</v>
       </c>
     </row>
     <row r="15">
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.0535</v>
+        <v>0.112</v>
       </c>
       <c r="F15" t="n">
-        <v>0.833</v>
+        <v>0.843</v>
       </c>
       <c r="G15" t="n">
-        <v>0.902</v>
+        <v>0.907</v>
       </c>
       <c r="H15" t="n">
-        <v>0.161</v>
+        <v>0.16</v>
       </c>
       <c r="I15" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0803</v>
+        <v>0.112</v>
       </c>
     </row>
     <row r="16">
@@ -1063,22 +1063,22 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.264</v>
+        <v>0.156</v>
       </c>
       <c r="F16" t="n">
-        <v>0.833</v>
+        <v>0.843</v>
       </c>
       <c r="G16" t="n">
         <v>0.791</v>
       </c>
       <c r="H16" t="n">
-        <v>0.161</v>
+        <v>0.16</v>
       </c>
       <c r="I16" t="n">
-        <v>0.19</v>
+        <v>0.191</v>
       </c>
       <c r="J16" t="n">
-        <v>0.264</v>
+        <v>0.176</v>
       </c>
     </row>
     <row r="17">
@@ -1103,22 +1103,22 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.112</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>0.833</v>
+        <v>0.843</v>
       </c>
       <c r="G17" t="n">
         <v>0.791</v>
       </c>
       <c r="H17" t="n">
-        <v>0.161</v>
+        <v>0.16</v>
       </c>
       <c r="I17" t="n">
-        <v>0.19</v>
+        <v>0.191</v>
       </c>
       <c r="J17" t="n">
-        <v>0.112</v>
+        <v>0.106</v>
       </c>
     </row>
     <row r="18">
@@ -1143,22 +1143,22 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.000685</v>
+        <v>0.00072</v>
       </c>
       <c r="F18" t="n">
-        <v>0.792</v>
+        <v>0.794</v>
       </c>
       <c r="G18" t="n">
         <v>0.912</v>
       </c>
       <c r="H18" t="n">
-        <v>0.204</v>
+        <v>0.202</v>
       </c>
       <c r="I18" t="n">
         <v>0.103</v>
       </c>
       <c r="J18" t="n">
-        <v>0.00205</v>
+        <v>0.00216</v>
       </c>
     </row>
     <row r="19">
@@ -1186,13 +1186,13 @@
         <v>0.000987</v>
       </c>
       <c r="F19" t="n">
-        <v>0.792</v>
+        <v>0.794</v>
       </c>
       <c r="G19" t="n">
         <v>0.912</v>
       </c>
       <c r="H19" t="n">
-        <v>0.204</v>
+        <v>0.202</v>
       </c>
       <c r="I19" t="n">
         <v>0.103</v>
@@ -1223,22 +1223,22 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.167</v>
+        <v>0.176</v>
       </c>
       <c r="F20" t="n">
-        <v>0.792</v>
+        <v>0.794</v>
       </c>
       <c r="G20" t="n">
         <v>0.839</v>
       </c>
       <c r="H20" t="n">
-        <v>0.204</v>
+        <v>0.202</v>
       </c>
       <c r="I20" t="n">
         <v>0.165</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2</v>
+        <v>0.176</v>
       </c>
     </row>
     <row r="21">
@@ -1263,22 +1263,22 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.06909999999999999</v>
+        <v>0.08840000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>0.792</v>
+        <v>0.794</v>
       </c>
       <c r="G21" t="n">
         <v>0.839</v>
       </c>
       <c r="H21" t="n">
-        <v>0.204</v>
+        <v>0.202</v>
       </c>
       <c r="I21" t="n">
         <v>0.165</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0829</v>
+        <v>0.106</v>
       </c>
     </row>
     <row r="22">
@@ -1303,22 +1303,22 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.0248</v>
+        <v>0.0232</v>
       </c>
       <c r="F22" t="n">
-        <v>0.779</v>
+        <v>0.78</v>
       </c>
       <c r="G22" t="n">
-        <v>0.842</v>
+        <v>0.844</v>
       </c>
       <c r="H22" t="n">
         <v>0.21</v>
       </c>
       <c r="I22" t="n">
-        <v>0.171</v>
+        <v>0.17</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0496</v>
+        <v>0.0464</v>
       </c>
     </row>
     <row r="23">
@@ -1343,22 +1343,22 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.0409</v>
+        <v>0.0356</v>
       </c>
       <c r="F23" t="n">
-        <v>0.779</v>
+        <v>0.78</v>
       </c>
       <c r="G23" t="n">
-        <v>0.842</v>
+        <v>0.844</v>
       </c>
       <c r="H23" t="n">
         <v>0.21</v>
       </c>
       <c r="I23" t="n">
-        <v>0.171</v>
+        <v>0.17</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0803</v>
+        <v>0.0712</v>
       </c>
     </row>
     <row r="24">
@@ -1383,10 +1383,10 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4.73e-05</v>
+        <v>4.72e-05</v>
       </c>
       <c r="F24" t="n">
-        <v>0.779</v>
+        <v>0.78</v>
       </c>
       <c r="G24" t="n">
         <v>0.678</v>
@@ -1395,10 +1395,10 @@
         <v>0.21</v>
       </c>
       <c r="I24" t="n">
-        <v>0.202</v>
+        <v>0.203</v>
       </c>
       <c r="J24" t="n">
-        <v>0.000284</v>
+        <v>0.000283</v>
       </c>
     </row>
     <row r="25">
@@ -1426,7 +1426,7 @@
         <v>0.000153</v>
       </c>
       <c r="F25" t="n">
-        <v>0.779</v>
+        <v>0.78</v>
       </c>
       <c r="G25" t="n">
         <v>0.678</v>
@@ -1435,7 +1435,7 @@
         <v>0.21</v>
       </c>
       <c r="I25" t="n">
-        <v>0.202</v>
+        <v>0.203</v>
       </c>
       <c r="J25" t="n">
         <v>0.000918</v>
@@ -1463,22 +1463,22 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.00988</v>
+        <v>0.0138</v>
       </c>
       <c r="F26" t="n">
-        <v>0.762</v>
+        <v>0.77</v>
       </c>
       <c r="G26" t="n">
-        <v>0.842</v>
+        <v>0.848</v>
       </c>
       <c r="H26" t="n">
-        <v>0.152</v>
+        <v>0.149</v>
       </c>
       <c r="I26" t="n">
-        <v>0.128</v>
+        <v>0.127</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0198</v>
+        <v>0.0276</v>
       </c>
     </row>
     <row r="27">
@@ -1503,22 +1503,22 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.0132</v>
+        <v>0.0186</v>
       </c>
       <c r="F27" t="n">
-        <v>0.762</v>
+        <v>0.77</v>
       </c>
       <c r="G27" t="n">
-        <v>0.842</v>
+        <v>0.848</v>
       </c>
       <c r="H27" t="n">
-        <v>0.152</v>
+        <v>0.149</v>
       </c>
       <c r="I27" t="n">
-        <v>0.128</v>
+        <v>0.127</v>
       </c>
       <c r="J27" t="n">
-        <v>0.0264</v>
+        <v>0.0372</v>
       </c>
     </row>
     <row r="28">
@@ -1543,22 +1543,22 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.345</v>
+        <v>0.378</v>
       </c>
       <c r="F28" t="n">
-        <v>0.762</v>
+        <v>0.77</v>
       </c>
       <c r="G28" t="n">
-        <v>0.794</v>
+        <v>0.799</v>
       </c>
       <c r="H28" t="n">
-        <v>0.152</v>
+        <v>0.149</v>
       </c>
       <c r="I28" t="n">
         <v>0.215</v>
       </c>
       <c r="J28" t="n">
-        <v>0.345</v>
+        <v>0.378</v>
       </c>
     </row>
     <row r="29">
@@ -1586,13 +1586,13 @@
         <v>0.345</v>
       </c>
       <c r="F29" t="n">
-        <v>0.762</v>
+        <v>0.77</v>
       </c>
       <c r="G29" t="n">
-        <v>0.794</v>
+        <v>0.799</v>
       </c>
       <c r="H29" t="n">
-        <v>0.152</v>
+        <v>0.149</v>
       </c>
       <c r="I29" t="n">
         <v>0.215</v>
@@ -1623,22 +1623,22 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.0912</v>
+        <v>0.0853</v>
       </c>
       <c r="F30" t="n">
-        <v>0.756</v>
+        <v>0.762</v>
       </c>
       <c r="G30" t="n">
-        <v>0.697</v>
+        <v>0.701</v>
       </c>
       <c r="H30" t="n">
-        <v>0.182</v>
+        <v>0.178</v>
       </c>
       <c r="I30" t="n">
-        <v>0.158</v>
+        <v>0.159</v>
       </c>
       <c r="J30" t="n">
-        <v>0.134</v>
+        <v>0.128</v>
       </c>
     </row>
     <row r="31">
@@ -1663,22 +1663,22 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.156</v>
+        <v>0.14</v>
       </c>
       <c r="F31" t="n">
-        <v>0.756</v>
+        <v>0.762</v>
       </c>
       <c r="G31" t="n">
-        <v>0.697</v>
+        <v>0.701</v>
       </c>
       <c r="H31" t="n">
-        <v>0.182</v>
+        <v>0.178</v>
       </c>
       <c r="I31" t="n">
-        <v>0.158</v>
+        <v>0.159</v>
       </c>
       <c r="J31" t="n">
-        <v>0.187</v>
+        <v>0.168</v>
       </c>
     </row>
     <row r="32">
@@ -1703,22 +1703,22 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.112</v>
+        <v>0.13</v>
       </c>
       <c r="F32" t="n">
-        <v>0.756</v>
+        <v>0.762</v>
       </c>
       <c r="G32" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="H32" t="n">
-        <v>0.182</v>
+        <v>0.178</v>
       </c>
       <c r="I32" t="n">
         <v>0.155</v>
       </c>
       <c r="J32" t="n">
-        <v>0.134</v>
+        <v>0.156</v>
       </c>
     </row>
     <row r="33">
@@ -1746,13 +1746,13 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="F33" t="n">
-        <v>0.756</v>
+        <v>0.762</v>
       </c>
       <c r="G33" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="H33" t="n">
-        <v>0.182</v>
+        <v>0.178</v>
       </c>
       <c r="I33" t="n">
         <v>0.155</v>
@@ -1783,22 +1783,22 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.000908</v>
+        <v>0.00078</v>
       </c>
       <c r="F34" t="n">
-        <v>0.679</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="G34" t="n">
-        <v>0.579</v>
+        <v>0.585</v>
       </c>
       <c r="H34" t="n">
-        <v>0.168</v>
+        <v>0.167</v>
       </c>
       <c r="I34" t="n">
-        <v>0.139</v>
+        <v>0.136</v>
       </c>
       <c r="J34" t="n">
-        <v>0.00272</v>
+        <v>0.00234</v>
       </c>
     </row>
     <row r="35">
@@ -1826,16 +1826,16 @@
         <v>0.00451</v>
       </c>
       <c r="F35" t="n">
-        <v>0.679</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="G35" t="n">
-        <v>0.579</v>
+        <v>0.585</v>
       </c>
       <c r="H35" t="n">
-        <v>0.168</v>
+        <v>0.167</v>
       </c>
       <c r="I35" t="n">
-        <v>0.139</v>
+        <v>0.136</v>
       </c>
       <c r="J35" t="n">
         <v>0.0135</v>
@@ -1863,22 +1863,22 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3.45e-05</v>
+        <v>4.46e-05</v>
       </c>
       <c r="F36" t="n">
-        <v>0.679</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="G36" t="n">
-        <v>0.837</v>
+        <v>0.841</v>
       </c>
       <c r="H36" t="n">
-        <v>0.168</v>
+        <v>0.167</v>
       </c>
       <c r="I36" t="n">
-        <v>0.158</v>
+        <v>0.156</v>
       </c>
       <c r="J36" t="n">
-        <v>0.000207</v>
+        <v>0.000268</v>
       </c>
     </row>
     <row r="37">
@@ -1906,16 +1906,16 @@
         <v>0.000153</v>
       </c>
       <c r="F37" t="n">
-        <v>0.679</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="G37" t="n">
-        <v>0.837</v>
+        <v>0.841</v>
       </c>
       <c r="H37" t="n">
-        <v>0.168</v>
+        <v>0.167</v>
       </c>
       <c r="I37" t="n">
-        <v>0.158</v>
+        <v>0.156</v>
       </c>
       <c r="J37" t="n">
         <v>0.000918</v>
@@ -2090,7 +2090,7 @@
         <v>0.6840000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.842</v>
+        <v>0.898</v>
       </c>
     </row>
     <row r="5">
@@ -2118,16 +2118,16 @@
         <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.947</v>
       </c>
       <c r="G5" t="n">
         <v>0.96</v>
       </c>
       <c r="H5" t="n">
-        <v>0.442</v>
+        <v>0.785</v>
       </c>
       <c r="I5" t="n">
-        <v>0.67</v>
+        <v>0.898</v>
       </c>
     </row>
     <row r="6">
@@ -2158,13 +2158,13 @@
         <v>0.8</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="H6" t="n">
-        <v>0.884</v>
+        <v>0.769</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0.898</v>
       </c>
     </row>
     <row r="7">
@@ -2192,16 +2192,16 @@
         <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>0.767</v>
+        <v>0.793</v>
       </c>
       <c r="G7" t="n">
-        <v>0.887</v>
+        <v>0.907</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00906</v>
+        <v>0.00911</v>
       </c>
       <c r="I7" t="n">
-        <v>0.029</v>
+        <v>0.0292</v>
       </c>
     </row>
     <row r="8">
@@ -2229,16 +2229,16 @@
         <v>7</v>
       </c>
       <c r="F8" t="n">
-        <v>0.827</v>
+        <v>0.847</v>
       </c>
       <c r="G8" t="n">
-        <v>0.887</v>
+        <v>0.893</v>
       </c>
       <c r="H8" t="n">
-        <v>0.187</v>
+        <v>0.303</v>
       </c>
       <c r="I8" t="n">
-        <v>0.393</v>
+        <v>0.606</v>
       </c>
     </row>
     <row r="9">
@@ -2312,7 +2312,7 @@
         <v>0.197</v>
       </c>
       <c r="I10" t="n">
-        <v>0.393</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="11">
@@ -2340,16 +2340,16 @@
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8</v>
+        <v>0.847</v>
       </c>
       <c r="G11" t="n">
-        <v>0.853</v>
+        <v>0.867</v>
       </c>
       <c r="H11" t="n">
-        <v>0.286</v>
+        <v>0.742</v>
       </c>
       <c r="I11" t="n">
-        <v>0.508</v>
+        <v>0.898</v>
       </c>
     </row>
     <row r="12">
@@ -2377,16 +2377,16 @@
         <v>11</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.707</v>
       </c>
       <c r="G12" t="n">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="H12" t="n">
-        <v>0.00395</v>
+        <v>0.0019</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0158</v>
+        <v>0.00761</v>
       </c>
     </row>
     <row r="13">
@@ -2423,7 +2423,7 @@
         <v>0.575</v>
       </c>
       <c r="I13" t="n">
-        <v>0.767</v>
+        <v>0.898</v>
       </c>
     </row>
     <row r="14">
@@ -2497,7 +2497,7 @@
         <v>0.461</v>
       </c>
       <c r="I15" t="n">
-        <v>0.67</v>
+        <v>0.819</v>
       </c>
     </row>
     <row r="16">
@@ -2525,16 +2525,16 @@
         <v>15</v>
       </c>
       <c r="F16" t="n">
-        <v>0.673</v>
+        <v>0.68</v>
       </c>
       <c r="G16" t="n">
-        <v>0.847</v>
+        <v>0.853</v>
       </c>
       <c r="H16" t="n">
-        <v>0.000662</v>
+        <v>0.0005820000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>0.00529</v>
+        <v>0.00356</v>
       </c>
     </row>
     <row r="17">
@@ -2562,16 +2562,16 @@
         <v>16</v>
       </c>
       <c r="F17" t="n">
-        <v>0.633</v>
+        <v>0.64</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="H17" t="n">
-        <v>0.00123</v>
+        <v>0.000668</v>
       </c>
       <c r="I17" t="n">
-        <v>0.00657</v>
+        <v>0.00356</v>
       </c>
     </row>
     <row r="18">
@@ -2608,7 +2608,7 @@
         <v>0.585</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.926</v>
       </c>
     </row>
     <row r="19">
@@ -2682,7 +2682,7 @@
         <v>0.491</v>
       </c>
       <c r="I20" t="n">
-        <v>0.873</v>
+        <v>0.917</v>
       </c>
     </row>
     <row r="21">
@@ -2710,16 +2710,16 @@
         <v>4</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="G21" t="n">
         <v>0.833</v>
       </c>
       <c r="H21" t="n">
-        <v>0.343</v>
+        <v>0.516</v>
       </c>
       <c r="I21" t="n">
-        <v>0.784</v>
+        <v>0.917</v>
       </c>
     </row>
     <row r="22">
@@ -2750,13 +2750,13 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>0.951</v>
+        <v>0.963</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>0.72</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>0.926</v>
       </c>
     </row>
     <row r="23">
@@ -2784,16 +2784,16 @@
         <v>6</v>
       </c>
       <c r="F23" t="n">
-        <v>0.925</v>
+        <v>0.969</v>
       </c>
       <c r="G23" t="n">
-        <v>0.921</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>0.699</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0.926</v>
       </c>
     </row>
     <row r="24">
@@ -2821,16 +2821,16 @@
         <v>7</v>
       </c>
       <c r="F24" t="n">
-        <v>0.904</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>0.915</v>
+        <v>0.926</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>0.752</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>0.926</v>
       </c>
     </row>
     <row r="25">
@@ -2932,10 +2932,10 @@
         <v>10</v>
       </c>
       <c r="F27" t="n">
-        <v>0.903</v>
+        <v>0.913</v>
       </c>
       <c r="G27" t="n">
-        <v>0.914</v>
+        <v>0.917</v>
       </c>
       <c r="H27" t="n">
         <v>1</v>
@@ -2969,16 +2969,16 @@
         <v>11</v>
       </c>
       <c r="F28" t="n">
-        <v>0.869</v>
+        <v>0.873</v>
       </c>
       <c r="G28" t="n">
-        <v>0.924</v>
+        <v>0.927</v>
       </c>
       <c r="H28" t="n">
-        <v>0.395</v>
+        <v>0.396</v>
       </c>
       <c r="I28" t="n">
-        <v>0.79</v>
+        <v>0.905</v>
       </c>
     </row>
     <row r="29">
@@ -3117,16 +3117,16 @@
         <v>15</v>
       </c>
       <c r="F32" t="n">
-        <v>0.61</v>
+        <v>0.617</v>
       </c>
       <c r="G32" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.826</v>
       </c>
       <c r="H32" t="n">
-        <v>0.00738</v>
+        <v>0.00635</v>
       </c>
       <c r="I32" t="n">
-        <v>0.059</v>
+        <v>0.0508</v>
       </c>
     </row>
     <row r="33">
@@ -3154,16 +3154,16 @@
         <v>16</v>
       </c>
       <c r="F33" t="n">
-        <v>0.5</v>
+        <v>0.509</v>
       </c>
       <c r="G33" t="n">
-        <v>0.717</v>
+        <v>0.733</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0231</v>
+        <v>0.0139</v>
       </c>
       <c r="I33" t="n">
-        <v>0.123</v>
+        <v>0.0743</v>
       </c>
     </row>
     <row r="34">
@@ -3237,7 +3237,7 @@
         <v>0.491</v>
       </c>
       <c r="I35" t="n">
-        <v>0.714</v>
+        <v>0.785</v>
       </c>
     </row>
     <row r="36">
@@ -3376,16 +3376,16 @@
         <v>6</v>
       </c>
       <c r="F39" t="n">
-        <v>0.674</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="G39" t="n">
-        <v>0.891</v>
+        <v>0.902</v>
       </c>
       <c r="H39" t="n">
-        <v>0.000568</v>
+        <v>0.000433</v>
       </c>
       <c r="I39" t="n">
-        <v>0.00908</v>
+        <v>0.0069</v>
       </c>
     </row>
     <row r="40">
@@ -3524,16 +3524,16 @@
         <v>10</v>
       </c>
       <c r="F43" t="n">
-        <v>0.7</v>
+        <v>0.787</v>
       </c>
       <c r="G43" t="n">
-        <v>0.8</v>
+        <v>0.825</v>
       </c>
       <c r="H43" t="n">
-        <v>0.201</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I43" t="n">
-        <v>0.321</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -3561,16 +3561,16 @@
         <v>11</v>
       </c>
       <c r="F44" t="n">
-        <v>0.582</v>
+        <v>0.604</v>
       </c>
       <c r="G44" t="n">
-        <v>0.802</v>
+        <v>0.835</v>
       </c>
       <c r="H44" t="n">
-        <v>0.00213</v>
+        <v>0.0008630000000000001</v>
       </c>
       <c r="I44" t="n">
-        <v>0.017</v>
+        <v>0.0069</v>
       </c>
     </row>
     <row r="45">
@@ -3718,7 +3718,7 @@
         <v>0.196</v>
       </c>
       <c r="I48" t="n">
-        <v>0.321</v>
+        <v>0.348</v>
       </c>
     </row>
     <row r="49">
@@ -3749,13 +3749,13 @@
         <v>0.527</v>
       </c>
       <c r="G49" t="n">
-        <v>0.782</v>
+        <v>0.8</v>
       </c>
       <c r="H49" t="n">
-        <v>0.008710000000000001</v>
+        <v>0.00439</v>
       </c>
       <c r="I49" t="n">
-        <v>0.0464</v>
+        <v>0.0234</v>
       </c>
     </row>
     <row r="50">
@@ -3792,7 +3792,7 @@
         <v>0.868</v>
       </c>
       <c r="I50" t="n">
-        <v>0.992</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3829,7 +3829,7 @@
         <v>0.251</v>
       </c>
       <c r="I51" t="n">
-        <v>0.653</v>
+        <v>0.803</v>
       </c>
     </row>
     <row r="52">
@@ -3866,7 +3866,7 @@
         <v>0.541</v>
       </c>
       <c r="I52" t="n">
-        <v>0.787</v>
+        <v>0.866</v>
       </c>
     </row>
     <row r="53">
@@ -3894,16 +3894,16 @@
         <v>4</v>
       </c>
       <c r="F53" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.947</v>
       </c>
       <c r="G53" t="n">
         <v>0.987</v>
       </c>
       <c r="H53" t="n">
-        <v>0.0349</v>
+        <v>0.103</v>
       </c>
       <c r="I53" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.803</v>
       </c>
     </row>
     <row r="54">
@@ -3940,7 +3940,7 @@
         <v>0.769</v>
       </c>
       <c r="I54" t="n">
-        <v>0.946</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3968,16 +3968,16 @@
         <v>6</v>
       </c>
       <c r="F55" t="n">
-        <v>0.767</v>
+        <v>0.793</v>
       </c>
       <c r="G55" t="n">
         <v>0.84</v>
       </c>
       <c r="H55" t="n">
-        <v>0.146</v>
+        <v>0.371</v>
       </c>
       <c r="I55" t="n">
-        <v>0.653</v>
+        <v>0.847</v>
       </c>
     </row>
     <row r="56">
@@ -4005,16 +4005,16 @@
         <v>7</v>
       </c>
       <c r="F56" t="n">
-        <v>0.827</v>
+        <v>0.847</v>
       </c>
       <c r="G56" t="n">
         <v>0.847</v>
       </c>
       <c r="H56" t="n">
-        <v>0.755</v>
+        <v>1</v>
       </c>
       <c r="I56" t="n">
-        <v>0.946</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -4051,7 +4051,7 @@
         <v>0.198</v>
       </c>
       <c r="I57" t="n">
-        <v>0.653</v>
+        <v>0.803</v>
       </c>
     </row>
     <row r="58">
@@ -4088,7 +4088,7 @@
         <v>0.247</v>
       </c>
       <c r="I58" t="n">
-        <v>0.653</v>
+        <v>0.803</v>
       </c>
     </row>
     <row r="59">
@@ -4116,16 +4116,16 @@
         <v>10</v>
       </c>
       <c r="F59" t="n">
-        <v>0.8</v>
+        <v>0.847</v>
       </c>
       <c r="G59" t="n">
-        <v>0.853</v>
+        <v>0.893</v>
       </c>
       <c r="H59" t="n">
-        <v>0.286</v>
+        <v>0.303</v>
       </c>
       <c r="I59" t="n">
-        <v>0.653</v>
+        <v>0.8080000000000001</v>
       </c>
     </row>
     <row r="60">
@@ -4153,16 +4153,16 @@
         <v>11</v>
       </c>
       <c r="F60" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.707</v>
       </c>
       <c r="G60" t="n">
         <v>0.787</v>
       </c>
       <c r="H60" t="n">
-        <v>0.0867</v>
+        <v>0.144</v>
       </c>
       <c r="I60" t="n">
-        <v>0.653</v>
+        <v>0.803</v>
       </c>
     </row>
     <row r="61">
@@ -4199,7 +4199,7 @@
         <v>0.449</v>
       </c>
       <c r="I61" t="n">
-        <v>0.787</v>
+        <v>0.866</v>
       </c>
     </row>
     <row r="62">
@@ -4236,7 +4236,7 @@
         <v>0.501</v>
       </c>
       <c r="I62" t="n">
-        <v>0.787</v>
+        <v>0.866</v>
       </c>
     </row>
     <row r="63">
@@ -4301,16 +4301,16 @@
         <v>15</v>
       </c>
       <c r="F64" t="n">
-        <v>0.673</v>
+        <v>0.68</v>
       </c>
       <c r="G64" t="n">
         <v>0.713</v>
       </c>
       <c r="H64" t="n">
-        <v>0.531</v>
+        <v>0.616</v>
       </c>
       <c r="I64" t="n">
-        <v>0.787</v>
+        <v>0.895</v>
       </c>
     </row>
     <row r="65">
@@ -4338,7 +4338,7 @@
         <v>16</v>
       </c>
       <c r="F65" t="n">
-        <v>0.633</v>
+        <v>0.64</v>
       </c>
       <c r="G65" t="n">
         <v>0.633</v>
@@ -4458,7 +4458,7 @@
         <v>0.277</v>
       </c>
       <c r="I68" t="n">
-        <v>0.654</v>
+        <v>0.651</v>
       </c>
     </row>
     <row r="69">
@@ -4486,16 +4486,16 @@
         <v>4</v>
       </c>
       <c r="F69" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="G69" t="n">
         <v>0.955</v>
       </c>
       <c r="H69" t="n">
-        <v>0.0316</v>
+        <v>0.0638</v>
       </c>
       <c r="I69" t="n">
-        <v>0.505</v>
+        <v>0.404</v>
       </c>
     </row>
     <row r="70">
@@ -4560,16 +4560,16 @@
         <v>6</v>
       </c>
       <c r="F71" t="n">
-        <v>0.925</v>
+        <v>0.969</v>
       </c>
       <c r="G71" t="n">
         <v>0.833</v>
       </c>
       <c r="H71" t="n">
-        <v>0.103</v>
+        <v>0.00604</v>
       </c>
       <c r="I71" t="n">
-        <v>0.654</v>
+        <v>0.09660000000000001</v>
       </c>
     </row>
     <row r="72">
@@ -4597,16 +4597,16 @@
         <v>7</v>
       </c>
       <c r="F72" t="n">
-        <v>0.904</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="G72" t="n">
         <v>0.844</v>
       </c>
       <c r="H72" t="n">
-        <v>0.348</v>
+        <v>0.0757</v>
       </c>
       <c r="I72" t="n">
-        <v>0.654</v>
+        <v>0.404</v>
       </c>
     </row>
     <row r="73">
@@ -4643,7 +4643,7 @@
         <v>0.138</v>
       </c>
       <c r="I73" t="n">
-        <v>0.654</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="74">
@@ -4708,16 +4708,16 @@
         <v>10</v>
       </c>
       <c r="F75" t="n">
-        <v>0.903</v>
+        <v>0.913</v>
       </c>
       <c r="G75" t="n">
-        <v>0.953</v>
+        <v>0.957</v>
       </c>
       <c r="H75" t="n">
-        <v>0.32</v>
+        <v>0.326</v>
       </c>
       <c r="I75" t="n">
-        <v>0.654</v>
+        <v>0.651</v>
       </c>
     </row>
     <row r="76">
@@ -4745,7 +4745,7 @@
         <v>11</v>
       </c>
       <c r="F76" t="n">
-        <v>0.869</v>
+        <v>0.873</v>
       </c>
       <c r="G76" t="n">
         <v>0.873</v>
@@ -4865,7 +4865,7 @@
         <v>0.284</v>
       </c>
       <c r="I79" t="n">
-        <v>0.654</v>
+        <v>0.651</v>
       </c>
     </row>
     <row r="80">
@@ -4893,16 +4893,16 @@
         <v>15</v>
       </c>
       <c r="F80" t="n">
-        <v>0.61</v>
+        <v>0.617</v>
       </c>
       <c r="G80" t="n">
         <v>0.707</v>
       </c>
       <c r="H80" t="n">
-        <v>0.282</v>
+        <v>0.285</v>
       </c>
       <c r="I80" t="n">
-        <v>0.654</v>
+        <v>0.651</v>
       </c>
     </row>
     <row r="81">
@@ -4930,7 +4930,7 @@
         <v>16</v>
       </c>
       <c r="F81" t="n">
-        <v>0.5</v>
+        <v>0.509</v>
       </c>
       <c r="G81" t="n">
         <v>0.5</v>
@@ -5050,7 +5050,7 @@
         <v>0.491</v>
       </c>
       <c r="I84" t="n">
-        <v>0.714</v>
+        <v>0.784</v>
       </c>
     </row>
     <row r="85">
@@ -5152,16 +5152,16 @@
         <v>6</v>
       </c>
       <c r="F87" t="n">
-        <v>0.674</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="G87" t="n">
         <v>0.924</v>
       </c>
       <c r="H87" t="n">
-        <v>3.3e-05</v>
+        <v>6.35e-05</v>
       </c>
       <c r="I87" t="n">
-        <v>0.000529</v>
+        <v>0.00102</v>
       </c>
     </row>
     <row r="88">
@@ -5300,16 +5300,16 @@
         <v>10</v>
       </c>
       <c r="F91" t="n">
-        <v>0.7</v>
+        <v>0.787</v>
       </c>
       <c r="G91" t="n">
-        <v>0.762</v>
+        <v>0.838</v>
       </c>
       <c r="H91" t="n">
-        <v>0.476</v>
+        <v>0.544</v>
       </c>
       <c r="I91" t="n">
-        <v>0.714</v>
+        <v>0.784</v>
       </c>
     </row>
     <row r="92">
@@ -5337,16 +5337,16 @@
         <v>11</v>
       </c>
       <c r="F92" t="n">
-        <v>0.582</v>
+        <v>0.604</v>
       </c>
       <c r="G92" t="n">
         <v>0.758</v>
       </c>
       <c r="H92" t="n">
-        <v>0.0176</v>
+        <v>0.0382</v>
       </c>
       <c r="I92" t="n">
-        <v>0.141</v>
+        <v>0.204</v>
       </c>
     </row>
     <row r="93">
@@ -5457,7 +5457,7 @@
         <v>0.407</v>
       </c>
       <c r="I95" t="n">
-        <v>0.714</v>
+        <v>0.724</v>
       </c>
     </row>
     <row r="96">
@@ -5531,7 +5531,7 @@
         <v>0.033</v>
       </c>
       <c r="I97" t="n">
-        <v>0.176</v>
+        <v>0.204</v>
       </c>
     </row>
     <row r="98">
@@ -5568,7 +5568,7 @@
         <v>0.312</v>
       </c>
       <c r="I98" t="n">
-        <v>0.833</v>
+        <v>0.908</v>
       </c>
     </row>
     <row r="99">
@@ -5707,13 +5707,13 @@
         <v>5</v>
       </c>
       <c r="F102" t="n">
-        <v>0.8</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="G102" t="n">
         <v>0.787</v>
       </c>
       <c r="H102" t="n">
-        <v>0.887</v>
+        <v>0.774</v>
       </c>
       <c r="I102" t="n">
         <v>1</v>
@@ -5892,16 +5892,16 @@
         <v>10</v>
       </c>
       <c r="F107" t="n">
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
       <c r="G107" t="n">
-        <v>0.833</v>
+        <v>0.867</v>
       </c>
       <c r="H107" t="n">
-        <v>0.306</v>
+        <v>0.341</v>
       </c>
       <c r="I107" t="n">
-        <v>0.833</v>
+        <v>0.908</v>
       </c>
     </row>
     <row r="108">
@@ -6114,16 +6114,16 @@
         <v>16</v>
       </c>
       <c r="F113" t="n">
-        <v>0.433</v>
+        <v>0.46</v>
       </c>
       <c r="G113" t="n">
         <v>0.7</v>
       </c>
       <c r="H113" t="n">
-        <v>4.85e-06</v>
+        <v>3.88e-05</v>
       </c>
       <c r="I113" t="n">
-        <v>7.76e-05</v>
+        <v>0.000621</v>
       </c>
     </row>
     <row r="114">
@@ -6299,16 +6299,16 @@
         <v>5</v>
       </c>
       <c r="F118" t="n">
-        <v>0.949</v>
+        <v>0.962</v>
       </c>
       <c r="G118" t="n">
         <v>1</v>
       </c>
       <c r="H118" t="n">
-        <v>0.123</v>
+        <v>0.248</v>
       </c>
       <c r="I118" t="n">
-        <v>0.248</v>
+        <v>0.444</v>
       </c>
     </row>
     <row r="119">
@@ -6484,10 +6484,10 @@
         <v>10</v>
       </c>
       <c r="F123" t="n">
-        <v>0.98</v>
+        <v>0.982</v>
       </c>
       <c r="G123" t="n">
-        <v>0.966</v>
+        <v>0.969</v>
       </c>
       <c r="H123" t="n">
         <v>1</v>
@@ -6567,7 +6567,7 @@
         <v>0.124</v>
       </c>
       <c r="I125" t="n">
-        <v>0.248</v>
+        <v>0.283</v>
       </c>
     </row>
     <row r="126">
@@ -6706,16 +6706,16 @@
         <v>16</v>
       </c>
       <c r="F129" t="n">
-        <v>0.364</v>
+        <v>0.38</v>
       </c>
       <c r="G129" t="n">
         <v>0.647</v>
       </c>
       <c r="H129" t="n">
-        <v>0.00519</v>
+        <v>0.00953</v>
       </c>
       <c r="I129" t="n">
-        <v>0.0277</v>
+        <v>0.0508</v>
       </c>
     </row>
     <row r="130">
@@ -7076,13 +7076,13 @@
         <v>10</v>
       </c>
       <c r="F139" t="n">
-        <v>0.6</v>
+        <v>0.675</v>
       </c>
       <c r="G139" t="n">
-        <v>0.713</v>
+        <v>0.775</v>
       </c>
       <c r="H139" t="n">
-        <v>0.183</v>
+        <v>0.215</v>
       </c>
       <c r="I139" t="n">
         <v>0.642</v>
@@ -7298,16 +7298,16 @@
         <v>16</v>
       </c>
       <c r="F145" t="n">
-        <v>0.727</v>
+        <v>0.745</v>
       </c>
       <c r="G145" t="n">
         <v>0.4</v>
       </c>
       <c r="H145" t="n">
-        <v>0.000985</v>
+        <v>0.000461</v>
       </c>
       <c r="I145" t="n">
-        <v>0.00788</v>
+        <v>0.00369</v>
       </c>
     </row>
     <row r="146">
@@ -7483,16 +7483,16 @@
         <v>5</v>
       </c>
       <c r="F150" t="n">
-        <v>0.8</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="G150" t="n">
         <v>0.84</v>
       </c>
       <c r="H150" t="n">
-        <v>0.453</v>
+        <v>0.545</v>
       </c>
       <c r="I150" t="n">
-        <v>0.604</v>
+        <v>0.727</v>
       </c>
     </row>
     <row r="151">
@@ -7640,7 +7640,7 @@
         <v>0.0356</v>
       </c>
       <c r="I154" t="n">
-        <v>0.0813</v>
+        <v>0.0949</v>
       </c>
     </row>
     <row r="155">
@@ -7668,16 +7668,16 @@
         <v>10</v>
       </c>
       <c r="F155" t="n">
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
       <c r="G155" t="n">
-        <v>0.88</v>
+        <v>0.9</v>
       </c>
       <c r="H155" t="n">
-        <v>0.0307</v>
+        <v>0.0663</v>
       </c>
       <c r="I155" t="n">
-        <v>0.0813</v>
+        <v>0.133</v>
       </c>
     </row>
     <row r="156">
@@ -7708,13 +7708,13 @@
         <v>0.787</v>
       </c>
       <c r="G156" t="n">
-        <v>0.8</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="H156" t="n">
-        <v>0.887</v>
+        <v>0.774</v>
       </c>
       <c r="I156" t="n">
-        <v>1</v>
+        <v>0.885</v>
       </c>
     </row>
     <row r="157">
@@ -7825,7 +7825,7 @@
         <v>0.0467</v>
       </c>
       <c r="I159" t="n">
-        <v>0.09329999999999999</v>
+        <v>0.107</v>
       </c>
     </row>
     <row r="160">
@@ -7862,7 +7862,7 @@
         <v>3.53e-06</v>
       </c>
       <c r="I160" t="n">
-        <v>2.82e-05</v>
+        <v>5.65e-05</v>
       </c>
     </row>
     <row r="161">
@@ -7890,16 +7890,16 @@
         <v>16</v>
       </c>
       <c r="F161" t="n">
-        <v>0.433</v>
+        <v>0.46</v>
       </c>
       <c r="G161" t="n">
         <v>0.72</v>
       </c>
       <c r="H161" t="n">
-        <v>7.67e-07</v>
+        <v>7.19e-06</v>
       </c>
       <c r="I161" t="n">
-        <v>1.23e-05</v>
+        <v>5.75e-05</v>
       </c>
     </row>
     <row r="162">
@@ -8075,13 +8075,13 @@
         <v>5</v>
       </c>
       <c r="F166" t="n">
-        <v>0.949</v>
+        <v>0.962</v>
       </c>
       <c r="G166" t="n">
         <v>0.964</v>
       </c>
       <c r="H166" t="n">
-        <v>0.715</v>
+        <v>1</v>
       </c>
       <c r="I166" t="n">
         <v>1</v>
@@ -8260,13 +8260,13 @@
         <v>10</v>
       </c>
       <c r="F171" t="n">
-        <v>0.98</v>
+        <v>0.982</v>
       </c>
       <c r="G171" t="n">
-        <v>0.956</v>
+        <v>0.958</v>
       </c>
       <c r="H171" t="n">
-        <v>0.639</v>
+        <v>0.631</v>
       </c>
       <c r="I171" t="n">
         <v>1</v>
@@ -8300,10 +8300,10 @@
         <v>0.864</v>
       </c>
       <c r="G172" t="n">
-        <v>0.877</v>
+        <v>0.878</v>
       </c>
       <c r="H172" t="n">
-        <v>1</v>
+        <v>0.819</v>
       </c>
       <c r="I172" t="n">
         <v>1</v>
@@ -8482,16 +8482,16 @@
         <v>16</v>
       </c>
       <c r="F177" t="n">
-        <v>0.364</v>
+        <v>0.38</v>
       </c>
       <c r="G177" t="n">
         <v>0.659</v>
       </c>
       <c r="H177" t="n">
-        <v>0.00163</v>
+        <v>0.00307</v>
       </c>
       <c r="I177" t="n">
-        <v>0.013</v>
+        <v>0.0246</v>
       </c>
     </row>
     <row r="178">
@@ -8824,7 +8824,7 @@
         <v>0.0174</v>
       </c>
       <c r="I186" t="n">
-        <v>0.0742</v>
+        <v>0.0697</v>
       </c>
     </row>
     <row r="187">
@@ -8852,16 +8852,16 @@
         <v>10</v>
       </c>
       <c r="F187" t="n">
-        <v>0.6</v>
+        <v>0.675</v>
       </c>
       <c r="G187" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.85</v>
       </c>
       <c r="H187" t="n">
-        <v>0.00518</v>
+        <v>0.0151</v>
       </c>
       <c r="I187" t="n">
-        <v>0.0415</v>
+        <v>0.0697</v>
       </c>
     </row>
     <row r="188">
@@ -8892,10 +8892,10 @@
         <v>0.769</v>
       </c>
       <c r="G188" t="n">
-        <v>0.78</v>
+        <v>0.791</v>
       </c>
       <c r="H188" t="n">
-        <v>1</v>
+        <v>0.858</v>
       </c>
       <c r="I188" t="n">
         <v>1</v>
@@ -9074,16 +9074,16 @@
         <v>16</v>
       </c>
       <c r="F193" t="n">
-        <v>0.727</v>
+        <v>0.745</v>
       </c>
       <c r="G193" t="n">
         <v>0.491</v>
       </c>
       <c r="H193" t="n">
-        <v>0.0185</v>
+        <v>0.0103</v>
       </c>
       <c r="I193" t="n">
-        <v>0.0742</v>
+        <v>0.0697</v>
       </c>
     </row>
     <row r="194">
@@ -9120,7 +9120,7 @@
         <v>0.318</v>
       </c>
       <c r="I194" t="n">
-        <v>0.75</v>
+        <v>0.826</v>
       </c>
     </row>
     <row r="195">
@@ -9231,7 +9231,7 @@
         <v>0.335</v>
       </c>
       <c r="I197" t="n">
-        <v>0.75</v>
+        <v>0.826</v>
       </c>
     </row>
     <row r="198">
@@ -9305,7 +9305,7 @@
         <v>0.375</v>
       </c>
       <c r="I199" t="n">
-        <v>0.75</v>
+        <v>0.826</v>
       </c>
     </row>
     <row r="200">
@@ -9407,16 +9407,16 @@
         <v>9</v>
       </c>
       <c r="F202" t="n">
-        <v>0.613</v>
+        <v>0.607</v>
       </c>
       <c r="G202" t="n">
         <v>0.553</v>
       </c>
       <c r="H202" t="n">
-        <v>0.349</v>
+        <v>0.413</v>
       </c>
       <c r="I202" t="n">
-        <v>0.75</v>
+        <v>0.826</v>
       </c>
     </row>
     <row r="203">
@@ -9444,16 +9444,16 @@
         <v>10</v>
       </c>
       <c r="F203" t="n">
-        <v>0.767</v>
+        <v>0.82</v>
       </c>
       <c r="G203" t="n">
-        <v>0.7</v>
+        <v>0.74</v>
       </c>
       <c r="H203" t="n">
-        <v>0.24</v>
+        <v>0.125</v>
       </c>
       <c r="I203" t="n">
-        <v>0.75</v>
+        <v>0.499</v>
       </c>
     </row>
     <row r="204">
@@ -9481,13 +9481,13 @@
         <v>11</v>
       </c>
       <c r="F204" t="n">
-        <v>0.74</v>
+        <v>0.747</v>
       </c>
       <c r="G204" t="n">
         <v>0.72</v>
       </c>
       <c r="H204" t="n">
-        <v>0.795</v>
+        <v>0.695</v>
       </c>
       <c r="I204" t="n">
         <v>1</v>
@@ -9669,10 +9669,10 @@
         <v>0.547</v>
       </c>
       <c r="G209" t="n">
-        <v>0.667</v>
+        <v>0.673</v>
       </c>
       <c r="H209" t="n">
-        <v>0.0443</v>
+        <v>0.0329</v>
       </c>
       <c r="I209" t="n">
         <v>0.464</v>
@@ -9897,7 +9897,7 @@
         <v>0.136</v>
       </c>
       <c r="I215" t="n">
-        <v>0.456</v>
+        <v>0.434</v>
       </c>
     </row>
     <row r="216">
@@ -10036,16 +10036,16 @@
         <v>10</v>
       </c>
       <c r="F219" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.949</v>
       </c>
       <c r="G219" t="n">
-        <v>0.872</v>
+        <v>0.887</v>
       </c>
       <c r="H219" t="n">
-        <v>0.305</v>
+        <v>0.303</v>
       </c>
       <c r="I219" t="n">
-        <v>0.696</v>
+        <v>0.6929999999999999</v>
       </c>
     </row>
     <row r="220">
@@ -10073,16 +10073,16 @@
         <v>11</v>
       </c>
       <c r="F220" t="n">
-        <v>0.871</v>
+        <v>0.873</v>
       </c>
       <c r="G220" t="n">
         <v>0.915</v>
       </c>
       <c r="H220" t="n">
-        <v>0.572</v>
+        <v>0.573</v>
       </c>
       <c r="I220" t="n">
-        <v>0.916</v>
+        <v>0.917</v>
       </c>
     </row>
     <row r="221">
@@ -10193,7 +10193,7 @@
         <v>0.102</v>
       </c>
       <c r="I223" t="n">
-        <v>0.456</v>
+        <v>0.406</v>
       </c>
     </row>
     <row r="224">
@@ -10261,13 +10261,13 @@
         <v>0.411</v>
       </c>
       <c r="G225" t="n">
-        <v>0.576</v>
+        <v>0.588</v>
       </c>
       <c r="H225" t="n">
-        <v>0.142</v>
+        <v>0.09959999999999999</v>
       </c>
       <c r="I225" t="n">
-        <v>0.456</v>
+        <v>0.406</v>
       </c>
     </row>
     <row r="226">
@@ -10304,7 +10304,7 @@
         <v>0.325</v>
       </c>
       <c r="I226" t="n">
-        <v>0.49</v>
+        <v>0.473</v>
       </c>
     </row>
     <row r="227">
@@ -10378,7 +10378,7 @@
         <v>0.205</v>
       </c>
       <c r="I228" t="n">
-        <v>0.49</v>
+        <v>0.473</v>
       </c>
     </row>
     <row r="229">
@@ -10415,7 +10415,7 @@
         <v>0.281</v>
       </c>
       <c r="I229" t="n">
-        <v>0.49</v>
+        <v>0.473</v>
       </c>
     </row>
     <row r="230">
@@ -10591,16 +10591,16 @@
         <v>9</v>
       </c>
       <c r="F234" t="n">
-        <v>0.556</v>
+        <v>0.548</v>
       </c>
       <c r="G234" t="n">
         <v>0.476</v>
       </c>
       <c r="H234" t="n">
-        <v>0.257</v>
+        <v>0.313</v>
       </c>
       <c r="I234" t="n">
-        <v>0.49</v>
+        <v>0.473</v>
       </c>
     </row>
     <row r="235">
@@ -10628,16 +10628,16 @@
         <v>10</v>
       </c>
       <c r="F235" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="G235" t="n">
-        <v>0.512</v>
+        <v>0.588</v>
       </c>
       <c r="H235" t="n">
-        <v>0.34</v>
+        <v>0.186</v>
       </c>
       <c r="I235" t="n">
-        <v>0.49</v>
+        <v>0.473</v>
       </c>
     </row>
     <row r="236">
@@ -10665,16 +10665,16 @@
         <v>11</v>
       </c>
       <c r="F236" t="n">
-        <v>0.67</v>
+        <v>0.681</v>
       </c>
       <c r="G236" t="n">
         <v>0.593</v>
       </c>
       <c r="H236" t="n">
-        <v>0.357</v>
+        <v>0.28</v>
       </c>
       <c r="I236" t="n">
-        <v>0.49</v>
+        <v>0.473</v>
       </c>
     </row>
     <row r="237">
@@ -10822,7 +10822,7 @@
         <v>0.211</v>
       </c>
       <c r="I240" t="n">
-        <v>0.49</v>
+        <v>0.473</v>
       </c>
     </row>
     <row r="241">
@@ -10853,10 +10853,10 @@
         <v>0.545</v>
       </c>
       <c r="G241" t="n">
-        <v>0.345</v>
+        <v>0.364</v>
       </c>
       <c r="H241" t="n">
-        <v>0.0546</v>
+        <v>0.0844</v>
       </c>
       <c r="I241" t="n">
         <v>0.413</v>
@@ -10896,7 +10896,7 @@
         <v>0.39</v>
       </c>
       <c r="I242" t="n">
-        <v>0.856</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="243">
@@ -11044,7 +11044,7 @@
         <v>0.428</v>
       </c>
       <c r="I246" t="n">
-        <v>0.856</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="247">
@@ -11183,16 +11183,16 @@
         <v>9</v>
       </c>
       <c r="F250" t="n">
-        <v>0.613</v>
+        <v>0.607</v>
       </c>
       <c r="G250" t="n">
         <v>0.8</v>
       </c>
       <c r="H250" t="n">
-        <v>0.000575</v>
+        <v>0.000371</v>
       </c>
       <c r="I250" t="n">
-        <v>0.0092</v>
+        <v>0.00593</v>
       </c>
     </row>
     <row r="251">
@@ -11220,16 +11220,16 @@
         <v>10</v>
       </c>
       <c r="F251" t="n">
-        <v>0.767</v>
+        <v>0.82</v>
       </c>
       <c r="G251" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.847</v>
       </c>
       <c r="H251" t="n">
-        <v>0.395</v>
+        <v>0.642</v>
       </c>
       <c r="I251" t="n">
-        <v>0.856</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="252">
@@ -11257,16 +11257,16 @@
         <v>11</v>
       </c>
       <c r="F252" t="n">
-        <v>0.74</v>
+        <v>0.747</v>
       </c>
       <c r="G252" t="n">
-        <v>0.647</v>
+        <v>0.653</v>
       </c>
       <c r="H252" t="n">
-        <v>0.103</v>
+        <v>0.101</v>
       </c>
       <c r="I252" t="n">
-        <v>0.331</v>
+        <v>0.324</v>
       </c>
     </row>
     <row r="253">
@@ -11747,7 +11747,7 @@
         <v>0.346</v>
       </c>
       <c r="I265" t="n">
-        <v>0.554</v>
+        <v>0.504</v>
       </c>
     </row>
     <row r="266">
@@ -11781,10 +11781,10 @@
         <v>0.944</v>
       </c>
       <c r="H266" t="n">
-        <v>0.479</v>
+        <v>0.481</v>
       </c>
       <c r="I266" t="n">
-        <v>0.68</v>
+        <v>0.641</v>
       </c>
     </row>
     <row r="267">
@@ -11812,16 +11812,16 @@
         <v>10</v>
       </c>
       <c r="F267" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.949</v>
       </c>
       <c r="G267" t="n">
-        <v>0.894</v>
+        <v>0.901</v>
       </c>
       <c r="H267" t="n">
-        <v>0.51</v>
+        <v>0.346</v>
       </c>
       <c r="I267" t="n">
-        <v>0.68</v>
+        <v>0.504</v>
       </c>
     </row>
     <row r="268">
@@ -11849,16 +11849,16 @@
         <v>11</v>
       </c>
       <c r="F268" t="n">
-        <v>0.871</v>
+        <v>0.873</v>
       </c>
       <c r="G268" t="n">
-        <v>0.711</v>
+        <v>0.714</v>
       </c>
       <c r="H268" t="n">
-        <v>0.0201</v>
+        <v>0.0203</v>
       </c>
       <c r="I268" t="n">
-        <v>0.107</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="269">
@@ -12265,7 +12265,7 @@
         <v>1.44e-05</v>
       </c>
       <c r="I279" t="n">
-        <v>0.000116</v>
+        <v>7.7e-05</v>
       </c>
     </row>
     <row r="280">
@@ -12367,16 +12367,16 @@
         <v>9</v>
       </c>
       <c r="F282" t="n">
-        <v>0.556</v>
+        <v>0.548</v>
       </c>
       <c r="G282" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="H282" t="n">
-        <v>2.29e-05</v>
+        <v>1.31e-05</v>
       </c>
       <c r="I282" t="n">
-        <v>0.000122</v>
+        <v>7.7e-05</v>
       </c>
     </row>
     <row r="283">
@@ -12404,16 +12404,16 @@
         <v>10</v>
       </c>
       <c r="F283" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="G283" t="n">
-        <v>0.738</v>
+        <v>0.8</v>
       </c>
       <c r="H283" t="n">
-        <v>0.0926</v>
+        <v>0.201</v>
       </c>
       <c r="I283" t="n">
-        <v>0.185</v>
+        <v>0.402</v>
       </c>
     </row>
     <row r="284">
@@ -12441,16 +12441,16 @@
         <v>11</v>
       </c>
       <c r="F284" t="n">
-        <v>0.67</v>
+        <v>0.681</v>
       </c>
       <c r="G284" t="n">
-        <v>0.703</v>
+        <v>0.714</v>
       </c>
       <c r="H284" t="n">
-        <v>0.749</v>
+        <v>0.747</v>
       </c>
       <c r="I284" t="n">
-        <v>0.799</v>
+        <v>0.797</v>
       </c>
     </row>
     <row r="285">
@@ -12635,7 +12635,7 @@
         <v>0.703</v>
       </c>
       <c r="I289" t="n">
-        <v>0.799</v>
+        <v>0.797</v>
       </c>
     </row>
   </sheetData>

--- a/eval/results/statistical_tests_full150.xlsx
+++ b/eval/results/statistical_tests_full150.xlsx
@@ -503,22 +503,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.000781</v>
+        <v>0.00116</v>
       </c>
       <c r="F2" t="n">
-        <v>0.831</v>
+        <v>0.844</v>
       </c>
       <c r="G2" t="n">
-        <v>0.898</v>
+        <v>0.91</v>
       </c>
       <c r="H2" t="n">
         <v>0.109</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0654</v>
+        <v>0.0633</v>
       </c>
       <c r="J2" t="n">
-        <v>0.00469</v>
+        <v>0.00696</v>
       </c>
     </row>
     <row r="3">
@@ -543,22 +543,22 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.0009790000000000001</v>
+        <v>0.0015</v>
       </c>
       <c r="F3" t="n">
-        <v>0.831</v>
+        <v>0.844</v>
       </c>
       <c r="G3" t="n">
-        <v>0.898</v>
+        <v>0.91</v>
       </c>
       <c r="H3" t="n">
         <v>0.109</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0654</v>
+        <v>0.0633</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00587</v>
+        <v>0.00564</v>
       </c>
     </row>
     <row r="4">
@@ -583,22 +583,22 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.139</v>
+        <v>0.655</v>
       </c>
       <c r="F4" t="n">
-        <v>0.831</v>
+        <v>0.844</v>
       </c>
       <c r="G4" t="n">
-        <v>0.846</v>
+        <v>0.848</v>
       </c>
       <c r="H4" t="n">
         <v>0.109</v>
       </c>
       <c r="I4" t="n">
-        <v>0.097</v>
+        <v>0.1</v>
       </c>
       <c r="J4" t="n">
-        <v>0.209</v>
+        <v>0.786</v>
       </c>
     </row>
     <row r="5">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.155</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>0.831</v>
+        <v>0.844</v>
       </c>
       <c r="G5" t="n">
-        <v>0.846</v>
+        <v>0.848</v>
       </c>
       <c r="H5" t="n">
         <v>0.109</v>
       </c>
       <c r="I5" t="n">
-        <v>0.097</v>
+        <v>0.1</v>
       </c>
       <c r="J5" t="n">
-        <v>0.232</v>
+        <v>0.887</v>
       </c>
     </row>
     <row r="6">
@@ -663,22 +663,22 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.0137</v>
+        <v>0.0144</v>
       </c>
       <c r="F6" t="n">
-        <v>0.801</v>
+        <v>0.803</v>
       </c>
       <c r="G6" t="n">
-        <v>0.851</v>
+        <v>0.854</v>
       </c>
       <c r="H6" t="n">
-        <v>0.148</v>
+        <v>0.149</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0917</v>
+        <v>0.0912</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0274</v>
+        <v>0.0288</v>
       </c>
     </row>
     <row r="7">
@@ -703,22 +703,22 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.0023</v>
+        <v>0.00188</v>
       </c>
       <c r="F7" t="n">
-        <v>0.801</v>
+        <v>0.803</v>
       </c>
       <c r="G7" t="n">
-        <v>0.851</v>
+        <v>0.854</v>
       </c>
       <c r="H7" t="n">
-        <v>0.148</v>
+        <v>0.149</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0917</v>
+        <v>0.0912</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0069</v>
+        <v>0.00564</v>
       </c>
     </row>
     <row r="8">
@@ -743,22 +743,22 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.0092</v>
+        <v>0.00688</v>
       </c>
       <c r="F8" t="n">
-        <v>0.801</v>
+        <v>0.803</v>
       </c>
       <c r="G8" t="n">
-        <v>0.871</v>
+        <v>0.876</v>
       </c>
       <c r="H8" t="n">
-        <v>0.148</v>
+        <v>0.149</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0737</v>
+        <v>0.0757</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0274</v>
+        <v>0.0206</v>
       </c>
     </row>
     <row r="9">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.008970000000000001</v>
+        <v>0.008959999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>0.801</v>
+        <v>0.803</v>
       </c>
       <c r="G9" t="n">
-        <v>0.871</v>
+        <v>0.876</v>
       </c>
       <c r="H9" t="n">
-        <v>0.148</v>
+        <v>0.149</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0737</v>
+        <v>0.0757</v>
       </c>
       <c r="J9" t="n">
         <v>0.0179</v>
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.543</v>
+        <v>0.622</v>
       </c>
       <c r="F10" t="n">
-        <v>0.78</v>
+        <v>0.783</v>
       </c>
       <c r="G10" t="n">
-        <v>0.788</v>
+        <v>0.79</v>
       </c>
       <c r="H10" t="n">
         <v>0.125</v>
       </c>
       <c r="I10" t="n">
-        <v>0.113</v>
+        <v>0.111</v>
       </c>
       <c r="J10" t="n">
-        <v>0.652</v>
+        <v>0.786</v>
       </c>
     </row>
     <row r="11">
@@ -863,22 +863,22 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.706</v>
+        <v>0.826</v>
       </c>
       <c r="F11" t="n">
-        <v>0.78</v>
+        <v>0.783</v>
       </c>
       <c r="G11" t="n">
-        <v>0.788</v>
+        <v>0.79</v>
       </c>
       <c r="H11" t="n">
         <v>0.125</v>
       </c>
       <c r="I11" t="n">
-        <v>0.113</v>
+        <v>0.111</v>
       </c>
       <c r="J11" t="n">
-        <v>0.82</v>
+        <v>0.887</v>
       </c>
     </row>
     <row r="12">
@@ -903,22 +903,22 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.882</v>
+        <v>0.915</v>
       </c>
       <c r="F12" t="n">
-        <v>0.78</v>
+        <v>0.783</v>
       </c>
       <c r="G12" t="n">
-        <v>0.782</v>
+        <v>0.785</v>
       </c>
       <c r="H12" t="n">
         <v>0.125</v>
       </c>
       <c r="I12" t="n">
-        <v>0.104</v>
+        <v>0.106</v>
       </c>
       <c r="J12" t="n">
-        <v>0.882</v>
+        <v>0.915</v>
       </c>
     </row>
     <row r="13">
@@ -943,22 +943,22 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.82</v>
+        <v>0.887</v>
       </c>
       <c r="F13" t="n">
-        <v>0.78</v>
+        <v>0.783</v>
       </c>
       <c r="G13" t="n">
-        <v>0.782</v>
+        <v>0.785</v>
       </c>
       <c r="H13" t="n">
         <v>0.125</v>
       </c>
       <c r="I13" t="n">
-        <v>0.104</v>
+        <v>0.106</v>
       </c>
       <c r="J13" t="n">
-        <v>0.82</v>
+        <v>0.887</v>
       </c>
     </row>
     <row r="14">
@@ -983,22 +983,22 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.0588</v>
+        <v>0.093</v>
       </c>
       <c r="F14" t="n">
-        <v>0.843</v>
+        <v>0.868</v>
       </c>
       <c r="G14" t="n">
-        <v>0.907</v>
+        <v>0.926</v>
       </c>
       <c r="H14" t="n">
-        <v>0.16</v>
+        <v>0.156</v>
       </c>
       <c r="I14" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.054</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0882</v>
+        <v>0.112</v>
       </c>
     </row>
     <row r="15">
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.112</v>
+        <v>0.221</v>
       </c>
       <c r="F15" t="n">
-        <v>0.843</v>
+        <v>0.868</v>
       </c>
       <c r="G15" t="n">
-        <v>0.907</v>
+        <v>0.926</v>
       </c>
       <c r="H15" t="n">
-        <v>0.16</v>
+        <v>0.156</v>
       </c>
       <c r="I15" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.054</v>
       </c>
       <c r="J15" t="n">
-        <v>0.112</v>
+        <v>0.221</v>
       </c>
     </row>
     <row r="16">
@@ -1063,22 +1063,22 @@
         </is>
       </c>
       <c r="E16" t="n">
+        <v>0.0173</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.868</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.792</v>
+      </c>
+      <c r="H16" t="n">
         <v>0.156</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.843</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.791</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.16</v>
       </c>
       <c r="I16" t="n">
         <v>0.191</v>
       </c>
       <c r="J16" t="n">
-        <v>0.176</v>
+        <v>0.0343</v>
       </c>
     </row>
     <row r="17">
@@ -1103,22 +1103,22 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.07389999999999999</v>
+        <v>0.00269</v>
       </c>
       <c r="F17" t="n">
-        <v>0.843</v>
+        <v>0.868</v>
       </c>
       <c r="G17" t="n">
-        <v>0.791</v>
+        <v>0.792</v>
       </c>
       <c r="H17" t="n">
-        <v>0.16</v>
+        <v>0.156</v>
       </c>
       <c r="I17" t="n">
         <v>0.191</v>
       </c>
       <c r="J17" t="n">
-        <v>0.106</v>
+        <v>0.00538</v>
       </c>
     </row>
     <row r="18">
@@ -1143,22 +1143,22 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.00072</v>
+        <v>0.000852</v>
       </c>
       <c r="F18" t="n">
-        <v>0.794</v>
+        <v>0.795</v>
       </c>
       <c r="G18" t="n">
-        <v>0.912</v>
+        <v>0.916</v>
       </c>
       <c r="H18" t="n">
-        <v>0.202</v>
+        <v>0.201</v>
       </c>
       <c r="I18" t="n">
-        <v>0.103</v>
+        <v>0.0941</v>
       </c>
       <c r="J18" t="n">
-        <v>0.00216</v>
+        <v>0.00256</v>
       </c>
     </row>
     <row r="19">
@@ -1186,16 +1186,16 @@
         <v>0.000987</v>
       </c>
       <c r="F19" t="n">
-        <v>0.794</v>
+        <v>0.795</v>
       </c>
       <c r="G19" t="n">
-        <v>0.912</v>
+        <v>0.916</v>
       </c>
       <c r="H19" t="n">
-        <v>0.202</v>
+        <v>0.201</v>
       </c>
       <c r="I19" t="n">
-        <v>0.103</v>
+        <v>0.0941</v>
       </c>
       <c r="J19" t="n">
         <v>0.00296</v>
@@ -1223,22 +1223,22 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.176</v>
+        <v>0.166</v>
       </c>
       <c r="F20" t="n">
-        <v>0.794</v>
+        <v>0.795</v>
       </c>
       <c r="G20" t="n">
-        <v>0.839</v>
+        <v>0.842</v>
       </c>
       <c r="H20" t="n">
-        <v>0.202</v>
+        <v>0.201</v>
       </c>
       <c r="I20" t="n">
-        <v>0.165</v>
+        <v>0.164</v>
       </c>
       <c r="J20" t="n">
-        <v>0.176</v>
+        <v>0.166</v>
       </c>
     </row>
     <row r="21">
@@ -1263,22 +1263,22 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.08840000000000001</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>0.794</v>
+        <v>0.795</v>
       </c>
       <c r="G21" t="n">
-        <v>0.839</v>
+        <v>0.842</v>
       </c>
       <c r="H21" t="n">
-        <v>0.202</v>
+        <v>0.201</v>
       </c>
       <c r="I21" t="n">
-        <v>0.165</v>
+        <v>0.164</v>
       </c>
       <c r="J21" t="n">
-        <v>0.106</v>
+        <v>0.0829</v>
       </c>
     </row>
     <row r="22">
@@ -1303,22 +1303,22 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.0232</v>
+        <v>0.0229</v>
       </c>
       <c r="F22" t="n">
-        <v>0.78</v>
+        <v>0.782</v>
       </c>
       <c r="G22" t="n">
-        <v>0.844</v>
+        <v>0.848</v>
       </c>
       <c r="H22" t="n">
-        <v>0.21</v>
+        <v>0.208</v>
       </c>
       <c r="I22" t="n">
-        <v>0.17</v>
+        <v>0.164</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0464</v>
+        <v>0.0343</v>
       </c>
     </row>
     <row r="23">
@@ -1346,19 +1346,19 @@
         <v>0.0356</v>
       </c>
       <c r="F23" t="n">
-        <v>0.78</v>
+        <v>0.782</v>
       </c>
       <c r="G23" t="n">
-        <v>0.844</v>
+        <v>0.848</v>
       </c>
       <c r="H23" t="n">
-        <v>0.21</v>
+        <v>0.208</v>
       </c>
       <c r="I23" t="n">
-        <v>0.17</v>
+        <v>0.164</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0712</v>
+        <v>0.0534</v>
       </c>
     </row>
     <row r="24">
@@ -1383,22 +1383,22 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4.72e-05</v>
+        <v>4.35e-05</v>
       </c>
       <c r="F24" t="n">
-        <v>0.78</v>
+        <v>0.782</v>
       </c>
       <c r="G24" t="n">
-        <v>0.678</v>
+        <v>0.681</v>
       </c>
       <c r="H24" t="n">
-        <v>0.21</v>
+        <v>0.208</v>
       </c>
       <c r="I24" t="n">
         <v>0.203</v>
       </c>
       <c r="J24" t="n">
-        <v>0.000283</v>
+        <v>0.000261</v>
       </c>
     </row>
     <row r="25">
@@ -1426,13 +1426,13 @@
         <v>0.000153</v>
       </c>
       <c r="F25" t="n">
-        <v>0.78</v>
+        <v>0.782</v>
       </c>
       <c r="G25" t="n">
-        <v>0.678</v>
+        <v>0.681</v>
       </c>
       <c r="H25" t="n">
-        <v>0.21</v>
+        <v>0.208</v>
       </c>
       <c r="I25" t="n">
         <v>0.203</v>
@@ -1463,22 +1463,22 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.0138</v>
+        <v>0.0155</v>
       </c>
       <c r="F26" t="n">
-        <v>0.77</v>
+        <v>0.783</v>
       </c>
       <c r="G26" t="n">
-        <v>0.848</v>
+        <v>0.861</v>
       </c>
       <c r="H26" t="n">
-        <v>0.149</v>
+        <v>0.157</v>
       </c>
       <c r="I26" t="n">
-        <v>0.127</v>
+        <v>0.13</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0276</v>
+        <v>0.031</v>
       </c>
     </row>
     <row r="27">
@@ -1503,22 +1503,22 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.0186</v>
+        <v>0.0199</v>
       </c>
       <c r="F27" t="n">
-        <v>0.77</v>
+        <v>0.783</v>
       </c>
       <c r="G27" t="n">
-        <v>0.848</v>
+        <v>0.861</v>
       </c>
       <c r="H27" t="n">
-        <v>0.149</v>
+        <v>0.157</v>
       </c>
       <c r="I27" t="n">
-        <v>0.127</v>
+        <v>0.13</v>
       </c>
       <c r="J27" t="n">
-        <v>0.0372</v>
+        <v>0.0398</v>
       </c>
     </row>
     <row r="28">
@@ -1543,22 +1543,22 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.378</v>
+        <v>0.492</v>
       </c>
       <c r="F28" t="n">
-        <v>0.77</v>
+        <v>0.783</v>
       </c>
       <c r="G28" t="n">
-        <v>0.799</v>
+        <v>0.806</v>
       </c>
       <c r="H28" t="n">
-        <v>0.149</v>
+        <v>0.157</v>
       </c>
       <c r="I28" t="n">
-        <v>0.215</v>
+        <v>0.222</v>
       </c>
       <c r="J28" t="n">
-        <v>0.378</v>
+        <v>0.492</v>
       </c>
     </row>
     <row r="29">
@@ -1586,16 +1586,16 @@
         <v>0.345</v>
       </c>
       <c r="F29" t="n">
-        <v>0.77</v>
+        <v>0.783</v>
       </c>
       <c r="G29" t="n">
-        <v>0.799</v>
+        <v>0.806</v>
       </c>
       <c r="H29" t="n">
-        <v>0.149</v>
+        <v>0.157</v>
       </c>
       <c r="I29" t="n">
-        <v>0.215</v>
+        <v>0.222</v>
       </c>
       <c r="J29" t="n">
         <v>0.345</v>
@@ -1623,22 +1623,22 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.0853</v>
+        <v>0.0833</v>
       </c>
       <c r="F30" t="n">
-        <v>0.762</v>
+        <v>0.767</v>
       </c>
       <c r="G30" t="n">
-        <v>0.701</v>
+        <v>0.709</v>
       </c>
       <c r="H30" t="n">
-        <v>0.178</v>
+        <v>0.18</v>
       </c>
       <c r="I30" t="n">
-        <v>0.159</v>
+        <v>0.162</v>
       </c>
       <c r="J30" t="n">
-        <v>0.128</v>
+        <v>0.118</v>
       </c>
     </row>
     <row r="31">
@@ -1666,16 +1666,16 @@
         <v>0.14</v>
       </c>
       <c r="F31" t="n">
-        <v>0.762</v>
+        <v>0.767</v>
       </c>
       <c r="G31" t="n">
-        <v>0.701</v>
+        <v>0.709</v>
       </c>
       <c r="H31" t="n">
-        <v>0.178</v>
+        <v>0.18</v>
       </c>
       <c r="I31" t="n">
-        <v>0.159</v>
+        <v>0.162</v>
       </c>
       <c r="J31" t="n">
         <v>0.168</v>
@@ -1703,22 +1703,22 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.13</v>
+        <v>0.0982</v>
       </c>
       <c r="F32" t="n">
-        <v>0.762</v>
+        <v>0.767</v>
       </c>
       <c r="G32" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.823</v>
       </c>
       <c r="H32" t="n">
-        <v>0.178</v>
+        <v>0.18</v>
       </c>
       <c r="I32" t="n">
-        <v>0.155</v>
+        <v>0.161</v>
       </c>
       <c r="J32" t="n">
-        <v>0.156</v>
+        <v>0.118</v>
       </c>
     </row>
     <row r="33">
@@ -1746,16 +1746,16 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="F33" t="n">
-        <v>0.762</v>
+        <v>0.767</v>
       </c>
       <c r="G33" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.823</v>
       </c>
       <c r="H33" t="n">
-        <v>0.178</v>
+        <v>0.18</v>
       </c>
       <c r="I33" t="n">
-        <v>0.155</v>
+        <v>0.161</v>
       </c>
       <c r="J33" t="n">
         <v>0.144</v>
@@ -1783,22 +1783,22 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.00078</v>
+        <v>0.000654</v>
       </c>
       <c r="F34" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="G34" t="n">
-        <v>0.585</v>
+        <v>0.59</v>
       </c>
       <c r="H34" t="n">
-        <v>0.167</v>
+        <v>0.171</v>
       </c>
       <c r="I34" t="n">
-        <v>0.136</v>
+        <v>0.132</v>
       </c>
       <c r="J34" t="n">
-        <v>0.00234</v>
+        <v>0.00196</v>
       </c>
     </row>
     <row r="35">
@@ -1826,16 +1826,16 @@
         <v>0.00451</v>
       </c>
       <c r="F35" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="G35" t="n">
-        <v>0.585</v>
+        <v>0.59</v>
       </c>
       <c r="H35" t="n">
-        <v>0.167</v>
+        <v>0.171</v>
       </c>
       <c r="I35" t="n">
-        <v>0.136</v>
+        <v>0.132</v>
       </c>
       <c r="J35" t="n">
         <v>0.0135</v>
@@ -1863,22 +1863,22 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4.46e-05</v>
+        <v>4.83e-05</v>
       </c>
       <c r="F36" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="G36" t="n">
-        <v>0.841</v>
+        <v>0.848</v>
       </c>
       <c r="H36" t="n">
-        <v>0.167</v>
+        <v>0.171</v>
       </c>
       <c r="I36" t="n">
-        <v>0.156</v>
+        <v>0.161</v>
       </c>
       <c r="J36" t="n">
-        <v>0.000268</v>
+        <v>0.00029</v>
       </c>
     </row>
     <row r="37">
@@ -1906,16 +1906,16 @@
         <v>0.000153</v>
       </c>
       <c r="F37" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="G37" t="n">
-        <v>0.841</v>
+        <v>0.848</v>
       </c>
       <c r="H37" t="n">
-        <v>0.167</v>
+        <v>0.171</v>
       </c>
       <c r="I37" t="n">
-        <v>0.156</v>
+        <v>0.161</v>
       </c>
       <c r="J37" t="n">
         <v>0.000918</v>
@@ -2016,7 +2016,7 @@
         <v>0.1</v>
       </c>
       <c r="I2" t="n">
-        <v>0.267</v>
+        <v>0.229</v>
       </c>
     </row>
     <row r="3">
@@ -2053,7 +2053,7 @@
         <v>8.69e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00139</v>
+        <v>0.00114</v>
       </c>
     </row>
     <row r="4">
@@ -2081,16 +2081,16 @@
         <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>0.973</v>
+        <v>0.98</v>
       </c>
       <c r="G4" t="n">
         <v>0.987</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6840000000000001</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0.898</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -2118,16 +2118,16 @@
         <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>0.947</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0.96</v>
+        <v>0.993</v>
       </c>
       <c r="H5" t="n">
-        <v>0.785</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0.898</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -2155,16 +2155,16 @@
         <v>5</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="G6" t="n">
-        <v>0.82</v>
+        <v>0.827</v>
       </c>
       <c r="H6" t="n">
-        <v>0.769</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>0.898</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -2192,16 +2192,16 @@
         <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>0.793</v>
+        <v>0.8</v>
       </c>
       <c r="G7" t="n">
         <v>0.907</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00911</v>
+        <v>0.0137</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0292</v>
+        <v>0.0438</v>
       </c>
     </row>
     <row r="8">
@@ -2229,16 +2229,16 @@
         <v>7</v>
       </c>
       <c r="F8" t="n">
-        <v>0.847</v>
+        <v>0.86</v>
       </c>
       <c r="G8" t="n">
-        <v>0.893</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>0.303</v>
+        <v>0.0564</v>
       </c>
       <c r="I8" t="n">
-        <v>0.606</v>
+        <v>0.151</v>
       </c>
     </row>
     <row r="9">
@@ -2306,13 +2306,13 @@
         <v>0.6870000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>0.76</v>
+        <v>0.767</v>
       </c>
       <c r="H10" t="n">
-        <v>0.197</v>
+        <v>0.154</v>
       </c>
       <c r="I10" t="n">
-        <v>0.45</v>
+        <v>0.308</v>
       </c>
     </row>
     <row r="11">
@@ -2340,16 +2340,16 @@
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>0.847</v>
+        <v>0.9</v>
       </c>
       <c r="G11" t="n">
-        <v>0.867</v>
+        <v>0.92</v>
       </c>
       <c r="H11" t="n">
-        <v>0.742</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.898</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -2377,16 +2377,16 @@
         <v>11</v>
       </c>
       <c r="F12" t="n">
-        <v>0.707</v>
+        <v>0.713</v>
       </c>
       <c r="G12" t="n">
-        <v>0.86</v>
+        <v>0.853</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0019</v>
+        <v>0.00482</v>
       </c>
       <c r="I12" t="n">
-        <v>0.00761</v>
+        <v>0.0193</v>
       </c>
     </row>
     <row r="13">
@@ -2423,7 +2423,7 @@
         <v>0.575</v>
       </c>
       <c r="I13" t="n">
-        <v>0.898</v>
+        <v>0.921</v>
       </c>
     </row>
     <row r="14">
@@ -2525,16 +2525,16 @@
         <v>15</v>
       </c>
       <c r="F16" t="n">
-        <v>0.68</v>
+        <v>0.707</v>
       </c>
       <c r="G16" t="n">
-        <v>0.853</v>
+        <v>0.873</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0005820000000000001</v>
+        <v>0.000595</v>
       </c>
       <c r="I16" t="n">
-        <v>0.00356</v>
+        <v>0.00317</v>
       </c>
     </row>
     <row r="17">
@@ -2562,16 +2562,16 @@
         <v>16</v>
       </c>
       <c r="F17" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="G17" t="n">
-        <v>0.82</v>
+        <v>0.853</v>
       </c>
       <c r="H17" t="n">
-        <v>0.000668</v>
+        <v>0.000143</v>
       </c>
       <c r="I17" t="n">
-        <v>0.00356</v>
+        <v>0.00114</v>
       </c>
     </row>
     <row r="18">
@@ -2608,7 +2608,7 @@
         <v>0.585</v>
       </c>
       <c r="I18" t="n">
-        <v>0.926</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -2673,16 +2673,16 @@
         <v>3</v>
       </c>
       <c r="F20" t="n">
-        <v>0.929</v>
+        <v>0.931</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>0.491</v>
+        <v>0.492</v>
       </c>
       <c r="I20" t="n">
-        <v>0.917</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -2710,16 +2710,16 @@
         <v>4</v>
       </c>
       <c r="F21" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>0.833</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0.516</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>0.917</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -2747,16 +2747,16 @@
         <v>5</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.963</v>
       </c>
       <c r="G22" t="n">
         <v>0.963</v>
       </c>
       <c r="H22" t="n">
-        <v>0.72</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>0.926</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -2784,7 +2784,7 @@
         <v>6</v>
       </c>
       <c r="F23" t="n">
-        <v>0.969</v>
+        <v>0.97</v>
       </c>
       <c r="G23" t="n">
         <v>0.9429999999999999</v>
@@ -2793,7 +2793,7 @@
         <v>0.699</v>
       </c>
       <c r="I23" t="n">
-        <v>0.926</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -2821,16 +2821,16 @@
         <v>7</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.957</v>
       </c>
       <c r="G24" t="n">
-        <v>0.926</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>0.752</v>
+        <v>0.73</v>
       </c>
       <c r="I24" t="n">
-        <v>0.926</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -2901,10 +2901,10 @@
         <v>0.95</v>
       </c>
       <c r="H26" t="n">
-        <v>0.227</v>
+        <v>0.228</v>
       </c>
       <c r="I26" t="n">
-        <v>0.725</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="27">
@@ -2932,10 +2932,10 @@
         <v>10</v>
       </c>
       <c r="F27" t="n">
-        <v>0.913</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>0.917</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="H27" t="n">
         <v>1</v>
@@ -2969,16 +2969,16 @@
         <v>11</v>
       </c>
       <c r="F28" t="n">
-        <v>0.873</v>
+        <v>0.889</v>
       </c>
       <c r="G28" t="n">
         <v>0.927</v>
       </c>
       <c r="H28" t="n">
-        <v>0.396</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>0.905</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -3089,7 +3089,7 @@
         <v>0.185</v>
       </c>
       <c r="I31" t="n">
-        <v>0.725</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="32">
@@ -3117,16 +3117,16 @@
         <v>15</v>
       </c>
       <c r="F32" t="n">
-        <v>0.617</v>
+        <v>0.649</v>
       </c>
       <c r="G32" t="n">
-        <v>0.826</v>
+        <v>0.864</v>
       </c>
       <c r="H32" t="n">
-        <v>0.00635</v>
+        <v>0.0037</v>
       </c>
       <c r="I32" t="n">
-        <v>0.0508</v>
+        <v>0.0296</v>
       </c>
     </row>
     <row r="33">
@@ -3154,16 +3154,16 @@
         <v>16</v>
       </c>
       <c r="F33" t="n">
-        <v>0.509</v>
+        <v>0.556</v>
       </c>
       <c r="G33" t="n">
-        <v>0.733</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0139</v>
+        <v>0.00743</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0743</v>
+        <v>0.0396</v>
       </c>
     </row>
     <row r="34">
@@ -3200,7 +3200,7 @@
         <v>0.0974</v>
       </c>
       <c r="I34" t="n">
-        <v>0.203</v>
+        <v>0.195</v>
       </c>
     </row>
     <row r="35">
@@ -3265,7 +3265,7 @@
         <v>3</v>
       </c>
       <c r="F36" t="n">
-        <v>0.929</v>
+        <v>0.964</v>
       </c>
       <c r="G36" t="n">
         <v>0.929</v>
@@ -3302,10 +3302,10 @@
         <v>4</v>
       </c>
       <c r="F37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" t="n">
         <v>0.955</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0.909</v>
       </c>
       <c r="H37" t="n">
         <v>1</v>
@@ -3339,10 +3339,10 @@
         <v>5</v>
       </c>
       <c r="F38" t="n">
-        <v>0.752</v>
+        <v>0.762</v>
       </c>
       <c r="G38" t="n">
-        <v>0.762</v>
+        <v>0.772</v>
       </c>
       <c r="H38" t="n">
         <v>1</v>
@@ -3376,16 +3376,16 @@
         <v>6</v>
       </c>
       <c r="F39" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.696</v>
       </c>
       <c r="G39" t="n">
         <v>0.902</v>
       </c>
       <c r="H39" t="n">
-        <v>0.000433</v>
+        <v>0.00077</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0069</v>
+        <v>0.0123</v>
       </c>
     </row>
     <row r="40">
@@ -3413,16 +3413,16 @@
         <v>7</v>
       </c>
       <c r="F40" t="n">
-        <v>0.776</v>
+        <v>0.788</v>
       </c>
       <c r="G40" t="n">
-        <v>0.882</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="H40" t="n">
-        <v>0.102</v>
+        <v>0.00612</v>
       </c>
       <c r="I40" t="n">
-        <v>0.203</v>
+        <v>0.0245</v>
       </c>
     </row>
     <row r="41">
@@ -3490,13 +3490,13 @@
         <v>0.635</v>
       </c>
       <c r="G42" t="n">
-        <v>0.754</v>
+        <v>0.762</v>
       </c>
       <c r="H42" t="n">
-        <v>0.0552</v>
+        <v>0.0391</v>
       </c>
       <c r="I42" t="n">
-        <v>0.167</v>
+        <v>0.104</v>
       </c>
     </row>
     <row r="43">
@@ -3524,16 +3524,16 @@
         <v>10</v>
       </c>
       <c r="F43" t="n">
-        <v>0.787</v>
+        <v>0.877</v>
       </c>
       <c r="G43" t="n">
-        <v>0.825</v>
+        <v>0.914</v>
       </c>
       <c r="H43" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.609</v>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>0.886</v>
       </c>
     </row>
     <row r="44">
@@ -3561,16 +3561,16 @@
         <v>11</v>
       </c>
       <c r="F44" t="n">
-        <v>0.604</v>
+        <v>0.609</v>
       </c>
       <c r="G44" t="n">
-        <v>0.835</v>
+        <v>0.826</v>
       </c>
       <c r="H44" t="n">
-        <v>0.0008630000000000001</v>
+        <v>0.00172</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0069</v>
+        <v>0.0137</v>
       </c>
     </row>
     <row r="45">
@@ -3607,7 +3607,7 @@
         <v>0.0625</v>
       </c>
       <c r="I45" t="n">
-        <v>0.167</v>
+        <v>0.143</v>
       </c>
     </row>
     <row r="46">
@@ -3681,7 +3681,7 @@
         <v>0.0216</v>
       </c>
       <c r="I47" t="n">
-        <v>0.0863</v>
+        <v>0.06909999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -3746,16 +3746,16 @@
         <v>16</v>
       </c>
       <c r="F49" t="n">
-        <v>0.527</v>
+        <v>0.526</v>
       </c>
       <c r="G49" t="n">
-        <v>0.8</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="H49" t="n">
-        <v>0.00439</v>
+        <v>0.00264</v>
       </c>
       <c r="I49" t="n">
-        <v>0.0234</v>
+        <v>0.0141</v>
       </c>
     </row>
     <row r="50">
@@ -3829,7 +3829,7 @@
         <v>0.251</v>
       </c>
       <c r="I51" t="n">
-        <v>0.803</v>
+        <v>0.974</v>
       </c>
     </row>
     <row r="52">
@@ -3857,16 +3857,16 @@
         <v>3</v>
       </c>
       <c r="F52" t="n">
-        <v>0.973</v>
+        <v>0.98</v>
       </c>
       <c r="G52" t="n">
         <v>0.953</v>
       </c>
       <c r="H52" t="n">
-        <v>0.541</v>
+        <v>0.335</v>
       </c>
       <c r="I52" t="n">
-        <v>0.866</v>
+        <v>0.974</v>
       </c>
     </row>
     <row r="53">
@@ -3894,16 +3894,16 @@
         <v>4</v>
       </c>
       <c r="F53" t="n">
-        <v>0.947</v>
+        <v>1</v>
       </c>
       <c r="G53" t="n">
-        <v>0.987</v>
+        <v>0.993</v>
       </c>
       <c r="H53" t="n">
-        <v>0.103</v>
+        <v>1</v>
       </c>
       <c r="I53" t="n">
-        <v>0.803</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3931,13 +3931,13 @@
         <v>5</v>
       </c>
       <c r="F54" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="G54" t="n">
-        <v>0.82</v>
+        <v>0.827</v>
       </c>
       <c r="H54" t="n">
-        <v>0.769</v>
+        <v>1</v>
       </c>
       <c r="I54" t="n">
         <v>1</v>
@@ -3968,16 +3968,16 @@
         <v>6</v>
       </c>
       <c r="F55" t="n">
-        <v>0.793</v>
+        <v>0.8</v>
       </c>
       <c r="G55" t="n">
         <v>0.84</v>
       </c>
       <c r="H55" t="n">
-        <v>0.371</v>
+        <v>0.453</v>
       </c>
       <c r="I55" t="n">
-        <v>0.847</v>
+        <v>0.974</v>
       </c>
     </row>
     <row r="56">
@@ -4005,13 +4005,13 @@
         <v>7</v>
       </c>
       <c r="F56" t="n">
-        <v>0.847</v>
+        <v>0.86</v>
       </c>
       <c r="G56" t="n">
-        <v>0.847</v>
+        <v>0.88</v>
       </c>
       <c r="H56" t="n">
-        <v>1</v>
+        <v>0.732</v>
       </c>
       <c r="I56" t="n">
         <v>1</v>
@@ -4051,7 +4051,7 @@
         <v>0.198</v>
       </c>
       <c r="I57" t="n">
-        <v>0.803</v>
+        <v>0.974</v>
       </c>
     </row>
     <row r="58">
@@ -4088,7 +4088,7 @@
         <v>0.247</v>
       </c>
       <c r="I58" t="n">
-        <v>0.803</v>
+        <v>0.974</v>
       </c>
     </row>
     <row r="59">
@@ -4116,16 +4116,16 @@
         <v>10</v>
       </c>
       <c r="F59" t="n">
-        <v>0.847</v>
+        <v>0.9</v>
       </c>
       <c r="G59" t="n">
-        <v>0.893</v>
+        <v>0.9</v>
       </c>
       <c r="H59" t="n">
-        <v>0.303</v>
+        <v>1</v>
       </c>
       <c r="I59" t="n">
-        <v>0.8080000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -4153,16 +4153,16 @@
         <v>11</v>
       </c>
       <c r="F60" t="n">
-        <v>0.707</v>
+        <v>0.713</v>
       </c>
       <c r="G60" t="n">
-        <v>0.787</v>
+        <v>0.78</v>
       </c>
       <c r="H60" t="n">
-        <v>0.144</v>
+        <v>0.232</v>
       </c>
       <c r="I60" t="n">
-        <v>0.803</v>
+        <v>0.974</v>
       </c>
     </row>
     <row r="61">
@@ -4199,7 +4199,7 @@
         <v>0.449</v>
       </c>
       <c r="I61" t="n">
-        <v>0.866</v>
+        <v>0.974</v>
       </c>
     </row>
     <row r="62">
@@ -4236,7 +4236,7 @@
         <v>0.501</v>
       </c>
       <c r="I62" t="n">
-        <v>0.866</v>
+        <v>0.974</v>
       </c>
     </row>
     <row r="63">
@@ -4301,16 +4301,16 @@
         <v>15</v>
       </c>
       <c r="F64" t="n">
-        <v>0.68</v>
+        <v>0.707</v>
       </c>
       <c r="G64" t="n">
         <v>0.713</v>
       </c>
       <c r="H64" t="n">
-        <v>0.616</v>
+        <v>1</v>
       </c>
       <c r="I64" t="n">
-        <v>0.895</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4338,16 +4338,16 @@
         <v>16</v>
       </c>
       <c r="F65" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="G65" t="n">
-        <v>0.633</v>
+        <v>0.62</v>
       </c>
       <c r="H65" t="n">
-        <v>1</v>
+        <v>0.548</v>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>0.974</v>
       </c>
     </row>
     <row r="66">
@@ -4384,7 +4384,7 @@
         <v>0.49</v>
       </c>
       <c r="I66" t="n">
-        <v>0.654</v>
+        <v>0.799</v>
       </c>
     </row>
     <row r="67">
@@ -4421,7 +4421,7 @@
         <v>0.458</v>
       </c>
       <c r="I67" t="n">
-        <v>0.654</v>
+        <v>0.799</v>
       </c>
     </row>
     <row r="68">
@@ -4449,16 +4449,16 @@
         <v>3</v>
       </c>
       <c r="F68" t="n">
-        <v>0.929</v>
+        <v>0.931</v>
       </c>
       <c r="G68" t="n">
         <v>0.8</v>
       </c>
       <c r="H68" t="n">
-        <v>0.277</v>
+        <v>0.166</v>
       </c>
       <c r="I68" t="n">
-        <v>0.651</v>
+        <v>0.664</v>
       </c>
     </row>
     <row r="69">
@@ -4486,16 +4486,16 @@
         <v>4</v>
       </c>
       <c r="F69" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="G69" t="n">
-        <v>0.955</v>
+        <v>0.957</v>
       </c>
       <c r="H69" t="n">
-        <v>0.0638</v>
+        <v>1</v>
       </c>
       <c r="I69" t="n">
-        <v>0.404</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4523,16 +4523,16 @@
         <v>5</v>
       </c>
       <c r="F70" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.963</v>
       </c>
       <c r="G70" t="n">
-        <v>0.93</v>
+        <v>0.931</v>
       </c>
       <c r="H70" t="n">
-        <v>1</v>
+        <v>0.499</v>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>0.799</v>
       </c>
     </row>
     <row r="71">
@@ -4560,16 +4560,16 @@
         <v>6</v>
       </c>
       <c r="F71" t="n">
-        <v>0.969</v>
+        <v>0.97</v>
       </c>
       <c r="G71" t="n">
         <v>0.833</v>
       </c>
       <c r="H71" t="n">
-        <v>0.00604</v>
+        <v>0.00578</v>
       </c>
       <c r="I71" t="n">
-        <v>0.09660000000000001</v>
+        <v>0.0925</v>
       </c>
     </row>
     <row r="72">
@@ -4597,16 +4597,16 @@
         <v>7</v>
       </c>
       <c r="F72" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.957</v>
       </c>
       <c r="G72" t="n">
-        <v>0.844</v>
+        <v>0.853</v>
       </c>
       <c r="H72" t="n">
-        <v>0.0757</v>
+        <v>0.0373</v>
       </c>
       <c r="I72" t="n">
-        <v>0.404</v>
+        <v>0.298</v>
       </c>
     </row>
     <row r="73">
@@ -4643,7 +4643,7 @@
         <v>0.138</v>
       </c>
       <c r="I73" t="n">
-        <v>0.55</v>
+        <v>0.664</v>
       </c>
     </row>
     <row r="74">
@@ -4680,7 +4680,7 @@
         <v>0.626</v>
       </c>
       <c r="I74" t="n">
-        <v>0.77</v>
+        <v>0.8179999999999999</v>
       </c>
     </row>
     <row r="75">
@@ -4708,16 +4708,16 @@
         <v>10</v>
       </c>
       <c r="F75" t="n">
-        <v>0.913</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="G75" t="n">
-        <v>0.957</v>
+        <v>0.958</v>
       </c>
       <c r="H75" t="n">
-        <v>0.326</v>
+        <v>0.72</v>
       </c>
       <c r="I75" t="n">
-        <v>0.651</v>
+        <v>0.823</v>
       </c>
     </row>
     <row r="76">
@@ -4745,7 +4745,7 @@
         <v>11</v>
       </c>
       <c r="F76" t="n">
-        <v>0.873</v>
+        <v>0.889</v>
       </c>
       <c r="G76" t="n">
         <v>0.873</v>
@@ -4791,7 +4791,7 @@
         <v>0.456</v>
       </c>
       <c r="I77" t="n">
-        <v>0.654</v>
+        <v>0.799</v>
       </c>
     </row>
     <row r="78">
@@ -4828,7 +4828,7 @@
         <v>0.473</v>
       </c>
       <c r="I78" t="n">
-        <v>0.654</v>
+        <v>0.799</v>
       </c>
     </row>
     <row r="79">
@@ -4865,7 +4865,7 @@
         <v>0.284</v>
       </c>
       <c r="I79" t="n">
-        <v>0.651</v>
+        <v>0.799</v>
       </c>
     </row>
     <row r="80">
@@ -4893,16 +4893,16 @@
         <v>15</v>
       </c>
       <c r="F80" t="n">
-        <v>0.617</v>
+        <v>0.649</v>
       </c>
       <c r="G80" t="n">
         <v>0.707</v>
       </c>
       <c r="H80" t="n">
-        <v>0.285</v>
+        <v>0.579</v>
       </c>
       <c r="I80" t="n">
-        <v>0.651</v>
+        <v>0.8179999999999999</v>
       </c>
     </row>
     <row r="81">
@@ -4930,16 +4930,16 @@
         <v>16</v>
       </c>
       <c r="F81" t="n">
-        <v>0.509</v>
+        <v>0.556</v>
       </c>
       <c r="G81" t="n">
         <v>0.5</v>
       </c>
       <c r="H81" t="n">
-        <v>1</v>
+        <v>0.664</v>
       </c>
       <c r="I81" t="n">
-        <v>1</v>
+        <v>0.8179999999999999</v>
       </c>
     </row>
     <row r="82">
@@ -5041,16 +5041,16 @@
         <v>3</v>
       </c>
       <c r="F84" t="n">
-        <v>0.929</v>
+        <v>0.964</v>
       </c>
       <c r="G84" t="n">
         <v>1</v>
       </c>
       <c r="H84" t="n">
-        <v>0.491</v>
+        <v>1</v>
       </c>
       <c r="I84" t="n">
-        <v>0.784</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -5078,10 +5078,10 @@
         <v>4</v>
       </c>
       <c r="F85" t="n">
-        <v>0.955</v>
+        <v>1</v>
       </c>
       <c r="G85" t="n">
-        <v>0.955</v>
+        <v>1</v>
       </c>
       <c r="H85" t="n">
         <v>1</v>
@@ -5115,16 +5115,16 @@
         <v>5</v>
       </c>
       <c r="F86" t="n">
-        <v>0.752</v>
+        <v>0.762</v>
       </c>
       <c r="G86" t="n">
-        <v>0.792</v>
+        <v>0.802</v>
       </c>
       <c r="H86" t="n">
-        <v>0.615</v>
+        <v>0.609</v>
       </c>
       <c r="I86" t="n">
-        <v>0.784</v>
+        <v>0.927</v>
       </c>
     </row>
     <row r="87">
@@ -5152,16 +5152,16 @@
         <v>6</v>
       </c>
       <c r="F87" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.696</v>
       </c>
       <c r="G87" t="n">
         <v>0.924</v>
       </c>
       <c r="H87" t="n">
-        <v>6.35e-05</v>
+        <v>0.00012</v>
       </c>
       <c r="I87" t="n">
-        <v>0.00102</v>
+        <v>0.00192</v>
       </c>
     </row>
     <row r="88">
@@ -5189,16 +5189,16 @@
         <v>7</v>
       </c>
       <c r="F88" t="n">
-        <v>0.776</v>
+        <v>0.788</v>
       </c>
       <c r="G88" t="n">
-        <v>0.894</v>
+        <v>0.953</v>
       </c>
       <c r="H88" t="n">
-        <v>0.0614</v>
+        <v>0.00231</v>
       </c>
       <c r="I88" t="n">
-        <v>0.246</v>
+        <v>0.0185</v>
       </c>
     </row>
     <row r="89">
@@ -5235,7 +5235,7 @@
         <v>0.637</v>
       </c>
       <c r="I89" t="n">
-        <v>0.784</v>
+        <v>0.927</v>
       </c>
     </row>
     <row r="90">
@@ -5300,16 +5300,16 @@
         <v>10</v>
       </c>
       <c r="F91" t="n">
-        <v>0.787</v>
+        <v>0.877</v>
       </c>
       <c r="G91" t="n">
-        <v>0.838</v>
+        <v>0.852</v>
       </c>
       <c r="H91" t="n">
-        <v>0.544</v>
+        <v>0.819</v>
       </c>
       <c r="I91" t="n">
-        <v>0.784</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -5337,16 +5337,16 @@
         <v>11</v>
       </c>
       <c r="F92" t="n">
-        <v>0.604</v>
+        <v>0.609</v>
       </c>
       <c r="G92" t="n">
-        <v>0.758</v>
+        <v>0.75</v>
       </c>
       <c r="H92" t="n">
-        <v>0.0382</v>
+        <v>0.0576</v>
       </c>
       <c r="I92" t="n">
-        <v>0.204</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="93">
@@ -5522,16 +5522,16 @@
         <v>16</v>
       </c>
       <c r="F97" t="n">
-        <v>0.527</v>
+        <v>0.526</v>
       </c>
       <c r="G97" t="n">
-        <v>0.309</v>
+        <v>0.298</v>
       </c>
       <c r="H97" t="n">
-        <v>0.033</v>
+        <v>0.022</v>
       </c>
       <c r="I97" t="n">
-        <v>0.204</v>
+        <v>0.117</v>
       </c>
     </row>
     <row r="98">
@@ -5568,7 +5568,7 @@
         <v>0.312</v>
       </c>
       <c r="I98" t="n">
-        <v>0.908</v>
+        <v>0.885</v>
       </c>
     </row>
     <row r="99">
@@ -5670,10 +5670,10 @@
         <v>4</v>
       </c>
       <c r="F101" t="n">
-        <v>0.98</v>
+        <v>0.987</v>
       </c>
       <c r="G101" t="n">
-        <v>0.98</v>
+        <v>0.987</v>
       </c>
       <c r="H101" t="n">
         <v>1</v>
@@ -5710,10 +5710,10 @@
         <v>0.8070000000000001</v>
       </c>
       <c r="G102" t="n">
-        <v>0.787</v>
+        <v>0.793</v>
       </c>
       <c r="H102" t="n">
-        <v>0.774</v>
+        <v>0.885</v>
       </c>
       <c r="I102" t="n">
         <v>1</v>
@@ -5744,16 +5744,16 @@
         <v>6</v>
       </c>
       <c r="F103" t="n">
-        <v>0.787</v>
+        <v>0.793</v>
       </c>
       <c r="G103" t="n">
         <v>0.853</v>
       </c>
       <c r="H103" t="n">
-        <v>0.176</v>
+        <v>0.226</v>
       </c>
       <c r="I103" t="n">
-        <v>0.703</v>
+        <v>0.885</v>
       </c>
     </row>
     <row r="104">
@@ -5781,13 +5781,13 @@
         <v>7</v>
       </c>
       <c r="F104" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.84</v>
       </c>
       <c r="G104" t="n">
-        <v>0.84</v>
+        <v>0.867</v>
       </c>
       <c r="H104" t="n">
-        <v>0.648</v>
+        <v>0.625</v>
       </c>
       <c r="I104" t="n">
         <v>1</v>
@@ -5892,16 +5892,16 @@
         <v>10</v>
       </c>
       <c r="F107" t="n">
-        <v>0.82</v>
+        <v>0.827</v>
       </c>
       <c r="G107" t="n">
-        <v>0.867</v>
+        <v>0.873</v>
       </c>
       <c r="H107" t="n">
-        <v>0.341</v>
+        <v>0.332</v>
       </c>
       <c r="I107" t="n">
-        <v>0.908</v>
+        <v>0.885</v>
       </c>
     </row>
     <row r="108">
@@ -5929,13 +5929,13 @@
         <v>11</v>
       </c>
       <c r="F108" t="n">
-        <v>0.787</v>
+        <v>0.773</v>
       </c>
       <c r="G108" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.793</v>
       </c>
       <c r="H108" t="n">
-        <v>0.774</v>
+        <v>0.779</v>
       </c>
       <c r="I108" t="n">
         <v>1</v>
@@ -6049,7 +6049,7 @@
         <v>0.135</v>
       </c>
       <c r="I111" t="n">
-        <v>0.703</v>
+        <v>0.721</v>
       </c>
     </row>
     <row r="112">
@@ -6117,13 +6117,13 @@
         <v>0.46</v>
       </c>
       <c r="G113" t="n">
-        <v>0.7</v>
+        <v>0.713</v>
       </c>
       <c r="H113" t="n">
-        <v>3.88e-05</v>
+        <v>1.28e-05</v>
       </c>
       <c r="I113" t="n">
-        <v>0.000621</v>
+        <v>0.000205</v>
       </c>
     </row>
     <row r="114">
@@ -6305,10 +6305,10 @@
         <v>1</v>
       </c>
       <c r="H118" t="n">
-        <v>0.248</v>
+        <v>0.247</v>
       </c>
       <c r="I118" t="n">
-        <v>0.444</v>
+        <v>0.446</v>
       </c>
     </row>
     <row r="119">
@@ -6336,16 +6336,16 @@
         <v>6</v>
       </c>
       <c r="F119" t="n">
-        <v>0.875</v>
+        <v>0.877</v>
       </c>
       <c r="G119" t="n">
         <v>0.961</v>
       </c>
       <c r="H119" t="n">
-        <v>0.08019999999999999</v>
+        <v>0.081</v>
       </c>
       <c r="I119" t="n">
-        <v>0.214</v>
+        <v>0.216</v>
       </c>
     </row>
     <row r="120">
@@ -6373,16 +6373,16 @@
         <v>7</v>
       </c>
       <c r="F120" t="n">
-        <v>0.88</v>
+        <v>0.886</v>
       </c>
       <c r="G120" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.945</v>
       </c>
       <c r="H120" t="n">
-        <v>0.25</v>
+        <v>0.251</v>
       </c>
       <c r="I120" t="n">
-        <v>0.444</v>
+        <v>0.446</v>
       </c>
     </row>
     <row r="121">
@@ -6487,7 +6487,7 @@
         <v>0.982</v>
       </c>
       <c r="G123" t="n">
-        <v>0.969</v>
+        <v>0.97</v>
       </c>
       <c r="H123" t="n">
         <v>1</v>
@@ -6521,10 +6521,10 @@
         <v>11</v>
       </c>
       <c r="F124" t="n">
-        <v>0.864</v>
+        <v>0.863</v>
       </c>
       <c r="G124" t="n">
-        <v>0.97</v>
+        <v>0.969</v>
       </c>
       <c r="H124" t="n">
         <v>0.038</v>
@@ -6706,16 +6706,16 @@
         <v>16</v>
       </c>
       <c r="F129" t="n">
-        <v>0.38</v>
+        <v>0.389</v>
       </c>
       <c r="G129" t="n">
-        <v>0.647</v>
+        <v>0.706</v>
       </c>
       <c r="H129" t="n">
-        <v>0.00953</v>
+        <v>0.00154</v>
       </c>
       <c r="I129" t="n">
-        <v>0.0508</v>
+        <v>0.008189999999999999</v>
       </c>
     </row>
     <row r="130">
@@ -6854,10 +6854,10 @@
         <v>4</v>
       </c>
       <c r="F133" t="n">
-        <v>0.864</v>
+        <v>0.909</v>
       </c>
       <c r="G133" t="n">
-        <v>0.864</v>
+        <v>0.909</v>
       </c>
       <c r="H133" t="n">
         <v>1</v>
@@ -6894,13 +6894,13 @@
         <v>0.743</v>
       </c>
       <c r="G134" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="H134" t="n">
-        <v>0.437</v>
+        <v>0.532</v>
       </c>
       <c r="I134" t="n">
-        <v>0.794</v>
+        <v>0.881</v>
       </c>
     </row>
     <row r="135">
@@ -6928,16 +6928,16 @@
         <v>6</v>
       </c>
       <c r="F135" t="n">
-        <v>0.761</v>
+        <v>0.772</v>
       </c>
       <c r="G135" t="n">
         <v>0.793</v>
       </c>
       <c r="H135" t="n">
-        <v>0.723</v>
+        <v>0.858</v>
       </c>
       <c r="I135" t="n">
-        <v>0.965</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136">
@@ -6965,10 +6965,10 @@
         <v>7</v>
       </c>
       <c r="F136" t="n">
-        <v>0.776</v>
+        <v>0.824</v>
       </c>
       <c r="G136" t="n">
-        <v>0.765</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="H136" t="n">
         <v>1</v>
@@ -7048,7 +7048,7 @@
         <v>0.791</v>
       </c>
       <c r="I138" t="n">
-        <v>0.974</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139">
@@ -7076,13 +7076,13 @@
         <v>10</v>
       </c>
       <c r="F139" t="n">
-        <v>0.675</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="G139" t="n">
-        <v>0.775</v>
+        <v>0.79</v>
       </c>
       <c r="H139" t="n">
-        <v>0.215</v>
+        <v>0.209</v>
       </c>
       <c r="I139" t="n">
         <v>0.642</v>
@@ -7113,16 +7113,16 @@
         <v>11</v>
       </c>
       <c r="F140" t="n">
-        <v>0.769</v>
+        <v>0.75</v>
       </c>
       <c r="G140" t="n">
-        <v>0.703</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="H140" t="n">
-        <v>0.4</v>
+        <v>0.413</v>
       </c>
       <c r="I140" t="n">
-        <v>0.794</v>
+        <v>0.881</v>
       </c>
     </row>
     <row r="141">
@@ -7233,7 +7233,7 @@
         <v>0.447</v>
       </c>
       <c r="I143" t="n">
-        <v>0.794</v>
+        <v>0.881</v>
       </c>
     </row>
     <row r="144">
@@ -7298,16 +7298,16 @@
         <v>16</v>
       </c>
       <c r="F145" t="n">
-        <v>0.745</v>
+        <v>0.737</v>
       </c>
       <c r="G145" t="n">
-        <v>0.4</v>
+        <v>0.421</v>
       </c>
       <c r="H145" t="n">
-        <v>0.000461</v>
+        <v>0.00115</v>
       </c>
       <c r="I145" t="n">
-        <v>0.00369</v>
+        <v>0.00923</v>
       </c>
     </row>
     <row r="146">
@@ -7446,16 +7446,16 @@
         <v>4</v>
       </c>
       <c r="F149" t="n">
-        <v>0.98</v>
+        <v>0.987</v>
       </c>
       <c r="G149" t="n">
-        <v>0.993</v>
+        <v>1</v>
       </c>
       <c r="H149" t="n">
-        <v>0.622</v>
+        <v>0.498</v>
       </c>
       <c r="I149" t="n">
-        <v>0.766</v>
+        <v>0.613</v>
       </c>
     </row>
     <row r="150">
@@ -7492,7 +7492,7 @@
         <v>0.545</v>
       </c>
       <c r="I150" t="n">
-        <v>0.727</v>
+        <v>0.623</v>
       </c>
     </row>
     <row r="151">
@@ -7520,16 +7520,16 @@
         <v>6</v>
       </c>
       <c r="F151" t="n">
-        <v>0.787</v>
+        <v>0.793</v>
       </c>
       <c r="G151" t="n">
-        <v>0.9</v>
+        <v>0.907</v>
       </c>
       <c r="H151" t="n">
-        <v>0.0105</v>
+        <v>0.00911</v>
       </c>
       <c r="I151" t="n">
-        <v>0.0419</v>
+        <v>0.0365</v>
       </c>
     </row>
     <row r="152">
@@ -7557,16 +7557,16 @@
         <v>7</v>
       </c>
       <c r="F152" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.84</v>
       </c>
       <c r="G152" t="n">
-        <v>0.873</v>
+        <v>0.927</v>
       </c>
       <c r="H152" t="n">
-        <v>0.204</v>
+        <v>0.0298</v>
       </c>
       <c r="I152" t="n">
-        <v>0.326</v>
+        <v>0.0793</v>
       </c>
     </row>
     <row r="153">
@@ -7640,7 +7640,7 @@
         <v>0.0356</v>
       </c>
       <c r="I154" t="n">
-        <v>0.0949</v>
+        <v>0.0813</v>
       </c>
     </row>
     <row r="155">
@@ -7668,16 +7668,16 @@
         <v>10</v>
       </c>
       <c r="F155" t="n">
-        <v>0.82</v>
+        <v>0.827</v>
       </c>
       <c r="G155" t="n">
-        <v>0.9</v>
+        <v>0.907</v>
       </c>
       <c r="H155" t="n">
-        <v>0.0663</v>
+        <v>0.0607</v>
       </c>
       <c r="I155" t="n">
-        <v>0.133</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="156">
@@ -7705,16 +7705,16 @@
         <v>11</v>
       </c>
       <c r="F156" t="n">
-        <v>0.787</v>
+        <v>0.773</v>
       </c>
       <c r="G156" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="H156" t="n">
-        <v>0.774</v>
+        <v>0.476</v>
       </c>
       <c r="I156" t="n">
-        <v>0.885</v>
+        <v>0.613</v>
       </c>
     </row>
     <row r="157">
@@ -7751,7 +7751,7 @@
         <v>0.126</v>
       </c>
       <c r="I157" t="n">
-        <v>0.223</v>
+        <v>0.201</v>
       </c>
     </row>
     <row r="158">
@@ -7825,7 +7825,7 @@
         <v>0.0467</v>
       </c>
       <c r="I159" t="n">
-        <v>0.107</v>
+        <v>0.09329999999999999</v>
       </c>
     </row>
     <row r="160">
@@ -7973,7 +7973,7 @@
         <v>0.0152</v>
       </c>
       <c r="I163" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.0703</v>
       </c>
     </row>
     <row r="164">
@@ -8112,16 +8112,16 @@
         <v>6</v>
       </c>
       <c r="F167" t="n">
-        <v>0.875</v>
+        <v>0.877</v>
       </c>
       <c r="G167" t="n">
-        <v>0.975</v>
+        <v>0.976</v>
       </c>
       <c r="H167" t="n">
-        <v>0.0175</v>
+        <v>0.0176</v>
       </c>
       <c r="I167" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.0703</v>
       </c>
     </row>
     <row r="168">
@@ -8149,16 +8149,16 @@
         <v>7</v>
       </c>
       <c r="F168" t="n">
-        <v>0.88</v>
+        <v>0.886</v>
       </c>
       <c r="G168" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H168" t="n">
-        <v>0.276</v>
+        <v>0.269</v>
       </c>
       <c r="I168" t="n">
-        <v>0.737</v>
+        <v>0.716</v>
       </c>
     </row>
     <row r="169">
@@ -8263,7 +8263,7 @@
         <v>0.982</v>
       </c>
       <c r="G171" t="n">
-        <v>0.958</v>
+        <v>0.959</v>
       </c>
       <c r="H171" t="n">
         <v>0.631</v>
@@ -8297,13 +8297,13 @@
         <v>11</v>
       </c>
       <c r="F172" t="n">
-        <v>0.864</v>
+        <v>0.863</v>
       </c>
       <c r="G172" t="n">
-        <v>0.878</v>
+        <v>0.89</v>
       </c>
       <c r="H172" t="n">
-        <v>0.819</v>
+        <v>0.639</v>
       </c>
       <c r="I172" t="n">
         <v>1</v>
@@ -8482,16 +8482,16 @@
         <v>16</v>
       </c>
       <c r="F177" t="n">
-        <v>0.38</v>
+        <v>0.389</v>
       </c>
       <c r="G177" t="n">
-        <v>0.659</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="H177" t="n">
-        <v>0.00307</v>
+        <v>0.0017</v>
       </c>
       <c r="I177" t="n">
-        <v>0.0246</v>
+        <v>0.0136</v>
       </c>
     </row>
     <row r="178">
@@ -8630,16 +8630,16 @@
         <v>4</v>
       </c>
       <c r="F181" t="n">
-        <v>0.864</v>
+        <v>0.909</v>
       </c>
       <c r="G181" t="n">
-        <v>0.955</v>
+        <v>1</v>
       </c>
       <c r="H181" t="n">
-        <v>0.607</v>
+        <v>0.488</v>
       </c>
       <c r="I181" t="n">
-        <v>0.827</v>
+        <v>0.735</v>
       </c>
     </row>
     <row r="182">
@@ -8676,7 +8676,7 @@
         <v>0.506</v>
       </c>
       <c r="I182" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.735</v>
       </c>
     </row>
     <row r="183">
@@ -8704,16 +8704,16 @@
         <v>6</v>
       </c>
       <c r="F183" t="n">
-        <v>0.761</v>
+        <v>0.772</v>
       </c>
       <c r="G183" t="n">
-        <v>0.859</v>
+        <v>0.87</v>
       </c>
       <c r="H183" t="n">
-        <v>0.132</v>
+        <v>0.123</v>
       </c>
       <c r="I183" t="n">
-        <v>0.302</v>
+        <v>0.247</v>
       </c>
     </row>
     <row r="184">
@@ -8741,16 +8741,16 @@
         <v>7</v>
       </c>
       <c r="F184" t="n">
-        <v>0.776</v>
+        <v>0.824</v>
       </c>
       <c r="G184" t="n">
-        <v>0.835</v>
+        <v>0.929</v>
       </c>
       <c r="H184" t="n">
-        <v>0.438</v>
+        <v>0.0602</v>
       </c>
       <c r="I184" t="n">
-        <v>0.779</v>
+        <v>0.138</v>
       </c>
     </row>
     <row r="185">
@@ -8787,7 +8787,7 @@
         <v>0.62</v>
       </c>
       <c r="I185" t="n">
-        <v>0.827</v>
+        <v>0.763</v>
       </c>
     </row>
     <row r="186">
@@ -8852,13 +8852,13 @@
         <v>10</v>
       </c>
       <c r="F187" t="n">
-        <v>0.675</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="G187" t="n">
-        <v>0.85</v>
+        <v>0.864</v>
       </c>
       <c r="H187" t="n">
-        <v>0.0151</v>
+        <v>0.0133</v>
       </c>
       <c r="I187" t="n">
         <v>0.0697</v>
@@ -8889,16 +8889,16 @@
         <v>11</v>
       </c>
       <c r="F188" t="n">
-        <v>0.769</v>
+        <v>0.75</v>
       </c>
       <c r="G188" t="n">
-        <v>0.791</v>
+        <v>0.793</v>
       </c>
       <c r="H188" t="n">
-        <v>0.858</v>
+        <v>0.599</v>
       </c>
       <c r="I188" t="n">
-        <v>1</v>
+        <v>0.763</v>
       </c>
     </row>
     <row r="189">
@@ -9009,7 +9009,7 @@
         <v>0.394</v>
       </c>
       <c r="I191" t="n">
-        <v>0.779</v>
+        <v>0.701</v>
       </c>
     </row>
     <row r="192">
@@ -9074,13 +9074,13 @@
         <v>16</v>
       </c>
       <c r="F193" t="n">
-        <v>0.745</v>
+        <v>0.737</v>
       </c>
       <c r="G193" t="n">
         <v>0.491</v>
       </c>
       <c r="H193" t="n">
-        <v>0.0103</v>
+        <v>0.012</v>
       </c>
       <c r="I193" t="n">
         <v>0.0697</v>
@@ -9222,16 +9222,16 @@
         <v>4</v>
       </c>
       <c r="F197" t="n">
-        <v>0.98</v>
+        <v>0.987</v>
       </c>
       <c r="G197" t="n">
         <v>0.953</v>
       </c>
       <c r="H197" t="n">
-        <v>0.335</v>
+        <v>0.173</v>
       </c>
       <c r="I197" t="n">
-        <v>0.826</v>
+        <v>0.554</v>
       </c>
     </row>
     <row r="198">
@@ -9259,10 +9259,10 @@
         <v>5</v>
       </c>
       <c r="F198" t="n">
-        <v>0.72</v>
+        <v>0.727</v>
       </c>
       <c r="G198" t="n">
-        <v>0.72</v>
+        <v>0.727</v>
       </c>
       <c r="H198" t="n">
         <v>1</v>
@@ -9333,16 +9333,16 @@
         <v>7</v>
       </c>
       <c r="F200" t="n">
+        <v>0.8070000000000001</v>
+      </c>
+      <c r="G200" t="n">
         <v>0.773</v>
       </c>
-      <c r="G200" t="n">
-        <v>0.76</v>
-      </c>
       <c r="H200" t="n">
-        <v>0.892</v>
+        <v>0.571</v>
       </c>
       <c r="I200" t="n">
-        <v>1</v>
+        <v>0.881</v>
       </c>
     </row>
     <row r="201">
@@ -9444,16 +9444,16 @@
         <v>10</v>
       </c>
       <c r="F203" t="n">
-        <v>0.82</v>
+        <v>0.827</v>
       </c>
       <c r="G203" t="n">
-        <v>0.74</v>
+        <v>0.747</v>
       </c>
       <c r="H203" t="n">
-        <v>0.125</v>
+        <v>0.121</v>
       </c>
       <c r="I203" t="n">
-        <v>0.499</v>
+        <v>0.483</v>
       </c>
     </row>
     <row r="204">
@@ -9481,16 +9481,16 @@
         <v>11</v>
       </c>
       <c r="F204" t="n">
-        <v>0.747</v>
+        <v>0.74</v>
       </c>
       <c r="G204" t="n">
-        <v>0.72</v>
+        <v>0.707</v>
       </c>
       <c r="H204" t="n">
-        <v>0.695</v>
+        <v>0.606</v>
       </c>
       <c r="I204" t="n">
-        <v>1</v>
+        <v>0.881</v>
       </c>
     </row>
     <row r="205">
@@ -9601,7 +9601,7 @@
         <v>0.579</v>
       </c>
       <c r="I207" t="n">
-        <v>1</v>
+        <v>0.881</v>
       </c>
     </row>
     <row r="208">
@@ -9666,16 +9666,16 @@
         <v>16</v>
       </c>
       <c r="F209" t="n">
-        <v>0.547</v>
+        <v>0.553</v>
       </c>
       <c r="G209" t="n">
-        <v>0.673</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="H209" t="n">
-        <v>0.0329</v>
+        <v>0.017</v>
       </c>
       <c r="I209" t="n">
-        <v>0.464</v>
+        <v>0.272</v>
       </c>
     </row>
     <row r="210">
@@ -9749,7 +9749,7 @@
         <v>0.0264</v>
       </c>
       <c r="I211" t="n">
-        <v>0.368</v>
+        <v>0.245</v>
       </c>
     </row>
     <row r="212">
@@ -9851,10 +9851,10 @@
         <v>5</v>
       </c>
       <c r="F214" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="G214" t="n">
-        <v>0.954</v>
+        <v>0.955</v>
       </c>
       <c r="H214" t="n">
         <v>1</v>
@@ -9925,13 +9925,13 @@
         <v>7</v>
       </c>
       <c r="F216" t="n">
-        <v>0.918</v>
+        <v>0.924</v>
       </c>
       <c r="G216" t="n">
-        <v>0.962</v>
+        <v>0.964</v>
       </c>
       <c r="H216" t="n">
-        <v>0.447</v>
+        <v>0.453</v>
       </c>
       <c r="I216" t="n">
         <v>0.862</v>
@@ -10036,16 +10036,16 @@
         <v>10</v>
       </c>
       <c r="F219" t="n">
-        <v>0.949</v>
+        <v>0.951</v>
       </c>
       <c r="G219" t="n">
-        <v>0.887</v>
+        <v>0.891</v>
       </c>
       <c r="H219" t="n">
-        <v>0.303</v>
+        <v>0.305</v>
       </c>
       <c r="I219" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.696</v>
       </c>
     </row>
     <row r="220">
@@ -10076,13 +10076,13 @@
         <v>0.873</v>
       </c>
       <c r="G220" t="n">
-        <v>0.915</v>
+        <v>0.914</v>
       </c>
       <c r="H220" t="n">
-        <v>0.573</v>
+        <v>0.574</v>
       </c>
       <c r="I220" t="n">
-        <v>0.917</v>
+        <v>0.919</v>
       </c>
     </row>
     <row r="221">
@@ -10230,7 +10230,7 @@
         <v>0.0459</v>
       </c>
       <c r="I224" t="n">
-        <v>0.368</v>
+        <v>0.245</v>
       </c>
     </row>
     <row r="225">
@@ -10258,16 +10258,16 @@
         <v>16</v>
       </c>
       <c r="F225" t="n">
-        <v>0.411</v>
+        <v>0.431</v>
       </c>
       <c r="G225" t="n">
-        <v>0.588</v>
+        <v>0.657</v>
       </c>
       <c r="H225" t="n">
-        <v>0.09959999999999999</v>
+        <v>0.039</v>
       </c>
       <c r="I225" t="n">
-        <v>0.406</v>
+        <v>0.245</v>
       </c>
     </row>
     <row r="226">
@@ -10304,7 +10304,7 @@
         <v>0.325</v>
       </c>
       <c r="I226" t="n">
-        <v>0.473</v>
+        <v>0.434</v>
       </c>
     </row>
     <row r="227">
@@ -10341,7 +10341,7 @@
         <v>0.1</v>
       </c>
       <c r="I227" t="n">
-        <v>0.413</v>
+        <v>0.396</v>
       </c>
     </row>
     <row r="228">
@@ -10378,7 +10378,7 @@
         <v>0.205</v>
       </c>
       <c r="I228" t="n">
-        <v>0.473</v>
+        <v>0.396</v>
       </c>
     </row>
     <row r="229">
@@ -10406,16 +10406,16 @@
         <v>4</v>
       </c>
       <c r="F229" t="n">
-        <v>0.864</v>
+        <v>0.909</v>
       </c>
       <c r="G229" t="n">
         <v>0.6820000000000001</v>
       </c>
       <c r="H229" t="n">
-        <v>0.281</v>
+        <v>0.132</v>
       </c>
       <c r="I229" t="n">
-        <v>0.473</v>
+        <v>0.396</v>
       </c>
     </row>
     <row r="230">
@@ -10443,10 +10443,10 @@
         <v>5</v>
       </c>
       <c r="F230" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="G230" t="n">
         <v>0.624</v>
-      </c>
-      <c r="G230" t="n">
-        <v>0.614</v>
       </c>
       <c r="H230" t="n">
         <v>1</v>
@@ -10489,7 +10489,7 @@
         <v>0.103</v>
       </c>
       <c r="I231" t="n">
-        <v>0.413</v>
+        <v>0.396</v>
       </c>
     </row>
     <row r="232">
@@ -10517,16 +10517,16 @@
         <v>7</v>
       </c>
       <c r="F232" t="n">
-        <v>0.659</v>
+        <v>0.718</v>
       </c>
       <c r="G232" t="n">
-        <v>0.6</v>
+        <v>0.624</v>
       </c>
       <c r="H232" t="n">
-        <v>0.525</v>
+        <v>0.253</v>
       </c>
       <c r="I232" t="n">
-        <v>0.647</v>
+        <v>0.405</v>
       </c>
     </row>
     <row r="233">
@@ -10600,7 +10600,7 @@
         <v>0.313</v>
       </c>
       <c r="I234" t="n">
-        <v>0.473</v>
+        <v>0.434</v>
       </c>
     </row>
     <row r="235">
@@ -10628,16 +10628,16 @@
         <v>10</v>
       </c>
       <c r="F235" t="n">
-        <v>0.7</v>
+        <v>0.716</v>
       </c>
       <c r="G235" t="n">
-        <v>0.588</v>
+        <v>0.605</v>
       </c>
       <c r="H235" t="n">
-        <v>0.186</v>
+        <v>0.184</v>
       </c>
       <c r="I235" t="n">
-        <v>0.473</v>
+        <v>0.396</v>
       </c>
     </row>
     <row r="236">
@@ -10665,16 +10665,16 @@
         <v>11</v>
       </c>
       <c r="F236" t="n">
-        <v>0.681</v>
+        <v>0.674</v>
       </c>
       <c r="G236" t="n">
-        <v>0.593</v>
+        <v>0.576</v>
       </c>
       <c r="H236" t="n">
-        <v>0.28</v>
+        <v>0.223</v>
       </c>
       <c r="I236" t="n">
-        <v>0.473</v>
+        <v>0.396</v>
       </c>
     </row>
     <row r="237">
@@ -10748,7 +10748,7 @@
         <v>0.067</v>
       </c>
       <c r="I238" t="n">
-        <v>0.413</v>
+        <v>0.396</v>
       </c>
     </row>
     <row r="239">
@@ -10785,7 +10785,7 @@
         <v>0.367</v>
       </c>
       <c r="I239" t="n">
-        <v>0.49</v>
+        <v>0.452</v>
       </c>
     </row>
     <row r="240">
@@ -10822,7 +10822,7 @@
         <v>0.211</v>
       </c>
       <c r="I240" t="n">
-        <v>0.473</v>
+        <v>0.396</v>
       </c>
     </row>
     <row r="241">
@@ -10850,16 +10850,16 @@
         <v>16</v>
       </c>
       <c r="F241" t="n">
-        <v>0.545</v>
+        <v>0.544</v>
       </c>
       <c r="G241" t="n">
-        <v>0.364</v>
+        <v>0.404</v>
       </c>
       <c r="H241" t="n">
-        <v>0.0844</v>
+        <v>0.189</v>
       </c>
       <c r="I241" t="n">
-        <v>0.413</v>
+        <v>0.396</v>
       </c>
     </row>
     <row r="242">
@@ -10896,7 +10896,7 @@
         <v>0.39</v>
       </c>
       <c r="I242" t="n">
-        <v>0.97</v>
+        <v>0.969</v>
       </c>
     </row>
     <row r="243">
@@ -10998,16 +10998,16 @@
         <v>4</v>
       </c>
       <c r="F245" t="n">
-        <v>0.98</v>
+        <v>0.987</v>
       </c>
       <c r="G245" t="n">
-        <v>0.967</v>
+        <v>0.973</v>
       </c>
       <c r="H245" t="n">
-        <v>0.723</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="I245" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
     </row>
     <row r="246">
@@ -11035,16 +11035,16 @@
         <v>5</v>
       </c>
       <c r="F246" t="n">
-        <v>0.72</v>
+        <v>0.727</v>
       </c>
       <c r="G246" t="n">
-        <v>0.767</v>
+        <v>0.773</v>
       </c>
       <c r="H246" t="n">
-        <v>0.428</v>
+        <v>0.424</v>
       </c>
       <c r="I246" t="n">
-        <v>0.97</v>
+        <v>0.969</v>
       </c>
     </row>
     <row r="247">
@@ -11109,16 +11109,16 @@
         <v>7</v>
       </c>
       <c r="F248" t="n">
-        <v>0.773</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="G248" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.84</v>
       </c>
       <c r="H248" t="n">
-        <v>0.571</v>
+        <v>0.545</v>
       </c>
       <c r="I248" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
     </row>
     <row r="249">
@@ -11220,16 +11220,16 @@
         <v>10</v>
       </c>
       <c r="F251" t="n">
-        <v>0.82</v>
+        <v>0.827</v>
       </c>
       <c r="G251" t="n">
         <v>0.847</v>
       </c>
       <c r="H251" t="n">
-        <v>0.642</v>
+        <v>0.755</v>
       </c>
       <c r="I251" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
     </row>
     <row r="252">
@@ -11257,16 +11257,16 @@
         <v>11</v>
       </c>
       <c r="F252" t="n">
-        <v>0.747</v>
+        <v>0.74</v>
       </c>
       <c r="G252" t="n">
-        <v>0.653</v>
+        <v>0.647</v>
       </c>
       <c r="H252" t="n">
-        <v>0.101</v>
+        <v>0.103</v>
       </c>
       <c r="I252" t="n">
-        <v>0.324</v>
+        <v>0.331</v>
       </c>
     </row>
     <row r="253">
@@ -11377,7 +11377,7 @@
         <v>0.6909999999999999</v>
       </c>
       <c r="I255" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
     </row>
     <row r="256">
@@ -11442,16 +11442,16 @@
         <v>16</v>
       </c>
       <c r="F257" t="n">
-        <v>0.547</v>
+        <v>0.553</v>
       </c>
       <c r="G257" t="n">
         <v>0.573</v>
       </c>
       <c r="H257" t="n">
-        <v>0.727</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="I257" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
     </row>
     <row r="258">
@@ -11525,7 +11525,7 @@
         <v>0.117</v>
       </c>
       <c r="I259" t="n">
-        <v>0.245</v>
+        <v>0.243</v>
       </c>
     </row>
     <row r="260">
@@ -11562,7 +11562,7 @@
         <v>0.827</v>
       </c>
       <c r="I260" t="n">
-        <v>0.986</v>
+        <v>1</v>
       </c>
     </row>
     <row r="261">
@@ -11593,13 +11593,13 @@
         <v>1</v>
       </c>
       <c r="G261" t="n">
-        <v>0.84</v>
+        <v>0.846</v>
       </c>
       <c r="H261" t="n">
-        <v>0.122</v>
+        <v>0.121</v>
       </c>
       <c r="I261" t="n">
-        <v>0.245</v>
+        <v>0.243</v>
       </c>
     </row>
     <row r="262">
@@ -11627,16 +11627,16 @@
         <v>5</v>
       </c>
       <c r="F262" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="G262" t="n">
-        <v>0.851</v>
+        <v>0.853</v>
       </c>
       <c r="H262" t="n">
-        <v>0.126</v>
+        <v>0.0828</v>
       </c>
       <c r="I262" t="n">
-        <v>0.245</v>
+        <v>0.221</v>
       </c>
     </row>
     <row r="263">
@@ -11701,16 +11701,16 @@
         <v>7</v>
       </c>
       <c r="F264" t="n">
-        <v>0.918</v>
+        <v>0.924</v>
       </c>
       <c r="G264" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="H264" t="n">
-        <v>0.0289</v>
+        <v>0.0297</v>
       </c>
       <c r="I264" t="n">
-        <v>0.116</v>
+        <v>0.119</v>
       </c>
     </row>
     <row r="265">
@@ -11747,7 +11747,7 @@
         <v>0.346</v>
       </c>
       <c r="I265" t="n">
-        <v>0.504</v>
+        <v>0.503</v>
       </c>
     </row>
     <row r="266">
@@ -11812,16 +11812,16 @@
         <v>10</v>
       </c>
       <c r="F267" t="n">
-        <v>0.949</v>
+        <v>0.951</v>
       </c>
       <c r="G267" t="n">
-        <v>0.901</v>
+        <v>0.903</v>
       </c>
       <c r="H267" t="n">
-        <v>0.346</v>
+        <v>0.342</v>
       </c>
       <c r="I267" t="n">
-        <v>0.504</v>
+        <v>0.503</v>
       </c>
     </row>
     <row r="268">
@@ -12034,16 +12034,16 @@
         <v>16</v>
       </c>
       <c r="F273" t="n">
-        <v>0.411</v>
+        <v>0.431</v>
       </c>
       <c r="G273" t="n">
-        <v>0.429</v>
+        <v>0.444</v>
       </c>
       <c r="H273" t="n">
-        <v>0.863</v>
+        <v>1</v>
       </c>
       <c r="I273" t="n">
-        <v>0.986</v>
+        <v>1</v>
       </c>
     </row>
     <row r="274">
@@ -12182,16 +12182,16 @@
         <v>4</v>
       </c>
       <c r="F277" t="n">
-        <v>0.864</v>
+        <v>0.909</v>
       </c>
       <c r="G277" t="n">
-        <v>0.955</v>
+        <v>1</v>
       </c>
       <c r="H277" t="n">
-        <v>0.607</v>
+        <v>0.488</v>
       </c>
       <c r="I277" t="n">
-        <v>0.784</v>
+        <v>0.651</v>
       </c>
     </row>
     <row r="278">
@@ -12219,16 +12219,16 @@
         <v>5</v>
       </c>
       <c r="F278" t="n">
-        <v>0.624</v>
+        <v>0.634</v>
       </c>
       <c r="G278" t="n">
-        <v>0.792</v>
+        <v>0.802</v>
       </c>
       <c r="H278" t="n">
-        <v>0.0129</v>
+        <v>0.012</v>
       </c>
       <c r="I278" t="n">
-        <v>0.0296</v>
+        <v>0.0274</v>
       </c>
     </row>
     <row r="279">
@@ -12265,7 +12265,7 @@
         <v>1.44e-05</v>
       </c>
       <c r="I279" t="n">
-        <v>7.7e-05</v>
+        <v>5.78e-05</v>
       </c>
     </row>
     <row r="280">
@@ -12293,16 +12293,16 @@
         <v>7</v>
       </c>
       <c r="F280" t="n">
-        <v>0.659</v>
+        <v>0.718</v>
       </c>
       <c r="G280" t="n">
-        <v>0.918</v>
+        <v>0.976</v>
       </c>
       <c r="H280" t="n">
-        <v>5.38e-05</v>
+        <v>2.09e-06</v>
       </c>
       <c r="I280" t="n">
-        <v>0.000172</v>
+        <v>1.67e-05</v>
       </c>
     </row>
     <row r="281">
@@ -12376,7 +12376,7 @@
         <v>1.31e-05</v>
       </c>
       <c r="I282" t="n">
-        <v>7.7e-05</v>
+        <v>5.78e-05</v>
       </c>
     </row>
     <row r="283">
@@ -12404,16 +12404,16 @@
         <v>10</v>
       </c>
       <c r="F283" t="n">
-        <v>0.7</v>
+        <v>0.716</v>
       </c>
       <c r="G283" t="n">
-        <v>0.8</v>
+        <v>0.802</v>
       </c>
       <c r="H283" t="n">
-        <v>0.201</v>
+        <v>0.27</v>
       </c>
       <c r="I283" t="n">
-        <v>0.402</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="284">
@@ -12441,16 +12441,16 @@
         <v>11</v>
       </c>
       <c r="F284" t="n">
-        <v>0.681</v>
+        <v>0.674</v>
       </c>
       <c r="G284" t="n">
-        <v>0.714</v>
+        <v>0.707</v>
       </c>
       <c r="H284" t="n">
-        <v>0.747</v>
+        <v>0.75</v>
       </c>
       <c r="I284" t="n">
-        <v>0.797</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="285">
@@ -12487,7 +12487,7 @@
         <v>3.96e-05</v>
       </c>
       <c r="I285" t="n">
-        <v>0.000158</v>
+        <v>0.000127</v>
       </c>
     </row>
     <row r="286">
@@ -12524,7 +12524,7 @@
         <v>0.488</v>
       </c>
       <c r="I286" t="n">
-        <v>0.71</v>
+        <v>0.651</v>
       </c>
     </row>
     <row r="287">
@@ -12626,16 +12626,16 @@
         <v>16</v>
       </c>
       <c r="F289" t="n">
-        <v>0.545</v>
+        <v>0.544</v>
       </c>
       <c r="G289" t="n">
         <v>0.491</v>
       </c>
       <c r="H289" t="n">
-        <v>0.703</v>
+        <v>0.708</v>
       </c>
       <c r="I289" t="n">
-        <v>0.797</v>
+        <v>0.8</v>
       </c>
     </row>
   </sheetData>

--- a/eval/results/statistical_tests_full150.xlsx
+++ b/eval/results/statistical_tests_full150.xlsx
@@ -506,16 +506,16 @@
         <v>0.00116</v>
       </c>
       <c r="F2" t="n">
-        <v>0.844</v>
+        <v>0.845</v>
       </c>
       <c r="G2" t="n">
-        <v>0.91</v>
+        <v>0.911</v>
       </c>
       <c r="H2" t="n">
-        <v>0.109</v>
+        <v>0.11</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0633</v>
+        <v>0.0636</v>
       </c>
       <c r="J2" t="n">
         <v>0.00696</v>
@@ -546,16 +546,16 @@
         <v>0.0015</v>
       </c>
       <c r="F3" t="n">
-        <v>0.844</v>
+        <v>0.845</v>
       </c>
       <c r="G3" t="n">
-        <v>0.91</v>
+        <v>0.911</v>
       </c>
       <c r="H3" t="n">
-        <v>0.109</v>
+        <v>0.11</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0633</v>
+        <v>0.0636</v>
       </c>
       <c r="J3" t="n">
         <v>0.00564</v>
@@ -586,16 +586,16 @@
         <v>0.655</v>
       </c>
       <c r="F4" t="n">
-        <v>0.844</v>
+        <v>0.845</v>
       </c>
       <c r="G4" t="n">
-        <v>0.848</v>
+        <v>0.849</v>
       </c>
       <c r="H4" t="n">
-        <v>0.109</v>
+        <v>0.11</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1</v>
+        <v>0.101</v>
       </c>
       <c r="J4" t="n">
         <v>0.786</v>
@@ -626,19 +626,19 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>0.844</v>
+        <v>0.845</v>
       </c>
       <c r="G5" t="n">
-        <v>0.848</v>
+        <v>0.849</v>
       </c>
       <c r="H5" t="n">
-        <v>0.109</v>
+        <v>0.11</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1</v>
+        <v>0.101</v>
       </c>
       <c r="J5" t="n">
-        <v>0.887</v>
+        <v>0.842</v>
       </c>
     </row>
     <row r="6">
@@ -663,7 +663,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.0144</v>
+        <v>0.0152</v>
       </c>
       <c r="F6" t="n">
         <v>0.803</v>
@@ -678,7 +678,7 @@
         <v>0.0912</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0288</v>
+        <v>0.0304</v>
       </c>
     </row>
     <row r="7">
@@ -749,13 +749,13 @@
         <v>0.803</v>
       </c>
       <c r="G8" t="n">
-        <v>0.876</v>
+        <v>0.877</v>
       </c>
       <c r="H8" t="n">
         <v>0.149</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0757</v>
+        <v>0.0759</v>
       </c>
       <c r="J8" t="n">
         <v>0.0206</v>
@@ -789,13 +789,13 @@
         <v>0.803</v>
       </c>
       <c r="G9" t="n">
-        <v>0.876</v>
+        <v>0.877</v>
       </c>
       <c r="H9" t="n">
         <v>0.149</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0757</v>
+        <v>0.0759</v>
       </c>
       <c r="J9" t="n">
         <v>0.0179</v>
@@ -823,16 +823,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.622</v>
+        <v>0.645</v>
       </c>
       <c r="F10" t="n">
-        <v>0.783</v>
+        <v>0.784</v>
       </c>
       <c r="G10" t="n">
-        <v>0.79</v>
+        <v>0.791</v>
       </c>
       <c r="H10" t="n">
-        <v>0.125</v>
+        <v>0.126</v>
       </c>
       <c r="I10" t="n">
         <v>0.111</v>
@@ -866,19 +866,19 @@
         <v>0.826</v>
       </c>
       <c r="F11" t="n">
-        <v>0.783</v>
+        <v>0.784</v>
       </c>
       <c r="G11" t="n">
-        <v>0.79</v>
+        <v>0.791</v>
       </c>
       <c r="H11" t="n">
-        <v>0.125</v>
+        <v>0.126</v>
       </c>
       <c r="I11" t="n">
         <v>0.111</v>
       </c>
       <c r="J11" t="n">
-        <v>0.887</v>
+        <v>0.842</v>
       </c>
     </row>
     <row r="12">
@@ -903,22 +903,22 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.915</v>
+        <v>0.866</v>
       </c>
       <c r="F12" t="n">
-        <v>0.783</v>
+        <v>0.784</v>
       </c>
       <c r="G12" t="n">
-        <v>0.785</v>
+        <v>0.787</v>
       </c>
       <c r="H12" t="n">
-        <v>0.125</v>
+        <v>0.126</v>
       </c>
       <c r="I12" t="n">
-        <v>0.106</v>
+        <v>0.107</v>
       </c>
       <c r="J12" t="n">
-        <v>0.915</v>
+        <v>0.866</v>
       </c>
     </row>
     <row r="13">
@@ -943,22 +943,22 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.887</v>
+        <v>0.842</v>
       </c>
       <c r="F13" t="n">
-        <v>0.783</v>
+        <v>0.784</v>
       </c>
       <c r="G13" t="n">
-        <v>0.785</v>
+        <v>0.787</v>
       </c>
       <c r="H13" t="n">
-        <v>0.125</v>
+        <v>0.126</v>
       </c>
       <c r="I13" t="n">
-        <v>0.106</v>
+        <v>0.107</v>
       </c>
       <c r="J13" t="n">
-        <v>0.887</v>
+        <v>0.842</v>
       </c>
     </row>
     <row r="14">
@@ -1143,7 +1143,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.000852</v>
+        <v>0.000855</v>
       </c>
       <c r="F18" t="n">
         <v>0.795</v>
@@ -1158,7 +1158,7 @@
         <v>0.0941</v>
       </c>
       <c r="J18" t="n">
-        <v>0.00256</v>
+        <v>0.00257</v>
       </c>
     </row>
     <row r="19">
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4.35e-05</v>
+        <v>4.65e-05</v>
       </c>
       <c r="F24" t="n">
         <v>0.782</v>
@@ -1398,7 +1398,7 @@
         <v>0.203</v>
       </c>
       <c r="J24" t="n">
-        <v>0.000261</v>
+        <v>0.000279</v>
       </c>
     </row>
     <row r="25">
@@ -1466,16 +1466,16 @@
         <v>0.0155</v>
       </c>
       <c r="F26" t="n">
-        <v>0.783</v>
+        <v>0.784</v>
       </c>
       <c r="G26" t="n">
-        <v>0.861</v>
+        <v>0.862</v>
       </c>
       <c r="H26" t="n">
-        <v>0.157</v>
+        <v>0.158</v>
       </c>
       <c r="I26" t="n">
-        <v>0.13</v>
+        <v>0.131</v>
       </c>
       <c r="J26" t="n">
         <v>0.031</v>
@@ -1506,16 +1506,16 @@
         <v>0.0199</v>
       </c>
       <c r="F27" t="n">
-        <v>0.783</v>
+        <v>0.784</v>
       </c>
       <c r="G27" t="n">
-        <v>0.861</v>
+        <v>0.862</v>
       </c>
       <c r="H27" t="n">
-        <v>0.157</v>
+        <v>0.158</v>
       </c>
       <c r="I27" t="n">
-        <v>0.13</v>
+        <v>0.131</v>
       </c>
       <c r="J27" t="n">
         <v>0.0398</v>
@@ -1546,13 +1546,13 @@
         <v>0.492</v>
       </c>
       <c r="F28" t="n">
-        <v>0.783</v>
+        <v>0.784</v>
       </c>
       <c r="G28" t="n">
-        <v>0.806</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="H28" t="n">
-        <v>0.157</v>
+        <v>0.158</v>
       </c>
       <c r="I28" t="n">
         <v>0.222</v>
@@ -1586,13 +1586,13 @@
         <v>0.345</v>
       </c>
       <c r="F29" t="n">
-        <v>0.783</v>
+        <v>0.784</v>
       </c>
       <c r="G29" t="n">
-        <v>0.806</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="H29" t="n">
-        <v>0.157</v>
+        <v>0.158</v>
       </c>
       <c r="I29" t="n">
         <v>0.222</v>
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.0833</v>
+        <v>0.0776</v>
       </c>
       <c r="F30" t="n">
-        <v>0.767</v>
+        <v>0.768</v>
       </c>
       <c r="G30" t="n">
         <v>0.709</v>
@@ -1638,7 +1638,7 @@
         <v>0.162</v>
       </c>
       <c r="J30" t="n">
-        <v>0.118</v>
+        <v>0.116</v>
       </c>
     </row>
     <row r="31">
@@ -1663,10 +1663,10 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.14</v>
+        <v>0.125</v>
       </c>
       <c r="F31" t="n">
-        <v>0.767</v>
+        <v>0.768</v>
       </c>
       <c r="G31" t="n">
         <v>0.709</v>
@@ -1678,7 +1678,7 @@
         <v>0.162</v>
       </c>
       <c r="J31" t="n">
-        <v>0.168</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="32">
@@ -1706,10 +1706,10 @@
         <v>0.0982</v>
       </c>
       <c r="F32" t="n">
-        <v>0.767</v>
+        <v>0.768</v>
       </c>
       <c r="G32" t="n">
-        <v>0.823</v>
+        <v>0.824</v>
       </c>
       <c r="H32" t="n">
         <v>0.18</v>
@@ -1746,10 +1746,10 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="F33" t="n">
-        <v>0.767</v>
+        <v>0.768</v>
       </c>
       <c r="G33" t="n">
-        <v>0.823</v>
+        <v>0.824</v>
       </c>
       <c r="H33" t="n">
         <v>0.18</v>
@@ -1783,13 +1783,13 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.000654</v>
+        <v>0.00062</v>
       </c>
       <c r="F34" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.695</v>
       </c>
       <c r="G34" t="n">
-        <v>0.59</v>
+        <v>0.591</v>
       </c>
       <c r="H34" t="n">
         <v>0.171</v>
@@ -1798,7 +1798,7 @@
         <v>0.132</v>
       </c>
       <c r="J34" t="n">
-        <v>0.00196</v>
+        <v>0.00186</v>
       </c>
     </row>
     <row r="35">
@@ -1826,10 +1826,10 @@
         <v>0.00451</v>
       </c>
       <c r="F35" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.695</v>
       </c>
       <c r="G35" t="n">
-        <v>0.59</v>
+        <v>0.591</v>
       </c>
       <c r="H35" t="n">
         <v>0.171</v>
@@ -1863,13 +1863,13 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4.83e-05</v>
+        <v>3.7e-05</v>
       </c>
       <c r="F36" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.695</v>
       </c>
       <c r="G36" t="n">
-        <v>0.848</v>
+        <v>0.852</v>
       </c>
       <c r="H36" t="n">
         <v>0.171</v>
@@ -1878,7 +1878,7 @@
         <v>0.161</v>
       </c>
       <c r="J36" t="n">
-        <v>0.00029</v>
+        <v>0.000222</v>
       </c>
     </row>
     <row r="37">
@@ -1906,10 +1906,10 @@
         <v>0.000153</v>
       </c>
       <c r="F37" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.695</v>
       </c>
       <c r="G37" t="n">
-        <v>0.848</v>
+        <v>0.852</v>
       </c>
       <c r="H37" t="n">
         <v>0.171</v>
@@ -2340,16 +2340,16 @@
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9</v>
+        <v>0.913</v>
       </c>
       <c r="G11" t="n">
-        <v>0.92</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.665</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0.967</v>
       </c>
     </row>
     <row r="12">
@@ -2932,10 +2932,10 @@
         <v>10</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="H27" t="n">
         <v>1</v>
@@ -3524,16 +3524,16 @@
         <v>10</v>
       </c>
       <c r="F43" t="n">
-        <v>0.877</v>
+        <v>0.901</v>
       </c>
       <c r="G43" t="n">
-        <v>0.914</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="H43" t="n">
-        <v>0.609</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="I43" t="n">
-        <v>0.886</v>
+        <v>0.821</v>
       </c>
     </row>
     <row r="44">
@@ -4116,10 +4116,10 @@
         <v>10</v>
       </c>
       <c r="F59" t="n">
-        <v>0.9</v>
+        <v>0.913</v>
       </c>
       <c r="G59" t="n">
-        <v>0.9</v>
+        <v>0.913</v>
       </c>
       <c r="H59" t="n">
         <v>1</v>
@@ -4708,10 +4708,10 @@
         <v>10</v>
       </c>
       <c r="F75" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="G75" t="n">
-        <v>0.958</v>
+        <v>0.959</v>
       </c>
       <c r="H75" t="n">
         <v>0.72</v>
@@ -5300,13 +5300,13 @@
         <v>10</v>
       </c>
       <c r="F91" t="n">
+        <v>0.901</v>
+      </c>
+      <c r="G91" t="n">
         <v>0.877</v>
       </c>
-      <c r="G91" t="n">
-        <v>0.852</v>
-      </c>
       <c r="H91" t="n">
-        <v>0.819</v>
+        <v>0.803</v>
       </c>
       <c r="I91" t="n">
         <v>1</v>
@@ -5568,7 +5568,7 @@
         <v>0.312</v>
       </c>
       <c r="I98" t="n">
-        <v>0.885</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="99">
@@ -5753,7 +5753,7 @@
         <v>0.226</v>
       </c>
       <c r="I103" t="n">
-        <v>0.885</v>
+        <v>0.903</v>
       </c>
     </row>
     <row r="104">
@@ -5892,16 +5892,16 @@
         <v>10</v>
       </c>
       <c r="F107" t="n">
-        <v>0.827</v>
+        <v>0.833</v>
       </c>
       <c r="G107" t="n">
         <v>0.873</v>
       </c>
       <c r="H107" t="n">
-        <v>0.332</v>
+        <v>0.415</v>
       </c>
       <c r="I107" t="n">
-        <v>0.885</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
@@ -6484,7 +6484,7 @@
         <v>10</v>
       </c>
       <c r="F123" t="n">
-        <v>0.982</v>
+        <v>0.983</v>
       </c>
       <c r="G123" t="n">
         <v>0.97</v>
@@ -6752,7 +6752,7 @@
         <v>0.241</v>
       </c>
       <c r="I130" t="n">
-        <v>0.642</v>
+        <v>0.742</v>
       </c>
     </row>
     <row r="131">
@@ -6789,7 +6789,7 @@
         <v>0.236</v>
       </c>
       <c r="I131" t="n">
-        <v>0.642</v>
+        <v>0.742</v>
       </c>
     </row>
     <row r="132">
@@ -7076,16 +7076,16 @@
         <v>10</v>
       </c>
       <c r="F139" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.704</v>
       </c>
       <c r="G139" t="n">
         <v>0.79</v>
       </c>
       <c r="H139" t="n">
-        <v>0.209</v>
+        <v>0.278</v>
       </c>
       <c r="I139" t="n">
-        <v>0.642</v>
+        <v>0.742</v>
       </c>
     </row>
     <row r="140">
@@ -7668,16 +7668,16 @@
         <v>10</v>
       </c>
       <c r="F155" t="n">
-        <v>0.827</v>
+        <v>0.833</v>
       </c>
       <c r="G155" t="n">
-        <v>0.907</v>
+        <v>0.913</v>
       </c>
       <c r="H155" t="n">
-        <v>0.0607</v>
+        <v>0.0551</v>
       </c>
       <c r="I155" t="n">
-        <v>0.108</v>
+        <v>0.098</v>
       </c>
     </row>
     <row r="156">
@@ -8260,13 +8260,13 @@
         <v>10</v>
       </c>
       <c r="F171" t="n">
-        <v>0.982</v>
+        <v>0.983</v>
       </c>
       <c r="G171" t="n">
         <v>0.959</v>
       </c>
       <c r="H171" t="n">
-        <v>0.631</v>
+        <v>0.63</v>
       </c>
       <c r="I171" t="n">
         <v>1</v>
@@ -8852,16 +8852,16 @@
         <v>10</v>
       </c>
       <c r="F187" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.704</v>
       </c>
       <c r="G187" t="n">
-        <v>0.864</v>
+        <v>0.877</v>
       </c>
       <c r="H187" t="n">
-        <v>0.0133</v>
+        <v>0.0114</v>
       </c>
       <c r="I187" t="n">
-        <v>0.0697</v>
+        <v>0.0639</v>
       </c>
     </row>
     <row r="188">
@@ -9083,7 +9083,7 @@
         <v>0.012</v>
       </c>
       <c r="I193" t="n">
-        <v>0.0697</v>
+        <v>0.0639</v>
       </c>
     </row>
     <row r="194">
@@ -9157,7 +9157,7 @@
         <v>0.0725</v>
       </c>
       <c r="I195" t="n">
-        <v>0.464</v>
+        <v>0.348</v>
       </c>
     </row>
     <row r="196">
@@ -9444,16 +9444,16 @@
         <v>10</v>
       </c>
       <c r="F203" t="n">
-        <v>0.827</v>
+        <v>0.84</v>
       </c>
       <c r="G203" t="n">
-        <v>0.747</v>
+        <v>0.753</v>
       </c>
       <c r="H203" t="n">
-        <v>0.121</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="I203" t="n">
-        <v>0.483</v>
+        <v>0.348</v>
       </c>
     </row>
     <row r="204">
@@ -9638,7 +9638,7 @@
         <v>0.08690000000000001</v>
       </c>
       <c r="I208" t="n">
-        <v>0.464</v>
+        <v>0.348</v>
       </c>
     </row>
     <row r="209">
@@ -10036,16 +10036,16 @@
         <v>10</v>
       </c>
       <c r="F219" t="n">
-        <v>0.951</v>
+        <v>0.952</v>
       </c>
       <c r="G219" t="n">
-        <v>0.891</v>
+        <v>0.893</v>
       </c>
       <c r="H219" t="n">
-        <v>0.305</v>
+        <v>0.303</v>
       </c>
       <c r="I219" t="n">
-        <v>0.696</v>
+        <v>0.6929999999999999</v>
       </c>
     </row>
     <row r="220">
@@ -10628,13 +10628,13 @@
         <v>10</v>
       </c>
       <c r="F235" t="n">
-        <v>0.716</v>
+        <v>0.741</v>
       </c>
       <c r="G235" t="n">
-        <v>0.605</v>
+        <v>0.617</v>
       </c>
       <c r="H235" t="n">
-        <v>0.184</v>
+        <v>0.129</v>
       </c>
       <c r="I235" t="n">
         <v>0.396</v>
@@ -10896,7 +10896,7 @@
         <v>0.39</v>
       </c>
       <c r="I242" t="n">
-        <v>0.969</v>
+        <v>0.848</v>
       </c>
     </row>
     <row r="243">
@@ -11044,7 +11044,7 @@
         <v>0.424</v>
       </c>
       <c r="I246" t="n">
-        <v>0.969</v>
+        <v>0.848</v>
       </c>
     </row>
     <row r="247">
@@ -11118,7 +11118,7 @@
         <v>0.545</v>
       </c>
       <c r="I248" t="n">
-        <v>1</v>
+        <v>0.969</v>
       </c>
     </row>
     <row r="249">
@@ -11220,16 +11220,16 @@
         <v>10</v>
       </c>
       <c r="F251" t="n">
-        <v>0.827</v>
+        <v>0.84</v>
       </c>
       <c r="G251" t="n">
-        <v>0.847</v>
+        <v>0.88</v>
       </c>
       <c r="H251" t="n">
-        <v>0.755</v>
+        <v>0.406</v>
       </c>
       <c r="I251" t="n">
-        <v>1</v>
+        <v>0.848</v>
       </c>
     </row>
     <row r="252">
@@ -11747,7 +11747,7 @@
         <v>0.346</v>
       </c>
       <c r="I265" t="n">
-        <v>0.503</v>
+        <v>0.554</v>
       </c>
     </row>
     <row r="266">
@@ -11784,7 +11784,7 @@
         <v>0.481</v>
       </c>
       <c r="I266" t="n">
-        <v>0.641</v>
+        <v>0.6820000000000001</v>
       </c>
     </row>
     <row r="267">
@@ -11812,16 +11812,16 @@
         <v>10</v>
       </c>
       <c r="F267" t="n">
-        <v>0.951</v>
+        <v>0.952</v>
       </c>
       <c r="G267" t="n">
-        <v>0.903</v>
+        <v>0.909</v>
       </c>
       <c r="H267" t="n">
-        <v>0.342</v>
+        <v>0.512</v>
       </c>
       <c r="I267" t="n">
-        <v>0.503</v>
+        <v>0.6820000000000001</v>
       </c>
     </row>
     <row r="268">
@@ -12404,16 +12404,16 @@
         <v>10</v>
       </c>
       <c r="F283" t="n">
-        <v>0.716</v>
+        <v>0.741</v>
       </c>
       <c r="G283" t="n">
-        <v>0.802</v>
+        <v>0.864</v>
       </c>
       <c r="H283" t="n">
-        <v>0.27</v>
+        <v>0.0747</v>
       </c>
       <c r="I283" t="n">
-        <v>0.54</v>
+        <v>0.149</v>
       </c>
     </row>
     <row r="284">

--- a/eval/results/statistical_tests_full150.xlsx
+++ b/eval/results/statistical_tests_full150.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Paired Tests" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Fisher Exact Test" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Table3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16673,4 +16674,650 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>QID</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>base_prec</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>FT_prec</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>QSP_prec</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>base_rec</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>FT_rec</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>QSP_rec</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>GPT-4o</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>50.9</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>89.3***</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>43.5</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>92.6</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>GPT-4o</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>94.3</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>83.3</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>69.6</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>90.2***</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>92.4***</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>GPT-4o</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>From what years were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>95.7</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>94.1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>85.3</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>78.8</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>94.1**</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>95.3**</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>GPT-4o</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>9</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>98.8</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>96.8</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>63.5</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>76.2*†</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>GPT-4o</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>11</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>88.9</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>92.7</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>87.3</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>60.9</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>82.6**</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>GPT-4o</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>14</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>96.6</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>89.3</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>76.7</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>91.8*†</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>83.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>GPT-4o</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>15</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>64.9</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>86.4**</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>70.7</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>74.6</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>85.1</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>61.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>GPT-4o</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>16</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>55.6</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>80.7**</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>52.6</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>80.7**</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>29.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Llama3.1-70B</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>6</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>From which countries were the sequenced samples obtained?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>87.7</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>96.1</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>97.6*†</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>77.2</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>79.3</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Llama3.1-70B</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>11</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>What type of samples were sequenced?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>86.2</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>96.9*†</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>68.5</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>79.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Llama3.1-70B</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>14</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>98.1***</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>88.6</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>78.1</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>71.2</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>84.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Llama3.1-70B</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>15</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>47.9</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>77.1***</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>78.3***</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>86.6</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>55.2</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>70.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Llama3.1-70B</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>16</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>38.9</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>70.6**</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>68.3**</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>73.7</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>42.1</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>49.1</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/eval/results/statistical_tests_full150.xlsx
+++ b/eval/results/statistical_tests_full150.xlsx
@@ -504,7 +504,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.0011</v>
+        <v>0.001</v>
       </c>
       <c r="F2" t="n">
         <v>0.835</v>
@@ -519,7 +519,7 @@
         <v>0.07190000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>0.00495</v>
+        <v>0.0045</v>
       </c>
     </row>
     <row r="3">
@@ -559,7 +559,7 @@
         <v>0.07190000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00561</v>
+        <v>0.00558</v>
       </c>
     </row>
     <row r="4">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.0107</v>
+        <v>0.01</v>
       </c>
       <c r="F4" t="n">
         <v>0.835</v>
@@ -599,7 +599,7 @@
         <v>0.0842</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0193</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="5">
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.0259</v>
+        <v>0.0243</v>
       </c>
       <c r="F5" t="n">
         <v>0.835</v>
@@ -639,7 +639,7 @@
         <v>0.0842</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0389</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="6">
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.37</v>
+        <v>0.347</v>
       </c>
       <c r="F6" t="n">
         <v>0.835</v>
@@ -679,7 +679,7 @@
         <v>0.103</v>
       </c>
       <c r="J6" t="n">
-        <v>0.476</v>
+        <v>0.446</v>
       </c>
     </row>
     <row r="7">
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.305</v>
+        <v>0.293</v>
       </c>
       <c r="F7" t="n">
         <v>0.835</v>
@@ -719,7 +719,7 @@
         <v>0.103</v>
       </c>
       <c r="J7" t="n">
-        <v>0.392</v>
+        <v>0.377</v>
       </c>
     </row>
     <row r="8">
@@ -744,7 +744,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.015</v>
+        <v>0.0144</v>
       </c>
       <c r="F8" t="n">
         <v>0.797</v>
@@ -759,7 +759,7 @@
         <v>0.0931</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0225</v>
+        <v>0.0216</v>
       </c>
     </row>
     <row r="9">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.00187</v>
+        <v>0.00186</v>
       </c>
       <c r="F9" t="n">
         <v>0.797</v>
@@ -799,7 +799,7 @@
         <v>0.0931</v>
       </c>
       <c r="J9" t="n">
-        <v>0.00561</v>
+        <v>0.00558</v>
       </c>
     </row>
     <row r="10">
@@ -824,7 +824,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.009090000000000001</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="F10" t="n">
         <v>0.797</v>
@@ -839,7 +839,7 @@
         <v>0.0796</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0193</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="11">
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.008920000000000001</v>
+        <v>0.008869999999999999</v>
       </c>
       <c r="F11" t="n">
         <v>0.797</v>
@@ -879,7 +879,7 @@
         <v>0.0796</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0161</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="12">
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.009090000000000001</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="F12" t="n">
         <v>0.797</v>
@@ -919,7 +919,7 @@
         <v>0.0796</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0193</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="13">
@@ -944,7 +944,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.008920000000000001</v>
+        <v>0.008869999999999999</v>
       </c>
       <c r="F13" t="n">
         <v>0.797</v>
@@ -959,7 +959,7 @@
         <v>0.0796</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0161</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="14">
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.661</v>
       </c>
       <c r="F14" t="n">
         <v>0.779</v>
@@ -999,7 +999,7 @@
         <v>0.116</v>
       </c>
       <c r="J14" t="n">
-        <v>0.77</v>
+        <v>0.744</v>
       </c>
     </row>
     <row r="15">
@@ -1039,7 +1039,7 @@
         <v>0.116</v>
       </c>
       <c r="J15" t="n">
-        <v>0.874</v>
+        <v>0.842</v>
       </c>
     </row>
     <row r="16">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2.51e-06</v>
+        <v>2.44e-06</v>
       </c>
       <c r="F16" t="n">
         <v>0.779</v>
@@ -1079,7 +1079,7 @@
         <v>0.155</v>
       </c>
       <c r="J16" t="n">
-        <v>2.26e-05</v>
+        <v>2.2e-05</v>
       </c>
     </row>
     <row r="17">
@@ -1144,7 +1144,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.931</v>
+        <v>0.914</v>
       </c>
       <c r="F18" t="n">
         <v>0.779</v>
@@ -1159,7 +1159,7 @@
         <v>0.11</v>
       </c>
       <c r="J18" t="n">
-        <v>0.931</v>
+        <v>0.914</v>
       </c>
     </row>
     <row r="19">
@@ -1184,7 +1184,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.887</v>
+        <v>0.842</v>
       </c>
       <c r="F19" t="n">
         <v>0.779</v>
@@ -1199,7 +1199,7 @@
         <v>0.11</v>
       </c>
       <c r="J19" t="n">
-        <v>0.887</v>
+        <v>0.842</v>
       </c>
     </row>
     <row r="20">
@@ -1224,7 +1224,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.09080000000000001</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="F20" t="n">
         <v>0.864</v>
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="F22" t="n">
         <v>0.864</v>
@@ -1319,7 +1319,7 @@
         <v>0.11</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.8090000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -1384,7 +1384,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.0252</v>
+        <v>0.0254</v>
       </c>
       <c r="F24" t="n">
         <v>0.864</v>
@@ -1399,7 +1399,7 @@
         <v>0.191</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0454</v>
+        <v>0.0457</v>
       </c>
     </row>
     <row r="25">
@@ -1464,7 +1464,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.000898</v>
+        <v>0.000894</v>
       </c>
       <c r="F26" t="n">
         <v>0.793</v>
@@ -1479,7 +1479,7 @@
         <v>0.0954</v>
       </c>
       <c r="J26" t="n">
-        <v>0.00269</v>
+        <v>0.00268</v>
       </c>
     </row>
     <row r="27">
@@ -1704,7 +1704,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.0244</v>
+        <v>0.0242</v>
       </c>
       <c r="F32" t="n">
         <v>0.778</v>
@@ -1719,7 +1719,7 @@
         <v>0.172</v>
       </c>
       <c r="J32" t="n">
-        <v>0.0454</v>
+        <v>0.0457</v>
       </c>
     </row>
     <row r="33">
@@ -1744,7 +1744,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.0409</v>
+        <v>0.0356</v>
       </c>
       <c r="F33" t="n">
         <v>0.778</v>
@@ -1759,7 +1759,7 @@
         <v>0.172</v>
       </c>
       <c r="J33" t="n">
-        <v>0.0736</v>
+        <v>0.0641</v>
       </c>
     </row>
     <row r="34">
@@ -1799,7 +1799,7 @@
         <v>0.259</v>
       </c>
       <c r="J34" t="n">
-        <v>0.000258</v>
+        <v>0.000261</v>
       </c>
     </row>
     <row r="35">
@@ -1864,7 +1864,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5.73e-05</v>
+        <v>5.79e-05</v>
       </c>
       <c r="F36" t="n">
         <v>0.778</v>
@@ -1879,7 +1879,7 @@
         <v>0.205</v>
       </c>
       <c r="J36" t="n">
-        <v>0.000258</v>
+        <v>0.000261</v>
       </c>
     </row>
     <row r="37">
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.011</v>
+        <v>0.0102</v>
       </c>
       <c r="F38" t="n">
-        <v>0.764</v>
+        <v>0.763</v>
       </c>
       <c r="G38" t="n">
         <v>0.842</v>
@@ -1959,7 +1959,7 @@
         <v>0.137</v>
       </c>
       <c r="J38" t="n">
-        <v>0.0247</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="39">
@@ -1984,10 +1984,10 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.0131</v>
+        <v>0.011</v>
       </c>
       <c r="F39" t="n">
-        <v>0.764</v>
+        <v>0.763</v>
       </c>
       <c r="G39" t="n">
         <v>0.842</v>
@@ -1999,7 +1999,7 @@
         <v>0.137</v>
       </c>
       <c r="J39" t="n">
-        <v>0.0295</v>
+        <v>0.0247</v>
       </c>
     </row>
     <row r="40">
@@ -2024,10 +2024,10 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.115</v>
+        <v>0.11</v>
       </c>
       <c r="F40" t="n">
-        <v>0.764</v>
+        <v>0.763</v>
       </c>
       <c r="G40" t="n">
         <v>0.8159999999999999</v>
@@ -2039,7 +2039,7 @@
         <v>0.185</v>
       </c>
       <c r="J40" t="n">
-        <v>0.129</v>
+        <v>0.124</v>
       </c>
     </row>
     <row r="41">
@@ -2067,7 +2067,7 @@
         <v>0.112</v>
       </c>
       <c r="F41" t="n">
-        <v>0.764</v>
+        <v>0.763</v>
       </c>
       <c r="G41" t="n">
         <v>0.8159999999999999</v>
@@ -2104,10 +2104,10 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.253</v>
+        <v>0.242</v>
       </c>
       <c r="F42" t="n">
-        <v>0.764</v>
+        <v>0.763</v>
       </c>
       <c r="G42" t="n">
         <v>0.798</v>
@@ -2119,7 +2119,7 @@
         <v>0.223</v>
       </c>
       <c r="J42" t="n">
-        <v>0.253</v>
+        <v>0.242</v>
       </c>
     </row>
     <row r="43">
@@ -2144,10 +2144,10 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.198</v>
+        <v>0.221</v>
       </c>
       <c r="F43" t="n">
-        <v>0.764</v>
+        <v>0.763</v>
       </c>
       <c r="G43" t="n">
         <v>0.798</v>
@@ -2159,7 +2159,7 @@
         <v>0.223</v>
       </c>
       <c r="J43" t="n">
-        <v>0.198</v>
+        <v>0.221</v>
       </c>
     </row>
     <row r="44">
@@ -2184,10 +2184,10 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.102</v>
+        <v>0.11</v>
       </c>
       <c r="F44" t="n">
-        <v>0.756</v>
+        <v>0.755</v>
       </c>
       <c r="G44" t="n">
         <v>0.703</v>
@@ -2199,7 +2199,7 @@
         <v>0.163</v>
       </c>
       <c r="J44" t="n">
-        <v>0.129</v>
+        <v>0.124</v>
       </c>
     </row>
     <row r="45">
@@ -2227,7 +2227,7 @@
         <v>0.156</v>
       </c>
       <c r="F45" t="n">
-        <v>0.756</v>
+        <v>0.755</v>
       </c>
       <c r="G45" t="n">
         <v>0.703</v>
@@ -2264,10 +2264,10 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.0569</v>
+        <v>0.0557</v>
       </c>
       <c r="F46" t="n">
-        <v>0.756</v>
+        <v>0.755</v>
       </c>
       <c r="G46" t="n">
         <v>0.8149999999999999</v>
@@ -2279,7 +2279,7 @@
         <v>0.162</v>
       </c>
       <c r="J46" t="n">
-        <v>0.0853</v>
+        <v>0.0835</v>
       </c>
     </row>
     <row r="47">
@@ -2304,10 +2304,10 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.064</v>
+        <v>0.0555</v>
       </c>
       <c r="F47" t="n">
-        <v>0.756</v>
+        <v>0.755</v>
       </c>
       <c r="G47" t="n">
         <v>0.8149999999999999</v>
@@ -2319,7 +2319,7 @@
         <v>0.162</v>
       </c>
       <c r="J47" t="n">
-        <v>0.096</v>
+        <v>0.0833</v>
       </c>
     </row>
     <row r="48">
@@ -2344,10 +2344,10 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.0569</v>
+        <v>0.0557</v>
       </c>
       <c r="F48" t="n">
-        <v>0.756</v>
+        <v>0.755</v>
       </c>
       <c r="G48" t="n">
         <v>0.8149999999999999</v>
@@ -2359,7 +2359,7 @@
         <v>0.162</v>
       </c>
       <c r="J48" t="n">
-        <v>0.0853</v>
+        <v>0.0835</v>
       </c>
     </row>
     <row r="49">
@@ -2384,10 +2384,10 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.064</v>
+        <v>0.0555</v>
       </c>
       <c r="F49" t="n">
-        <v>0.756</v>
+        <v>0.755</v>
       </c>
       <c r="G49" t="n">
         <v>0.8149999999999999</v>
@@ -2399,7 +2399,7 @@
         <v>0.162</v>
       </c>
       <c r="J49" t="n">
-        <v>0.096</v>
+        <v>0.0833</v>
       </c>
     </row>
     <row r="50">
@@ -2424,10 +2424,10 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.000581</v>
+        <v>0.000603</v>
       </c>
       <c r="F50" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="G50" t="n">
         <v>0.579</v>
@@ -2439,7 +2439,7 @@
         <v>0.147</v>
       </c>
       <c r="J50" t="n">
-        <v>0.00174</v>
+        <v>0.00181</v>
       </c>
     </row>
     <row r="51">
@@ -2467,7 +2467,7 @@
         <v>0.00377</v>
       </c>
       <c r="F51" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="G51" t="n">
         <v>0.579</v>
@@ -2504,10 +2504,10 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3.28e-07</v>
+        <v>3.2e-07</v>
       </c>
       <c r="F52" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="G52" t="n">
         <v>0.324</v>
@@ -2519,7 +2519,7 @@
         <v>0.226</v>
       </c>
       <c r="J52" t="n">
-        <v>2.95e-06</v>
+        <v>2.88e-06</v>
       </c>
     </row>
     <row r="53">
@@ -2547,7 +2547,7 @@
         <v>6.1e-05</v>
       </c>
       <c r="F53" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="G53" t="n">
         <v>0.324</v>
@@ -2584,10 +2584,10 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3.44e-05</v>
+        <v>3.05e-05</v>
       </c>
       <c r="F54" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="G54" t="n">
         <v>0.84</v>
@@ -2599,7 +2599,7 @@
         <v>0.174</v>
       </c>
       <c r="J54" t="n">
-        <v>0.000155</v>
+        <v>0.000137</v>
       </c>
     </row>
     <row r="55">
@@ -2627,7 +2627,7 @@
         <v>6.1e-05</v>
       </c>
       <c r="F55" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="G55" t="n">
         <v>0.84</v>
@@ -2664,7 +2664,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.00346</v>
+        <v>0.00322</v>
       </c>
       <c r="F56" t="n">
         <v>0.797</v>
@@ -2679,7 +2679,7 @@
         <v>0.0919</v>
       </c>
       <c r="J56" t="n">
-        <v>0.0156</v>
+        <v>0.0145</v>
       </c>
     </row>
     <row r="57">
@@ -2744,7 +2744,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.199</v>
+        <v>0.193</v>
       </c>
       <c r="F58" t="n">
         <v>0.797</v>
@@ -2759,7 +2759,7 @@
         <v>0.149</v>
       </c>
       <c r="J58" t="n">
-        <v>0.256</v>
+        <v>0.248</v>
       </c>
     </row>
     <row r="59">
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.516</v>
+        <v>0.529</v>
       </c>
       <c r="F60" t="n">
         <v>0.797</v>
@@ -2839,7 +2839,7 @@
         <v>0.188</v>
       </c>
       <c r="J60" t="n">
-        <v>0.516</v>
+        <v>0.529</v>
       </c>
     </row>
     <row r="61">
@@ -2864,7 +2864,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.98</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F61" t="n">
         <v>0.797</v>
@@ -2879,7 +2879,7 @@
         <v>0.188</v>
       </c>
       <c r="J61" t="n">
-        <v>0.98</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="62">
@@ -2904,10 +2904,10 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.0154</v>
+        <v>0.0151</v>
       </c>
       <c r="F62" t="n">
-        <v>0.757</v>
+        <v>0.756</v>
       </c>
       <c r="G62" t="n">
         <v>0.789</v>
@@ -2919,7 +2919,7 @@
         <v>0.137</v>
       </c>
       <c r="J62" t="n">
-        <v>0.0277</v>
+        <v>0.0272</v>
       </c>
     </row>
     <row r="63">
@@ -2947,7 +2947,7 @@
         <v>0.0076</v>
       </c>
       <c r="F63" t="n">
-        <v>0.757</v>
+        <v>0.756</v>
       </c>
       <c r="G63" t="n">
         <v>0.789</v>
@@ -2984,10 +2984,10 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.007889999999999999</v>
+        <v>0.00765</v>
       </c>
       <c r="F64" t="n">
-        <v>0.757</v>
+        <v>0.756</v>
       </c>
       <c r="G64" t="n">
         <v>0.819</v>
@@ -2999,7 +2999,7 @@
         <v>0.144</v>
       </c>
       <c r="J64" t="n">
-        <v>0.0178</v>
+        <v>0.0172</v>
       </c>
     </row>
     <row r="65">
@@ -3027,7 +3027,7 @@
         <v>0.00629</v>
       </c>
       <c r="F65" t="n">
-        <v>0.757</v>
+        <v>0.756</v>
       </c>
       <c r="G65" t="n">
         <v>0.819</v>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.007889999999999999</v>
+        <v>0.00765</v>
       </c>
       <c r="F66" t="n">
-        <v>0.757</v>
+        <v>0.756</v>
       </c>
       <c r="G66" t="n">
         <v>0.819</v>
@@ -3079,7 +3079,7 @@
         <v>0.144</v>
       </c>
       <c r="J66" t="n">
-        <v>0.0178</v>
+        <v>0.0172</v>
       </c>
     </row>
     <row r="67">
@@ -3107,7 +3107,7 @@
         <v>0.00629</v>
       </c>
       <c r="F67" t="n">
-        <v>0.757</v>
+        <v>0.756</v>
       </c>
       <c r="G67" t="n">
         <v>0.819</v>
@@ -3144,10 +3144,10 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.0881</v>
+        <v>0.0897</v>
       </c>
       <c r="F68" t="n">
-        <v>0.71</v>
+        <v>0.709</v>
       </c>
       <c r="G68" t="n">
         <v>0.68</v>
@@ -3159,7 +3159,7 @@
         <v>0.149</v>
       </c>
       <c r="J68" t="n">
-        <v>0.132</v>
+        <v>0.135</v>
       </c>
     </row>
     <row r="69">
@@ -3187,7 +3187,7 @@
         <v>0.105</v>
       </c>
       <c r="F69" t="n">
-        <v>0.71</v>
+        <v>0.709</v>
       </c>
       <c r="G69" t="n">
         <v>0.68</v>
@@ -3224,10 +3224,10 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>7.24e-08</v>
+        <v>7.08e-08</v>
       </c>
       <c r="F70" t="n">
-        <v>0.71</v>
+        <v>0.709</v>
       </c>
       <c r="G70" t="n">
         <v>0.33</v>
@@ -3239,7 +3239,7 @@
         <v>0.154</v>
       </c>
       <c r="J70" t="n">
-        <v>6.52e-07</v>
+        <v>6.37e-07</v>
       </c>
     </row>
     <row r="71">
@@ -3267,7 +3267,7 @@
         <v>3.05e-05</v>
       </c>
       <c r="F71" t="n">
-        <v>0.71</v>
+        <v>0.709</v>
       </c>
       <c r="G71" t="n">
         <v>0.33</v>
@@ -3304,10 +3304,10 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.249</v>
+        <v>0.24</v>
       </c>
       <c r="F72" t="n">
-        <v>0.71</v>
+        <v>0.709</v>
       </c>
       <c r="G72" t="n">
         <v>0.734</v>
@@ -3319,7 +3319,7 @@
         <v>0.175</v>
       </c>
       <c r="J72" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="73">
@@ -3347,7 +3347,7 @@
         <v>0.211</v>
       </c>
       <c r="F73" t="n">
-        <v>0.71</v>
+        <v>0.709</v>
       </c>
       <c r="G73" t="n">
         <v>0.734</v>
@@ -3781,13 +3781,13 @@
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>0.86</v>
+        <v>0.853</v>
       </c>
       <c r="G11" t="n">
         <v>0.873</v>
       </c>
       <c r="H11" t="n">
-        <v>0.865</v>
+        <v>0.737</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
@@ -4373,7 +4373,7 @@
         <v>10</v>
       </c>
       <c r="F27" t="n">
-        <v>0.929</v>
+        <v>0.928</v>
       </c>
       <c r="G27" t="n">
         <v>0.931</v>
@@ -4965,13 +4965,13 @@
         <v>10</v>
       </c>
       <c r="F43" t="n">
-        <v>0.802</v>
+        <v>0.79</v>
       </c>
       <c r="G43" t="n">
         <v>0.827</v>
       </c>
       <c r="H43" t="n">
-        <v>0.84</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I43" t="n">
         <v>1</v>
@@ -5557,16 +5557,16 @@
         <v>10</v>
       </c>
       <c r="F59" t="n">
-        <v>0.861</v>
+        <v>0.853</v>
       </c>
       <c r="G59" t="n">
         <v>0.876</v>
       </c>
       <c r="H59" t="n">
-        <v>0.737</v>
+        <v>0.616</v>
       </c>
       <c r="I59" t="n">
-        <v>1</v>
+        <v>0.897</v>
       </c>
     </row>
     <row r="60">
@@ -6149,16 +6149,16 @@
         <v>10</v>
       </c>
       <c r="F75" t="n">
-        <v>0.86</v>
+        <v>0.853</v>
       </c>
       <c r="G75" t="n">
         <v>0.893</v>
       </c>
       <c r="H75" t="n">
-        <v>0.483</v>
+        <v>0.386</v>
       </c>
       <c r="I75" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.771</v>
       </c>
     </row>
     <row r="76">
@@ -6741,7 +6741,7 @@
         <v>10</v>
       </c>
       <c r="F91" t="n">
-        <v>0.929</v>
+        <v>0.928</v>
       </c>
       <c r="G91" t="n">
         <v>0.9330000000000001</v>
@@ -7046,7 +7046,7 @@
         <v>0.236</v>
       </c>
       <c r="I99" t="n">
-        <v>0.538</v>
+        <v>0.531</v>
       </c>
     </row>
     <row r="100">
@@ -7333,16 +7333,16 @@
         <v>10</v>
       </c>
       <c r="F107" t="n">
-        <v>0.802</v>
+        <v>0.79</v>
       </c>
       <c r="G107" t="n">
         <v>0.864</v>
       </c>
       <c r="H107" t="n">
-        <v>0.399</v>
+        <v>0.299</v>
       </c>
       <c r="I107" t="n">
-        <v>0.71</v>
+        <v>0.531</v>
       </c>
     </row>
     <row r="108">
@@ -7416,7 +7416,7 @@
         <v>0.269</v>
       </c>
       <c r="I109" t="n">
-        <v>0.538</v>
+        <v>0.531</v>
       </c>
     </row>
     <row r="110">
@@ -7823,7 +7823,7 @@
         <v>0.294</v>
       </c>
       <c r="I120" t="n">
-        <v>0.658</v>
+        <v>0.585</v>
       </c>
     </row>
     <row r="121">
@@ -7860,7 +7860,7 @@
         <v>0.272</v>
       </c>
       <c r="I121" t="n">
-        <v>0.658</v>
+        <v>0.585</v>
       </c>
     </row>
     <row r="122">
@@ -7925,16 +7925,16 @@
         <v>10</v>
       </c>
       <c r="F123" t="n">
-        <v>0.861</v>
+        <v>0.853</v>
       </c>
       <c r="G123" t="n">
         <v>0.897</v>
       </c>
       <c r="H123" t="n">
-        <v>0.382</v>
+        <v>0.299</v>
       </c>
       <c r="I123" t="n">
-        <v>0.679</v>
+        <v>0.585</v>
       </c>
     </row>
     <row r="124">
@@ -8156,7 +8156,7 @@
         <v>0.329</v>
       </c>
       <c r="I129" t="n">
-        <v>0.658</v>
+        <v>0.585</v>
       </c>
     </row>
     <row r="130">
@@ -8517,13 +8517,13 @@
         <v>10</v>
       </c>
       <c r="F139" t="n">
-        <v>0.86</v>
+        <v>0.853</v>
       </c>
       <c r="G139" t="n">
         <v>0.867</v>
       </c>
       <c r="H139" t="n">
-        <v>1</v>
+        <v>0.868</v>
       </c>
       <c r="I139" t="n">
         <v>1</v>
@@ -9109,16 +9109,16 @@
         <v>10</v>
       </c>
       <c r="F155" t="n">
-        <v>0.929</v>
+        <v>0.928</v>
       </c>
       <c r="G155" t="n">
         <v>0.955</v>
       </c>
       <c r="H155" t="n">
-        <v>0.719</v>
+        <v>0.718</v>
       </c>
       <c r="I155" t="n">
-        <v>0.885</v>
+        <v>0.884</v>
       </c>
     </row>
     <row r="156">
@@ -9701,7 +9701,7 @@
         <v>10</v>
       </c>
       <c r="F171" t="n">
-        <v>0.802</v>
+        <v>0.79</v>
       </c>
       <c r="G171" t="n">
         <v>0.79</v>
@@ -10293,16 +10293,16 @@
         <v>10</v>
       </c>
       <c r="F187" t="n">
-        <v>0.861</v>
+        <v>0.853</v>
       </c>
       <c r="G187" t="n">
         <v>0.865</v>
       </c>
       <c r="H187" t="n">
-        <v>1</v>
+        <v>0.868</v>
       </c>
       <c r="I187" t="n">
-        <v>1</v>
+        <v>0.957</v>
       </c>
     </row>
     <row r="188">
@@ -10487,7 +10487,7 @@
         <v>0.897</v>
       </c>
       <c r="I192" t="n">
-        <v>1</v>
+        <v>0.957</v>
       </c>
     </row>
     <row r="193">
@@ -10746,7 +10746,7 @@
         <v>0.176</v>
       </c>
       <c r="I199" t="n">
-        <v>0.703</v>
+        <v>0.5629999999999999</v>
       </c>
     </row>
     <row r="200">
@@ -10885,16 +10885,16 @@
         <v>10</v>
       </c>
       <c r="F203" t="n">
-        <v>0.793</v>
+        <v>0.787</v>
       </c>
       <c r="G203" t="n">
         <v>0.853</v>
       </c>
       <c r="H203" t="n">
-        <v>0.226</v>
+        <v>0.176</v>
       </c>
       <c r="I203" t="n">
-        <v>0.722</v>
+        <v>0.5629999999999999</v>
       </c>
     </row>
     <row r="204">
@@ -11042,7 +11042,7 @@
         <v>0.135</v>
       </c>
       <c r="I207" t="n">
-        <v>0.703</v>
+        <v>0.5629999999999999</v>
       </c>
     </row>
     <row r="208">
@@ -11477,7 +11477,7 @@
         <v>10</v>
       </c>
       <c r="F219" t="n">
-        <v>0.981</v>
+        <v>0.98</v>
       </c>
       <c r="G219" t="n">
         <v>0.968</v>
@@ -11819,7 +11819,7 @@
         <v>0.101</v>
       </c>
       <c r="I228" t="n">
-        <v>0.502</v>
+        <v>0.405</v>
       </c>
     </row>
     <row r="229">
@@ -12069,16 +12069,16 @@
         <v>10</v>
       </c>
       <c r="F235" t="n">
-        <v>0.63</v>
+        <v>0.617</v>
       </c>
       <c r="G235" t="n">
         <v>0.753</v>
       </c>
       <c r="H235" t="n">
-        <v>0.125</v>
+        <v>0.0902</v>
       </c>
       <c r="I235" t="n">
-        <v>0.502</v>
+        <v>0.405</v>
       </c>
     </row>
     <row r="236">
@@ -12661,13 +12661,13 @@
         <v>10</v>
       </c>
       <c r="F251" t="n">
-        <v>0.767</v>
+        <v>0.758</v>
       </c>
       <c r="G251" t="n">
         <v>0.847</v>
       </c>
       <c r="H251" t="n">
-        <v>0.0951</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="I251" t="n">
         <v>1</v>
@@ -13253,16 +13253,16 @@
         <v>10</v>
       </c>
       <c r="F267" t="n">
-        <v>0.793</v>
+        <v>0.787</v>
       </c>
       <c r="G267" t="n">
         <v>0.873</v>
       </c>
       <c r="H267" t="n">
-        <v>0.0877</v>
+        <v>0.0644</v>
       </c>
       <c r="I267" t="n">
-        <v>0.175</v>
+        <v>0.129</v>
       </c>
     </row>
     <row r="268">
@@ -13845,13 +13845,13 @@
         <v>10</v>
       </c>
       <c r="F283" t="n">
-        <v>0.981</v>
+        <v>0.98</v>
       </c>
       <c r="G283" t="n">
         <v>0.956</v>
       </c>
       <c r="H283" t="n">
-        <v>0.632</v>
+        <v>0.634</v>
       </c>
       <c r="I283" t="n">
         <v>1</v>
@@ -14437,16 +14437,16 @@
         <v>10</v>
       </c>
       <c r="F299" t="n">
-        <v>0.63</v>
+        <v>0.617</v>
       </c>
       <c r="G299" t="n">
         <v>0.802</v>
       </c>
       <c r="H299" t="n">
-        <v>0.0229</v>
+        <v>0.0149</v>
       </c>
       <c r="I299" t="n">
-        <v>0.183</v>
+        <v>0.119</v>
       </c>
     </row>
     <row r="300">
@@ -14927,7 +14927,7 @@
         <v>0.0196</v>
       </c>
       <c r="I312" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.0552</v>
       </c>
     </row>
     <row r="313">
@@ -15029,16 +15029,16 @@
         <v>10</v>
       </c>
       <c r="F315" t="n">
-        <v>0.767</v>
+        <v>0.758</v>
       </c>
       <c r="G315" t="n">
         <v>0.872</v>
       </c>
       <c r="H315" t="n">
-        <v>0.0282</v>
+        <v>0.0136</v>
       </c>
       <c r="I315" t="n">
-        <v>0.0751</v>
+        <v>0.0543</v>
       </c>
     </row>
     <row r="316">
@@ -15223,7 +15223,7 @@
         <v>0.0207</v>
       </c>
       <c r="I320" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.0552</v>
       </c>
     </row>
     <row r="321">
@@ -15621,16 +15621,16 @@
         <v>10</v>
       </c>
       <c r="F331" t="n">
-        <v>0.793</v>
+        <v>0.787</v>
       </c>
       <c r="G331" t="n">
         <v>0.873</v>
       </c>
       <c r="H331" t="n">
-        <v>0.0877</v>
+        <v>0.0644</v>
       </c>
       <c r="I331" t="n">
-        <v>0.175</v>
+        <v>0.129</v>
       </c>
     </row>
     <row r="332">
@@ -16213,13 +16213,13 @@
         <v>10</v>
       </c>
       <c r="F347" t="n">
-        <v>0.981</v>
+        <v>0.98</v>
       </c>
       <c r="G347" t="n">
         <v>0.956</v>
       </c>
       <c r="H347" t="n">
-        <v>0.632</v>
+        <v>0.634</v>
       </c>
       <c r="I347" t="n">
         <v>1</v>
@@ -16805,16 +16805,16 @@
         <v>10</v>
       </c>
       <c r="F363" t="n">
-        <v>0.63</v>
+        <v>0.617</v>
       </c>
       <c r="G363" t="n">
         <v>0.802</v>
       </c>
       <c r="H363" t="n">
-        <v>0.0229</v>
+        <v>0.0149</v>
       </c>
       <c r="I363" t="n">
-        <v>0.183</v>
+        <v>0.119</v>
       </c>
     </row>
     <row r="364">
@@ -17295,7 +17295,7 @@
         <v>0.0196</v>
       </c>
       <c r="I376" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.0552</v>
       </c>
     </row>
     <row r="377">
@@ -17397,16 +17397,16 @@
         <v>10</v>
       </c>
       <c r="F379" t="n">
-        <v>0.767</v>
+        <v>0.758</v>
       </c>
       <c r="G379" t="n">
         <v>0.872</v>
       </c>
       <c r="H379" t="n">
-        <v>0.0282</v>
+        <v>0.0136</v>
       </c>
       <c r="I379" t="n">
-        <v>0.0751</v>
+        <v>0.0543</v>
       </c>
     </row>
     <row r="380">
@@ -17591,7 +17591,7 @@
         <v>0.0207</v>
       </c>
       <c r="I384" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.0552</v>
       </c>
     </row>
     <row r="385">
@@ -17989,13 +17989,13 @@
         <v>10</v>
       </c>
       <c r="F395" t="n">
-        <v>0.827</v>
+        <v>0.82</v>
       </c>
       <c r="G395" t="n">
         <v>0.727</v>
       </c>
       <c r="H395" t="n">
-        <v>0.0518</v>
+        <v>0.0725</v>
       </c>
       <c r="I395" t="n">
         <v>0.348</v>
@@ -18581,16 +18581,16 @@
         <v>10</v>
       </c>
       <c r="F411" t="n">
-        <v>0.951</v>
+        <v>0.95</v>
       </c>
       <c r="G411" t="n">
         <v>0.885</v>
       </c>
       <c r="H411" t="n">
-        <v>0.297</v>
+        <v>0.299</v>
       </c>
       <c r="I411" t="n">
-        <v>0.68</v>
+        <v>0.6830000000000001</v>
       </c>
     </row>
     <row r="412">
@@ -19173,13 +19173,13 @@
         <v>10</v>
       </c>
       <c r="F427" t="n">
-        <v>0.716</v>
+        <v>0.704</v>
       </c>
       <c r="G427" t="n">
         <v>0.5679999999999999</v>
       </c>
       <c r="H427" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.102</v>
       </c>
       <c r="I427" t="n">
         <v>0.353</v>
@@ -19765,16 +19765,16 @@
         <v>10</v>
       </c>
       <c r="F443" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="G443" t="n">
         <v>0.6919999999999999</v>
       </c>
       <c r="H443" t="n">
-        <v>0.0172</v>
+        <v>0.0354</v>
       </c>
       <c r="I443" t="n">
-        <v>0.276</v>
+        <v>0.5659999999999999</v>
       </c>
     </row>
     <row r="444">
@@ -20357,16 +20357,16 @@
         <v>10</v>
       </c>
       <c r="F459" t="n">
-        <v>0.827</v>
+        <v>0.82</v>
       </c>
       <c r="G459" t="n">
         <v>0.46</v>
       </c>
       <c r="H459" t="n">
-        <v>3.59e-11</v>
+        <v>9.33e-11</v>
       </c>
       <c r="I459" t="n">
-        <v>1.92e-10</v>
+        <v>4.98e-10</v>
       </c>
     </row>
     <row r="460">
@@ -20949,16 +20949,16 @@
         <v>10</v>
       </c>
       <c r="F475" t="n">
-        <v>0.951</v>
+        <v>0.95</v>
       </c>
       <c r="G475" t="n">
         <v>0.5</v>
       </c>
       <c r="H475" t="n">
-        <v>5.15e-07</v>
+        <v>6.21e-07</v>
       </c>
       <c r="I475" t="n">
-        <v>4.12e-06</v>
+        <v>4.97e-06</v>
       </c>
     </row>
     <row r="476">
@@ -21541,16 +21541,16 @@
         <v>10</v>
       </c>
       <c r="F491" t="n">
-        <v>0.716</v>
+        <v>0.704</v>
       </c>
       <c r="G491" t="n">
         <v>0.21</v>
       </c>
       <c r="H491" t="n">
-        <v>1.16e-10</v>
+        <v>3.31e-10</v>
       </c>
       <c r="I491" t="n">
-        <v>1.85e-09</v>
+        <v>4.13e-09</v>
       </c>
     </row>
     <row r="492">
@@ -22133,16 +22133,16 @@
         <v>10</v>
       </c>
       <c r="F507" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="G507" t="n">
         <v>0.296</v>
       </c>
       <c r="H507" t="n">
-        <v>1.77e-17</v>
+        <v>6.74e-17</v>
       </c>
       <c r="I507" t="n">
-        <v>2.83e-16</v>
+        <v>1.08e-15</v>
       </c>
     </row>
     <row r="508">
@@ -22725,13 +22725,13 @@
         <v>10</v>
       </c>
       <c r="F523" t="n">
-        <v>0.827</v>
+        <v>0.82</v>
       </c>
       <c r="G523" t="n">
         <v>0.833</v>
       </c>
       <c r="H523" t="n">
-        <v>1</v>
+        <v>0.879</v>
       </c>
       <c r="I523" t="n">
         <v>1</v>
@@ -23317,13 +23317,13 @@
         <v>10</v>
       </c>
       <c r="F539" t="n">
-        <v>0.951</v>
+        <v>0.95</v>
       </c>
       <c r="G539" t="n">
         <v>0.9</v>
       </c>
       <c r="H539" t="n">
-        <v>0.337</v>
+        <v>0.34</v>
       </c>
       <c r="I539" t="n">
         <v>0.503</v>
@@ -23659,7 +23659,7 @@
         <v>0.352</v>
       </c>
       <c r="I548" t="n">
-        <v>0.625</v>
+        <v>0.592</v>
       </c>
     </row>
     <row r="549">
@@ -23909,16 +23909,16 @@
         <v>10</v>
       </c>
       <c r="F555" t="n">
-        <v>0.716</v>
+        <v>0.704</v>
       </c>
       <c r="G555" t="n">
         <v>0.778</v>
       </c>
       <c r="H555" t="n">
-        <v>0.47</v>
+        <v>0.37</v>
       </c>
       <c r="I555" t="n">
-        <v>0.651</v>
+        <v>0.592</v>
       </c>
     </row>
     <row r="556">
@@ -24103,7 +24103,7 @@
         <v>0.33</v>
       </c>
       <c r="I560" t="n">
-        <v>0.625</v>
+        <v>0.592</v>
       </c>
     </row>
     <row r="561">
@@ -24288,7 +24288,7 @@
         <v>0.681</v>
       </c>
       <c r="I565" t="n">
-        <v>1</v>
+        <v>0.991</v>
       </c>
     </row>
     <row r="566">
@@ -24436,7 +24436,7 @@
         <v>0.75</v>
       </c>
       <c r="I569" t="n">
-        <v>1</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="570">
@@ -24501,16 +24501,16 @@
         <v>10</v>
       </c>
       <c r="F571" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="G571" t="n">
         <v>0.834</v>
       </c>
       <c r="H571" t="n">
-        <v>0.759</v>
+        <v>0.647</v>
       </c>
       <c r="I571" t="n">
-        <v>1</v>
+        <v>0.991</v>
       </c>
     </row>
     <row r="572">
@@ -24658,7 +24658,7 @@
         <v>0.598</v>
       </c>
       <c r="I575" t="n">
-        <v>1</v>
+        <v>0.991</v>
       </c>
     </row>
     <row r="576">
@@ -24695,7 +24695,7 @@
         <v>0.556</v>
       </c>
       <c r="I576" t="n">
-        <v>1</v>
+        <v>0.991</v>
       </c>
     </row>
     <row r="577">
@@ -25352,7 +25352,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>98.1</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -25367,7 +25367,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>61.7</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">

--- a/eval/results/statistical_tests_full150.xlsx
+++ b/eval/results/statistical_tests_full150.xlsx
@@ -519,7 +519,7 @@
         <v>0.07190000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0045</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -559,7 +559,7 @@
         <v>0.07190000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00558</v>
+        <v>0.008370000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -799,7 +799,7 @@
         <v>0.0931</v>
       </c>
       <c r="J9" t="n">
-        <v>0.00558</v>
+        <v>0.008370000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -879,7 +879,7 @@
         <v>0.0796</v>
       </c>
       <c r="J11" t="n">
-        <v>0.016</v>
+        <v>0.0175</v>
       </c>
     </row>
     <row r="12">
@@ -959,7 +959,7 @@
         <v>0.0796</v>
       </c>
       <c r="J13" t="n">
-        <v>0.016</v>
+        <v>0.0175</v>
       </c>
     </row>
     <row r="14">
@@ -1064,22 +1064,22 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2.44e-06</v>
+        <v>0.00558</v>
       </c>
       <c r="F16" t="n">
         <v>0.779</v>
       </c>
       <c r="G16" t="n">
-        <v>0.556</v>
+        <v>0.705</v>
       </c>
       <c r="H16" t="n">
         <v>0.132</v>
       </c>
       <c r="I16" t="n">
-        <v>0.155</v>
+        <v>0.107</v>
       </c>
       <c r="J16" t="n">
-        <v>2.2e-05</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="17">
@@ -1104,22 +1104,22 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.000436</v>
+        <v>0.009719999999999999</v>
       </c>
       <c r="F17" t="n">
         <v>0.779</v>
       </c>
       <c r="G17" t="n">
-        <v>0.556</v>
+        <v>0.705</v>
       </c>
       <c r="H17" t="n">
         <v>0.132</v>
       </c>
       <c r="I17" t="n">
-        <v>0.155</v>
+        <v>0.107</v>
       </c>
       <c r="J17" t="n">
-        <v>0.00392</v>
+        <v>0.0175</v>
       </c>
     </row>
     <row r="18">
@@ -1399,7 +1399,7 @@
         <v>0.191</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0457</v>
+        <v>0.0571</v>
       </c>
     </row>
     <row r="25">
@@ -1439,7 +1439,7 @@
         <v>0.191</v>
       </c>
       <c r="J25" t="n">
-        <v>0.00756</v>
+        <v>0.0101</v>
       </c>
     </row>
     <row r="26">
@@ -1479,7 +1479,7 @@
         <v>0.0954</v>
       </c>
       <c r="J26" t="n">
-        <v>0.00268</v>
+        <v>0.00402</v>
       </c>
     </row>
     <row r="27">
@@ -1519,7 +1519,7 @@
         <v>0.0954</v>
       </c>
       <c r="J27" t="n">
-        <v>0.00296</v>
+        <v>0.00444</v>
       </c>
     </row>
     <row r="28">
@@ -1719,7 +1719,7 @@
         <v>0.172</v>
       </c>
       <c r="J32" t="n">
-        <v>0.0457</v>
+        <v>0.0571</v>
       </c>
     </row>
     <row r="33">
@@ -1759,7 +1759,7 @@
         <v>0.172</v>
       </c>
       <c r="J33" t="n">
-        <v>0.0641</v>
+        <v>0.0801</v>
       </c>
     </row>
     <row r="34">
@@ -1784,22 +1784,22 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5.44e-05</v>
+        <v>0.0514</v>
       </c>
       <c r="F34" t="n">
         <v>0.778</v>
       </c>
       <c r="G34" t="n">
-        <v>0.494</v>
+        <v>0.676</v>
       </c>
       <c r="H34" t="n">
         <v>0.214</v>
       </c>
       <c r="I34" t="n">
-        <v>0.259</v>
+        <v>0.226</v>
       </c>
       <c r="J34" t="n">
-        <v>0.000261</v>
+        <v>0.0925</v>
       </c>
     </row>
     <row r="35">
@@ -1824,22 +1824,22 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3.05e-05</v>
+        <v>0.0468</v>
       </c>
       <c r="F35" t="n">
         <v>0.778</v>
       </c>
       <c r="G35" t="n">
-        <v>0.494</v>
+        <v>0.676</v>
       </c>
       <c r="H35" t="n">
         <v>0.214</v>
       </c>
       <c r="I35" t="n">
-        <v>0.259</v>
+        <v>0.226</v>
       </c>
       <c r="J35" t="n">
-        <v>0.000275</v>
+        <v>0.0842</v>
       </c>
     </row>
     <row r="36">
@@ -1879,7 +1879,7 @@
         <v>0.205</v>
       </c>
       <c r="J36" t="n">
-        <v>0.000261</v>
+        <v>0.000521</v>
       </c>
     </row>
     <row r="37">
@@ -1919,7 +1919,7 @@
         <v>0.205</v>
       </c>
       <c r="J37" t="n">
-        <v>0.000688</v>
+        <v>0.00138</v>
       </c>
     </row>
     <row r="38">
@@ -2439,7 +2439,7 @@
         <v>0.147</v>
       </c>
       <c r="J50" t="n">
-        <v>0.00181</v>
+        <v>0.00271</v>
       </c>
     </row>
     <row r="51">
@@ -2479,7 +2479,7 @@
         <v>0.147</v>
       </c>
       <c r="J51" t="n">
-        <v>0.0113</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="52">
@@ -2504,22 +2504,22 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3.2e-07</v>
+        <v>0.00257</v>
       </c>
       <c r="F52" t="n">
         <v>0.6840000000000001</v>
       </c>
       <c r="G52" t="n">
-        <v>0.324</v>
+        <v>0.587</v>
       </c>
       <c r="H52" t="n">
         <v>0.18</v>
       </c>
       <c r="I52" t="n">
-        <v>0.226</v>
+        <v>0.163</v>
       </c>
       <c r="J52" t="n">
-        <v>2.88e-06</v>
+        <v>0.00771</v>
       </c>
     </row>
     <row r="53">
@@ -2544,22 +2544,22 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6.1e-05</v>
+        <v>0.00641</v>
       </c>
       <c r="F53" t="n">
         <v>0.6840000000000001</v>
       </c>
       <c r="G53" t="n">
-        <v>0.324</v>
+        <v>0.587</v>
       </c>
       <c r="H53" t="n">
         <v>0.18</v>
       </c>
       <c r="I53" t="n">
-        <v>0.226</v>
+        <v>0.163</v>
       </c>
       <c r="J53" t="n">
-        <v>0.000275</v>
+        <v>0.0192</v>
       </c>
     </row>
     <row r="54">
@@ -2599,7 +2599,7 @@
         <v>0.174</v>
       </c>
       <c r="J54" t="n">
-        <v>0.000137</v>
+        <v>0.000275</v>
       </c>
     </row>
     <row r="55">
@@ -2639,7 +2639,7 @@
         <v>0.174</v>
       </c>
       <c r="J55" t="n">
-        <v>0.000275</v>
+        <v>0.000549</v>
       </c>
     </row>
     <row r="56">
@@ -3224,22 +3224,22 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>7.08e-08</v>
+        <v>0.00277</v>
       </c>
       <c r="F70" t="n">
         <v>0.709</v>
       </c>
       <c r="G70" t="n">
-        <v>0.33</v>
+        <v>0.596</v>
       </c>
       <c r="H70" t="n">
         <v>0.153</v>
       </c>
       <c r="I70" t="n">
-        <v>0.154</v>
+        <v>0.137</v>
       </c>
       <c r="J70" t="n">
-        <v>6.37e-07</v>
+        <v>0.0145</v>
       </c>
     </row>
     <row r="71">
@@ -3264,22 +3264,22 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3.05e-05</v>
+        <v>0.00121</v>
       </c>
       <c r="F71" t="n">
         <v>0.709</v>
       </c>
       <c r="G71" t="n">
-        <v>0.33</v>
+        <v>0.596</v>
       </c>
       <c r="H71" t="n">
         <v>0.153</v>
       </c>
       <c r="I71" t="n">
-        <v>0.154</v>
+        <v>0.137</v>
       </c>
       <c r="J71" t="n">
-        <v>0.000275</v>
+        <v>0.0109</v>
       </c>
     </row>
     <row r="72">
@@ -20027,13 +20027,13 @@
         <v>0.82</v>
       </c>
       <c r="G450" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.707</v>
       </c>
       <c r="H450" t="n">
-        <v>0.0151</v>
+        <v>0.0293</v>
       </c>
       <c r="I450" t="n">
-        <v>0.0186</v>
+        <v>0.09379999999999999</v>
       </c>
     </row>
     <row r="451">
@@ -20064,13 +20064,13 @@
         <v>0.873</v>
       </c>
       <c r="G451" t="n">
-        <v>0.42</v>
+        <v>0.707</v>
       </c>
       <c r="H451" t="n">
-        <v>8.4e-17</v>
+        <v>0.000595</v>
       </c>
       <c r="I451" t="n">
-        <v>1.34e-15</v>
+        <v>0.00317</v>
       </c>
     </row>
     <row r="452">
@@ -20101,13 +20101,13 @@
         <v>0.873</v>
       </c>
       <c r="G452" t="n">
-        <v>0.573</v>
+        <v>0.653</v>
       </c>
       <c r="H452" t="n">
-        <v>7.1e-09</v>
+        <v>1.05e-05</v>
       </c>
       <c r="I452" t="n">
-        <v>2.84e-08</v>
+        <v>8.43e-05</v>
       </c>
     </row>
     <row r="453">
@@ -20138,13 +20138,13 @@
         <v>0.987</v>
       </c>
       <c r="G453" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.767</v>
       </c>
       <c r="H453" t="n">
-        <v>1.93e-13</v>
+        <v>1.37e-09</v>
       </c>
       <c r="I453" t="n">
-        <v>1.54e-12</v>
+        <v>2.19e-08</v>
       </c>
     </row>
     <row r="454">
@@ -20175,13 +20175,13 @@
         <v>0.727</v>
       </c>
       <c r="G454" t="n">
-        <v>0.407</v>
+        <v>0.62</v>
       </c>
       <c r="H454" t="n">
-        <v>3.29e-08</v>
+        <v>0.0645</v>
       </c>
       <c r="I454" t="n">
-        <v>1.05e-07</v>
+        <v>0.148</v>
       </c>
     </row>
     <row r="455">
@@ -20212,13 +20212,13 @@
         <v>0.68</v>
       </c>
       <c r="G455" t="n">
-        <v>0.427</v>
+        <v>0.7</v>
       </c>
       <c r="H455" t="n">
-        <v>1.57e-05</v>
+        <v>0.803</v>
       </c>
       <c r="I455" t="n">
-        <v>2.59e-05</v>
+        <v>0.918</v>
       </c>
     </row>
     <row r="456">
@@ -20249,13 +20249,13 @@
         <v>0.8070000000000001</v>
       </c>
       <c r="G456" t="n">
-        <v>0.54</v>
+        <v>0.74</v>
       </c>
       <c r="H456" t="n">
-        <v>1.24e-06</v>
+        <v>0.214</v>
       </c>
       <c r="I456" t="n">
-        <v>3.31e-06</v>
+        <v>0.343</v>
       </c>
     </row>
     <row r="457">
@@ -20286,7 +20286,7 @@
         <v>0.927</v>
       </c>
       <c r="G457" t="n">
-        <v>0.92</v>
+        <v>0.927</v>
       </c>
       <c r="H457" t="n">
         <v>1</v>
@@ -20323,13 +20323,13 @@
         <v>0.593</v>
       </c>
       <c r="G458" t="n">
-        <v>0.32</v>
+        <v>0.533</v>
       </c>
       <c r="H458" t="n">
-        <v>3.1e-06</v>
+        <v>0.352</v>
       </c>
       <c r="I458" t="n">
-        <v>7.08e-06</v>
+        <v>0.469</v>
       </c>
     </row>
     <row r="459">
@@ -20360,13 +20360,13 @@
         <v>0.82</v>
       </c>
       <c r="G459" t="n">
-        <v>0.46</v>
+        <v>0.673</v>
       </c>
       <c r="H459" t="n">
-        <v>9.33e-11</v>
+        <v>0.00511</v>
       </c>
       <c r="I459" t="n">
-        <v>4.98e-10</v>
+        <v>0.0204</v>
       </c>
     </row>
     <row r="460">
@@ -20397,13 +20397,13 @@
         <v>0.733</v>
       </c>
       <c r="G460" t="n">
-        <v>0.467</v>
+        <v>0.62</v>
       </c>
       <c r="H460" t="n">
-        <v>3.71e-06</v>
+        <v>0.048</v>
       </c>
       <c r="I460" t="n">
-        <v>7.41e-06</v>
+        <v>0.128</v>
       </c>
     </row>
     <row r="461">
@@ -20434,13 +20434,13 @@
         <v>0.793</v>
       </c>
       <c r="G461" t="n">
-        <v>0.62</v>
+        <v>0.74</v>
       </c>
       <c r="H461" t="n">
-        <v>0.00145</v>
+        <v>0.339</v>
       </c>
       <c r="I461" t="n">
-        <v>0.0021</v>
+        <v>0.469</v>
       </c>
     </row>
     <row r="462">
@@ -20471,13 +20471,13 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="G462" t="n">
-        <v>0.76</v>
+        <v>0.947</v>
       </c>
       <c r="H462" t="n">
-        <v>1.62e-05</v>
+        <v>1</v>
       </c>
       <c r="I462" t="n">
-        <v>2.59e-05</v>
+        <v>1</v>
       </c>
     </row>
     <row r="463">
@@ -20508,13 +20508,13 @@
         <v>0.76</v>
       </c>
       <c r="G463" t="n">
-        <v>0.613</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="H463" t="n">
-        <v>0.00877</v>
+        <v>0.197</v>
       </c>
       <c r="I463" t="n">
-        <v>0.0117</v>
+        <v>0.343</v>
       </c>
     </row>
     <row r="464">
@@ -20545,13 +20545,13 @@
         <v>0.613</v>
       </c>
       <c r="G464" t="n">
-        <v>0.48</v>
+        <v>0.64</v>
       </c>
       <c r="H464" t="n">
-        <v>0.0274</v>
+        <v>0.72</v>
       </c>
       <c r="I464" t="n">
-        <v>0.0313</v>
+        <v>0.887</v>
       </c>
     </row>
     <row r="465">
@@ -20582,13 +20582,13 @@
         <v>0.513</v>
       </c>
       <c r="G465" t="n">
-        <v>0.507</v>
+        <v>0.62</v>
       </c>
       <c r="H465" t="n">
-        <v>1</v>
+        <v>0.0803</v>
       </c>
       <c r="I465" t="n">
-        <v>1</v>
+        <v>0.161</v>
       </c>
     </row>
     <row r="466">
@@ -20619,13 +20619,13 @@
         <v>0.931</v>
       </c>
       <c r="G466" t="n">
-        <v>0.733</v>
+        <v>0.738</v>
       </c>
       <c r="H466" t="n">
-        <v>0.000229</v>
+        <v>0.000256</v>
       </c>
       <c r="I466" t="n">
-        <v>0.000612</v>
+        <v>0.00205</v>
       </c>
     </row>
     <row r="467">
@@ -20656,13 +20656,13 @@
         <v>0.591</v>
       </c>
       <c r="G467" t="n">
-        <v>0.194</v>
+        <v>0.351</v>
       </c>
       <c r="H467" t="n">
-        <v>5.03e-06</v>
+        <v>0.0262</v>
       </c>
       <c r="I467" t="n">
-        <v>2.01e-05</v>
+        <v>0.0964</v>
       </c>
     </row>
     <row r="468">
@@ -20693,13 +20693,13 @@
         <v>0.615</v>
       </c>
       <c r="G468" t="n">
-        <v>0.235</v>
+        <v>0.329</v>
       </c>
       <c r="H468" t="n">
-        <v>0.000153</v>
+        <v>0.00483</v>
       </c>
       <c r="I468" t="n">
-        <v>0.000489</v>
+        <v>0.0258</v>
       </c>
     </row>
     <row r="469">
@@ -20730,13 +20730,13 @@
         <v>1</v>
       </c>
       <c r="G469" t="n">
-        <v>0.125</v>
+        <v>0.356</v>
       </c>
       <c r="H469" t="n">
-        <v>8.43e-11</v>
+        <v>2.84e-07</v>
       </c>
       <c r="I469" t="n">
-        <v>1.35e-09</v>
+        <v>4.54e-06</v>
       </c>
     </row>
     <row r="470">
@@ -20767,13 +20767,13 @@
         <v>0.9409999999999999</v>
       </c>
       <c r="G470" t="n">
-        <v>0.7</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="H470" t="n">
-        <v>0.00247</v>
+        <v>0.0361</v>
       </c>
       <c r="I470" t="n">
-        <v>0.00495</v>
+        <v>0.0964</v>
       </c>
     </row>
     <row r="471">
@@ -20804,13 +20804,13 @@
         <v>1</v>
       </c>
       <c r="G471" t="n">
-        <v>0.6</v>
+        <v>0.927</v>
       </c>
       <c r="H471" t="n">
-        <v>3.94e-06</v>
+        <v>0.127</v>
       </c>
       <c r="I471" t="n">
-        <v>2.01e-05</v>
+        <v>0.253</v>
       </c>
     </row>
     <row r="472">
@@ -20841,13 +20841,13 @@
         <v>0.924</v>
       </c>
       <c r="G472" t="n">
-        <v>0.786</v>
+        <v>0.897</v>
       </c>
       <c r="H472" t="n">
-        <v>0.079</v>
+        <v>0.754</v>
       </c>
       <c r="I472" t="n">
-        <v>0.115</v>
+        <v>0.804</v>
       </c>
     </row>
     <row r="473">
@@ -20878,7 +20878,7 @@
         <v>0.375</v>
       </c>
       <c r="G473" t="n">
-        <v>0.2</v>
+        <v>0.375</v>
       </c>
       <c r="H473" t="n">
         <v>1</v>
@@ -20915,13 +20915,13 @@
         <v>0.971</v>
       </c>
       <c r="G474" t="n">
-        <v>0.929</v>
+        <v>0.952</v>
       </c>
       <c r="H474" t="n">
-        <v>0.577</v>
+        <v>0.667</v>
       </c>
       <c r="I474" t="n">
-        <v>0.659</v>
+        <v>0.762</v>
       </c>
     </row>
     <row r="475">
@@ -20952,13 +20952,13 @@
         <v>0.95</v>
       </c>
       <c r="G475" t="n">
-        <v>0.5</v>
+        <v>0.82</v>
       </c>
       <c r="H475" t="n">
-        <v>6.21e-07</v>
+        <v>0.0355</v>
       </c>
       <c r="I475" t="n">
-        <v>4.97e-06</v>
+        <v>0.0964</v>
       </c>
     </row>
     <row r="476">
@@ -20989,13 +20989,13 @@
         <v>0.871</v>
       </c>
       <c r="G476" t="n">
-        <v>0.731</v>
+        <v>0.797</v>
       </c>
       <c r="H476" t="n">
-        <v>0.126</v>
+        <v>0.339</v>
       </c>
       <c r="I476" t="n">
-        <v>0.168</v>
+        <v>0.493</v>
       </c>
     </row>
     <row r="477">
@@ -21026,13 +21026,13 @@
         <v>0.857</v>
       </c>
       <c r="G477" t="n">
-        <v>0.591</v>
+        <v>0.704</v>
       </c>
       <c r="H477" t="n">
-        <v>0.0283</v>
+        <v>0.0906</v>
       </c>
       <c r="I477" t="n">
-        <v>0.0502</v>
+        <v>0.207</v>
       </c>
     </row>
     <row r="478">
@@ -21063,13 +21063,13 @@
         <v>0.731</v>
       </c>
       <c r="G478" t="n">
-        <v>0.308</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="H478" t="n">
-        <v>0.00106</v>
+        <v>0.22</v>
       </c>
       <c r="I478" t="n">
-        <v>0.00242</v>
+        <v>0.391</v>
       </c>
     </row>
     <row r="479">
@@ -21100,13 +21100,13 @@
         <v>0.761</v>
       </c>
       <c r="G479" t="n">
-        <v>0.703</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="H479" t="n">
-        <v>0.644</v>
+        <v>0.447</v>
       </c>
       <c r="I479" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.573</v>
       </c>
     </row>
     <row r="480">
@@ -21137,13 +21137,13 @@
         <v>0.554</v>
       </c>
       <c r="G480" t="n">
-        <v>0.366</v>
+        <v>0.633</v>
       </c>
       <c r="H480" t="n">
-        <v>0.0576</v>
+        <v>0.465</v>
       </c>
       <c r="I480" t="n">
-        <v>0.0921</v>
+        <v>0.573</v>
       </c>
     </row>
     <row r="481">
@@ -21174,13 +21174,13 @@
         <v>0.379</v>
       </c>
       <c r="G481" t="n">
-        <v>0.207</v>
+        <v>0.5</v>
       </c>
       <c r="H481" t="n">
-        <v>0.153</v>
+        <v>0.281</v>
       </c>
       <c r="I481" t="n">
-        <v>0.189</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="482">
@@ -21211,13 +21211,13 @@
         <v>0.794</v>
       </c>
       <c r="G482" t="n">
-        <v>0.863</v>
+        <v>0.882</v>
       </c>
       <c r="H482" t="n">
-        <v>0.265</v>
+        <v>0.127</v>
       </c>
       <c r="I482" t="n">
-        <v>0.283</v>
+        <v>0.297</v>
       </c>
     </row>
     <row r="483">
@@ -21248,13 +21248,13 @@
         <v>0.963</v>
       </c>
       <c r="G483" t="n">
-        <v>0.704</v>
+        <v>0.741</v>
       </c>
       <c r="H483" t="n">
-        <v>0.0243</v>
+        <v>0.0504</v>
       </c>
       <c r="I483" t="n">
-        <v>0.0324</v>
+        <v>0.205</v>
       </c>
     </row>
     <row r="484">
@@ -21285,13 +21285,13 @@
         <v>0.857</v>
       </c>
       <c r="G484" t="n">
-        <v>0.571</v>
+        <v>0.821</v>
       </c>
       <c r="H484" t="n">
-        <v>0.0366</v>
+        <v>1</v>
       </c>
       <c r="I484" t="n">
-        <v>0.0418</v>
+        <v>1</v>
       </c>
     </row>
     <row r="485">
@@ -21322,13 +21322,13 @@
         <v>0.909</v>
       </c>
       <c r="G485" t="n">
-        <v>0.182</v>
+        <v>0.727</v>
       </c>
       <c r="H485" t="n">
-        <v>1.96e-06</v>
+        <v>0.24</v>
       </c>
       <c r="I485" t="n">
-        <v>4.47e-06</v>
+        <v>0.427</v>
       </c>
     </row>
     <row r="486">
@@ -21359,13 +21359,13 @@
         <v>0.634</v>
       </c>
       <c r="G486" t="n">
-        <v>0.208</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="H486" t="n">
-        <v>1.14e-09</v>
+        <v>0.389</v>
       </c>
       <c r="I486" t="n">
-        <v>6.06e-09</v>
+        <v>0.479</v>
       </c>
     </row>
     <row r="487">
@@ -21396,13 +21396,13 @@
         <v>0.478</v>
       </c>
       <c r="G487" t="n">
-        <v>0.196</v>
+        <v>0.554</v>
       </c>
       <c r="H487" t="n">
-        <v>8.21e-05</v>
+        <v>0.376</v>
       </c>
       <c r="I487" t="n">
-        <v>0.000131</v>
+        <v>0.479</v>
       </c>
     </row>
     <row r="488">
@@ -21433,13 +21433,13 @@
         <v>0.718</v>
       </c>
       <c r="G488" t="n">
-        <v>0.259</v>
+        <v>0.612</v>
       </c>
       <c r="H488" t="n">
-        <v>2.98e-09</v>
+        <v>0.193</v>
       </c>
       <c r="I488" t="n">
-        <v>1.19e-08</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="489">
@@ -21470,13 +21470,13 @@
         <v>0.333</v>
       </c>
       <c r="G489" t="n">
-        <v>0.111</v>
+        <v>0.333</v>
       </c>
       <c r="H489" t="n">
-        <v>0.576</v>
+        <v>1</v>
       </c>
       <c r="I489" t="n">
-        <v>0.576</v>
+        <v>1</v>
       </c>
     </row>
     <row r="490">
@@ -21507,13 +21507,13 @@
         <v>0.532</v>
       </c>
       <c r="G490" t="n">
-        <v>0.206</v>
+        <v>0.468</v>
       </c>
       <c r="H490" t="n">
-        <v>1.26e-07</v>
+        <v>0.378</v>
       </c>
       <c r="I490" t="n">
-        <v>3.36e-07</v>
+        <v>0.479</v>
       </c>
     </row>
     <row r="491">
@@ -21544,13 +21544,13 @@
         <v>0.704</v>
       </c>
       <c r="G491" t="n">
-        <v>0.21</v>
+        <v>0.506</v>
       </c>
       <c r="H491" t="n">
-        <v>3.31e-10</v>
+        <v>0.0156</v>
       </c>
       <c r="I491" t="n">
-        <v>4.13e-09</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="492">
@@ -21581,13 +21581,13 @@
         <v>0.663</v>
       </c>
       <c r="G492" t="n">
-        <v>0.207</v>
+        <v>0.511</v>
       </c>
       <c r="H492" t="n">
-        <v>5.16e-10</v>
+        <v>0.0513</v>
       </c>
       <c r="I492" t="n">
-        <v>4.13e-09</v>
+        <v>0.205</v>
       </c>
     </row>
     <row r="493">
@@ -21618,13 +21618,13 @@
         <v>0.59</v>
       </c>
       <c r="G493" t="n">
-        <v>0.213</v>
+        <v>0.623</v>
       </c>
       <c r="H493" t="n">
-        <v>3.85e-05</v>
+        <v>0.853</v>
       </c>
       <c r="I493" t="n">
-        <v>6.84e-05</v>
+        <v>0.975</v>
       </c>
     </row>
     <row r="494">
@@ -21655,13 +21655,13 @@
         <v>0.905</v>
       </c>
       <c r="G494" t="n">
-        <v>0.571</v>
+        <v>0.667</v>
       </c>
       <c r="H494" t="n">
-        <v>0.0325</v>
+        <v>0.13</v>
       </c>
       <c r="I494" t="n">
-        <v>0.04</v>
+        <v>0.297</v>
       </c>
     </row>
     <row r="495">
@@ -21692,13 +21692,13 @@
         <v>0.74</v>
       </c>
       <c r="G495" t="n">
-        <v>0.356</v>
+        <v>0.644</v>
       </c>
       <c r="H495" t="n">
-        <v>5.53e-06</v>
+        <v>0.282</v>
       </c>
       <c r="I495" t="n">
-        <v>1.11e-05</v>
+        <v>0.451</v>
       </c>
     </row>
     <row r="496">
@@ -21729,13 +21729,13 @@
         <v>0.6870000000000001</v>
       </c>
       <c r="G496" t="n">
-        <v>0.224</v>
+        <v>0.463</v>
       </c>
       <c r="H496" t="n">
-        <v>1.17e-07</v>
+        <v>0.0141</v>
       </c>
       <c r="I496" t="n">
-        <v>3.36e-07</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="497">
@@ -21766,13 +21766,13 @@
         <v>0.439</v>
       </c>
       <c r="G497" t="n">
-        <v>0.105</v>
+        <v>0.281</v>
       </c>
       <c r="H497" t="n">
-        <v>0.000107</v>
+        <v>0.118</v>
       </c>
       <c r="I497" t="n">
-        <v>0.000155</v>
+        <v>0.297</v>
       </c>
     </row>
     <row r="498">
@@ -21803,13 +21803,13 @@
         <v>0.857</v>
       </c>
       <c r="G498" t="n">
-        <v>0.793</v>
+        <v>0.804</v>
       </c>
       <c r="H498" t="n">
-        <v>0.0939</v>
+        <v>0.19</v>
       </c>
       <c r="I498" t="n">
-        <v>0.1</v>
+        <v>0.338</v>
       </c>
     </row>
     <row r="499">
@@ -21840,13 +21840,13 @@
         <v>0.732</v>
       </c>
       <c r="G499" t="n">
-        <v>0.304</v>
+        <v>0.476</v>
       </c>
       <c r="H499" t="n">
-        <v>8.200000000000001e-09</v>
+        <v>0.00173</v>
       </c>
       <c r="I499" t="n">
-        <v>1.87e-08</v>
+        <v>0.00902</v>
       </c>
     </row>
     <row r="500">
@@ -21877,13 +21877,13 @@
         <v>0.716</v>
       </c>
       <c r="G500" t="n">
-        <v>0.333</v>
+        <v>0.469</v>
       </c>
       <c r="H500" t="n">
-        <v>1.57e-06</v>
+        <v>0.00226</v>
       </c>
       <c r="I500" t="n">
-        <v>2.28e-06</v>
+        <v>0.00902</v>
       </c>
     </row>
     <row r="501">
@@ -21914,13 +21914,13 @@
         <v>0.952</v>
       </c>
       <c r="G501" t="n">
-        <v>0.148</v>
+        <v>0.478</v>
       </c>
       <c r="H501" t="n">
-        <v>2.81e-16</v>
+        <v>8.46e-08</v>
       </c>
       <c r="I501" t="n">
-        <v>2.25e-15</v>
+        <v>1.35e-06</v>
       </c>
     </row>
     <row r="502">
@@ -21951,13 +21951,13 @@
         <v>0.757</v>
       </c>
       <c r="G502" t="n">
-        <v>0.321</v>
+        <v>0.667</v>
       </c>
       <c r="H502" t="n">
-        <v>2.54e-14</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="I502" t="n">
-        <v>1.35e-13</v>
+        <v>0.194</v>
       </c>
     </row>
     <row r="503">
@@ -21988,13 +21988,13 @@
         <v>0.647</v>
       </c>
       <c r="G503" t="n">
-        <v>0.295</v>
+        <v>0.694</v>
       </c>
       <c r="H503" t="n">
-        <v>1.58e-08</v>
+        <v>0.448</v>
       </c>
       <c r="I503" t="n">
-        <v>3.17e-08</v>
+        <v>0.597</v>
       </c>
     </row>
     <row r="504">
@@ -22025,13 +22025,13 @@
         <v>0.8080000000000001</v>
       </c>
       <c r="G504" t="n">
-        <v>0.389</v>
+        <v>0.727</v>
       </c>
       <c r="H504" t="n">
-        <v>3.5e-12</v>
+        <v>0.128</v>
       </c>
       <c r="I504" t="n">
-        <v>1.12e-11</v>
+        <v>0.292</v>
       </c>
     </row>
     <row r="505">
@@ -22062,13 +22062,13 @@
         <v>0.353</v>
       </c>
       <c r="G505" t="n">
-        <v>0.143</v>
+        <v>0.353</v>
       </c>
       <c r="H505" t="n">
-        <v>0.24</v>
+        <v>1</v>
       </c>
       <c r="I505" t="n">
-        <v>0.24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="506">
@@ -22099,13 +22099,13 @@
         <v>0.6870000000000001</v>
       </c>
       <c r="G506" t="n">
-        <v>0.338</v>
+        <v>0.628</v>
       </c>
       <c r="H506" t="n">
-        <v>7.07e-11</v>
+        <v>0.237</v>
       </c>
       <c r="I506" t="n">
-        <v>1.89e-10</v>
+        <v>0.345</v>
       </c>
     </row>
     <row r="507">
@@ -22136,13 +22136,13 @@
         <v>0.8090000000000001</v>
       </c>
       <c r="G507" t="n">
-        <v>0.296</v>
+        <v>0.626</v>
       </c>
       <c r="H507" t="n">
-        <v>6.74e-17</v>
+        <v>0.0011</v>
       </c>
       <c r="I507" t="n">
-        <v>1.08e-15</v>
+        <v>0.008829999999999999</v>
       </c>
     </row>
     <row r="508">
@@ -22173,13 +22173,13 @@
         <v>0.753</v>
       </c>
       <c r="G508" t="n">
-        <v>0.322</v>
+        <v>0.623</v>
       </c>
       <c r="H508" t="n">
-        <v>5.6e-13</v>
+        <v>0.0145</v>
       </c>
       <c r="I508" t="n">
-        <v>2.24e-12</v>
+        <v>0.0464</v>
       </c>
     </row>
     <row r="509">
@@ -22210,13 +22210,13 @@
         <v>0.699</v>
       </c>
       <c r="G509" t="n">
-        <v>0.313</v>
+        <v>0.661</v>
       </c>
       <c r="H509" t="n">
-        <v>1.82e-07</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="I509" t="n">
-        <v>2.92e-07</v>
+        <v>0.649</v>
       </c>
     </row>
     <row r="510">
@@ -22247,13 +22247,13 @@
         <v>0.8090000000000001</v>
       </c>
       <c r="G510" t="n">
-        <v>0.4</v>
+        <v>0.778</v>
       </c>
       <c r="H510" t="n">
-        <v>2.7e-05</v>
+        <v>0.788</v>
       </c>
       <c r="I510" t="n">
-        <v>3.16e-05</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="511">
@@ -22284,13 +22284,13 @@
         <v>0.75</v>
       </c>
       <c r="G511" t="n">
-        <v>0.473</v>
+        <v>0.667</v>
       </c>
       <c r="H511" t="n">
-        <v>7.37e-06</v>
+        <v>0.151</v>
       </c>
       <c r="I511" t="n">
-        <v>9.830000000000001e-06</v>
+        <v>0.303</v>
       </c>
     </row>
     <row r="512">
@@ -22321,13 +22321,13 @@
         <v>0.613</v>
       </c>
       <c r="G512" t="n">
-        <v>0.278</v>
+        <v>0.534</v>
       </c>
       <c r="H512" t="n">
-        <v>9.46e-08</v>
+        <v>0.212</v>
       </c>
       <c r="I512" t="n">
-        <v>1.68e-07</v>
+        <v>0.339</v>
       </c>
     </row>
     <row r="513">
@@ -22358,13 +22358,13 @@
         <v>0.407</v>
       </c>
       <c r="G513" t="n">
-        <v>0.14</v>
+        <v>0.36</v>
       </c>
       <c r="H513" t="n">
-        <v>2.76e-05</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="I513" t="n">
-        <v>3.16e-05</v>
+        <v>0.649</v>
       </c>
     </row>
     <row r="514">
@@ -25587,7 +25587,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -25602,7 +25602,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>86.3***</t>
+          <t>88.2***</t>
         </is>
       </c>
     </row>
@@ -25632,7 +25632,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>35.1</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -25647,7 +25647,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>74.1</t>
         </is>
       </c>
     </row>
@@ -25677,7 +25677,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -25692,7 +25692,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>20.8*</t>
+          <t>56.4*</t>
         </is>
       </c>
     </row>
@@ -25722,7 +25722,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -25737,7 +25737,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>19.6***</t>
+          <t>55.4***</t>
         </is>
       </c>
     </row>
@@ -25767,7 +25767,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -25782,7 +25782,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>25.9***</t>
+          <t>61.2***</t>
         </is>
       </c>
     </row>
@@ -25812,7 +25812,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>92.9</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -25827,7 +25827,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>20.6***</t>
+          <t>46.8***</t>
         </is>
       </c>
     </row>
@@ -25857,7 +25857,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>59.1</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -25872,7 +25872,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>21.3***</t>
+          <t>62.3***</t>
         </is>
       </c>
     </row>
@@ -25902,7 +25902,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>70.3</t>
+          <t>69.1</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -25917,7 +25917,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>35.6***</t>
+          <t>64.4***</t>
         </is>
       </c>
     </row>
@@ -25947,7 +25947,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>63.3</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -25962,7 +25962,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>46.3</t>
         </is>
       </c>
     </row>
@@ -25992,7 +25992,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -26007,7 +26007,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>28.1</t>
         </is>
       </c>
     </row>

--- a/eval/results/statistical_tests_full150.xlsx
+++ b/eval/results/statistical_tests_full150.xlsx
@@ -24746,7 +24746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24803,41 +24803,41 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>94.1</t>
+          <t>89.3***</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>94.2</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>94.1</t>
+          <t>92.6</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>95.1</t>
+          <t>100.0</t>
         </is>
       </c>
     </row>
@@ -24848,41 +24848,41 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>96.9</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>89.3***</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>92.6</t>
+          <t>90.2***</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>92.4***</t>
         </is>
       </c>
     </row>
@@ -24893,41 +24893,41 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>96.9</t>
+          <t>95.7</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>90.2***</t>
+          <t>92.9*†</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>90.2***</t>
+          <t>95.3**</t>
         </is>
       </c>
     </row>
@@ -24938,41 +24938,41 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>95.7</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>92.6</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>92.9*†</t>
+          <t>81.5**</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>91.8**</t>
+          <t>75.0*†</t>
         </is>
       </c>
     </row>
@@ -24983,41 +24983,41 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>98.7</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>85.9**</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>60.3</t>
+          <t>70.1</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>73.0*†</t>
+          <t>82.1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>61.2</t>
         </is>
       </c>
     </row>
@@ -25028,176 +25028,176 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>92.6</t>
+          <t>78.0**</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>81.5**</t>
+          <t>68.4*†</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>87.0*†</t>
+          <t>29.8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GPT-4o</t>
+          <t>Llama3.1-70B</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>91.8*†</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>93.1***</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GPT-4o</t>
+          <t>Llama3.1-70B</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>63.5</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>85.9**</t>
+          <t>98.1***</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>70.1</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>82.1</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>64.2</t>
+          <t>84.9</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GPT-4o</t>
+          <t>Llama3.1-70B</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>78.0**</t>
+          <t>77.1***</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>64.3</t>
+          <t>78.3***</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>68.4*†</t>
+          <t>55.2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>70.1</t>
         </is>
       </c>
     </row>
@@ -25208,806 +25208,311 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>36.5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>69.7**</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>68.3***</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>66.7</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>93.1***</t>
+          <t>49.1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Llama3.1-70B</t>
+          <t>Llama3.1-8B</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>96.1</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>97.5*†</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>100.0***</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Llama3.1-70B</t>
+          <t>Llama3.1-8B</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>84.9</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>60.9</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>92.9</t>
+          <t>79.3***</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Llama3.1-70B</t>
+          <t>Llama3.1-8B</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>96.8</t>
+          <t>96.4</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>61.7</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>62.4</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>80.2*†</t>
+          <t>97.6***</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Llama3.1-70B</t>
+          <t>Llama3.1-8B</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>97.1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>96.9*†</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>78.6***</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Llama3.1-70B</t>
+          <t>Llama3.1-8B</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>98.1***</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>69.1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>78.1</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>84.9</t>
+          <t>91.8***</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Llama3.1-70B</t>
+          <t>Llama3.1-8B</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>77.1***</t>
+          <t>88.9</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>78.3***</t>
+          <t>65.1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>55.2</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>70.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Llama3.1-70B</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>16</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>36.5</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>69.7**</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>68.3***</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>40.4</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>49.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Llama3.1-8B</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>93.1</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>91.4</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>73.8</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>79.4</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>72.5</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>88.2***</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Llama3.1-8B</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>2</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>59.1</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>87.5*†</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>35.1</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>96.3</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>77.8</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>74.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Llama3.1-8B</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>5</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>94.1</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>95.5</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>81.4</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>63.4</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>62.4</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>56.4*</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Llama3.1-8B</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>6</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>From which countries were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>93.3</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>92.7</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>47.8</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>60.9</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>55.4***</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Llama3.1-8B</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>7</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>From what years were the sequenced samples obtained?</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>92.4</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>96.4</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>89.7</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>71.8</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>62.4</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>61.2***</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Llama3.1-8B</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>9</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>97.1</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>98.3</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>95.2</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>53.2</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>46.8</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>46.8***</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Llama3.1-8B</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>12</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>85.7</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>92.3</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>70.4</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>62.3***</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Llama3.1-8B</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>14</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>76.1</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>88.9</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>69.1</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>65.8</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>64.4***</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Llama3.1-8B</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>15</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>55.4</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>73.1*†</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>63.3</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>68.7</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>56.7</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>46.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Llama3.1-8B</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>16</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>37.9</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>57.1</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>43.9</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>28.1</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>28.1</t>
+          <t>97.3***</t>
         </is>
       </c>
     </row>

--- a/eval/results/statistical_tests_full150.xlsx
+++ b/eval/results/statistical_tests_full150.xlsx
@@ -599,7 +599,7 @@
         <v>0.0842</v>
       </c>
       <c r="J4" t="n">
-        <v>0.018</v>
+        <v>0.0225</v>
       </c>
     </row>
     <row r="5">
@@ -639,7 +639,7 @@
         <v>0.0842</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0364</v>
+        <v>0.0437</v>
       </c>
     </row>
     <row r="6">
@@ -719,7 +719,7 @@
         <v>0.103</v>
       </c>
       <c r="J7" t="n">
-        <v>0.377</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="8">
@@ -759,7 +759,7 @@
         <v>0.0931</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0216</v>
+        <v>0.0259</v>
       </c>
     </row>
     <row r="9">
@@ -824,22 +824,22 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.161</v>
       </c>
       <c r="F10" t="n">
         <v>0.797</v>
       </c>
       <c r="G10" t="n">
-        <v>0.87</v>
+        <v>0.829</v>
       </c>
       <c r="H10" t="n">
         <v>0.155</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0796</v>
+        <v>0.11</v>
       </c>
       <c r="J10" t="n">
-        <v>0.018</v>
+        <v>0.242</v>
       </c>
     </row>
     <row r="11">
@@ -864,22 +864,22 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.008869999999999999</v>
+        <v>0.393</v>
       </c>
       <c r="F11" t="n">
         <v>0.797</v>
       </c>
       <c r="G11" t="n">
-        <v>0.87</v>
+        <v>0.829</v>
       </c>
       <c r="H11" t="n">
         <v>0.155</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0796</v>
+        <v>0.11</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0175</v>
+        <v>0.505</v>
       </c>
     </row>
     <row r="12">
@@ -919,7 +919,7 @@
         <v>0.0796</v>
       </c>
       <c r="J12" t="n">
-        <v>0.018</v>
+        <v>0.0225</v>
       </c>
     </row>
     <row r="13">
@@ -959,7 +959,7 @@
         <v>0.0796</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0175</v>
+        <v>0.0219</v>
       </c>
     </row>
     <row r="14">
@@ -1079,7 +1079,7 @@
         <v>0.107</v>
       </c>
       <c r="J16" t="n">
-        <v>0.018</v>
+        <v>0.0225</v>
       </c>
     </row>
     <row r="17">
@@ -1119,7 +1119,7 @@
         <v>0.107</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0175</v>
+        <v>0.0219</v>
       </c>
     </row>
     <row r="18">
@@ -1239,7 +1239,7 @@
         <v>0.0584</v>
       </c>
       <c r="J20" t="n">
-        <v>0.136</v>
+        <v>0.116</v>
       </c>
     </row>
     <row r="21">
@@ -1399,7 +1399,7 @@
         <v>0.191</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0571</v>
+        <v>0.0457</v>
       </c>
     </row>
     <row r="25">
@@ -1439,7 +1439,7 @@
         <v>0.191</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0101</v>
+        <v>0.00756</v>
       </c>
     </row>
     <row r="26">
@@ -1544,22 +1544,22 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.164</v>
+        <v>0.00718</v>
       </c>
       <c r="F28" t="n">
         <v>0.793</v>
       </c>
       <c r="G28" t="n">
-        <v>0.841</v>
+        <v>0.921</v>
       </c>
       <c r="H28" t="n">
         <v>0.205</v>
       </c>
       <c r="I28" t="n">
-        <v>0.164</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="J28" t="n">
-        <v>0.184</v>
+        <v>0.0215</v>
       </c>
     </row>
     <row r="29">
@@ -1584,22 +1584,22 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.06909999999999999</v>
+        <v>0.00179</v>
       </c>
       <c r="F29" t="n">
         <v>0.793</v>
       </c>
       <c r="G29" t="n">
-        <v>0.841</v>
+        <v>0.921</v>
       </c>
       <c r="H29" t="n">
         <v>0.205</v>
       </c>
       <c r="I29" t="n">
-        <v>0.164</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="J29" t="n">
-        <v>0.0888</v>
+        <v>0.00537</v>
       </c>
     </row>
     <row r="30">
@@ -1719,7 +1719,7 @@
         <v>0.172</v>
       </c>
       <c r="J32" t="n">
-        <v>0.0571</v>
+        <v>0.0457</v>
       </c>
     </row>
     <row r="33">
@@ -1759,7 +1759,7 @@
         <v>0.172</v>
       </c>
       <c r="J33" t="n">
-        <v>0.0801</v>
+        <v>0.0641</v>
       </c>
     </row>
     <row r="34">
@@ -1799,7 +1799,7 @@
         <v>0.226</v>
       </c>
       <c r="J34" t="n">
-        <v>0.0925</v>
+        <v>0.0771</v>
       </c>
     </row>
     <row r="35">
@@ -1839,7 +1839,7 @@
         <v>0.226</v>
       </c>
       <c r="J35" t="n">
-        <v>0.0842</v>
+        <v>0.0702</v>
       </c>
     </row>
     <row r="36">
@@ -1999,7 +1999,7 @@
         <v>0.137</v>
       </c>
       <c r="J39" t="n">
-        <v>0.0247</v>
+        <v>0.0198</v>
       </c>
     </row>
     <row r="40">
@@ -2264,22 +2264,22 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.0557</v>
+        <v>0.0131</v>
       </c>
       <c r="F46" t="n">
         <v>0.755</v>
       </c>
       <c r="G46" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.615</v>
       </c>
       <c r="H46" t="n">
         <v>0.185</v>
       </c>
       <c r="I46" t="n">
-        <v>0.162</v>
+        <v>0.211</v>
       </c>
       <c r="J46" t="n">
-        <v>0.0835</v>
+        <v>0.0236</v>
       </c>
     </row>
     <row r="47">
@@ -2304,22 +2304,22 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.0555</v>
+        <v>0.00898</v>
       </c>
       <c r="F47" t="n">
         <v>0.755</v>
       </c>
       <c r="G47" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.615</v>
       </c>
       <c r="H47" t="n">
         <v>0.185</v>
       </c>
       <c r="I47" t="n">
-        <v>0.162</v>
+        <v>0.211</v>
       </c>
       <c r="J47" t="n">
-        <v>0.0833</v>
+        <v>0.0198</v>
       </c>
     </row>
     <row r="48">
@@ -2799,7 +2799,7 @@
         <v>0.149</v>
       </c>
       <c r="J59" t="n">
-        <v>0.0866</v>
+        <v>0.104</v>
       </c>
     </row>
     <row r="60">
@@ -2919,7 +2919,7 @@
         <v>0.137</v>
       </c>
       <c r="J62" t="n">
-        <v>0.0272</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="63">
@@ -2959,7 +2959,7 @@
         <v>0.137</v>
       </c>
       <c r="J63" t="n">
-        <v>0.0137</v>
+        <v>0.0171</v>
       </c>
     </row>
     <row r="64">
@@ -2984,22 +2984,22 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.00765</v>
+        <v>0.117</v>
       </c>
       <c r="F64" t="n">
         <v>0.756</v>
       </c>
       <c r="G64" t="n">
-        <v>0.819</v>
+        <v>0.717</v>
       </c>
       <c r="H64" t="n">
         <v>0.169</v>
       </c>
       <c r="I64" t="n">
-        <v>0.144</v>
+        <v>0.186</v>
       </c>
       <c r="J64" t="n">
-        <v>0.0172</v>
+        <v>0.176</v>
       </c>
     </row>
     <row r="65">
@@ -3024,22 +3024,22 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.00629</v>
+        <v>0.175</v>
       </c>
       <c r="F65" t="n">
         <v>0.756</v>
       </c>
       <c r="G65" t="n">
-        <v>0.819</v>
+        <v>0.717</v>
       </c>
       <c r="H65" t="n">
         <v>0.169</v>
       </c>
       <c r="I65" t="n">
-        <v>0.144</v>
+        <v>0.186</v>
       </c>
       <c r="J65" t="n">
-        <v>0.0137</v>
+        <v>0.225</v>
       </c>
     </row>
     <row r="66">
@@ -3079,7 +3079,7 @@
         <v>0.144</v>
       </c>
       <c r="J66" t="n">
-        <v>0.0172</v>
+        <v>0.0229</v>
       </c>
     </row>
     <row r="67">
@@ -3119,7 +3119,7 @@
         <v>0.144</v>
       </c>
       <c r="J67" t="n">
-        <v>0.0137</v>
+        <v>0.0171</v>
       </c>
     </row>
     <row r="68">
@@ -3159,7 +3159,7 @@
         <v>0.149</v>
       </c>
       <c r="J68" t="n">
-        <v>0.135</v>
+        <v>0.161</v>
       </c>
     </row>
     <row r="69">
@@ -3199,7 +3199,7 @@
         <v>0.149</v>
       </c>
       <c r="J69" t="n">
-        <v>0.135</v>
+        <v>0.158</v>
       </c>
     </row>
     <row r="70">
@@ -12923,13 +12923,13 @@
         <v>0.773</v>
       </c>
       <c r="G258" t="n">
-        <v>0.88</v>
+        <v>0.907</v>
       </c>
       <c r="H258" t="n">
-        <v>0.0215</v>
+        <v>0.0025</v>
       </c>
       <c r="I258" t="n">
-        <v>0.0689</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="259">
@@ -12960,13 +12960,13 @@
         <v>0.947</v>
       </c>
       <c r="G259" t="n">
-        <v>0.827</v>
+        <v>0.907</v>
       </c>
       <c r="H259" t="n">
-        <v>0.00162</v>
+        <v>0.268</v>
       </c>
       <c r="I259" t="n">
-        <v>0.008630000000000001</v>
+        <v>0.581</v>
       </c>
     </row>
     <row r="260">
@@ -12997,13 +12997,13 @@
         <v>0.92</v>
       </c>
       <c r="G260" t="n">
-        <v>0.953</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="H260" t="n">
-        <v>0.343</v>
+        <v>0.825</v>
       </c>
       <c r="I260" t="n">
-        <v>0.499</v>
+        <v>0.873</v>
       </c>
     </row>
     <row r="261">
@@ -13034,13 +13034,13 @@
         <v>0.987</v>
       </c>
       <c r="G261" t="n">
-        <v>1</v>
+        <v>0.953</v>
       </c>
       <c r="H261" t="n">
-        <v>0.498</v>
+        <v>0.173</v>
       </c>
       <c r="I261" t="n">
-        <v>0.653</v>
+        <v>0.554</v>
       </c>
     </row>
     <row r="262">
@@ -13071,13 +13071,13 @@
         <v>0.8070000000000001</v>
       </c>
       <c r="G262" t="n">
-        <v>0.84</v>
+        <v>0.78</v>
       </c>
       <c r="H262" t="n">
-        <v>0.545</v>
+        <v>0.669</v>
       </c>
       <c r="I262" t="n">
-        <v>0.653</v>
+        <v>0.823</v>
       </c>
     </row>
     <row r="263">
@@ -13108,13 +13108,13 @@
         <v>0.787</v>
       </c>
       <c r="G263" t="n">
-        <v>0.9</v>
+        <v>0.833</v>
       </c>
       <c r="H263" t="n">
-        <v>0.0105</v>
+        <v>0.377</v>
       </c>
       <c r="I263" t="n">
-        <v>0.0419</v>
+        <v>0.604</v>
       </c>
     </row>
     <row r="264">
@@ -13145,13 +13145,13 @@
         <v>0.84</v>
       </c>
       <c r="G264" t="n">
-        <v>0.927</v>
+        <v>0.853</v>
       </c>
       <c r="H264" t="n">
-        <v>0.0298</v>
+        <v>0.873</v>
       </c>
       <c r="I264" t="n">
-        <v>0.0793</v>
+        <v>0.873</v>
       </c>
     </row>
     <row r="265">
@@ -13182,13 +13182,13 @@
         <v>0.9330000000000001</v>
       </c>
       <c r="G265" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.947</v>
       </c>
       <c r="H265" t="n">
-        <v>1</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="I265" t="n">
-        <v>1</v>
+        <v>0.873</v>
       </c>
     </row>
     <row r="266">
@@ -13219,13 +13219,13 @@
         <v>0.66</v>
       </c>
       <c r="G266" t="n">
-        <v>0.747</v>
+        <v>0.6</v>
       </c>
       <c r="H266" t="n">
-        <v>0.129</v>
+        <v>0.339</v>
       </c>
       <c r="I266" t="n">
-        <v>0.207</v>
+        <v>0.602</v>
       </c>
     </row>
     <row r="267">
@@ -13256,13 +13256,13 @@
         <v>0.787</v>
       </c>
       <c r="G267" t="n">
-        <v>0.873</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="H267" t="n">
-        <v>0.0644</v>
+        <v>0.665</v>
       </c>
       <c r="I267" t="n">
-        <v>0.129</v>
+        <v>0.823</v>
       </c>
     </row>
     <row r="268">
@@ -13293,13 +13293,13 @@
         <v>0.773</v>
       </c>
       <c r="G268" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.713</v>
       </c>
       <c r="H268" t="n">
-        <v>0.571</v>
+        <v>0.29</v>
       </c>
       <c r="I268" t="n">
-        <v>0.653</v>
+        <v>0.581</v>
       </c>
     </row>
     <row r="269">
@@ -13330,13 +13330,13 @@
         <v>0.833</v>
       </c>
       <c r="G269" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="H269" t="n">
-        <v>0.126</v>
+        <v>0.631</v>
       </c>
       <c r="I269" t="n">
-        <v>0.207</v>
+        <v>0.823</v>
       </c>
     </row>
     <row r="270">
@@ -13367,13 +13367,13 @@
         <v>0.973</v>
       </c>
       <c r="G270" t="n">
-        <v>0.967</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H270" t="n">
-        <v>1</v>
+        <v>0.256</v>
       </c>
       <c r="I270" t="n">
-        <v>1</v>
+        <v>0.581</v>
       </c>
     </row>
     <row r="271">
@@ -13404,13 +13404,13 @@
         <v>0.78</v>
       </c>
       <c r="G271" t="n">
-        <v>0.873</v>
+        <v>0.867</v>
       </c>
       <c r="H271" t="n">
-        <v>0.0467</v>
+        <v>0.06859999999999999</v>
       </c>
       <c r="I271" t="n">
-        <v>0.107</v>
+        <v>0.274</v>
       </c>
     </row>
     <row r="272">
@@ -13441,13 +13441,13 @@
         <v>0.513</v>
       </c>
       <c r="G272" t="n">
-        <v>0.78</v>
+        <v>0.66</v>
       </c>
       <c r="H272" t="n">
-        <v>2.03e-06</v>
+        <v>0.0137</v>
       </c>
       <c r="I272" t="n">
-        <v>1.62e-05</v>
+        <v>0.07290000000000001</v>
       </c>
     </row>
     <row r="273">
@@ -13478,13 +13478,13 @@
         <v>0.433</v>
       </c>
       <c r="G273" t="n">
-        <v>0.72</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="H273" t="n">
-        <v>7.67e-07</v>
+        <v>8.65e-06</v>
       </c>
       <c r="I273" t="n">
-        <v>1.23e-05</v>
+        <v>0.000138</v>
       </c>
     </row>
     <row r="274">
@@ -13515,10 +13515,10 @@
         <v>0.915</v>
       </c>
       <c r="G274" t="n">
-        <v>0.896</v>
+        <v>0.915</v>
       </c>
       <c r="H274" t="n">
-        <v>0.804</v>
+        <v>1</v>
       </c>
       <c r="I274" t="n">
         <v>1</v>
@@ -13552,13 +13552,13 @@
         <v>0.771</v>
       </c>
       <c r="G275" t="n">
-        <v>0.509</v>
+        <v>0.741</v>
       </c>
       <c r="H275" t="n">
-        <v>0.0152</v>
+        <v>1</v>
       </c>
       <c r="I275" t="n">
-        <v>0.07000000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="276">
@@ -13589,13 +13589,13 @@
         <v>0.711</v>
       </c>
       <c r="G276" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.846</v>
       </c>
       <c r="H276" t="n">
-        <v>0.404</v>
+        <v>0.245</v>
       </c>
       <c r="I276" t="n">
-        <v>0.924</v>
+        <v>0.5590000000000001</v>
       </c>
     </row>
     <row r="277">
@@ -13663,10 +13663,10 @@
         <v>0.962</v>
       </c>
       <c r="G278" t="n">
-        <v>0.964</v>
+        <v>0.986</v>
       </c>
       <c r="H278" t="n">
-        <v>1</v>
+        <v>0.622</v>
       </c>
       <c r="I278" t="n">
         <v>1</v>
@@ -13700,13 +13700,13 @@
         <v>0.875</v>
       </c>
       <c r="G279" t="n">
-        <v>0.975</v>
+        <v>1</v>
       </c>
       <c r="H279" t="n">
-        <v>0.0175</v>
+        <v>0.002</v>
       </c>
       <c r="I279" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.007979999999999999</v>
       </c>
     </row>
     <row r="280">
@@ -13737,13 +13737,13 @@
         <v>0.886</v>
       </c>
       <c r="G280" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.985</v>
       </c>
       <c r="H280" t="n">
-        <v>0.269</v>
+        <v>0.0228</v>
       </c>
       <c r="I280" t="n">
-        <v>0.716</v>
+        <v>0.0731</v>
       </c>
     </row>
     <row r="281">
@@ -13774,7 +13774,7 @@
         <v>0.4</v>
       </c>
       <c r="G281" t="n">
-        <v>0.444</v>
+        <v>0.667</v>
       </c>
       <c r="H281" t="n">
         <v>1</v>
@@ -13811,10 +13811,10 @@
         <v>0.963</v>
       </c>
       <c r="G282" t="n">
-        <v>0.958</v>
+        <v>0.985</v>
       </c>
       <c r="H282" t="n">
-        <v>1</v>
+        <v>0.626</v>
       </c>
       <c r="I282" t="n">
         <v>1</v>
@@ -13848,10 +13848,10 @@
         <v>0.98</v>
       </c>
       <c r="G283" t="n">
-        <v>0.956</v>
+        <v>0.982</v>
       </c>
       <c r="H283" t="n">
-        <v>0.634</v>
+        <v>1</v>
       </c>
       <c r="I283" t="n">
         <v>1</v>
@@ -13885,13 +13885,13 @@
         <v>0.863</v>
       </c>
       <c r="G284" t="n">
-        <v>0.889</v>
+        <v>0.945</v>
       </c>
       <c r="H284" t="n">
-        <v>0.641</v>
+        <v>0.156</v>
       </c>
       <c r="I284" t="n">
-        <v>1</v>
+        <v>0.415</v>
       </c>
     </row>
     <row r="285">
@@ -13922,13 +13922,13 @@
         <v>0.875</v>
       </c>
       <c r="G285" t="n">
-        <v>0.897</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="H285" t="n">
-        <v>0.766</v>
+        <v>0.487</v>
       </c>
       <c r="I285" t="n">
-        <v>1</v>
+        <v>0.973</v>
       </c>
     </row>
     <row r="286">
@@ -13959,7 +13959,7 @@
         <v>0.87</v>
       </c>
       <c r="G286" t="n">
-        <v>0.864</v>
+        <v>0.929</v>
       </c>
       <c r="H286" t="n">
         <v>1</v>
@@ -13996,13 +13996,13 @@
         <v>0.77</v>
       </c>
       <c r="G287" t="n">
-        <v>0.886</v>
+        <v>1</v>
       </c>
       <c r="H287" t="n">
-        <v>0.0804</v>
+        <v>7.68e-05</v>
       </c>
       <c r="I287" t="n">
-        <v>0.257</v>
+        <v>0.0011</v>
       </c>
     </row>
     <row r="288">
@@ -14033,13 +14033,13 @@
         <v>0.475</v>
       </c>
       <c r="G288" t="n">
-        <v>0.783</v>
+        <v>0.9</v>
       </c>
       <c r="H288" t="n">
-        <v>0.000103</v>
+        <v>0.000434</v>
       </c>
       <c r="I288" t="n">
-        <v>0.00165</v>
+        <v>0.00232</v>
       </c>
     </row>
     <row r="289">
@@ -14070,13 +14070,13 @@
         <v>0.365</v>
       </c>
       <c r="G289" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.923</v>
       </c>
       <c r="H289" t="n">
-        <v>0.0007739999999999999</v>
+        <v>0.000137</v>
       </c>
       <c r="I289" t="n">
-        <v>0.00619</v>
+        <v>0.0011</v>
       </c>
     </row>
     <row r="290">
@@ -14107,13 +14107,13 @@
         <v>0.735</v>
       </c>
       <c r="G290" t="n">
-        <v>0.931</v>
+        <v>0.951</v>
       </c>
       <c r="H290" t="n">
-        <v>0.000261</v>
+        <v>2.89e-05</v>
       </c>
       <c r="I290" t="n">
-        <v>0.00418</v>
+        <v>0.000154</v>
       </c>
     </row>
     <row r="291">
@@ -14144,13 +14144,13 @@
         <v>1</v>
       </c>
       <c r="G291" t="n">
-        <v>1</v>
+        <v>0.741</v>
       </c>
       <c r="H291" t="n">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="I291" t="n">
-        <v>1</v>
+        <v>0.0401</v>
       </c>
     </row>
     <row r="292">
@@ -14181,13 +14181,13 @@
         <v>0.964</v>
       </c>
       <c r="G292" t="n">
-        <v>0.964</v>
+        <v>0.786</v>
       </c>
       <c r="H292" t="n">
-        <v>1</v>
+        <v>0.101</v>
       </c>
       <c r="I292" t="n">
-        <v>1</v>
+        <v>0.231</v>
       </c>
     </row>
     <row r="293">
@@ -14218,13 +14218,13 @@
         <v>0.909</v>
       </c>
       <c r="G293" t="n">
-        <v>1</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="H293" t="n">
-        <v>0.488</v>
+        <v>0.132</v>
       </c>
       <c r="I293" t="n">
-        <v>0.735</v>
+        <v>0.265</v>
       </c>
     </row>
     <row r="294">
@@ -14255,13 +14255,13 @@
         <v>0.743</v>
       </c>
       <c r="G294" t="n">
-        <v>0.792</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="H294" t="n">
-        <v>0.506</v>
+        <v>0.437</v>
       </c>
       <c r="I294" t="n">
-        <v>0.735</v>
+        <v>0.636</v>
       </c>
     </row>
     <row r="295">
@@ -14292,13 +14292,13 @@
         <v>0.761</v>
       </c>
       <c r="G295" t="n">
-        <v>0.859</v>
+        <v>0.728</v>
       </c>
       <c r="H295" t="n">
-        <v>0.132</v>
+        <v>0.736</v>
       </c>
       <c r="I295" t="n">
-        <v>0.264</v>
+        <v>0.841</v>
       </c>
     </row>
     <row r="296">
@@ -14329,13 +14329,13 @@
         <v>0.824</v>
       </c>
       <c r="G296" t="n">
-        <v>0.929</v>
+        <v>0.753</v>
       </c>
       <c r="H296" t="n">
-        <v>0.0602</v>
+        <v>0.348</v>
       </c>
       <c r="I296" t="n">
-        <v>0.195</v>
+        <v>0.5570000000000001</v>
       </c>
     </row>
     <row r="297">
@@ -14366,13 +14366,13 @@
         <v>0.222</v>
       </c>
       <c r="G297" t="n">
-        <v>0.444</v>
+        <v>0.222</v>
       </c>
       <c r="H297" t="n">
-        <v>0.62</v>
+        <v>1</v>
       </c>
       <c r="I297" t="n">
-        <v>0.827</v>
+        <v>1</v>
       </c>
     </row>
     <row r="298">
@@ -14403,13 +14403,13 @@
         <v>0.619</v>
       </c>
       <c r="G298" t="n">
-        <v>0.73</v>
+        <v>0.532</v>
       </c>
       <c r="H298" t="n">
-        <v>0.08019999999999999</v>
+        <v>0.202</v>
       </c>
       <c r="I298" t="n">
-        <v>0.2</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="299">
@@ -14440,13 +14440,13 @@
         <v>0.617</v>
       </c>
       <c r="G299" t="n">
-        <v>0.802</v>
+        <v>0.667</v>
       </c>
       <c r="H299" t="n">
-        <v>0.0149</v>
+        <v>0.623</v>
       </c>
       <c r="I299" t="n">
-        <v>0.119</v>
+        <v>0.767</v>
       </c>
     </row>
     <row r="300">
@@ -14477,13 +14477,13 @@
         <v>0.75</v>
       </c>
       <c r="G300" t="n">
-        <v>0.783</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="H300" t="n">
-        <v>0.728</v>
+        <v>0.0126</v>
       </c>
       <c r="I300" t="n">
-        <v>0.896</v>
+        <v>0.0404</v>
       </c>
     </row>
     <row r="301">
@@ -14514,13 +14514,13 @@
         <v>0.6889999999999999</v>
       </c>
       <c r="G301" t="n">
-        <v>0.852</v>
+        <v>0.705</v>
       </c>
       <c r="H301" t="n">
-        <v>0.0515</v>
+        <v>1</v>
       </c>
       <c r="I301" t="n">
-        <v>0.195</v>
+        <v>1</v>
       </c>
     </row>
     <row r="302">
@@ -14551,13 +14551,13 @@
         <v>0.952</v>
       </c>
       <c r="G302" t="n">
-        <v>0.905</v>
+        <v>0.619</v>
       </c>
       <c r="H302" t="n">
-        <v>1</v>
+        <v>0.0205</v>
       </c>
       <c r="I302" t="n">
-        <v>1</v>
+        <v>0.0546</v>
       </c>
     </row>
     <row r="303">
@@ -14588,13 +14588,13 @@
         <v>0.781</v>
       </c>
       <c r="G303" t="n">
-        <v>0.849</v>
+        <v>0.726</v>
       </c>
       <c r="H303" t="n">
-        <v>0.394</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="I303" t="n">
-        <v>0.701</v>
+        <v>0.753</v>
       </c>
     </row>
     <row r="304">
@@ -14625,13 +14625,13 @@
         <v>0.851</v>
       </c>
       <c r="G304" t="n">
-        <v>0.701</v>
+        <v>0.269</v>
       </c>
       <c r="H304" t="n">
-        <v>0.061</v>
+        <v>8.54e-12</v>
       </c>
       <c r="I304" t="n">
-        <v>0.195</v>
+        <v>1.37e-10</v>
       </c>
     </row>
     <row r="305">
@@ -14662,13 +14662,13 @@
         <v>0.667</v>
       </c>
       <c r="G305" t="n">
-        <v>0.491</v>
+        <v>0.211</v>
       </c>
       <c r="H305" t="n">
-        <v>0.0873</v>
+        <v>1.56e-06</v>
       </c>
       <c r="I305" t="n">
-        <v>0.2</v>
+        <v>1.25e-05</v>
       </c>
     </row>
     <row r="306">
@@ -14699,13 +14699,13 @@
         <v>0.8149999999999999</v>
       </c>
       <c r="G306" t="n">
-        <v>0.913</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="H306" t="n">
-        <v>0.0046</v>
+        <v>0.000568</v>
       </c>
       <c r="I306" t="n">
-        <v>0.05</v>
+        <v>0.00908</v>
       </c>
     </row>
     <row r="307">
@@ -14736,13 +14736,13 @@
         <v>0.871</v>
       </c>
       <c r="G307" t="n">
-        <v>0.675</v>
+        <v>0.741</v>
       </c>
       <c r="H307" t="n">
-        <v>0.009379999999999999</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="I307" t="n">
-        <v>0.05</v>
+        <v>0.222</v>
       </c>
     </row>
     <row r="308">
@@ -14773,13 +14773,13 @@
         <v>0.8179999999999999</v>
       </c>
       <c r="G308" t="n">
-        <v>0.885</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="H308" t="n">
-        <v>0.328</v>
+        <v>1</v>
       </c>
       <c r="I308" t="n">
-        <v>0.438</v>
+        <v>1</v>
       </c>
     </row>
     <row r="309">
@@ -14810,13 +14810,13 @@
         <v>0.952</v>
       </c>
       <c r="G309" t="n">
-        <v>1</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="H309" t="n">
-        <v>0.236</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="I309" t="n">
-        <v>0.343</v>
+        <v>0.222</v>
       </c>
     </row>
     <row r="310">
@@ -14847,13 +14847,13 @@
         <v>0.838</v>
       </c>
       <c r="G310" t="n">
-        <v>0.87</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="H310" t="n">
-        <v>0.458</v>
+        <v>0.485</v>
       </c>
       <c r="I310" t="n">
-        <v>0.522</v>
+        <v>0.747</v>
       </c>
     </row>
     <row r="311">
@@ -14884,13 +14884,13 @@
         <v>0.8139999999999999</v>
       </c>
       <c r="G311" t="n">
-        <v>0.913</v>
+        <v>0.843</v>
       </c>
       <c r="H311" t="n">
-        <v>0.00769</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="I311" t="n">
-        <v>0.05</v>
+        <v>0.747</v>
       </c>
     </row>
     <row r="312">
@@ -14921,13 +14921,13 @@
         <v>0.854</v>
       </c>
       <c r="G312" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.853</v>
       </c>
       <c r="H312" t="n">
-        <v>0.0196</v>
+        <v>1</v>
       </c>
       <c r="I312" t="n">
-        <v>0.0552</v>
+        <v>1</v>
       </c>
     </row>
     <row r="313">
@@ -14958,13 +14958,13 @@
         <v>0.286</v>
       </c>
       <c r="G313" t="n">
-        <v>0.444</v>
+        <v>0.333</v>
       </c>
       <c r="H313" t="n">
-        <v>0.471</v>
+        <v>1</v>
       </c>
       <c r="I313" t="n">
-        <v>0.522</v>
+        <v>1</v>
       </c>
     </row>
     <row r="314">
@@ -14995,13 +14995,13 @@
         <v>0.754</v>
       </c>
       <c r="G314" t="n">
-        <v>0.829</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="H314" t="n">
-        <v>0.0576</v>
+        <v>0.181</v>
       </c>
       <c r="I314" t="n">
-        <v>0.102</v>
+        <v>0.361</v>
       </c>
     </row>
     <row r="315">
@@ -15032,13 +15032,13 @@
         <v>0.758</v>
       </c>
       <c r="G315" t="n">
-        <v>0.872</v>
+        <v>0.794</v>
       </c>
       <c r="H315" t="n">
-        <v>0.0136</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="I315" t="n">
-        <v>0.0543</v>
+        <v>0.747</v>
       </c>
     </row>
     <row r="316">
@@ -15069,13 +15069,13 @@
         <v>0.802</v>
       </c>
       <c r="G316" t="n">
-        <v>0.832</v>
+        <v>0.707</v>
       </c>
       <c r="H316" t="n">
-        <v>0.489</v>
+        <v>0.0504</v>
       </c>
       <c r="I316" t="n">
-        <v>0.522</v>
+        <v>0.222</v>
       </c>
     </row>
     <row r="317">
@@ -15106,13 +15106,13 @@
         <v>0.771</v>
       </c>
       <c r="G317" t="n">
-        <v>0.874</v>
+        <v>0.804</v>
       </c>
       <c r="H317" t="n">
-        <v>0.0545</v>
+        <v>0.619</v>
       </c>
       <c r="I317" t="n">
-        <v>0.102</v>
+        <v>0.762</v>
       </c>
     </row>
     <row r="318">
@@ -15143,13 +15143,13 @@
         <v>0.909</v>
       </c>
       <c r="G318" t="n">
-        <v>0.884</v>
+        <v>0.743</v>
       </c>
       <c r="H318" t="n">
-        <v>0.739</v>
+        <v>0.0675</v>
       </c>
       <c r="I318" t="n">
-        <v>0.739</v>
+        <v>0.222</v>
       </c>
     </row>
     <row r="319">
@@ -15180,13 +15180,13 @@
         <v>0.776</v>
       </c>
       <c r="G319" t="n">
-        <v>0.867</v>
+        <v>0.841</v>
       </c>
       <c r="H319" t="n">
-        <v>0.0472</v>
+        <v>0.219</v>
       </c>
       <c r="I319" t="n">
-        <v>0.102</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="320">
@@ -15217,13 +15217,13 @@
         <v>0.61</v>
       </c>
       <c r="G320" t="n">
-        <v>0.74</v>
+        <v>0.414</v>
       </c>
       <c r="H320" t="n">
-        <v>0.0207</v>
+        <v>0.00276</v>
       </c>
       <c r="I320" t="n">
-        <v>0.0552</v>
+        <v>0.0221</v>
       </c>
     </row>
     <row r="321">
@@ -15254,13 +15254,13 @@
         <v>0.472</v>
       </c>
       <c r="G321" t="n">
-        <v>0.571</v>
+        <v>0.343</v>
       </c>
       <c r="H321" t="n">
-        <v>0.126</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="I321" t="n">
-        <v>0.202</v>
+        <v>0.222</v>
       </c>
     </row>
     <row r="322">
@@ -24746,7 +24746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25118,41 +25118,41 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>98.1***</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>78.1</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>84.9</t>
+          <t>92.9</t>
         </is>
       </c>
     </row>
@@ -25163,41 +25163,41 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>77.1***</t>
+          <t>98.1***</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>78.3***</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>55.2</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>70.1</t>
+          <t>84.9</t>
         </is>
       </c>
     </row>
@@ -25208,86 +25208,86 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>69.7**</t>
+          <t>77.1***</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>68.3***</t>
+          <t>78.3***</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>55.2</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>70.1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Llama3.1-8B</t>
+          <t>Llama3.1-70B</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>93.1</t>
+          <t>36.5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>69.7**</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>68.3***</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>66.7</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>100.0***</t>
+          <t>49.1</t>
         </is>
       </c>
     </row>
@@ -25298,41 +25298,41 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>84.9</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>60.9</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>79.3***</t>
+          <t>100.0***</t>
         </is>
       </c>
     </row>
@@ -25343,41 +25343,41 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>96.4</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>84.9</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>62.4</t>
+          <t>60.9</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>97.6***</t>
+          <t>79.3***</t>
         </is>
       </c>
     </row>
@@ -25388,41 +25388,41 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>97.1</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>96.4</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>62.4</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>78.6***</t>
+          <t>97.6***</t>
         </is>
       </c>
     </row>
@@ -25433,41 +25433,41 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>97.1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>92.3</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.1</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>91.8***</t>
+          <t>78.6***</t>
         </is>
       </c>
     </row>
@@ -25478,39 +25478,84 @@
         </is>
       </c>
       <c r="B17" t="n">
+        <v>12</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>85.7</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>92.3</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>69.1</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>91.8***</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
         <v>14</v>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>76.1</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>88.9</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>65.1</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>74.0</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>65.8</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>97.3***</t>
         </is>

--- a/eval/results/statistical_tests_full150.xlsx
+++ b/eval/results/statistical_tests_full150.xlsx
@@ -519,7 +519,7 @@
         <v>0.07190000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0072</v>
       </c>
     </row>
     <row r="3">
@@ -559,7 +559,7 @@
         <v>0.07190000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>0.008370000000000001</v>
+        <v>0.00957</v>
       </c>
     </row>
     <row r="4">
@@ -599,7 +599,7 @@
         <v>0.0842</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0225</v>
+        <v>0.0262</v>
       </c>
     </row>
     <row r="5">
@@ -639,7 +639,7 @@
         <v>0.0842</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0437</v>
+        <v>0.0486</v>
       </c>
     </row>
     <row r="6">
@@ -679,7 +679,7 @@
         <v>0.103</v>
       </c>
       <c r="J6" t="n">
-        <v>0.446</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="7">
@@ -719,7 +719,7 @@
         <v>0.103</v>
       </c>
       <c r="J7" t="n">
-        <v>0.44</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="8">
@@ -759,7 +759,7 @@
         <v>0.0931</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0259</v>
+        <v>0.032</v>
       </c>
     </row>
     <row r="9">
@@ -799,7 +799,7 @@
         <v>0.0931</v>
       </c>
       <c r="J9" t="n">
-        <v>0.008370000000000001</v>
+        <v>0.00957</v>
       </c>
     </row>
     <row r="10">
@@ -839,7 +839,7 @@
         <v>0.11</v>
       </c>
       <c r="J10" t="n">
-        <v>0.242</v>
+        <v>0.211</v>
       </c>
     </row>
     <row r="11">
@@ -879,7 +879,7 @@
         <v>0.11</v>
       </c>
       <c r="J11" t="n">
-        <v>0.505</v>
+        <v>0.442</v>
       </c>
     </row>
     <row r="12">
@@ -919,7 +919,7 @@
         <v>0.0796</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0225</v>
+        <v>0.0262</v>
       </c>
     </row>
     <row r="13">
@@ -959,7 +959,7 @@
         <v>0.0796</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0219</v>
+        <v>0.0216</v>
       </c>
     </row>
     <row r="14">
@@ -999,7 +999,7 @@
         <v>0.116</v>
       </c>
       <c r="J14" t="n">
-        <v>0.744</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="15">
@@ -1039,7 +1039,7 @@
         <v>0.116</v>
       </c>
       <c r="J15" t="n">
-        <v>0.842</v>
+        <v>0.823</v>
       </c>
     </row>
     <row r="16">
@@ -1079,7 +1079,7 @@
         <v>0.107</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0225</v>
+        <v>0.0223</v>
       </c>
     </row>
     <row r="17">
@@ -1199,7 +1199,7 @@
         <v>0.11</v>
       </c>
       <c r="J19" t="n">
-        <v>0.842</v>
+        <v>0.866</v>
       </c>
     </row>
     <row r="20">
@@ -1239,7 +1239,7 @@
         <v>0.0584</v>
       </c>
       <c r="J20" t="n">
-        <v>0.116</v>
+        <v>0.141</v>
       </c>
     </row>
     <row r="21">
@@ -1279,7 +1279,7 @@
         <v>0.0584</v>
       </c>
       <c r="J21" t="n">
-        <v>0.249</v>
+        <v>0.265</v>
       </c>
     </row>
     <row r="22">
@@ -1319,7 +1319,7 @@
         <v>0.11</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.832</v>
       </c>
     </row>
     <row r="23">
@@ -1359,7 +1359,7 @@
         <v>0.11</v>
       </c>
       <c r="J23" t="n">
-        <v>0.46</v>
+        <v>0.502</v>
       </c>
     </row>
     <row r="24">
@@ -1399,7 +1399,7 @@
         <v>0.191</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0457</v>
+        <v>0.0481</v>
       </c>
     </row>
     <row r="25">
@@ -1439,7 +1439,7 @@
         <v>0.191</v>
       </c>
       <c r="J25" t="n">
-        <v>0.00756</v>
+        <v>0.0134</v>
       </c>
     </row>
     <row r="26">
@@ -1479,7 +1479,7 @@
         <v>0.0954</v>
       </c>
       <c r="J26" t="n">
-        <v>0.00402</v>
+        <v>0.0072</v>
       </c>
     </row>
     <row r="27">
@@ -1519,7 +1519,7 @@
         <v>0.0954</v>
       </c>
       <c r="J27" t="n">
-        <v>0.00444</v>
+        <v>0.00957</v>
       </c>
     </row>
     <row r="28">
@@ -1559,7 +1559,7 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="J28" t="n">
-        <v>0.0215</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="29">
@@ -1599,7 +1599,7 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="J29" t="n">
-        <v>0.00537</v>
+        <v>0.00957</v>
       </c>
     </row>
     <row r="30">
@@ -1639,7 +1639,7 @@
         <v>0.164</v>
       </c>
       <c r="J30" t="n">
-        <v>0.184</v>
+        <v>0.211</v>
       </c>
     </row>
     <row r="31">
@@ -1679,7 +1679,7 @@
         <v>0.164</v>
       </c>
       <c r="J31" t="n">
-        <v>0.0888</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="32">
@@ -1719,7 +1719,7 @@
         <v>0.172</v>
       </c>
       <c r="J32" t="n">
-        <v>0.0457</v>
+        <v>0.0481</v>
       </c>
     </row>
     <row r="33">
@@ -1759,7 +1759,7 @@
         <v>0.172</v>
       </c>
       <c r="J33" t="n">
-        <v>0.0641</v>
+        <v>0.0675</v>
       </c>
     </row>
     <row r="34">
@@ -1799,7 +1799,7 @@
         <v>0.226</v>
       </c>
       <c r="J34" t="n">
-        <v>0.0771</v>
+        <v>0.0925</v>
       </c>
     </row>
     <row r="35">
@@ -1839,7 +1839,7 @@
         <v>0.226</v>
       </c>
       <c r="J35" t="n">
-        <v>0.0702</v>
+        <v>0.0842</v>
       </c>
     </row>
     <row r="36">
@@ -1879,7 +1879,7 @@
         <v>0.205</v>
       </c>
       <c r="J36" t="n">
-        <v>0.000521</v>
+        <v>0.00104</v>
       </c>
     </row>
     <row r="37">
@@ -1919,7 +1919,7 @@
         <v>0.205</v>
       </c>
       <c r="J37" t="n">
-        <v>0.00138</v>
+        <v>0.00275</v>
       </c>
     </row>
     <row r="38">
@@ -1959,7 +1959,7 @@
         <v>0.137</v>
       </c>
       <c r="J38" t="n">
-        <v>0.023</v>
+        <v>0.0262</v>
       </c>
     </row>
     <row r="39">
@@ -1999,7 +1999,7 @@
         <v>0.137</v>
       </c>
       <c r="J39" t="n">
-        <v>0.0198</v>
+        <v>0.0233</v>
       </c>
     </row>
     <row r="40">
@@ -2039,7 +2039,7 @@
         <v>0.185</v>
       </c>
       <c r="J40" t="n">
-        <v>0.124</v>
+        <v>0.158</v>
       </c>
     </row>
     <row r="41">
@@ -2079,7 +2079,7 @@
         <v>0.185</v>
       </c>
       <c r="J41" t="n">
-        <v>0.144</v>
+        <v>0.161</v>
       </c>
     </row>
     <row r="42">
@@ -2119,7 +2119,7 @@
         <v>0.223</v>
       </c>
       <c r="J42" t="n">
-        <v>0.242</v>
+        <v>0.281</v>
       </c>
     </row>
     <row r="43">
@@ -2159,7 +2159,7 @@
         <v>0.223</v>
       </c>
       <c r="J43" t="n">
-        <v>0.221</v>
+        <v>0.265</v>
       </c>
     </row>
     <row r="44">
@@ -2199,7 +2199,7 @@
         <v>0.163</v>
       </c>
       <c r="J44" t="n">
-        <v>0.124</v>
+        <v>0.158</v>
       </c>
     </row>
     <row r="45">
@@ -2239,7 +2239,7 @@
         <v>0.163</v>
       </c>
       <c r="J45" t="n">
-        <v>0.175</v>
+        <v>0.216</v>
       </c>
     </row>
     <row r="46">
@@ -2279,7 +2279,7 @@
         <v>0.211</v>
       </c>
       <c r="J46" t="n">
-        <v>0.0236</v>
+        <v>0.0314</v>
       </c>
     </row>
     <row r="47">
@@ -2319,7 +2319,7 @@
         <v>0.211</v>
       </c>
       <c r="J47" t="n">
-        <v>0.0198</v>
+        <v>0.0216</v>
       </c>
     </row>
     <row r="48">
@@ -2359,7 +2359,7 @@
         <v>0.162</v>
       </c>
       <c r="J48" t="n">
-        <v>0.0835</v>
+        <v>0.0955</v>
       </c>
     </row>
     <row r="49">
@@ -2399,7 +2399,7 @@
         <v>0.162</v>
       </c>
       <c r="J49" t="n">
-        <v>0.0833</v>
+        <v>0.0944</v>
       </c>
     </row>
     <row r="50">
@@ -2439,7 +2439,7 @@
         <v>0.147</v>
       </c>
       <c r="J50" t="n">
-        <v>0.00271</v>
+        <v>0.0072</v>
       </c>
     </row>
     <row r="51">
@@ -2479,7 +2479,7 @@
         <v>0.147</v>
       </c>
       <c r="J51" t="n">
-        <v>0.017</v>
+        <v>0.0136</v>
       </c>
     </row>
     <row r="52">
@@ -2519,7 +2519,7 @@
         <v>0.163</v>
       </c>
       <c r="J52" t="n">
-        <v>0.00771</v>
+        <v>0.0142</v>
       </c>
     </row>
     <row r="53">
@@ -2599,7 +2599,7 @@
         <v>0.174</v>
       </c>
       <c r="J54" t="n">
-        <v>0.000275</v>
+        <v>0.00104</v>
       </c>
     </row>
     <row r="55">
@@ -2639,7 +2639,7 @@
         <v>0.174</v>
       </c>
       <c r="J55" t="n">
-        <v>0.000549</v>
+        <v>0.0022</v>
       </c>
     </row>
     <row r="56">
@@ -2759,7 +2759,7 @@
         <v>0.149</v>
       </c>
       <c r="J58" t="n">
-        <v>0.248</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="59">
@@ -2799,7 +2799,7 @@
         <v>0.149</v>
       </c>
       <c r="J59" t="n">
-        <v>0.104</v>
+        <v>0.0944</v>
       </c>
     </row>
     <row r="60">
@@ -2839,7 +2839,7 @@
         <v>0.188</v>
       </c>
       <c r="J60" t="n">
-        <v>0.529</v>
+        <v>0.577</v>
       </c>
     </row>
     <row r="61">
@@ -2919,7 +2919,7 @@
         <v>0.137</v>
       </c>
       <c r="J62" t="n">
-        <v>0.034</v>
+        <v>0.032</v>
       </c>
     </row>
     <row r="63">
@@ -2959,7 +2959,7 @@
         <v>0.137</v>
       </c>
       <c r="J63" t="n">
-        <v>0.0171</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="64">
@@ -2999,7 +2999,7 @@
         <v>0.186</v>
       </c>
       <c r="J64" t="n">
-        <v>0.176</v>
+        <v>0.162</v>
       </c>
     </row>
     <row r="65">
@@ -3039,7 +3039,7 @@
         <v>0.186</v>
       </c>
       <c r="J65" t="n">
-        <v>0.225</v>
+        <v>0.233</v>
       </c>
     </row>
     <row r="66">
@@ -3079,7 +3079,7 @@
         <v>0.144</v>
       </c>
       <c r="J66" t="n">
-        <v>0.0229</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="67">
@@ -3119,7 +3119,7 @@
         <v>0.144</v>
       </c>
       <c r="J67" t="n">
-        <v>0.0171</v>
+        <v>0.0192</v>
       </c>
     </row>
     <row r="68">
@@ -3159,7 +3159,7 @@
         <v>0.149</v>
       </c>
       <c r="J68" t="n">
-        <v>0.161</v>
+        <v>0.141</v>
       </c>
     </row>
     <row r="69">
@@ -3239,7 +3239,7 @@
         <v>0.137</v>
       </c>
       <c r="J70" t="n">
-        <v>0.0145</v>
+        <v>0.0142</v>
       </c>
     </row>
     <row r="71">
@@ -3279,7 +3279,7 @@
         <v>0.137</v>
       </c>
       <c r="J71" t="n">
-        <v>0.0109</v>
+        <v>0.00957</v>
       </c>
     </row>
     <row r="72">
@@ -3319,7 +3319,7 @@
         <v>0.175</v>
       </c>
       <c r="J72" t="n">
-        <v>0.27</v>
+        <v>0.281</v>
       </c>
     </row>
     <row r="73">
@@ -3359,7 +3359,7 @@
         <v>0.175</v>
       </c>
       <c r="J73" t="n">
-        <v>0.237</v>
+        <v>0.265</v>
       </c>
     </row>
   </sheetData>

--- a/eval/results/statistical_tests_full150.xlsx
+++ b/eval/results/statistical_tests_full150.xlsx
@@ -3457,7 +3457,7 @@
         <v>0.1</v>
       </c>
       <c r="I2" t="n">
-        <v>0.229</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="3">
@@ -3494,7 +3494,7 @@
         <v>8.69e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00139</v>
+        <v>0.000782</v>
       </c>
     </row>
     <row r="4">
@@ -3642,7 +3642,7 @@
         <v>0.00911</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0292</v>
+        <v>0.0473</v>
       </c>
     </row>
     <row r="8">
@@ -3679,7 +3679,7 @@
         <v>0.0911</v>
       </c>
       <c r="I8" t="n">
-        <v>0.229</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="9">
@@ -3753,7 +3753,7 @@
         <v>0.166</v>
       </c>
       <c r="I10" t="n">
-        <v>0.331</v>
+        <v>0.373</v>
       </c>
     </row>
     <row r="11">
@@ -3790,7 +3790,7 @@
         <v>0.737</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0.879</v>
       </c>
     </row>
     <row r="12">
@@ -3827,7 +3827,7 @@
         <v>0.00532</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0213</v>
+        <v>0.0239</v>
       </c>
     </row>
     <row r="13">
@@ -3864,7 +3864,7 @@
         <v>0.575</v>
       </c>
       <c r="I13" t="n">
-        <v>0.921</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -3938,7 +3938,7 @@
         <v>0.461</v>
       </c>
       <c r="I15" t="n">
-        <v>0.819</v>
+        <v>0.744</v>
       </c>
     </row>
     <row r="16">
@@ -3975,7 +3975,7 @@
         <v>0.000507</v>
       </c>
       <c r="I16" t="n">
-        <v>0.00406</v>
+        <v>0.00152</v>
       </c>
     </row>
     <row r="17">
@@ -4012,7 +4012,7 @@
         <v>0.000809</v>
       </c>
       <c r="I17" t="n">
-        <v>0.00431</v>
+        <v>0.00182</v>
       </c>
     </row>
     <row r="18">
@@ -4086,7 +4086,7 @@
         <v>0.0005820000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>0.00932</v>
+        <v>0.00524</v>
       </c>
     </row>
     <row r="20">
@@ -4123,7 +4123,7 @@
         <v>0.492</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>0.738</v>
       </c>
     </row>
     <row r="21">
@@ -4234,7 +4234,7 @@
         <v>0.699</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0.699</v>
       </c>
     </row>
     <row r="24">
@@ -4271,7 +4271,7 @@
         <v>0.729</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>0.754</v>
       </c>
     </row>
     <row r="25">
@@ -4345,7 +4345,7 @@
         <v>0.229</v>
       </c>
       <c r="I26" t="n">
-        <v>0.734</v>
+        <v>0.858</v>
       </c>
     </row>
     <row r="27">
@@ -4419,7 +4419,7 @@
         <v>0.5590000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>0.721</v>
       </c>
     </row>
     <row r="29">
@@ -4456,7 +4456,7 @@
         <v>0.294</v>
       </c>
       <c r="I29" t="n">
-        <v>0.784</v>
+        <v>0.529</v>
       </c>
     </row>
     <row r="30">
@@ -4530,7 +4530,7 @@
         <v>0.185</v>
       </c>
       <c r="I31" t="n">
-        <v>0.734</v>
+        <v>0.238</v>
       </c>
     </row>
     <row r="32">
@@ -4567,7 +4567,7 @@
         <v>0.00339</v>
       </c>
       <c r="I32" t="n">
-        <v>0.0272</v>
+        <v>0.00763</v>
       </c>
     </row>
     <row r="33">
@@ -4604,7 +4604,7 @@
         <v>0.00637</v>
       </c>
       <c r="I33" t="n">
-        <v>0.034</v>
+        <v>0.0143</v>
       </c>
     </row>
     <row r="34">
@@ -4641,7 +4641,7 @@
         <v>0.0974</v>
       </c>
       <c r="I34" t="n">
-        <v>0.195</v>
+        <v>0.175</v>
       </c>
     </row>
     <row r="35">
@@ -4678,7 +4678,7 @@
         <v>0.491</v>
       </c>
       <c r="I35" t="n">
-        <v>0.785</v>
+        <v>0.736</v>
       </c>
     </row>
     <row r="36">
@@ -4826,7 +4826,7 @@
         <v>0.000433</v>
       </c>
       <c r="I39" t="n">
-        <v>0.00694</v>
+        <v>0.000974</v>
       </c>
     </row>
     <row r="40">
@@ -4863,7 +4863,7 @@
         <v>0.0141</v>
       </c>
       <c r="I40" t="n">
-        <v>0.0563</v>
+        <v>0.0423</v>
       </c>
     </row>
     <row r="41">
@@ -4937,7 +4937,7 @@
         <v>0.0447</v>
       </c>
       <c r="I42" t="n">
-        <v>0.119</v>
+        <v>0.134</v>
       </c>
     </row>
     <row r="43">
@@ -4974,7 +4974,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>0.776</v>
       </c>
     </row>
     <row r="44">
@@ -5011,7 +5011,7 @@
         <v>0.00195</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0156</v>
+        <v>0.00877</v>
       </c>
     </row>
     <row r="45">
@@ -5048,7 +5048,7 @@
         <v>0.0625</v>
       </c>
       <c r="I45" t="n">
-        <v>0.143</v>
+        <v>0.188</v>
       </c>
     </row>
     <row r="46">
@@ -5122,7 +5122,7 @@
         <v>0.0216</v>
       </c>
       <c r="I47" t="n">
-        <v>0.06909999999999999</v>
+        <v>0.09719999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -5159,7 +5159,7 @@
         <v>0.155</v>
       </c>
       <c r="I48" t="n">
-        <v>0.276</v>
+        <v>0.279</v>
       </c>
     </row>
     <row r="49">
@@ -5196,7 +5196,7 @@
         <v>0.0138</v>
       </c>
       <c r="I49" t="n">
-        <v>0.0563</v>
+        <v>0.0414</v>
       </c>
     </row>
     <row r="50">
@@ -5233,7 +5233,7 @@
         <v>0.0728</v>
       </c>
       <c r="I50" t="n">
-        <v>0.146</v>
+        <v>0.164</v>
       </c>
     </row>
     <row r="51">
@@ -5270,7 +5270,7 @@
         <v>0.00158</v>
       </c>
       <c r="I51" t="n">
-        <v>0.00634</v>
+        <v>0.00779</v>
       </c>
     </row>
     <row r="52">
@@ -5381,7 +5381,7 @@
         <v>0.883</v>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>0.993</v>
       </c>
     </row>
     <row r="55">
@@ -5418,7 +5418,7 @@
         <v>0.00202</v>
       </c>
       <c r="I55" t="n">
-        <v>0.00645</v>
+        <v>0.009090000000000001</v>
       </c>
     </row>
     <row r="56">
@@ -5455,7 +5455,7 @@
         <v>0.0404</v>
       </c>
       <c r="I56" t="n">
-        <v>0.108</v>
+        <v>0.182</v>
       </c>
     </row>
     <row r="57">
@@ -5529,7 +5529,7 @@
         <v>0.058</v>
       </c>
       <c r="I58" t="n">
-        <v>0.133</v>
+        <v>0.131</v>
       </c>
     </row>
     <row r="59">
@@ -5566,7 +5566,7 @@
         <v>0.616</v>
       </c>
       <c r="I59" t="n">
-        <v>0.897</v>
+        <v>0.728</v>
       </c>
     </row>
     <row r="60">
@@ -5603,7 +5603,7 @@
         <v>0.000901</v>
       </c>
       <c r="I60" t="n">
-        <v>0.00634</v>
+        <v>0.00405</v>
       </c>
     </row>
     <row r="61">
@@ -5640,7 +5640,7 @@
         <v>0.34</v>
       </c>
       <c r="I61" t="n">
-        <v>0.544</v>
+        <v>0.765</v>
       </c>
     </row>
     <row r="62">
@@ -5714,7 +5714,7 @@
         <v>0.2</v>
       </c>
       <c r="I63" t="n">
-        <v>0.356</v>
+        <v>0.493</v>
       </c>
     </row>
     <row r="64">
@@ -5751,7 +5751,7 @@
         <v>0.0012</v>
       </c>
       <c r="I64" t="n">
-        <v>0.00634</v>
+        <v>0.0108</v>
       </c>
     </row>
     <row r="65">
@@ -5788,7 +5788,7 @@
         <v>0.000152</v>
       </c>
       <c r="I65" t="n">
-        <v>0.00243</v>
+        <v>0.00137</v>
       </c>
     </row>
     <row r="66">
@@ -5825,7 +5825,7 @@
         <v>0.06370000000000001</v>
       </c>
       <c r="I66" t="n">
-        <v>0.255</v>
+        <v>0.143</v>
       </c>
     </row>
     <row r="67">
@@ -5862,7 +5862,7 @@
         <v>0.000683</v>
       </c>
       <c r="I67" t="n">
-        <v>0.00546</v>
+        <v>0.00205</v>
       </c>
     </row>
     <row r="68">
@@ -5899,7 +5899,7 @@
         <v>0.723</v>
       </c>
       <c r="I68" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -6010,7 +6010,7 @@
         <v>0.124</v>
       </c>
       <c r="I71" t="n">
-        <v>0.396</v>
+        <v>0.279</v>
       </c>
     </row>
     <row r="72">
@@ -6047,7 +6047,7 @@
         <v>0.483</v>
       </c>
       <c r="I72" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="73">
@@ -6084,7 +6084,7 @@
         <v>0.572</v>
       </c>
       <c r="I73" t="n">
-        <v>0.833</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -6121,7 +6121,7 @@
         <v>0.04</v>
       </c>
       <c r="I74" t="n">
-        <v>0.213</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="75">
@@ -6158,7 +6158,7 @@
         <v>0.386</v>
       </c>
       <c r="I75" t="n">
-        <v>0.771</v>
+        <v>0.695</v>
       </c>
     </row>
     <row r="76">
@@ -6195,7 +6195,7 @@
         <v>0.000595</v>
       </c>
       <c r="I76" t="n">
-        <v>0.00546</v>
+        <v>0.00536</v>
       </c>
     </row>
     <row r="77">
@@ -6269,7 +6269,7 @@
         <v>0.723</v>
       </c>
       <c r="I78" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -6306,7 +6306,7 @@
         <v>0.51</v>
       </c>
       <c r="I79" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.744</v>
       </c>
     </row>
     <row r="80">
@@ -6343,7 +6343,7 @@
         <v>0.247</v>
       </c>
       <c r="I80" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="81">
@@ -6380,7 +6380,7 @@
         <v>0.222</v>
       </c>
       <c r="I81" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.285</v>
       </c>
     </row>
     <row r="82">
@@ -6417,7 +6417,7 @@
         <v>0.584</v>
       </c>
       <c r="I82" t="n">
-        <v>0.849</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -6454,7 +6454,7 @@
         <v>0.00324</v>
       </c>
       <c r="I83" t="n">
-        <v>0.0375</v>
+        <v>0.0146</v>
       </c>
     </row>
     <row r="84">
@@ -6491,7 +6491,7 @@
         <v>0.672</v>
       </c>
       <c r="I84" t="n">
-        <v>0.887</v>
+        <v>0.864</v>
       </c>
     </row>
     <row r="85">
@@ -6565,7 +6565,7 @@
         <v>0.721</v>
       </c>
       <c r="I86" t="n">
-        <v>0.887</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
@@ -6602,7 +6602,7 @@
         <v>0.07530000000000001</v>
       </c>
       <c r="I87" t="n">
-        <v>0.402</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="88">
@@ -6639,7 +6639,7 @@
         <v>0.228</v>
       </c>
       <c r="I88" t="n">
-        <v>0.609</v>
+        <v>0.404</v>
       </c>
     </row>
     <row r="89">
@@ -6676,7 +6676,7 @@
         <v>0.545</v>
       </c>
       <c r="I89" t="n">
-        <v>0.849</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -6713,7 +6713,7 @@
         <v>0.389</v>
       </c>
       <c r="I90" t="n">
-        <v>0.778</v>
+        <v>0.858</v>
       </c>
     </row>
     <row r="91">
@@ -6787,7 +6787,7 @@
         <v>0.574</v>
       </c>
       <c r="I92" t="n">
-        <v>0.849</v>
+        <v>0.721</v>
       </c>
     </row>
     <row r="93">
@@ -6824,7 +6824,7 @@
         <v>0.108</v>
       </c>
       <c r="I93" t="n">
-        <v>0.404</v>
+        <v>0.279</v>
       </c>
     </row>
     <row r="94">
@@ -6898,7 +6898,7 @@
         <v>0.00468</v>
       </c>
       <c r="I95" t="n">
-        <v>0.0375</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="96">
@@ -6935,7 +6935,7 @@
         <v>0.126</v>
       </c>
       <c r="I96" t="n">
-        <v>0.404</v>
+        <v>0.189</v>
       </c>
     </row>
     <row r="97">
@@ -6972,7 +6972,7 @@
         <v>0.288</v>
       </c>
       <c r="I97" t="n">
-        <v>0.658</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="98">
@@ -7009,7 +7009,7 @@
         <v>0.0515</v>
       </c>
       <c r="I98" t="n">
-        <v>0.137</v>
+        <v>0.116</v>
       </c>
     </row>
     <row r="99">
@@ -7046,7 +7046,7 @@
         <v>0.236</v>
       </c>
       <c r="I99" t="n">
-        <v>0.531</v>
+        <v>0.425</v>
       </c>
     </row>
     <row r="100">
@@ -7157,7 +7157,7 @@
         <v>0.735</v>
       </c>
       <c r="I102" t="n">
-        <v>0.981</v>
+        <v>0.945</v>
       </c>
     </row>
     <row r="103">
@@ -7194,7 +7194,7 @@
         <v>0.000433</v>
       </c>
       <c r="I103" t="n">
-        <v>0.00347</v>
+        <v>0.000974</v>
       </c>
     </row>
     <row r="104">
@@ -7231,7 +7231,7 @@
         <v>0.0288</v>
       </c>
       <c r="I104" t="n">
-        <v>0.115</v>
+        <v>0.0648</v>
       </c>
     </row>
     <row r="105">
@@ -7268,7 +7268,7 @@
         <v>0.637</v>
       </c>
       <c r="I105" t="n">
-        <v>0.927</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -7305,7 +7305,7 @@
         <v>0.00991</v>
       </c>
       <c r="I106" t="n">
-        <v>0.0528</v>
+        <v>0.0446</v>
       </c>
     </row>
     <row r="107">
@@ -7342,7 +7342,7 @@
         <v>0.299</v>
       </c>
       <c r="I107" t="n">
-        <v>0.531</v>
+        <v>0.538</v>
       </c>
     </row>
     <row r="108">
@@ -7379,7 +7379,7 @@
         <v>4.79e-05</v>
       </c>
       <c r="I108" t="n">
-        <v>0.000766</v>
+        <v>0.000431</v>
       </c>
     </row>
     <row r="109">
@@ -7416,7 +7416,7 @@
         <v>0.269</v>
       </c>
       <c r="I109" t="n">
-        <v>0.531</v>
+        <v>0.484</v>
       </c>
     </row>
     <row r="110">
@@ -7490,7 +7490,7 @@
         <v>0.0429</v>
       </c>
       <c r="I111" t="n">
-        <v>0.137</v>
+        <v>0.129</v>
       </c>
     </row>
     <row r="112">
@@ -7527,7 +7527,7 @@
         <v>0.581</v>
       </c>
       <c r="I112" t="n">
-        <v>0.927</v>
+        <v>0.581</v>
       </c>
     </row>
     <row r="113">
@@ -7564,7 +7564,7 @@
         <v>0.851</v>
       </c>
       <c r="I113" t="n">
-        <v>1</v>
+        <v>0.957</v>
       </c>
     </row>
     <row r="114">
@@ -7601,7 +7601,7 @@
         <v>0.0449</v>
       </c>
       <c r="I114" t="n">
-        <v>0.144</v>
+        <v>0.135</v>
       </c>
     </row>
     <row r="115">
@@ -7638,7 +7638,7 @@
         <v>0.008710000000000001</v>
       </c>
       <c r="I115" t="n">
-        <v>0.0571</v>
+        <v>0.0211</v>
       </c>
     </row>
     <row r="116">
@@ -7675,7 +7675,7 @@
         <v>0.717</v>
       </c>
       <c r="I116" t="n">
-        <v>0.882</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
@@ -7712,7 +7712,7 @@
         <v>0.494</v>
       </c>
       <c r="I117" t="n">
-        <v>0.791</v>
+        <v>0.889</v>
       </c>
     </row>
     <row r="118">
@@ -7749,7 +7749,7 @@
         <v>0.882</v>
       </c>
       <c r="I118" t="n">
-        <v>0.882</v>
+        <v>0.993</v>
       </c>
     </row>
     <row r="119">
@@ -7786,7 +7786,7 @@
         <v>0.0225</v>
       </c>
       <c r="I119" t="n">
-        <v>0.08989999999999999</v>
+        <v>0.0506</v>
       </c>
     </row>
     <row r="120">
@@ -7823,7 +7823,7 @@
         <v>0.294</v>
       </c>
       <c r="I120" t="n">
-        <v>0.585</v>
+        <v>0.482</v>
       </c>
     </row>
     <row r="121">
@@ -7860,7 +7860,7 @@
         <v>0.272</v>
       </c>
       <c r="I121" t="n">
-        <v>0.585</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122">
@@ -7897,7 +7897,7 @@
         <v>0.0107</v>
       </c>
       <c r="I122" t="n">
-        <v>0.0571</v>
+        <v>0.0481</v>
       </c>
     </row>
     <row r="123">
@@ -7934,7 +7934,7 @@
         <v>0.299</v>
       </c>
       <c r="I123" t="n">
-        <v>0.585</v>
+        <v>0.538</v>
       </c>
     </row>
     <row r="124">
@@ -7971,7 +7971,7 @@
         <v>3.8e-05</v>
       </c>
       <c r="I124" t="n">
-        <v>0.000608</v>
+        <v>0.000342</v>
       </c>
     </row>
     <row r="125">
@@ -8008,7 +8008,7 @@
         <v>0.859</v>
       </c>
       <c r="I125" t="n">
-        <v>0.882</v>
+        <v>0.872</v>
       </c>
     </row>
     <row r="126">
@@ -8045,7 +8045,7 @@
         <v>0.714</v>
       </c>
       <c r="I126" t="n">
-        <v>0.882</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127">
@@ -8082,7 +8082,7 @@
         <v>0.869</v>
       </c>
       <c r="I127" t="n">
-        <v>0.882</v>
+        <v>0.978</v>
       </c>
     </row>
     <row r="128">
@@ -8119,7 +8119,7 @@
         <v>0.598</v>
       </c>
       <c r="I128" t="n">
-        <v>0.87</v>
+        <v>0.793</v>
       </c>
     </row>
     <row r="129">
@@ -8156,7 +8156,7 @@
         <v>0.329</v>
       </c>
       <c r="I129" t="n">
-        <v>0.585</v>
+        <v>0.592</v>
       </c>
     </row>
     <row r="130">
@@ -8193,7 +8193,7 @@
         <v>0.868</v>
       </c>
       <c r="I130" t="n">
-        <v>1</v>
+        <v>0.868</v>
       </c>
     </row>
     <row r="131">
@@ -8230,7 +8230,7 @@
         <v>0.251</v>
       </c>
       <c r="I131" t="n">
-        <v>1</v>
+        <v>0.301</v>
       </c>
     </row>
     <row r="132">
@@ -8378,7 +8378,7 @@
         <v>0.371</v>
       </c>
       <c r="I135" t="n">
-        <v>1</v>
+        <v>0.424</v>
       </c>
     </row>
     <row r="136">
@@ -8415,7 +8415,7 @@
         <v>0.732</v>
       </c>
       <c r="I136" t="n">
-        <v>1</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="137">
@@ -8452,7 +8452,7 @@
         <v>0.198</v>
       </c>
       <c r="I137" t="n">
-        <v>1</v>
+        <v>0.891</v>
       </c>
     </row>
     <row r="138">
@@ -8489,7 +8489,7 @@
         <v>0.457</v>
       </c>
       <c r="I138" t="n">
-        <v>1</v>
+        <v>0.536</v>
       </c>
     </row>
     <row r="139">
@@ -8526,7 +8526,7 @@
         <v>0.868</v>
       </c>
       <c r="I139" t="n">
-        <v>1</v>
+        <v>0.879</v>
       </c>
     </row>
     <row r="140">
@@ -8563,7 +8563,7 @@
         <v>0.186</v>
       </c>
       <c r="I140" t="n">
-        <v>1</v>
+        <v>0.335</v>
       </c>
     </row>
     <row r="141">
@@ -8711,7 +8711,7 @@
         <v>0.706</v>
       </c>
       <c r="I144" t="n">
-        <v>1</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="145">
@@ -8785,7 +8785,7 @@
         <v>0.49</v>
       </c>
       <c r="I146" t="n">
-        <v>0.726</v>
+        <v>1</v>
       </c>
     </row>
     <row r="147">
@@ -8822,7 +8822,7 @@
         <v>0.458</v>
       </c>
       <c r="I147" t="n">
-        <v>0.726</v>
+        <v>0.588</v>
       </c>
     </row>
     <row r="148">
@@ -8859,7 +8859,7 @@
         <v>0.166</v>
       </c>
       <c r="I148" t="n">
-        <v>0.664</v>
+        <v>0.498</v>
       </c>
     </row>
     <row r="149">
@@ -8933,7 +8933,7 @@
         <v>0.499</v>
       </c>
       <c r="I150" t="n">
-        <v>0.726</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151">
@@ -8970,7 +8970,7 @@
         <v>0.00604</v>
       </c>
       <c r="I151" t="n">
-        <v>0.09660000000000001</v>
+        <v>0.0181</v>
       </c>
     </row>
     <row r="152">
@@ -9007,7 +9007,7 @@
         <v>0.0373</v>
       </c>
       <c r="I152" t="n">
-        <v>0.298</v>
+        <v>0.112</v>
       </c>
     </row>
     <row r="153">
@@ -9044,7 +9044,7 @@
         <v>0.138</v>
       </c>
       <c r="I153" t="n">
-        <v>0.664</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154">
@@ -9081,7 +9081,7 @@
         <v>0.624</v>
       </c>
       <c r="I154" t="n">
-        <v>0.832</v>
+        <v>0.858</v>
       </c>
     </row>
     <row r="155">
@@ -9118,7 +9118,7 @@
         <v>0.718</v>
       </c>
       <c r="I155" t="n">
-        <v>0.884</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156">
@@ -9192,7 +9192,7 @@
         <v>0.456</v>
       </c>
       <c r="I157" t="n">
-        <v>0.726</v>
+        <v>0.548</v>
       </c>
     </row>
     <row r="158">
@@ -9229,7 +9229,7 @@
         <v>0.473</v>
       </c>
       <c r="I158" t="n">
-        <v>0.726</v>
+        <v>1</v>
       </c>
     </row>
     <row r="159">
@@ -9266,7 +9266,7 @@
         <v>0.284</v>
       </c>
       <c r="I159" t="n">
-        <v>0.726</v>
+        <v>0.319</v>
       </c>
     </row>
     <row r="160">
@@ -9303,7 +9303,7 @@
         <v>0.458</v>
       </c>
       <c r="I160" t="n">
-        <v>0.726</v>
+        <v>0.523</v>
       </c>
     </row>
     <row r="161">
@@ -9377,7 +9377,7 @@
         <v>0.166</v>
       </c>
       <c r="I162" t="n">
-        <v>0.463</v>
+        <v>0.213</v>
       </c>
     </row>
     <row r="163">
@@ -9525,7 +9525,7 @@
         <v>0.609</v>
       </c>
       <c r="I166" t="n">
-        <v>0.927</v>
+        <v>0.913</v>
       </c>
     </row>
     <row r="167">
@@ -9562,7 +9562,7 @@
         <v>6.35e-05</v>
       </c>
       <c r="I167" t="n">
-        <v>0.00102</v>
+        <v>0.000286</v>
       </c>
     </row>
     <row r="168">
@@ -9599,7 +9599,7 @@
         <v>0.00231</v>
       </c>
       <c r="I168" t="n">
-        <v>0.0185</v>
+        <v>0.0104</v>
       </c>
     </row>
     <row r="169">
@@ -9636,7 +9636,7 @@
         <v>0.637</v>
       </c>
       <c r="I169" t="n">
-        <v>0.927</v>
+        <v>1</v>
       </c>
     </row>
     <row r="170">
@@ -9673,7 +9673,7 @@
         <v>0.294</v>
       </c>
       <c r="I170" t="n">
-        <v>0.672</v>
+        <v>0.425</v>
       </c>
     </row>
     <row r="171">
@@ -9747,7 +9747,7 @@
         <v>0.0405</v>
       </c>
       <c r="I172" t="n">
-        <v>0.216</v>
+        <v>0.0911</v>
       </c>
     </row>
     <row r="173">
@@ -9784,7 +9784,7 @@
         <v>0.11</v>
       </c>
       <c r="I173" t="n">
-        <v>0.439</v>
+        <v>0.247</v>
       </c>
     </row>
     <row r="174">
@@ -9858,7 +9858,7 @@
         <v>0.407</v>
       </c>
       <c r="I175" t="n">
-        <v>0.724</v>
+        <v>0.503</v>
       </c>
     </row>
     <row r="176">
@@ -9895,7 +9895,7 @@
         <v>0.363</v>
       </c>
       <c r="I176" t="n">
-        <v>0.724</v>
+        <v>0.408</v>
       </c>
     </row>
     <row r="177">
@@ -9932,7 +9932,7 @@
         <v>0.174</v>
       </c>
       <c r="I177" t="n">
-        <v>0.463</v>
+        <v>0.224</v>
       </c>
     </row>
     <row r="178">
@@ -9969,7 +9969,7 @@
         <v>0.628</v>
       </c>
       <c r="I178" t="n">
-        <v>0.913</v>
+        <v>0.707</v>
       </c>
     </row>
     <row r="179">
@@ -10006,7 +10006,7 @@
         <v>0.423</v>
       </c>
       <c r="I179" t="n">
-        <v>0.752</v>
+        <v>0.476</v>
       </c>
     </row>
     <row r="180">
@@ -10043,7 +10043,7 @@
         <v>0.329</v>
       </c>
       <c r="I180" t="n">
-        <v>0.752</v>
+        <v>0.987</v>
       </c>
     </row>
     <row r="181">
@@ -10117,7 +10117,7 @@
         <v>0.769</v>
       </c>
       <c r="I182" t="n">
-        <v>0.947</v>
+        <v>0.993</v>
       </c>
     </row>
     <row r="183">
@@ -10154,7 +10154,7 @@
         <v>0.07580000000000001</v>
       </c>
       <c r="I183" t="n">
-        <v>0.607</v>
+        <v>0.136</v>
       </c>
     </row>
     <row r="184">
@@ -10191,7 +10191,7 @@
         <v>0.393</v>
       </c>
       <c r="I184" t="n">
-        <v>0.752</v>
+        <v>0.505</v>
       </c>
     </row>
     <row r="185">
@@ -10228,7 +10228,7 @@
         <v>0.156</v>
       </c>
       <c r="I185" t="n">
-        <v>0.752</v>
+        <v>1</v>
       </c>
     </row>
     <row r="186">
@@ -10265,7 +10265,7 @@
         <v>0.294</v>
       </c>
       <c r="I186" t="n">
-        <v>0.752</v>
+        <v>0.331</v>
       </c>
     </row>
     <row r="187">
@@ -10302,7 +10302,7 @@
         <v>0.868</v>
       </c>
       <c r="I187" t="n">
-        <v>0.957</v>
+        <v>0.868</v>
       </c>
     </row>
     <row r="188">
@@ -10339,7 +10339,7 @@
         <v>0.0515</v>
       </c>
       <c r="I188" t="n">
-        <v>0.607</v>
+        <v>0.0927</v>
       </c>
     </row>
     <row r="189">
@@ -10376,7 +10376,7 @@
         <v>0.247</v>
       </c>
       <c r="I189" t="n">
-        <v>0.752</v>
+        <v>0.741</v>
       </c>
     </row>
     <row r="190">
@@ -10413,7 +10413,7 @@
         <v>0.488</v>
       </c>
       <c r="I190" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
     </row>
     <row r="191">
@@ -10450,7 +10450,7 @@
         <v>0.726</v>
       </c>
       <c r="I191" t="n">
-        <v>0.947</v>
+        <v>0.9330000000000001</v>
       </c>
     </row>
     <row r="192">
@@ -10487,7 +10487,7 @@
         <v>0.897</v>
       </c>
       <c r="I192" t="n">
-        <v>0.957</v>
+        <v>0.897</v>
       </c>
     </row>
     <row r="193">
@@ -10524,7 +10524,7 @@
         <v>0.194</v>
       </c>
       <c r="I193" t="n">
-        <v>0.752</v>
+        <v>0.436</v>
       </c>
     </row>
     <row r="194">
@@ -10561,7 +10561,7 @@
         <v>0.312</v>
       </c>
       <c r="I194" t="n">
-        <v>0.833</v>
+        <v>0.409</v>
       </c>
     </row>
     <row r="195">
@@ -10746,7 +10746,7 @@
         <v>0.176</v>
       </c>
       <c r="I199" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.317</v>
       </c>
     </row>
     <row r="200">
@@ -10783,7 +10783,7 @@
         <v>0.747</v>
       </c>
       <c r="I200" t="n">
-        <v>1</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="201">
@@ -10857,7 +10857,7 @@
         <v>0.536</v>
       </c>
       <c r="I202" t="n">
-        <v>1</v>
+        <v>0.536</v>
       </c>
     </row>
     <row r="203">
@@ -10894,7 +10894,7 @@
         <v>0.176</v>
       </c>
       <c r="I203" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.396</v>
       </c>
     </row>
     <row r="204">
@@ -10931,7 +10931,7 @@
         <v>0.779</v>
       </c>
       <c r="I204" t="n">
-        <v>1</v>
+        <v>0.779</v>
       </c>
     </row>
     <row r="205">
@@ -11042,7 +11042,7 @@
         <v>0.135</v>
       </c>
       <c r="I207" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.405</v>
       </c>
     </row>
     <row r="208">
@@ -11079,7 +11079,7 @@
         <v>0.000212</v>
       </c>
       <c r="I208" t="n">
-        <v>0.0017</v>
+        <v>0.000954</v>
       </c>
     </row>
     <row r="209">
@@ -11116,7 +11116,7 @@
         <v>2.67e-06</v>
       </c>
       <c r="I209" t="n">
-        <v>4.27e-05</v>
+        <v>1.2e-05</v>
       </c>
     </row>
     <row r="210">
@@ -11190,7 +11190,7 @@
         <v>0.523</v>
       </c>
       <c r="I211" t="n">
-        <v>0.698</v>
+        <v>0.588</v>
       </c>
     </row>
     <row r="212">
@@ -11227,7 +11227,7 @@
         <v>0.0623</v>
       </c>
       <c r="I212" t="n">
-        <v>0.199</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="213">
@@ -11301,7 +11301,7 @@
         <v>0.247</v>
       </c>
       <c r="I214" t="n">
-        <v>0.449</v>
+        <v>0.741</v>
       </c>
     </row>
     <row r="215">
@@ -11338,7 +11338,7 @@
         <v>0.08019999999999999</v>
       </c>
       <c r="I215" t="n">
-        <v>0.214</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="216">
@@ -11375,7 +11375,7 @@
         <v>0.252</v>
       </c>
       <c r="I216" t="n">
-        <v>0.449</v>
+        <v>0.404</v>
       </c>
     </row>
     <row r="217">
@@ -11412,7 +11412,7 @@
         <v>0.524</v>
       </c>
       <c r="I217" t="n">
-        <v>0.698</v>
+        <v>1</v>
       </c>
     </row>
     <row r="218">
@@ -11449,7 +11449,7 @@
         <v>0.364</v>
       </c>
       <c r="I218" t="n">
-        <v>0.583</v>
+        <v>0.858</v>
       </c>
     </row>
     <row r="219">
@@ -11523,7 +11523,7 @@
         <v>0.038</v>
       </c>
       <c r="I220" t="n">
-        <v>0.152</v>
+        <v>0.171</v>
       </c>
     </row>
     <row r="221">
@@ -11560,7 +11560,7 @@
         <v>0.124</v>
       </c>
       <c r="I221" t="n">
-        <v>0.283</v>
+        <v>0.279</v>
       </c>
     </row>
     <row r="222">
@@ -11597,7 +11597,7 @@
         <v>0.613</v>
       </c>
       <c r="I222" t="n">
-        <v>0.755</v>
+        <v>1</v>
       </c>
     </row>
     <row r="223">
@@ -11634,7 +11634,7 @@
         <v>0.0005330000000000001</v>
       </c>
       <c r="I223" t="n">
-        <v>0.00428</v>
+        <v>0.0024</v>
       </c>
     </row>
     <row r="224">
@@ -11671,7 +11671,7 @@
         <v>0.000535</v>
       </c>
       <c r="I224" t="n">
-        <v>0.00428</v>
+        <v>0.0016</v>
       </c>
     </row>
     <row r="225">
@@ -11708,7 +11708,7 @@
         <v>0.00117</v>
       </c>
       <c r="I225" t="n">
-        <v>0.00623</v>
+        <v>0.00351</v>
       </c>
     </row>
     <row r="226">
@@ -11745,7 +11745,7 @@
         <v>0.241</v>
       </c>
       <c r="I226" t="n">
-        <v>0.642</v>
+        <v>0.271</v>
       </c>
     </row>
     <row r="227">
@@ -11782,7 +11782,7 @@
         <v>0.236</v>
       </c>
       <c r="I227" t="n">
-        <v>0.642</v>
+        <v>0.425</v>
       </c>
     </row>
     <row r="228">
@@ -11819,7 +11819,7 @@
         <v>0.101</v>
       </c>
       <c r="I228" t="n">
-        <v>0.405</v>
+        <v>0.455</v>
       </c>
     </row>
     <row r="229">
@@ -11893,7 +11893,7 @@
         <v>0.532</v>
       </c>
       <c r="I230" t="n">
-        <v>0.881</v>
+        <v>0.913</v>
       </c>
     </row>
     <row r="231">
@@ -11930,7 +11930,7 @@
         <v>0.723</v>
       </c>
       <c r="I231" t="n">
-        <v>0.89</v>
+        <v>0.736</v>
       </c>
     </row>
     <row r="232">
@@ -11967,7 +11967,7 @@
         <v>0.845</v>
       </c>
       <c r="I232" t="n">
-        <v>0.965</v>
+        <v>0.845</v>
       </c>
     </row>
     <row r="233">
@@ -12041,7 +12041,7 @@
         <v>0.695</v>
       </c>
       <c r="I234" t="n">
-        <v>0.89</v>
+        <v>0.695</v>
       </c>
     </row>
     <row r="235">
@@ -12078,7 +12078,7 @@
         <v>0.0902</v>
       </c>
       <c r="I235" t="n">
-        <v>0.405</v>
+        <v>0.229</v>
       </c>
     </row>
     <row r="236">
@@ -12115,7 +12115,7 @@
         <v>0.413</v>
       </c>
       <c r="I236" t="n">
-        <v>0.881</v>
+        <v>0.531</v>
       </c>
     </row>
     <row r="237">
@@ -12152,7 +12152,7 @@
         <v>0.5679999999999999</v>
       </c>
       <c r="I237" t="n">
-        <v>0.881</v>
+        <v>0.852</v>
       </c>
     </row>
     <row r="238">
@@ -12189,7 +12189,7 @@
         <v>0.606</v>
       </c>
       <c r="I238" t="n">
-        <v>0.881</v>
+        <v>1</v>
       </c>
     </row>
     <row r="239">
@@ -12226,7 +12226,7 @@
         <v>0.447</v>
       </c>
       <c r="I239" t="n">
-        <v>0.881</v>
+        <v>0.503</v>
       </c>
     </row>
     <row r="240">
@@ -12263,7 +12263,7 @@
         <v>0.000275</v>
       </c>
       <c r="I240" t="n">
-        <v>0.0044</v>
+        <v>0.00124</v>
       </c>
     </row>
     <row r="241">
@@ -12300,7 +12300,7 @@
         <v>0.00827</v>
       </c>
       <c r="I241" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.0372</v>
       </c>
     </row>
     <row r="242">
@@ -12337,7 +12337,7 @@
         <v>0.207</v>
       </c>
       <c r="I242" t="n">
-        <v>1</v>
+        <v>0.276</v>
       </c>
     </row>
     <row r="243">
@@ -12485,7 +12485,7 @@
         <v>0.672</v>
       </c>
       <c r="I246" t="n">
-        <v>1</v>
+        <v>0.993</v>
       </c>
     </row>
     <row r="247">
@@ -12522,7 +12522,7 @@
         <v>0.183</v>
       </c>
       <c r="I247" t="n">
-        <v>1</v>
+        <v>0.235</v>
       </c>
     </row>
     <row r="248">
@@ -12559,7 +12559,7 @@
         <v>0.751</v>
       </c>
       <c r="I248" t="n">
-        <v>1</v>
+        <v>0.845</v>
       </c>
     </row>
     <row r="249">
@@ -12633,7 +12633,7 @@
         <v>0.486</v>
       </c>
       <c r="I250" t="n">
-        <v>1</v>
+        <v>0.486</v>
       </c>
     </row>
     <row r="251">
@@ -12670,7 +12670,7 @@
         <v>0.06909999999999999</v>
       </c>
       <c r="I251" t="n">
-        <v>1</v>
+        <v>0.155</v>
       </c>
     </row>
     <row r="252">
@@ -12744,7 +12744,7 @@
         <v>0.872</v>
       </c>
       <c r="I253" t="n">
-        <v>1</v>
+        <v>0.872</v>
       </c>
     </row>
     <row r="254">
@@ -12818,7 +12818,7 @@
         <v>0.364</v>
       </c>
       <c r="I255" t="n">
-        <v>1</v>
+        <v>0.655</v>
       </c>
     </row>
     <row r="256">
@@ -12855,7 +12855,7 @@
         <v>0.625</v>
       </c>
       <c r="I256" t="n">
-        <v>1</v>
+        <v>0.793</v>
       </c>
     </row>
     <row r="257">
@@ -12892,7 +12892,7 @@
         <v>0.599</v>
       </c>
       <c r="I257" t="n">
-        <v>1</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="258">
@@ -12929,7 +12929,7 @@
         <v>0.0025</v>
       </c>
       <c r="I258" t="n">
-        <v>0.02</v>
+        <v>0.0225</v>
       </c>
     </row>
     <row r="259">
@@ -12966,7 +12966,7 @@
         <v>0.268</v>
       </c>
       <c r="I259" t="n">
-        <v>0.581</v>
+        <v>0.301</v>
       </c>
     </row>
     <row r="260">
@@ -13003,7 +13003,7 @@
         <v>0.825</v>
       </c>
       <c r="I260" t="n">
-        <v>0.873</v>
+        <v>1</v>
       </c>
     </row>
     <row r="261">
@@ -13040,7 +13040,7 @@
         <v>0.173</v>
       </c>
       <c r="I261" t="n">
-        <v>0.554</v>
+        <v>0.519</v>
       </c>
     </row>
     <row r="262">
@@ -13077,7 +13077,7 @@
         <v>0.669</v>
       </c>
       <c r="I262" t="n">
-        <v>0.823</v>
+        <v>1</v>
       </c>
     </row>
     <row r="263">
@@ -13114,7 +13114,7 @@
         <v>0.377</v>
       </c>
       <c r="I263" t="n">
-        <v>0.604</v>
+        <v>0.424</v>
       </c>
     </row>
     <row r="264">
@@ -13188,7 +13188,7 @@
         <v>0.8090000000000001</v>
       </c>
       <c r="I265" t="n">
-        <v>0.873</v>
+        <v>1</v>
       </c>
     </row>
     <row r="266">
@@ -13225,7 +13225,7 @@
         <v>0.339</v>
       </c>
       <c r="I266" t="n">
-        <v>0.602</v>
+        <v>0.528</v>
       </c>
     </row>
     <row r="267">
@@ -13262,7 +13262,7 @@
         <v>0.665</v>
       </c>
       <c r="I267" t="n">
-        <v>0.823</v>
+        <v>0.879</v>
       </c>
     </row>
     <row r="268">
@@ -13299,7 +13299,7 @@
         <v>0.29</v>
       </c>
       <c r="I268" t="n">
-        <v>0.581</v>
+        <v>0.435</v>
       </c>
     </row>
     <row r="269">
@@ -13336,7 +13336,7 @@
         <v>0.631</v>
       </c>
       <c r="I269" t="n">
-        <v>0.823</v>
+        <v>1</v>
       </c>
     </row>
     <row r="270">
@@ -13373,7 +13373,7 @@
         <v>0.256</v>
       </c>
       <c r="I270" t="n">
-        <v>0.581</v>
+        <v>1</v>
       </c>
     </row>
     <row r="271">
@@ -13410,7 +13410,7 @@
         <v>0.06859999999999999</v>
       </c>
       <c r="I271" t="n">
-        <v>0.274</v>
+        <v>0.309</v>
       </c>
     </row>
     <row r="272">
@@ -13447,7 +13447,7 @@
         <v>0.0137</v>
       </c>
       <c r="I272" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.0308</v>
       </c>
     </row>
     <row r="273">
@@ -13484,7 +13484,7 @@
         <v>8.65e-06</v>
       </c>
       <c r="I273" t="n">
-        <v>0.000138</v>
+        <v>2.59e-05</v>
       </c>
     </row>
     <row r="274">
@@ -13595,7 +13595,7 @@
         <v>0.245</v>
       </c>
       <c r="I276" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.551</v>
       </c>
     </row>
     <row r="277">
@@ -13706,7 +13706,7 @@
         <v>0.002</v>
       </c>
       <c r="I279" t="n">
-        <v>0.007979999999999999</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="280">
@@ -13743,7 +13743,7 @@
         <v>0.0228</v>
       </c>
       <c r="I280" t="n">
-        <v>0.0731</v>
+        <v>0.112</v>
       </c>
     </row>
     <row r="281">
@@ -13817,7 +13817,7 @@
         <v>0.626</v>
       </c>
       <c r="I282" t="n">
-        <v>1</v>
+        <v>0.858</v>
       </c>
     </row>
     <row r="283">
@@ -13891,7 +13891,7 @@
         <v>0.156</v>
       </c>
       <c r="I284" t="n">
-        <v>0.415</v>
+        <v>0.468</v>
       </c>
     </row>
     <row r="285">
@@ -13928,7 +13928,7 @@
         <v>0.487</v>
       </c>
       <c r="I285" t="n">
-        <v>0.973</v>
+        <v>0.548</v>
       </c>
     </row>
     <row r="286">
@@ -14002,7 +14002,7 @@
         <v>7.68e-05</v>
       </c>
       <c r="I287" t="n">
-        <v>0.0011</v>
+        <v>0.000691</v>
       </c>
     </row>
     <row r="288">
@@ -14039,7 +14039,7 @@
         <v>0.000434</v>
       </c>
       <c r="I288" t="n">
-        <v>0.00232</v>
+        <v>0.0016</v>
       </c>
     </row>
     <row r="289">
@@ -14076,7 +14076,7 @@
         <v>0.000137</v>
       </c>
       <c r="I289" t="n">
-        <v>0.0011</v>
+        <v>0.00123</v>
       </c>
     </row>
     <row r="290">
@@ -14113,7 +14113,7 @@
         <v>2.89e-05</v>
       </c>
       <c r="I290" t="n">
-        <v>0.000154</v>
+        <v>0.00013</v>
       </c>
     </row>
     <row r="291">
@@ -14150,7 +14150,7 @@
         <v>0.01</v>
       </c>
       <c r="I291" t="n">
-        <v>0.0401</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="292">
@@ -14187,7 +14187,7 @@
         <v>0.101</v>
       </c>
       <c r="I292" t="n">
-        <v>0.231</v>
+        <v>0.455</v>
       </c>
     </row>
     <row r="293">
@@ -14224,7 +14224,7 @@
         <v>0.132</v>
       </c>
       <c r="I293" t="n">
-        <v>0.265</v>
+        <v>0.594</v>
       </c>
     </row>
     <row r="294">
@@ -14261,7 +14261,7 @@
         <v>0.437</v>
       </c>
       <c r="I294" t="n">
-        <v>0.636</v>
+        <v>0.913</v>
       </c>
     </row>
     <row r="295">
@@ -14298,7 +14298,7 @@
         <v>0.736</v>
       </c>
       <c r="I295" t="n">
-        <v>0.841</v>
+        <v>0.736</v>
       </c>
     </row>
     <row r="296">
@@ -14335,7 +14335,7 @@
         <v>0.348</v>
       </c>
       <c r="I296" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.391</v>
       </c>
     </row>
     <row r="297">
@@ -14409,7 +14409,7 @@
         <v>0.202</v>
       </c>
       <c r="I298" t="n">
-        <v>0.36</v>
+        <v>0.364</v>
       </c>
     </row>
     <row r="299">
@@ -14446,7 +14446,7 @@
         <v>0.623</v>
       </c>
       <c r="I299" t="n">
-        <v>0.767</v>
+        <v>0.776</v>
       </c>
     </row>
     <row r="300">
@@ -14483,7 +14483,7 @@
         <v>0.0126</v>
       </c>
       <c r="I300" t="n">
-        <v>0.0404</v>
+        <v>0.0378</v>
       </c>
     </row>
     <row r="301">
@@ -14557,7 +14557,7 @@
         <v>0.0205</v>
       </c>
       <c r="I302" t="n">
-        <v>0.0546</v>
+        <v>0.184</v>
       </c>
     </row>
     <row r="303">
@@ -14594,7 +14594,7 @@
         <v>0.5649999999999999</v>
       </c>
       <c r="I303" t="n">
-        <v>0.753</v>
+        <v>0.5649999999999999</v>
       </c>
     </row>
     <row r="304">
@@ -14631,7 +14631,7 @@
         <v>8.54e-12</v>
       </c>
       <c r="I304" t="n">
-        <v>1.37e-10</v>
+        <v>7.69e-11</v>
       </c>
     </row>
     <row r="305">
@@ -14668,7 +14668,7 @@
         <v>1.56e-06</v>
       </c>
       <c r="I305" t="n">
-        <v>1.25e-05</v>
+        <v>1.4e-05</v>
       </c>
     </row>
     <row r="306">
@@ -14705,7 +14705,7 @@
         <v>0.000568</v>
       </c>
       <c r="I306" t="n">
-        <v>0.00908</v>
+        <v>0.00511</v>
       </c>
     </row>
     <row r="307">
@@ -14742,7 +14742,7 @@
         <v>0.09719999999999999</v>
       </c>
       <c r="I307" t="n">
-        <v>0.222</v>
+        <v>0.146</v>
       </c>
     </row>
     <row r="308">
@@ -14816,7 +14816,7 @@
         <v>0.07489999999999999</v>
       </c>
       <c r="I309" t="n">
-        <v>0.222</v>
+        <v>0.225</v>
       </c>
     </row>
     <row r="310">
@@ -14853,7 +14853,7 @@
         <v>0.485</v>
       </c>
       <c r="I310" t="n">
-        <v>0.747</v>
+        <v>0.993</v>
       </c>
     </row>
     <row r="311">
@@ -14890,7 +14890,7 @@
         <v>0.5610000000000001</v>
       </c>
       <c r="I311" t="n">
-        <v>0.747</v>
+        <v>0.5610000000000001</v>
       </c>
     </row>
     <row r="312">
@@ -15001,7 +15001,7 @@
         <v>0.181</v>
       </c>
       <c r="I314" t="n">
-        <v>0.361</v>
+        <v>0.326</v>
       </c>
     </row>
     <row r="315">
@@ -15038,7 +15038,7 @@
         <v>0.5580000000000001</v>
       </c>
       <c r="I315" t="n">
-        <v>0.747</v>
+        <v>0.728</v>
       </c>
     </row>
     <row r="316">
@@ -15075,7 +15075,7 @@
         <v>0.0504</v>
       </c>
       <c r="I316" t="n">
-        <v>0.222</v>
+        <v>0.0927</v>
       </c>
     </row>
     <row r="317">
@@ -15112,7 +15112,7 @@
         <v>0.619</v>
       </c>
       <c r="I317" t="n">
-        <v>0.762</v>
+        <v>0.872</v>
       </c>
     </row>
     <row r="318">
@@ -15149,7 +15149,7 @@
         <v>0.0675</v>
       </c>
       <c r="I318" t="n">
-        <v>0.222</v>
+        <v>0.608</v>
       </c>
     </row>
     <row r="319">
@@ -15186,7 +15186,7 @@
         <v>0.219</v>
       </c>
       <c r="I319" t="n">
-        <v>0.39</v>
+        <v>0.493</v>
       </c>
     </row>
     <row r="320">
@@ -15223,7 +15223,7 @@
         <v>0.00276</v>
       </c>
       <c r="I320" t="n">
-        <v>0.0221</v>
+        <v>0.0124</v>
       </c>
     </row>
     <row r="321">
@@ -15260,7 +15260,7 @@
         <v>0.08309999999999999</v>
       </c>
       <c r="I321" t="n">
-        <v>0.222</v>
+        <v>0.374</v>
       </c>
     </row>
     <row r="322">
@@ -15297,7 +15297,7 @@
         <v>0.0215</v>
       </c>
       <c r="I322" t="n">
-        <v>0.0689</v>
+        <v>0.08790000000000001</v>
       </c>
     </row>
     <row r="323">
@@ -15334,7 +15334,7 @@
         <v>0.00162</v>
       </c>
       <c r="I323" t="n">
-        <v>0.008630000000000001</v>
+        <v>0.00364</v>
       </c>
     </row>
     <row r="324">
@@ -15371,7 +15371,7 @@
         <v>0.343</v>
       </c>
       <c r="I324" t="n">
-        <v>0.499</v>
+        <v>1</v>
       </c>
     </row>
     <row r="325">
@@ -15408,7 +15408,7 @@
         <v>0.498</v>
       </c>
       <c r="I325" t="n">
-        <v>0.653</v>
+        <v>1</v>
       </c>
     </row>
     <row r="326">
@@ -15445,7 +15445,7 @@
         <v>0.545</v>
       </c>
       <c r="I326" t="n">
-        <v>0.653</v>
+        <v>1</v>
       </c>
     </row>
     <row r="327">
@@ -15482,7 +15482,7 @@
         <v>0.0105</v>
       </c>
       <c r="I327" t="n">
-        <v>0.0419</v>
+        <v>0.0473</v>
       </c>
     </row>
     <row r="328">
@@ -15519,7 +15519,7 @@
         <v>0.0298</v>
       </c>
       <c r="I328" t="n">
-        <v>0.0793</v>
+        <v>0.268</v>
       </c>
     </row>
     <row r="329">
@@ -15593,7 +15593,7 @@
         <v>0.129</v>
       </c>
       <c r="I330" t="n">
-        <v>0.207</v>
+        <v>0.373</v>
       </c>
     </row>
     <row r="331">
@@ -15630,7 +15630,7 @@
         <v>0.0644</v>
       </c>
       <c r="I331" t="n">
-        <v>0.129</v>
+        <v>0.217</v>
       </c>
     </row>
     <row r="332">
@@ -15667,7 +15667,7 @@
         <v>0.571</v>
       </c>
       <c r="I332" t="n">
-        <v>0.653</v>
+        <v>0.6840000000000001</v>
       </c>
     </row>
     <row r="333">
@@ -15704,7 +15704,7 @@
         <v>0.126</v>
       </c>
       <c r="I333" t="n">
-        <v>0.207</v>
+        <v>1</v>
       </c>
     </row>
     <row r="334">
@@ -15778,7 +15778,7 @@
         <v>0.0467</v>
       </c>
       <c r="I335" t="n">
-        <v>0.107</v>
+        <v>0.309</v>
       </c>
     </row>
     <row r="336">
@@ -15815,7 +15815,7 @@
         <v>2.03e-06</v>
       </c>
       <c r="I336" t="n">
-        <v>1.62e-05</v>
+        <v>1.83e-05</v>
       </c>
     </row>
     <row r="337">
@@ -15852,7 +15852,7 @@
         <v>7.67e-07</v>
       </c>
       <c r="I337" t="n">
-        <v>1.23e-05</v>
+        <v>6.9e-06</v>
       </c>
     </row>
     <row r="338">
@@ -15926,7 +15926,7 @@
         <v>0.0152</v>
       </c>
       <c r="I339" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.0456</v>
       </c>
     </row>
     <row r="340">
@@ -15963,7 +15963,7 @@
         <v>0.404</v>
       </c>
       <c r="I340" t="n">
-        <v>0.924</v>
+        <v>0.727</v>
       </c>
     </row>
     <row r="341">
@@ -16074,7 +16074,7 @@
         <v>0.0175</v>
       </c>
       <c r="I343" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.0394</v>
       </c>
     </row>
     <row r="344">
@@ -16111,7 +16111,7 @@
         <v>0.269</v>
       </c>
       <c r="I344" t="n">
-        <v>0.716</v>
+        <v>0.404</v>
       </c>
     </row>
     <row r="345">
@@ -16259,7 +16259,7 @@
         <v>0.641</v>
       </c>
       <c r="I348" t="n">
-        <v>1</v>
+        <v>0.721</v>
       </c>
     </row>
     <row r="349">
@@ -16296,7 +16296,7 @@
         <v>0.766</v>
       </c>
       <c r="I349" t="n">
-        <v>1</v>
+        <v>0.766</v>
       </c>
     </row>
     <row r="350">
@@ -16370,7 +16370,7 @@
         <v>0.0804</v>
       </c>
       <c r="I351" t="n">
-        <v>0.257</v>
+        <v>0.181</v>
       </c>
     </row>
     <row r="352">
@@ -16407,7 +16407,7 @@
         <v>0.000103</v>
       </c>
       <c r="I352" t="n">
-        <v>0.00165</v>
+        <v>0.000927</v>
       </c>
     </row>
     <row r="353">
@@ -16444,7 +16444,7 @@
         <v>0.0007739999999999999</v>
       </c>
       <c r="I353" t="n">
-        <v>0.00619</v>
+        <v>0.00348</v>
       </c>
     </row>
     <row r="354">
@@ -16481,7 +16481,7 @@
         <v>0.000261</v>
       </c>
       <c r="I354" t="n">
-        <v>0.00418</v>
+        <v>0.000783</v>
       </c>
     </row>
     <row r="355">
@@ -16592,7 +16592,7 @@
         <v>0.488</v>
       </c>
       <c r="I357" t="n">
-        <v>0.735</v>
+        <v>0.878</v>
       </c>
     </row>
     <row r="358">
@@ -16629,7 +16629,7 @@
         <v>0.506</v>
       </c>
       <c r="I358" t="n">
-        <v>0.735</v>
+        <v>0.913</v>
       </c>
     </row>
     <row r="359">
@@ -16666,7 +16666,7 @@
         <v>0.132</v>
       </c>
       <c r="I359" t="n">
-        <v>0.264</v>
+        <v>0.198</v>
       </c>
     </row>
     <row r="360">
@@ -16703,7 +16703,7 @@
         <v>0.0602</v>
       </c>
       <c r="I360" t="n">
-        <v>0.195</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="361">
@@ -16740,7 +16740,7 @@
         <v>0.62</v>
       </c>
       <c r="I361" t="n">
-        <v>0.827</v>
+        <v>1</v>
       </c>
     </row>
     <row r="362">
@@ -16777,7 +16777,7 @@
         <v>0.08019999999999999</v>
       </c>
       <c r="I362" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="363">
@@ -16814,7 +16814,7 @@
         <v>0.0149</v>
       </c>
       <c r="I363" t="n">
-        <v>0.119</v>
+        <v>0.0702</v>
       </c>
     </row>
     <row r="364">
@@ -16851,7 +16851,7 @@
         <v>0.728</v>
       </c>
       <c r="I364" t="n">
-        <v>0.896</v>
+        <v>0.752</v>
       </c>
     </row>
     <row r="365">
@@ -16888,7 +16888,7 @@
         <v>0.0515</v>
       </c>
       <c r="I365" t="n">
-        <v>0.195</v>
+        <v>0.188</v>
       </c>
     </row>
     <row r="366">
@@ -16962,7 +16962,7 @@
         <v>0.394</v>
       </c>
       <c r="I367" t="n">
-        <v>0.701</v>
+        <v>0.503</v>
       </c>
     </row>
     <row r="368">
@@ -16999,7 +16999,7 @@
         <v>0.061</v>
       </c>
       <c r="I368" t="n">
-        <v>0.195</v>
+        <v>0.137</v>
       </c>
     </row>
     <row r="369">
@@ -17036,7 +17036,7 @@
         <v>0.0873</v>
       </c>
       <c r="I369" t="n">
-        <v>0.2</v>
+        <v>0.177</v>
       </c>
     </row>
     <row r="370">
@@ -17073,7 +17073,7 @@
         <v>0.0046</v>
       </c>
       <c r="I370" t="n">
-        <v>0.05</v>
+        <v>0.0207</v>
       </c>
     </row>
     <row r="371">
@@ -17110,7 +17110,7 @@
         <v>0.009379999999999999</v>
       </c>
       <c r="I371" t="n">
-        <v>0.05</v>
+        <v>0.0211</v>
       </c>
     </row>
     <row r="372">
@@ -17147,7 +17147,7 @@
         <v>0.328</v>
       </c>
       <c r="I372" t="n">
-        <v>0.438</v>
+        <v>0.987</v>
       </c>
     </row>
     <row r="373">
@@ -17184,7 +17184,7 @@
         <v>0.236</v>
       </c>
       <c r="I373" t="n">
-        <v>0.343</v>
+        <v>0.531</v>
       </c>
     </row>
     <row r="374">
@@ -17221,7 +17221,7 @@
         <v>0.458</v>
       </c>
       <c r="I374" t="n">
-        <v>0.522</v>
+        <v>0.993</v>
       </c>
     </row>
     <row r="375">
@@ -17258,7 +17258,7 @@
         <v>0.00769</v>
       </c>
       <c r="I375" t="n">
-        <v>0.05</v>
+        <v>0.0231</v>
       </c>
     </row>
     <row r="376">
@@ -17295,7 +17295,7 @@
         <v>0.0196</v>
       </c>
       <c r="I376" t="n">
-        <v>0.0552</v>
+        <v>0.176</v>
       </c>
     </row>
     <row r="377">
@@ -17332,7 +17332,7 @@
         <v>0.471</v>
       </c>
       <c r="I377" t="n">
-        <v>0.522</v>
+        <v>1</v>
       </c>
     </row>
     <row r="378">
@@ -17369,7 +17369,7 @@
         <v>0.0576</v>
       </c>
       <c r="I378" t="n">
-        <v>0.102</v>
+        <v>0.131</v>
       </c>
     </row>
     <row r="379">
@@ -17406,7 +17406,7 @@
         <v>0.0136</v>
       </c>
       <c r="I379" t="n">
-        <v>0.0543</v>
+        <v>0.0612</v>
       </c>
     </row>
     <row r="380">
@@ -17443,7 +17443,7 @@
         <v>0.489</v>
       </c>
       <c r="I380" t="n">
-        <v>0.522</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="381">
@@ -17480,7 +17480,7 @@
         <v>0.0545</v>
       </c>
       <c r="I381" t="n">
-        <v>0.102</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="382">
@@ -17517,7 +17517,7 @@
         <v>0.739</v>
       </c>
       <c r="I382" t="n">
-        <v>0.739</v>
+        <v>1</v>
       </c>
     </row>
     <row r="383">
@@ -17554,7 +17554,7 @@
         <v>0.0472</v>
       </c>
       <c r="I383" t="n">
-        <v>0.102</v>
+        <v>0.425</v>
       </c>
     </row>
     <row r="384">
@@ -17591,7 +17591,7 @@
         <v>0.0207</v>
       </c>
       <c r="I384" t="n">
-        <v>0.0552</v>
+        <v>0.0621</v>
       </c>
     </row>
     <row r="385">
@@ -17628,7 +17628,7 @@
         <v>0.126</v>
       </c>
       <c r="I385" t="n">
-        <v>0.202</v>
+        <v>0.378</v>
       </c>
     </row>
     <row r="386">
@@ -17665,7 +17665,7 @@
         <v>0.318</v>
       </c>
       <c r="I386" t="n">
-        <v>0.849</v>
+        <v>0.409</v>
       </c>
     </row>
     <row r="387">
@@ -17702,7 +17702,7 @@
         <v>0.0725</v>
       </c>
       <c r="I387" t="n">
-        <v>0.348</v>
+        <v>0.109</v>
       </c>
     </row>
     <row r="388">
@@ -17776,7 +17776,7 @@
         <v>0.173</v>
       </c>
       <c r="I389" t="n">
-        <v>0.554</v>
+        <v>0.519</v>
       </c>
     </row>
     <row r="390">
@@ -17850,7 +17850,7 @@
         <v>0.375</v>
       </c>
       <c r="I391" t="n">
-        <v>0.857</v>
+        <v>0.424</v>
       </c>
     </row>
     <row r="392">
@@ -17887,7 +17887,7 @@
         <v>0.571</v>
       </c>
       <c r="I392" t="n">
-        <v>0.885</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="393">
@@ -17961,7 +17961,7 @@
         <v>0.484</v>
       </c>
       <c r="I394" t="n">
-        <v>0.885</v>
+        <v>0.536</v>
       </c>
     </row>
     <row r="395">
@@ -17998,7 +17998,7 @@
         <v>0.0725</v>
       </c>
       <c r="I395" t="n">
-        <v>0.348</v>
+        <v>0.217</v>
       </c>
     </row>
     <row r="396">
@@ -18035,7 +18035,7 @@
         <v>0.608</v>
       </c>
       <c r="I396" t="n">
-        <v>0.885</v>
+        <v>0.6840000000000001</v>
       </c>
     </row>
     <row r="397">
@@ -18146,7 +18146,7 @@
         <v>0.579</v>
       </c>
       <c r="I399" t="n">
-        <v>0.885</v>
+        <v>0.744</v>
       </c>
     </row>
     <row r="400">
@@ -18183,7 +18183,7 @@
         <v>0.08690000000000001</v>
       </c>
       <c r="I400" t="n">
-        <v>0.348</v>
+        <v>0.156</v>
       </c>
     </row>
     <row r="401">
@@ -18220,7 +18220,7 @@
         <v>0.0261</v>
       </c>
       <c r="I401" t="n">
-        <v>0.348</v>
+        <v>0.047</v>
       </c>
     </row>
     <row r="402">
@@ -18294,7 +18294,7 @@
         <v>0.0264</v>
       </c>
       <c r="I403" t="n">
-        <v>0.368</v>
+        <v>0.0475</v>
       </c>
     </row>
     <row r="404">
@@ -18442,7 +18442,7 @@
         <v>0.136</v>
       </c>
       <c r="I407" t="n">
-        <v>0.434</v>
+        <v>0.153</v>
       </c>
     </row>
     <row r="408">
@@ -18479,7 +18479,7 @@
         <v>0.453</v>
       </c>
       <c r="I408" t="n">
-        <v>0.862</v>
+        <v>0.582</v>
       </c>
     </row>
     <row r="409">
@@ -18590,7 +18590,7 @@
         <v>0.299</v>
       </c>
       <c r="I411" t="n">
-        <v>0.6830000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="412">
@@ -18627,7 +18627,7 @@
         <v>0.574</v>
       </c>
       <c r="I412" t="n">
-        <v>0.919</v>
+        <v>0.721</v>
       </c>
     </row>
     <row r="413">
@@ -18664,7 +18664,7 @@
         <v>0.485</v>
       </c>
       <c r="I413" t="n">
-        <v>0.862</v>
+        <v>0.548</v>
       </c>
     </row>
     <row r="414">
@@ -18701,7 +18701,7 @@
         <v>0.222</v>
       </c>
       <c r="I414" t="n">
-        <v>0.591</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="415">
@@ -18738,7 +18738,7 @@
         <v>0.102</v>
       </c>
       <c r="I415" t="n">
-        <v>0.434</v>
+        <v>0.184</v>
       </c>
     </row>
     <row r="416">
@@ -18775,7 +18775,7 @@
         <v>0.0459</v>
       </c>
       <c r="I416" t="n">
-        <v>0.368</v>
+        <v>0.08260000000000001</v>
       </c>
     </row>
     <row r="417">
@@ -18812,7 +18812,7 @@
         <v>0.112</v>
       </c>
       <c r="I417" t="n">
-        <v>0.434</v>
+        <v>0.202</v>
       </c>
     </row>
     <row r="418">
@@ -18849,7 +18849,7 @@
         <v>0.325</v>
       </c>
       <c r="I418" t="n">
-        <v>0.465</v>
+        <v>0.325</v>
       </c>
     </row>
     <row r="419">
@@ -18886,7 +18886,7 @@
         <v>0.1</v>
       </c>
       <c r="I419" t="n">
-        <v>0.353</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="420">
@@ -18923,7 +18923,7 @@
         <v>0.205</v>
       </c>
       <c r="I420" t="n">
-        <v>0.401</v>
+        <v>0.615</v>
       </c>
     </row>
     <row r="421">
@@ -18960,7 +18960,7 @@
         <v>0.132</v>
       </c>
       <c r="I421" t="n">
-        <v>0.353</v>
+        <v>0.594</v>
       </c>
     </row>
     <row r="422">
@@ -19034,7 +19034,7 @@
         <v>0.103</v>
       </c>
       <c r="I423" t="n">
-        <v>0.353</v>
+        <v>0.185</v>
       </c>
     </row>
     <row r="424">
@@ -19071,7 +19071,7 @@
         <v>0.253</v>
       </c>
       <c r="I424" t="n">
-        <v>0.405</v>
+        <v>0.325</v>
       </c>
     </row>
     <row r="425">
@@ -19145,7 +19145,7 @@
         <v>0.378</v>
       </c>
       <c r="I426" t="n">
-        <v>0.465</v>
+        <v>0.425</v>
       </c>
     </row>
     <row r="427">
@@ -19182,7 +19182,7 @@
         <v>0.102</v>
       </c>
       <c r="I427" t="n">
-        <v>0.353</v>
+        <v>0.229</v>
       </c>
     </row>
     <row r="428">
@@ -19219,7 +19219,7 @@
         <v>0.226</v>
       </c>
       <c r="I428" t="n">
-        <v>0.401</v>
+        <v>0.339</v>
       </c>
     </row>
     <row r="429">
@@ -19293,7 +19293,7 @@
         <v>0.067</v>
       </c>
       <c r="I430" t="n">
-        <v>0.353</v>
+        <v>0.301</v>
       </c>
     </row>
     <row r="431">
@@ -19330,7 +19330,7 @@
         <v>0.367</v>
       </c>
       <c r="I431" t="n">
-        <v>0.465</v>
+        <v>0.503</v>
       </c>
     </row>
     <row r="432">
@@ -19367,7 +19367,7 @@
         <v>0.211</v>
       </c>
       <c r="I432" t="n">
-        <v>0.401</v>
+        <v>0.317</v>
       </c>
     </row>
     <row r="433">
@@ -19404,7 +19404,7 @@
         <v>0.118</v>
       </c>
       <c r="I433" t="n">
-        <v>0.353</v>
+        <v>0.177</v>
       </c>
     </row>
     <row r="434">
@@ -19441,7 +19441,7 @@
         <v>0.215</v>
       </c>
       <c r="I434" t="n">
-        <v>0.641</v>
+        <v>0.276</v>
       </c>
     </row>
     <row r="435">
@@ -19478,7 +19478,7 @@
         <v>0.28</v>
       </c>
       <c r="I435" t="n">
-        <v>0.641</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="436">
@@ -19515,7 +19515,7 @@
         <v>0.445</v>
       </c>
       <c r="I436" t="n">
-        <v>0.791</v>
+        <v>1</v>
       </c>
     </row>
     <row r="437">
@@ -19552,7 +19552,7 @@
         <v>0.07489999999999999</v>
       </c>
       <c r="I437" t="n">
-        <v>0.6</v>
+        <v>0.225</v>
       </c>
     </row>
     <row r="438">
@@ -19626,7 +19626,7 @@
         <v>0.124</v>
       </c>
       <c r="I439" t="n">
-        <v>0.641</v>
+        <v>0.186</v>
       </c>
     </row>
     <row r="440">
@@ -19663,7 +19663,7 @@
         <v>0.321</v>
       </c>
       <c r="I440" t="n">
-        <v>0.641</v>
+        <v>0.482</v>
       </c>
     </row>
     <row r="441">
@@ -19737,7 +19737,7 @@
         <v>0.281</v>
       </c>
       <c r="I442" t="n">
-        <v>0.641</v>
+        <v>0.331</v>
       </c>
     </row>
     <row r="443">
@@ -19774,7 +19774,7 @@
         <v>0.0354</v>
       </c>
       <c r="I443" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.106</v>
       </c>
     </row>
     <row r="444">
@@ -19811,7 +19811,7 @@
         <v>0.309</v>
       </c>
       <c r="I444" t="n">
-        <v>0.641</v>
+        <v>0.428</v>
       </c>
     </row>
     <row r="445">
@@ -19848,7 +19848,7 @@
         <v>0.759</v>
       </c>
       <c r="I445" t="n">
-        <v>0.951</v>
+        <v>0.872</v>
       </c>
     </row>
     <row r="446">
@@ -19885,7 +19885,7 @@
         <v>0.592</v>
       </c>
       <c r="I446" t="n">
-        <v>0.947</v>
+        <v>1</v>
       </c>
     </row>
     <row r="447">
@@ -19959,7 +19959,7 @@
         <v>0.705</v>
       </c>
       <c r="I448" t="n">
-        <v>0.951</v>
+        <v>0.793</v>
       </c>
     </row>
     <row r="449">
@@ -19996,7 +19996,7 @@
         <v>0.773</v>
       </c>
       <c r="I449" t="n">
-        <v>0.951</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="450">
@@ -20033,7 +20033,7 @@
         <v>0.0293</v>
       </c>
       <c r="I450" t="n">
-        <v>0.09379999999999999</v>
+        <v>0.08790000000000001</v>
       </c>
     </row>
     <row r="451">
@@ -20070,7 +20070,7 @@
         <v>0.000595</v>
       </c>
       <c r="I451" t="n">
-        <v>0.00317</v>
+        <v>0.00205</v>
       </c>
     </row>
     <row r="452">
@@ -20107,7 +20107,7 @@
         <v>1.05e-05</v>
       </c>
       <c r="I452" t="n">
-        <v>8.43e-05</v>
+        <v>9.450000000000001e-05</v>
       </c>
     </row>
     <row r="453">
@@ -20144,7 +20144,7 @@
         <v>1.37e-09</v>
       </c>
       <c r="I453" t="n">
-        <v>2.19e-08</v>
+        <v>1.23e-08</v>
       </c>
     </row>
     <row r="454">
@@ -20181,7 +20181,7 @@
         <v>0.0645</v>
       </c>
       <c r="I454" t="n">
-        <v>0.148</v>
+        <v>0.581</v>
       </c>
     </row>
     <row r="455">
@@ -20218,7 +20218,7 @@
         <v>0.803</v>
       </c>
       <c r="I455" t="n">
-        <v>0.918</v>
+        <v>0.803</v>
       </c>
     </row>
     <row r="456">
@@ -20255,7 +20255,7 @@
         <v>0.214</v>
       </c>
       <c r="I456" t="n">
-        <v>0.343</v>
+        <v>0.642</v>
       </c>
     </row>
     <row r="457">
@@ -20329,7 +20329,7 @@
         <v>0.352</v>
       </c>
       <c r="I458" t="n">
-        <v>0.469</v>
+        <v>0.528</v>
       </c>
     </row>
     <row r="459">
@@ -20366,7 +20366,7 @@
         <v>0.00511</v>
       </c>
       <c r="I459" t="n">
-        <v>0.0204</v>
+        <v>0.046</v>
       </c>
     </row>
     <row r="460">
@@ -20403,7 +20403,7 @@
         <v>0.048</v>
       </c>
       <c r="I460" t="n">
-        <v>0.128</v>
+        <v>0.144</v>
       </c>
     </row>
     <row r="461">
@@ -20440,7 +20440,7 @@
         <v>0.339</v>
       </c>
       <c r="I461" t="n">
-        <v>0.469</v>
+        <v>1</v>
       </c>
     </row>
     <row r="462">
@@ -20514,7 +20514,7 @@
         <v>0.197</v>
       </c>
       <c r="I463" t="n">
-        <v>0.343</v>
+        <v>0.443</v>
       </c>
     </row>
     <row r="464">
@@ -20551,7 +20551,7 @@
         <v>0.72</v>
       </c>
       <c r="I464" t="n">
-        <v>0.887</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="465">
@@ -20588,7 +20588,7 @@
         <v>0.0803</v>
       </c>
       <c r="I465" t="n">
-        <v>0.161</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="466">
@@ -20625,7 +20625,7 @@
         <v>0.000256</v>
       </c>
       <c r="I466" t="n">
-        <v>0.00205</v>
+        <v>0.0023</v>
       </c>
     </row>
     <row r="467">
@@ -20662,7 +20662,7 @@
         <v>0.0262</v>
       </c>
       <c r="I467" t="n">
-        <v>0.0964</v>
+        <v>0.0475</v>
       </c>
     </row>
     <row r="468">
@@ -20699,7 +20699,7 @@
         <v>0.00483</v>
       </c>
       <c r="I468" t="n">
-        <v>0.0258</v>
+        <v>0.0435</v>
       </c>
     </row>
     <row r="469">
@@ -20736,7 +20736,7 @@
         <v>2.84e-07</v>
       </c>
       <c r="I469" t="n">
-        <v>4.54e-06</v>
+        <v>2.56e-06</v>
       </c>
     </row>
     <row r="470">
@@ -20773,7 +20773,7 @@
         <v>0.0361</v>
       </c>
       <c r="I470" t="n">
-        <v>0.0964</v>
+        <v>0.325</v>
       </c>
     </row>
     <row r="471">
@@ -20810,7 +20810,7 @@
         <v>0.127</v>
       </c>
       <c r="I471" t="n">
-        <v>0.253</v>
+        <v>0.153</v>
       </c>
     </row>
     <row r="472">
@@ -20847,7 +20847,7 @@
         <v>0.754</v>
       </c>
       <c r="I472" t="n">
-        <v>0.804</v>
+        <v>0.754</v>
       </c>
     </row>
     <row r="473">
@@ -20921,7 +20921,7 @@
         <v>0.667</v>
       </c>
       <c r="I474" t="n">
-        <v>0.762</v>
+        <v>0.858</v>
       </c>
     </row>
     <row r="475">
@@ -20958,7 +20958,7 @@
         <v>0.0355</v>
       </c>
       <c r="I475" t="n">
-        <v>0.0964</v>
+        <v>0.319</v>
       </c>
     </row>
     <row r="476">
@@ -20995,7 +20995,7 @@
         <v>0.339</v>
       </c>
       <c r="I476" t="n">
-        <v>0.493</v>
+        <v>0.721</v>
       </c>
     </row>
     <row r="477">
@@ -21032,7 +21032,7 @@
         <v>0.0906</v>
       </c>
       <c r="I477" t="n">
-        <v>0.207</v>
+        <v>0.279</v>
       </c>
     </row>
     <row r="478">
@@ -21069,7 +21069,7 @@
         <v>0.22</v>
       </c>
       <c r="I478" t="n">
-        <v>0.391</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="479">
@@ -21106,7 +21106,7 @@
         <v>0.447</v>
       </c>
       <c r="I479" t="n">
-        <v>0.573</v>
+        <v>0.447</v>
       </c>
     </row>
     <row r="480">
@@ -21143,7 +21143,7 @@
         <v>0.465</v>
       </c>
       <c r="I480" t="n">
-        <v>0.573</v>
+        <v>0.523</v>
       </c>
     </row>
     <row r="481">
@@ -21180,7 +21180,7 @@
         <v>0.281</v>
       </c>
       <c r="I481" t="n">
-        <v>0.45</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="482">
@@ -21217,7 +21217,7 @@
         <v>0.127</v>
       </c>
       <c r="I482" t="n">
-        <v>0.297</v>
+        <v>0.191</v>
       </c>
     </row>
     <row r="483">
@@ -21254,7 +21254,7 @@
         <v>0.0504</v>
       </c>
       <c r="I483" t="n">
-        <v>0.205</v>
+        <v>0.227</v>
       </c>
     </row>
     <row r="484">
@@ -21328,7 +21328,7 @@
         <v>0.24</v>
       </c>
       <c r="I485" t="n">
-        <v>0.427</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="486">
@@ -21365,7 +21365,7 @@
         <v>0.389</v>
       </c>
       <c r="I486" t="n">
-        <v>0.479</v>
+        <v>0.913</v>
       </c>
     </row>
     <row r="487">
@@ -21402,7 +21402,7 @@
         <v>0.376</v>
       </c>
       <c r="I487" t="n">
-        <v>0.479</v>
+        <v>0.483</v>
       </c>
     </row>
     <row r="488">
@@ -21439,7 +21439,7 @@
         <v>0.193</v>
       </c>
       <c r="I488" t="n">
-        <v>0.387</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="489">
@@ -21513,7 +21513,7 @@
         <v>0.378</v>
       </c>
       <c r="I490" t="n">
-        <v>0.479</v>
+        <v>0.425</v>
       </c>
     </row>
     <row r="491">
@@ -21550,7 +21550,7 @@
         <v>0.0156</v>
       </c>
       <c r="I491" t="n">
-        <v>0.125</v>
+        <v>0.0702</v>
       </c>
     </row>
     <row r="492">
@@ -21587,7 +21587,7 @@
         <v>0.0513</v>
       </c>
       <c r="I492" t="n">
-        <v>0.205</v>
+        <v>0.09229999999999999</v>
       </c>
     </row>
     <row r="493">
@@ -21624,7 +21624,7 @@
         <v>0.853</v>
       </c>
       <c r="I493" t="n">
-        <v>0.975</v>
+        <v>1</v>
       </c>
     </row>
     <row r="494">
@@ -21661,7 +21661,7 @@
         <v>0.13</v>
       </c>
       <c r="I494" t="n">
-        <v>0.297</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="495">
@@ -21698,7 +21698,7 @@
         <v>0.282</v>
       </c>
       <c r="I495" t="n">
-        <v>0.451</v>
+        <v>0.503</v>
       </c>
     </row>
     <row r="496">
@@ -21735,7 +21735,7 @@
         <v>0.0141</v>
       </c>
       <c r="I496" t="n">
-        <v>0.125</v>
+        <v>0.0423</v>
       </c>
     </row>
     <row r="497">
@@ -21772,7 +21772,7 @@
         <v>0.118</v>
       </c>
       <c r="I497" t="n">
-        <v>0.297</v>
+        <v>0.177</v>
       </c>
     </row>
     <row r="498">
@@ -21809,7 +21809,7 @@
         <v>0.19</v>
       </c>
       <c r="I498" t="n">
-        <v>0.338</v>
+        <v>0.276</v>
       </c>
     </row>
     <row r="499">
@@ -21846,7 +21846,7 @@
         <v>0.00173</v>
       </c>
       <c r="I499" t="n">
-        <v>0.00902</v>
+        <v>0.00779</v>
       </c>
     </row>
     <row r="500">
@@ -21883,7 +21883,7 @@
         <v>0.00226</v>
       </c>
       <c r="I500" t="n">
-        <v>0.00902</v>
+        <v>0.0203</v>
       </c>
     </row>
     <row r="501">
@@ -21920,7 +21920,7 @@
         <v>8.46e-08</v>
       </c>
       <c r="I501" t="n">
-        <v>1.35e-06</v>
+        <v>7.61e-07</v>
       </c>
     </row>
     <row r="502">
@@ -21957,7 +21957,7 @@
         <v>0.07290000000000001</v>
       </c>
       <c r="I502" t="n">
-        <v>0.194</v>
+        <v>0.535</v>
       </c>
     </row>
     <row r="503">
@@ -21994,7 +21994,7 @@
         <v>0.448</v>
       </c>
       <c r="I503" t="n">
-        <v>0.597</v>
+        <v>0.504</v>
       </c>
     </row>
     <row r="504">
@@ -22031,7 +22031,7 @@
         <v>0.128</v>
       </c>
       <c r="I504" t="n">
-        <v>0.292</v>
+        <v>0.288</v>
       </c>
     </row>
     <row r="505">
@@ -22105,7 +22105,7 @@
         <v>0.237</v>
       </c>
       <c r="I506" t="n">
-        <v>0.345</v>
+        <v>0.331</v>
       </c>
     </row>
     <row r="507">
@@ -22142,7 +22142,7 @@
         <v>0.0011</v>
       </c>
       <c r="I507" t="n">
-        <v>0.008829999999999999</v>
+        <v>0.009900000000000001</v>
       </c>
     </row>
     <row r="508">
@@ -22179,7 +22179,7 @@
         <v>0.0145</v>
       </c>
       <c r="I508" t="n">
-        <v>0.0464</v>
+        <v>0.0435</v>
       </c>
     </row>
     <row r="509">
@@ -22216,7 +22216,7 @@
         <v>0.5639999999999999</v>
       </c>
       <c r="I509" t="n">
-        <v>0.649</v>
+        <v>0.872</v>
       </c>
     </row>
     <row r="510">
@@ -22253,7 +22253,7 @@
         <v>0.788</v>
       </c>
       <c r="I510" t="n">
-        <v>0.84</v>
+        <v>1</v>
       </c>
     </row>
     <row r="511">
@@ -22290,7 +22290,7 @@
         <v>0.151</v>
       </c>
       <c r="I511" t="n">
-        <v>0.303</v>
+        <v>0.493</v>
       </c>
     </row>
     <row r="512">
@@ -22327,7 +22327,7 @@
         <v>0.212</v>
       </c>
       <c r="I512" t="n">
-        <v>0.339</v>
+        <v>0.477</v>
       </c>
     </row>
     <row r="513">
@@ -22364,7 +22364,7 @@
         <v>0.5679999999999999</v>
       </c>
       <c r="I513" t="n">
-        <v>0.649</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="514">
@@ -22401,7 +22401,7 @@
         <v>0.39</v>
       </c>
       <c r="I514" t="n">
-        <v>0.969</v>
+        <v>0.439</v>
       </c>
     </row>
     <row r="515">
@@ -22438,7 +22438,7 @@
         <v>0.0113</v>
       </c>
       <c r="I515" t="n">
-        <v>0.0699</v>
+        <v>0.0203</v>
       </c>
     </row>
     <row r="516">
@@ -22549,7 +22549,7 @@
         <v>0.424</v>
       </c>
       <c r="I518" t="n">
-        <v>0.969</v>
+        <v>1</v>
       </c>
     </row>
     <row r="519">
@@ -22586,7 +22586,7 @@
         <v>0.0498</v>
       </c>
       <c r="I519" t="n">
-        <v>0.199</v>
+        <v>0.149</v>
       </c>
     </row>
     <row r="520">
@@ -22623,7 +22623,7 @@
         <v>0.545</v>
       </c>
       <c r="I520" t="n">
-        <v>1</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="521">
@@ -22660,7 +22660,7 @@
         <v>0.0131</v>
       </c>
       <c r="I521" t="n">
-        <v>0.0699</v>
+        <v>0.118</v>
       </c>
     </row>
     <row r="522">
@@ -22697,7 +22697,7 @@
         <v>0.000733</v>
       </c>
       <c r="I522" t="n">
-        <v>0.0117</v>
+        <v>0.0066</v>
       </c>
     </row>
     <row r="523">
@@ -22734,7 +22734,7 @@
         <v>0.879</v>
       </c>
       <c r="I523" t="n">
-        <v>1</v>
+        <v>0.879</v>
       </c>
     </row>
     <row r="524">
@@ -22771,7 +22771,7 @@
         <v>0.105</v>
       </c>
       <c r="I524" t="n">
-        <v>0.337</v>
+        <v>0.236</v>
       </c>
     </row>
     <row r="525">
@@ -22882,7 +22882,7 @@
         <v>0.6909999999999999</v>
       </c>
       <c r="I527" t="n">
-        <v>1</v>
+        <v>0.777</v>
       </c>
     </row>
     <row r="528">
@@ -22919,7 +22919,7 @@
         <v>0.905</v>
       </c>
       <c r="I528" t="n">
-        <v>1</v>
+        <v>0.905</v>
       </c>
     </row>
     <row r="529">
@@ -22956,7 +22956,7 @@
         <v>0.644</v>
       </c>
       <c r="I529" t="n">
-        <v>1</v>
+        <v>0.725</v>
       </c>
     </row>
     <row r="530">
@@ -22993,7 +22993,7 @@
         <v>0.000553</v>
       </c>
       <c r="I530" t="n">
-        <v>0.00885</v>
+        <v>0.00249</v>
       </c>
     </row>
     <row r="531">
@@ -23030,7 +23030,7 @@
         <v>0.117</v>
       </c>
       <c r="I531" t="n">
-        <v>0.243</v>
+        <v>0.176</v>
       </c>
     </row>
     <row r="532">
@@ -23067,7 +23067,7 @@
         <v>0.827</v>
       </c>
       <c r="I532" t="n">
-        <v>0.977</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="533">
@@ -23104,7 +23104,7 @@
         <v>0.121</v>
       </c>
       <c r="I533" t="n">
-        <v>0.243</v>
+        <v>0.544</v>
       </c>
     </row>
     <row r="534">
@@ -23141,7 +23141,7 @@
         <v>0.0828</v>
       </c>
       <c r="I534" t="n">
-        <v>0.221</v>
+        <v>0.373</v>
       </c>
     </row>
     <row r="535">
@@ -23178,7 +23178,7 @@
         <v>0.00441</v>
       </c>
       <c r="I535" t="n">
-        <v>0.0353</v>
+        <v>0.0181</v>
       </c>
     </row>
     <row r="536">
@@ -23215,7 +23215,7 @@
         <v>0.0297</v>
       </c>
       <c r="I536" t="n">
-        <v>0.119</v>
+        <v>0.112</v>
       </c>
     </row>
     <row r="537">
@@ -23252,7 +23252,7 @@
         <v>0.346</v>
       </c>
       <c r="I537" t="n">
-        <v>0.503</v>
+        <v>1</v>
       </c>
     </row>
     <row r="538">
@@ -23289,7 +23289,7 @@
         <v>0.481</v>
       </c>
       <c r="I538" t="n">
-        <v>0.641</v>
+        <v>0.858</v>
       </c>
     </row>
     <row r="539">
@@ -23326,7 +23326,7 @@
         <v>0.34</v>
       </c>
       <c r="I539" t="n">
-        <v>0.503</v>
+        <v>1</v>
       </c>
     </row>
     <row r="540">
@@ -23363,7 +23363,7 @@
         <v>0.0201</v>
       </c>
       <c r="I540" t="n">
-        <v>0.107</v>
+        <v>0.171</v>
       </c>
     </row>
     <row r="541">
@@ -23400,7 +23400,7 @@
         <v>0.0508</v>
       </c>
       <c r="I541" t="n">
-        <v>0.162</v>
+        <v>0.279</v>
       </c>
     </row>
     <row r="542">
@@ -23474,7 +23474,7 @@
         <v>0.138</v>
       </c>
       <c r="I543" t="n">
-        <v>0.245</v>
+        <v>0.207</v>
       </c>
     </row>
     <row r="544">
@@ -23548,7 +23548,7 @@
         <v>0.855</v>
       </c>
       <c r="I545" t="n">
-        <v>0.977</v>
+        <v>0.962</v>
       </c>
     </row>
     <row r="546">
@@ -23585,7 +23585,7 @@
         <v>3.03e-07</v>
       </c>
       <c r="I546" t="n">
-        <v>4.85e-06</v>
+        <v>2.73e-06</v>
       </c>
     </row>
     <row r="547">
@@ -23659,7 +23659,7 @@
         <v>0.352</v>
       </c>
       <c r="I548" t="n">
-        <v>0.592</v>
+        <v>0.792</v>
       </c>
     </row>
     <row r="549">
@@ -23696,7 +23696,7 @@
         <v>0.488</v>
       </c>
       <c r="I549" t="n">
-        <v>0.651</v>
+        <v>0.878</v>
       </c>
     </row>
     <row r="550">
@@ -23733,7 +23733,7 @@
         <v>0.012</v>
       </c>
       <c r="I550" t="n">
-        <v>0.0274</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="551">
@@ -23770,7 +23770,7 @@
         <v>1.44e-05</v>
       </c>
       <c r="I551" t="n">
-        <v>7.7e-05</v>
+        <v>0.00013</v>
       </c>
     </row>
     <row r="552">
@@ -23807,7 +23807,7 @@
         <v>2.09e-06</v>
       </c>
       <c r="I552" t="n">
-        <v>1.67e-05</v>
+        <v>1.88e-05</v>
       </c>
     </row>
     <row r="553">
@@ -23844,7 +23844,7 @@
         <v>0.637</v>
       </c>
       <c r="I553" t="n">
-        <v>0.784</v>
+        <v>1</v>
       </c>
     </row>
     <row r="554">
@@ -23881,7 +23881,7 @@
         <v>3.3e-05</v>
       </c>
       <c r="I554" t="n">
-        <v>0.000127</v>
+        <v>0.000297</v>
       </c>
     </row>
     <row r="555">
@@ -23918,7 +23918,7 @@
         <v>0.37</v>
       </c>
       <c r="I555" t="n">
-        <v>0.592</v>
+        <v>0.555</v>
       </c>
     </row>
     <row r="556">
@@ -23955,7 +23955,7 @@
         <v>0.752</v>
       </c>
       <c r="I556" t="n">
-        <v>0.86</v>
+        <v>0.752</v>
       </c>
     </row>
     <row r="557">
@@ -23992,7 +23992,7 @@
         <v>3.96e-05</v>
       </c>
       <c r="I557" t="n">
-        <v>0.000127</v>
+        <v>0.000356</v>
       </c>
     </row>
     <row r="558">
@@ -24029,7 +24029,7 @@
         <v>0.488</v>
       </c>
       <c r="I558" t="n">
-        <v>0.651</v>
+        <v>1</v>
       </c>
     </row>
     <row r="559">
@@ -24066,7 +24066,7 @@
         <v>7.38e-05</v>
       </c>
       <c r="I559" t="n">
-        <v>0.000197</v>
+        <v>0.000664</v>
       </c>
     </row>
     <row r="560">
@@ -24103,7 +24103,7 @@
         <v>0.33</v>
       </c>
       <c r="I560" t="n">
-        <v>0.592</v>
+        <v>0.408</v>
       </c>
     </row>
     <row r="561">
@@ -24214,7 +24214,7 @@
         <v>0.0697</v>
       </c>
       <c r="I563" t="n">
-        <v>0.358</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="564">
@@ -24288,7 +24288,7 @@
         <v>0.681</v>
       </c>
       <c r="I565" t="n">
-        <v>0.991</v>
+        <v>1</v>
       </c>
     </row>
     <row r="566">
@@ -24325,7 +24325,7 @@
         <v>0.119</v>
       </c>
       <c r="I566" t="n">
-        <v>0.358</v>
+        <v>0.535</v>
       </c>
     </row>
     <row r="567">
@@ -24362,7 +24362,7 @@
         <v>0.0006400000000000001</v>
       </c>
       <c r="I567" t="n">
-        <v>0.00512</v>
+        <v>0.00576</v>
       </c>
     </row>
     <row r="568">
@@ -24399,7 +24399,7 @@
         <v>0.101</v>
       </c>
       <c r="I568" t="n">
-        <v>0.358</v>
+        <v>0.288</v>
       </c>
     </row>
     <row r="569">
@@ -24436,7 +24436,7 @@
         <v>0.75</v>
       </c>
       <c r="I569" t="n">
-        <v>0.999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="570">
@@ -24473,7 +24473,7 @@
         <v>3.48e-05</v>
       </c>
       <c r="I570" t="n">
-        <v>0.000556</v>
+        <v>0.000313</v>
       </c>
     </row>
     <row r="571">
@@ -24510,7 +24510,7 @@
         <v>0.647</v>
       </c>
       <c r="I571" t="n">
-        <v>0.991</v>
+        <v>0.728</v>
       </c>
     </row>
     <row r="572">
@@ -24547,7 +24547,7 @@
         <v>0.333</v>
       </c>
       <c r="I572" t="n">
-        <v>0.761</v>
+        <v>0.428</v>
       </c>
     </row>
     <row r="573">
@@ -24584,7 +24584,7 @@
         <v>0.134</v>
       </c>
       <c r="I573" t="n">
-        <v>0.358</v>
+        <v>0.603</v>
       </c>
     </row>
     <row r="574">
@@ -24658,7 +24658,7 @@
         <v>0.598</v>
       </c>
       <c r="I575" t="n">
-        <v>0.991</v>
+        <v>0.897</v>
       </c>
     </row>
     <row r="576">
@@ -24695,7 +24695,7 @@
         <v>0.556</v>
       </c>
       <c r="I576" t="n">
-        <v>0.991</v>
+        <v>0.793</v>
       </c>
     </row>
     <row r="577">
@@ -24922,7 +24922,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>92.9*†</t>
+          <t>92.9*</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -25057,7 +25057,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>68.4*†</t>
+          <t>68.4*</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">

--- a/eval/results/statistical_tests_full150.xlsx
+++ b/eval/results/statistical_tests_full150.xlsx
@@ -24746,7 +24746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24817,7 +24817,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>89.3***</t>
+          <t>89.3**</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -24877,12 +24877,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>90.2***</t>
+          <t>90.2**</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>92.4***</t>
+          <t>92.4**</t>
         </is>
       </c>
     </row>
@@ -24927,7 +24927,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>95.3**</t>
+          <t>95.3*</t>
         </is>
       </c>
     </row>
@@ -24938,41 +24938,41 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>92.6</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>60.3</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>81.5**</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>75.0*†</t>
+          <t>67.5</t>
         </is>
       </c>
     </row>
@@ -24983,41 +24983,41 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>63.5</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>85.9**</t>
+          <t>92.6</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>70.1</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>82.1</t>
+          <t>81.5**</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>75.0</t>
         </is>
       </c>
     </row>
@@ -25028,86 +25028,86 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>78.0**</t>
+          <t>85.9**</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>70.1</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>68.4*</t>
+          <t>82.1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>61.2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Llama3.1-70B</t>
+          <t>GPT-4o</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>78.0*</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>68.4*</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>93.1***</t>
+          <t>29.8</t>
         </is>
       </c>
     </row>
@@ -25118,41 +25118,41 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>92.9</t>
+          <t>93.1**</t>
         </is>
       </c>
     </row>
@@ -25163,41 +25163,41 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>98.1***</t>
+          <t>96.1</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>97.5*</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>78.1</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>84.9</t>
+          <t>85.9</t>
         </is>
       </c>
     </row>
@@ -25208,41 +25208,41 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>77.1***</t>
+          <t>98.1**</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>78.3***</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>55.2</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>70.1</t>
+          <t>84.9</t>
         </is>
       </c>
     </row>
@@ -25253,86 +25253,86 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>69.7**</t>
+          <t>77.1**</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>68.3***</t>
+          <t>78.3**</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>55.2</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>70.1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Llama3.1-8B</t>
+          <t>Llama3.1-70B</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>93.1</t>
+          <t>36.5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>69.7**</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>68.3**</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>66.7</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>100.0***</t>
+          <t>49.1</t>
         </is>
       </c>
     </row>
@@ -25343,41 +25343,41 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>84.9</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>60.9</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>79.3***</t>
+          <t>100.0**</t>
         </is>
       </c>
     </row>
@@ -25388,41 +25388,41 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>59.1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>96.4</t>
+          <t>87.5*</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>62.4</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>97.6***</t>
+          <t>100.0</t>
         </is>
       </c>
     </row>
@@ -25433,41 +25433,41 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>97.1</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>84.9</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>60.9</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>78.6***</t>
+          <t>79.3**</t>
         </is>
       </c>
     </row>
@@ -25478,41 +25478,41 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>92.3</t>
+          <t>96.4</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.1</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>62.4</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>91.8***</t>
+          <t>97.6**</t>
         </is>
       </c>
     </row>
@@ -25523,41 +25523,131 @@
         </is>
       </c>
       <c r="B18" t="n">
+        <v>9</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Which HIV genes were reported to have been sequenced?</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>97.1</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>98.3</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>94.3</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>53.2</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>46.8</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>78.6**</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>12</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>85.7</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>92.3</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>69.1</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>91.8**</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
         <v>14</v>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>76.1</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>88.9</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>65.1</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>74.0</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>65.8</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>97.3***</t>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>97.3**</t>
         </is>
       </c>
     </row>

--- a/eval/results/statistical_tests_full150.xlsx
+++ b/eval/results/statistical_tests_full150.xlsx
@@ -504,22 +504,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.001</v>
+        <v>0.0009790000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>0.835</v>
+        <v>0.837</v>
       </c>
       <c r="G2" t="n">
-        <v>0.901</v>
+        <v>0.903</v>
       </c>
       <c r="H2" t="n">
-        <v>0.117</v>
+        <v>0.115</v>
       </c>
       <c r="I2" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.0697</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0072</v>
+        <v>0.00705</v>
       </c>
     </row>
     <row r="3">
@@ -547,19 +547,19 @@
         <v>0.00146</v>
       </c>
       <c r="F3" t="n">
-        <v>0.835</v>
+        <v>0.837</v>
       </c>
       <c r="G3" t="n">
-        <v>0.901</v>
+        <v>0.903</v>
       </c>
       <c r="H3" t="n">
-        <v>0.117</v>
+        <v>0.115</v>
       </c>
       <c r="I3" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.0697</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00957</v>
+        <v>0.00967</v>
       </c>
     </row>
     <row r="4">
@@ -584,22 +584,22 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.01</v>
+        <v>0.0104</v>
       </c>
       <c r="F4" t="n">
-        <v>0.835</v>
+        <v>0.837</v>
       </c>
       <c r="G4" t="n">
-        <v>0.878</v>
+        <v>0.88</v>
       </c>
       <c r="H4" t="n">
-        <v>0.117</v>
+        <v>0.115</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0842</v>
+        <v>0.0828</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0262</v>
+        <v>0.0267</v>
       </c>
     </row>
     <row r="5">
@@ -627,16 +627,16 @@
         <v>0.0243</v>
       </c>
       <c r="F5" t="n">
-        <v>0.835</v>
+        <v>0.837</v>
       </c>
       <c r="G5" t="n">
-        <v>0.878</v>
+        <v>0.88</v>
       </c>
       <c r="H5" t="n">
-        <v>0.117</v>
+        <v>0.115</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0842</v>
+        <v>0.0828</v>
       </c>
       <c r="J5" t="n">
         <v>0.0486</v>
@@ -664,22 +664,22 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.347</v>
+        <v>0.364</v>
       </c>
       <c r="F6" t="n">
-        <v>0.835</v>
+        <v>0.837</v>
       </c>
       <c r="G6" t="n">
-        <v>0.843</v>
+        <v>0.845</v>
       </c>
       <c r="H6" t="n">
-        <v>0.117</v>
+        <v>0.115</v>
       </c>
       <c r="I6" t="n">
-        <v>0.103</v>
+        <v>0.102</v>
       </c>
       <c r="J6" t="n">
-        <v>0.39</v>
+        <v>0.409</v>
       </c>
     </row>
     <row r="7">
@@ -704,22 +704,22 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.293</v>
+        <v>0.306</v>
       </c>
       <c r="F7" t="n">
-        <v>0.835</v>
+        <v>0.837</v>
       </c>
       <c r="G7" t="n">
-        <v>0.843</v>
+        <v>0.845</v>
       </c>
       <c r="H7" t="n">
-        <v>0.117</v>
+        <v>0.115</v>
       </c>
       <c r="I7" t="n">
-        <v>0.103</v>
+        <v>0.102</v>
       </c>
       <c r="J7" t="n">
-        <v>0.34</v>
+        <v>0.355</v>
       </c>
     </row>
     <row r="8">
@@ -744,22 +744,22 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.0144</v>
+        <v>0.0142</v>
       </c>
       <c r="F8" t="n">
-        <v>0.797</v>
+        <v>0.799</v>
       </c>
       <c r="G8" t="n">
-        <v>0.851</v>
+        <v>0.853</v>
       </c>
       <c r="H8" t="n">
-        <v>0.155</v>
+        <v>0.154</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0931</v>
+        <v>0.0919</v>
       </c>
       <c r="J8" t="n">
-        <v>0.032</v>
+        <v>0.0301</v>
       </c>
     </row>
     <row r="9">
@@ -784,22 +784,22 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.00186</v>
+        <v>0.00188</v>
       </c>
       <c r="F9" t="n">
-        <v>0.797</v>
+        <v>0.799</v>
       </c>
       <c r="G9" t="n">
-        <v>0.851</v>
+        <v>0.853</v>
       </c>
       <c r="H9" t="n">
-        <v>0.155</v>
+        <v>0.154</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0931</v>
+        <v>0.0919</v>
       </c>
       <c r="J9" t="n">
-        <v>0.00957</v>
+        <v>0.00967</v>
       </c>
     </row>
     <row r="10">
@@ -824,19 +824,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.161</v>
+        <v>0.159</v>
       </c>
       <c r="F10" t="n">
-        <v>0.797</v>
+        <v>0.799</v>
       </c>
       <c r="G10" t="n">
-        <v>0.829</v>
+        <v>0.831</v>
       </c>
       <c r="H10" t="n">
-        <v>0.155</v>
+        <v>0.154</v>
       </c>
       <c r="I10" t="n">
-        <v>0.11</v>
+        <v>0.109</v>
       </c>
       <c r="J10" t="n">
         <v>0.211</v>
@@ -864,22 +864,22 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.393</v>
+        <v>0.438</v>
       </c>
       <c r="F11" t="n">
-        <v>0.797</v>
+        <v>0.799</v>
       </c>
       <c r="G11" t="n">
-        <v>0.829</v>
+        <v>0.831</v>
       </c>
       <c r="H11" t="n">
-        <v>0.155</v>
+        <v>0.154</v>
       </c>
       <c r="I11" t="n">
-        <v>0.11</v>
+        <v>0.109</v>
       </c>
       <c r="J11" t="n">
-        <v>0.442</v>
+        <v>0.493</v>
       </c>
     </row>
     <row r="12">
@@ -904,22 +904,22 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.008540000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>0.797</v>
+        <v>0.799</v>
       </c>
       <c r="G12" t="n">
-        <v>0.87</v>
+        <v>0.873</v>
       </c>
       <c r="H12" t="n">
-        <v>0.155</v>
+        <v>0.154</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0796</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0262</v>
+        <v>0.0256</v>
       </c>
     </row>
     <row r="13">
@@ -944,19 +944,19 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.008869999999999999</v>
+        <v>0.008920000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>0.797</v>
+        <v>0.799</v>
       </c>
       <c r="G13" t="n">
-        <v>0.87</v>
+        <v>0.873</v>
       </c>
       <c r="H13" t="n">
-        <v>0.155</v>
+        <v>0.154</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0796</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="J13" t="n">
         <v>0.0216</v>
@@ -987,16 +987,16 @@
         <v>0.661</v>
       </c>
       <c r="F14" t="n">
-        <v>0.779</v>
+        <v>0.78</v>
       </c>
       <c r="G14" t="n">
-        <v>0.785</v>
+        <v>0.787</v>
       </c>
       <c r="H14" t="n">
-        <v>0.132</v>
+        <v>0.13</v>
       </c>
       <c r="I14" t="n">
-        <v>0.116</v>
+        <v>0.115</v>
       </c>
       <c r="J14" t="n">
         <v>0.7</v>
@@ -1024,22 +1024,22 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.777</v>
+        <v>0.753</v>
       </c>
       <c r="F15" t="n">
-        <v>0.779</v>
+        <v>0.78</v>
       </c>
       <c r="G15" t="n">
-        <v>0.785</v>
+        <v>0.787</v>
       </c>
       <c r="H15" t="n">
-        <v>0.132</v>
+        <v>0.13</v>
       </c>
       <c r="I15" t="n">
-        <v>0.116</v>
+        <v>0.115</v>
       </c>
       <c r="J15" t="n">
-        <v>0.823</v>
+        <v>0.797</v>
       </c>
     </row>
     <row r="16">
@@ -1067,16 +1067,16 @@
         <v>0.00558</v>
       </c>
       <c r="F16" t="n">
-        <v>0.779</v>
+        <v>0.78</v>
       </c>
       <c r="G16" t="n">
-        <v>0.705</v>
+        <v>0.707</v>
       </c>
       <c r="H16" t="n">
-        <v>0.132</v>
+        <v>0.13</v>
       </c>
       <c r="I16" t="n">
-        <v>0.107</v>
+        <v>0.106</v>
       </c>
       <c r="J16" t="n">
         <v>0.0223</v>
@@ -1104,22 +1104,22 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.009719999999999999</v>
+        <v>0.0106</v>
       </c>
       <c r="F17" t="n">
-        <v>0.779</v>
+        <v>0.78</v>
       </c>
       <c r="G17" t="n">
-        <v>0.705</v>
+        <v>0.707</v>
       </c>
       <c r="H17" t="n">
-        <v>0.132</v>
+        <v>0.13</v>
       </c>
       <c r="I17" t="n">
-        <v>0.107</v>
+        <v>0.106</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0219</v>
+        <v>0.0233</v>
       </c>
     </row>
     <row r="18">
@@ -1147,13 +1147,13 @@
         <v>0.914</v>
       </c>
       <c r="F18" t="n">
-        <v>0.779</v>
+        <v>0.78</v>
       </c>
       <c r="G18" t="n">
-        <v>0.781</v>
+        <v>0.782</v>
       </c>
       <c r="H18" t="n">
-        <v>0.132</v>
+        <v>0.13</v>
       </c>
       <c r="I18" t="n">
         <v>0.11</v>
@@ -1184,22 +1184,22 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.842</v>
+        <v>0.82</v>
       </c>
       <c r="F19" t="n">
-        <v>0.779</v>
+        <v>0.78</v>
       </c>
       <c r="G19" t="n">
-        <v>0.781</v>
+        <v>0.782</v>
       </c>
       <c r="H19" t="n">
-        <v>0.132</v>
+        <v>0.13</v>
       </c>
       <c r="I19" t="n">
         <v>0.11</v>
       </c>
       <c r="J19" t="n">
-        <v>0.866</v>
+        <v>0.843</v>
       </c>
     </row>
     <row r="20">
@@ -1384,7 +1384,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.0254</v>
+        <v>0.0253</v>
       </c>
       <c r="F24" t="n">
         <v>0.864</v>
@@ -1399,7 +1399,7 @@
         <v>0.191</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0481</v>
+        <v>0.0479</v>
       </c>
     </row>
     <row r="25">
@@ -1464,7 +1464,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.000894</v>
+        <v>0.0009</v>
       </c>
       <c r="F26" t="n">
         <v>0.793</v>
@@ -1479,7 +1479,7 @@
         <v>0.0954</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0072</v>
+        <v>0.00705</v>
       </c>
     </row>
     <row r="27">
@@ -1519,7 +1519,7 @@
         <v>0.0954</v>
       </c>
       <c r="J27" t="n">
-        <v>0.00957</v>
+        <v>0.00967</v>
       </c>
     </row>
     <row r="28">
@@ -1544,7 +1544,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.00718</v>
+        <v>0.00721</v>
       </c>
       <c r="F28" t="n">
         <v>0.793</v>
@@ -1559,7 +1559,7 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="J28" t="n">
-        <v>0.025</v>
+        <v>0.0243</v>
       </c>
     </row>
     <row r="29">
@@ -1599,7 +1599,7 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="J29" t="n">
-        <v>0.00957</v>
+        <v>0.00967</v>
       </c>
     </row>
     <row r="30">
@@ -1719,7 +1719,7 @@
         <v>0.172</v>
       </c>
       <c r="J32" t="n">
-        <v>0.0481</v>
+        <v>0.0479</v>
       </c>
     </row>
     <row r="33">
@@ -1799,7 +1799,7 @@
         <v>0.226</v>
       </c>
       <c r="J34" t="n">
-        <v>0.0925</v>
+        <v>0.0922</v>
       </c>
     </row>
     <row r="35">
@@ -1944,22 +1944,22 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.0102</v>
+        <v>0.00993</v>
       </c>
       <c r="F38" t="n">
-        <v>0.763</v>
+        <v>0.765</v>
       </c>
       <c r="G38" t="n">
-        <v>0.842</v>
+        <v>0.845</v>
       </c>
       <c r="H38" t="n">
-        <v>0.166</v>
+        <v>0.165</v>
       </c>
       <c r="I38" t="n">
         <v>0.137</v>
       </c>
       <c r="J38" t="n">
-        <v>0.0262</v>
+        <v>0.0267</v>
       </c>
     </row>
     <row r="39">
@@ -1987,13 +1987,13 @@
         <v>0.011</v>
       </c>
       <c r="F39" t="n">
-        <v>0.763</v>
+        <v>0.765</v>
       </c>
       <c r="G39" t="n">
-        <v>0.842</v>
+        <v>0.845</v>
       </c>
       <c r="H39" t="n">
-        <v>0.166</v>
+        <v>0.165</v>
       </c>
       <c r="I39" t="n">
         <v>0.137</v>
@@ -2024,22 +2024,22 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.11</v>
+        <v>0.109</v>
       </c>
       <c r="F40" t="n">
-        <v>0.763</v>
+        <v>0.765</v>
       </c>
       <c r="G40" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="H40" t="n">
-        <v>0.166</v>
+        <v>0.165</v>
       </c>
       <c r="I40" t="n">
         <v>0.185</v>
       </c>
       <c r="J40" t="n">
-        <v>0.158</v>
+        <v>0.157</v>
       </c>
     </row>
     <row r="41">
@@ -2067,13 +2067,13 @@
         <v>0.112</v>
       </c>
       <c r="F41" t="n">
-        <v>0.763</v>
+        <v>0.765</v>
       </c>
       <c r="G41" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="H41" t="n">
-        <v>0.166</v>
+        <v>0.165</v>
       </c>
       <c r="I41" t="n">
         <v>0.185</v>
@@ -2104,22 +2104,22 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.242</v>
+        <v>0.243</v>
       </c>
       <c r="F42" t="n">
-        <v>0.763</v>
+        <v>0.765</v>
       </c>
       <c r="G42" t="n">
-        <v>0.798</v>
+        <v>0.8</v>
       </c>
       <c r="H42" t="n">
-        <v>0.166</v>
+        <v>0.165</v>
       </c>
       <c r="I42" t="n">
-        <v>0.223</v>
+        <v>0.224</v>
       </c>
       <c r="J42" t="n">
-        <v>0.281</v>
+        <v>0.282</v>
       </c>
     </row>
     <row r="43">
@@ -2147,16 +2147,16 @@
         <v>0.221</v>
       </c>
       <c r="F43" t="n">
-        <v>0.763</v>
+        <v>0.765</v>
       </c>
       <c r="G43" t="n">
-        <v>0.798</v>
+        <v>0.8</v>
       </c>
       <c r="H43" t="n">
-        <v>0.166</v>
+        <v>0.165</v>
       </c>
       <c r="I43" t="n">
-        <v>0.223</v>
+        <v>0.224</v>
       </c>
       <c r="J43" t="n">
         <v>0.265</v>
@@ -2184,22 +2184,22 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.11</v>
+        <v>0.109</v>
       </c>
       <c r="F44" t="n">
-        <v>0.755</v>
+        <v>0.758</v>
       </c>
       <c r="G44" t="n">
-        <v>0.703</v>
+        <v>0.706</v>
       </c>
       <c r="H44" t="n">
         <v>0.185</v>
       </c>
       <c r="I44" t="n">
-        <v>0.163</v>
+        <v>0.164</v>
       </c>
       <c r="J44" t="n">
-        <v>0.158</v>
+        <v>0.157</v>
       </c>
     </row>
     <row r="45">
@@ -2224,22 +2224,22 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.156</v>
+        <v>0.14</v>
       </c>
       <c r="F45" t="n">
-        <v>0.755</v>
+        <v>0.758</v>
       </c>
       <c r="G45" t="n">
-        <v>0.703</v>
+        <v>0.706</v>
       </c>
       <c r="H45" t="n">
         <v>0.185</v>
       </c>
       <c r="I45" t="n">
-        <v>0.163</v>
+        <v>0.164</v>
       </c>
       <c r="J45" t="n">
-        <v>0.216</v>
+        <v>0.194</v>
       </c>
     </row>
     <row r="46">
@@ -2264,22 +2264,22 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.0131</v>
+        <v>0.0129</v>
       </c>
       <c r="F46" t="n">
-        <v>0.755</v>
+        <v>0.758</v>
       </c>
       <c r="G46" t="n">
-        <v>0.615</v>
+        <v>0.617</v>
       </c>
       <c r="H46" t="n">
         <v>0.185</v>
       </c>
       <c r="I46" t="n">
-        <v>0.211</v>
+        <v>0.212</v>
       </c>
       <c r="J46" t="n">
-        <v>0.0314</v>
+        <v>0.0301</v>
       </c>
     </row>
     <row r="47">
@@ -2307,16 +2307,16 @@
         <v>0.00898</v>
       </c>
       <c r="F47" t="n">
-        <v>0.755</v>
+        <v>0.758</v>
       </c>
       <c r="G47" t="n">
-        <v>0.615</v>
+        <v>0.617</v>
       </c>
       <c r="H47" t="n">
         <v>0.185</v>
       </c>
       <c r="I47" t="n">
-        <v>0.211</v>
+        <v>0.212</v>
       </c>
       <c r="J47" t="n">
         <v>0.0216</v>
@@ -2344,13 +2344,13 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.0557</v>
+        <v>0.0538</v>
       </c>
       <c r="F48" t="n">
-        <v>0.755</v>
+        <v>0.758</v>
       </c>
       <c r="G48" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="H48" t="n">
         <v>0.185</v>
@@ -2359,7 +2359,7 @@
         <v>0.162</v>
       </c>
       <c r="J48" t="n">
-        <v>0.0955</v>
+        <v>0.0922</v>
       </c>
     </row>
     <row r="49">
@@ -2387,10 +2387,10 @@
         <v>0.0555</v>
       </c>
       <c r="F49" t="n">
-        <v>0.755</v>
+        <v>0.758</v>
       </c>
       <c r="G49" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="H49" t="n">
         <v>0.185</v>
@@ -2424,22 +2424,22 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.000603</v>
+        <v>0.000634</v>
       </c>
       <c r="F50" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="G50" t="n">
-        <v>0.579</v>
+        <v>0.58</v>
       </c>
       <c r="H50" t="n">
-        <v>0.18</v>
+        <v>0.179</v>
       </c>
       <c r="I50" t="n">
         <v>0.147</v>
       </c>
       <c r="J50" t="n">
-        <v>0.0072</v>
+        <v>0.00705</v>
       </c>
     </row>
     <row r="51">
@@ -2467,13 +2467,13 @@
         <v>0.00377</v>
       </c>
       <c r="F51" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="G51" t="n">
-        <v>0.579</v>
+        <v>0.58</v>
       </c>
       <c r="H51" t="n">
-        <v>0.18</v>
+        <v>0.179</v>
       </c>
       <c r="I51" t="n">
         <v>0.147</v>
@@ -2504,22 +2504,22 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.00257</v>
+        <v>0.0026</v>
       </c>
       <c r="F52" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="G52" t="n">
-        <v>0.587</v>
+        <v>0.589</v>
       </c>
       <c r="H52" t="n">
-        <v>0.18</v>
+        <v>0.179</v>
       </c>
       <c r="I52" t="n">
         <v>0.163</v>
       </c>
       <c r="J52" t="n">
-        <v>0.0142</v>
+        <v>0.0141</v>
       </c>
     </row>
     <row r="53">
@@ -2547,13 +2547,13 @@
         <v>0.00641</v>
       </c>
       <c r="F53" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="G53" t="n">
-        <v>0.587</v>
+        <v>0.589</v>
       </c>
       <c r="H53" t="n">
-        <v>0.18</v>
+        <v>0.179</v>
       </c>
       <c r="I53" t="n">
         <v>0.163</v>
@@ -2584,19 +2584,19 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3.05e-05</v>
+        <v>3.17e-05</v>
       </c>
       <c r="F54" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="G54" t="n">
-        <v>0.84</v>
+        <v>0.842</v>
       </c>
       <c r="H54" t="n">
-        <v>0.18</v>
+        <v>0.179</v>
       </c>
       <c r="I54" t="n">
-        <v>0.174</v>
+        <v>0.173</v>
       </c>
       <c r="J54" t="n">
         <v>0.00104</v>
@@ -2627,16 +2627,16 @@
         <v>6.1e-05</v>
       </c>
       <c r="F55" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="G55" t="n">
-        <v>0.84</v>
+        <v>0.842</v>
       </c>
       <c r="H55" t="n">
-        <v>0.18</v>
+        <v>0.179</v>
       </c>
       <c r="I55" t="n">
-        <v>0.174</v>
+        <v>0.173</v>
       </c>
       <c r="J55" t="n">
         <v>0.0022</v>
@@ -2664,22 +2664,22 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.00322</v>
+        <v>0.00321</v>
       </c>
       <c r="F56" t="n">
-        <v>0.797</v>
+        <v>0.798</v>
       </c>
       <c r="G56" t="n">
-        <v>0.874</v>
+        <v>0.875</v>
       </c>
       <c r="H56" t="n">
         <v>0.132</v>
       </c>
       <c r="I56" t="n">
-        <v>0.0919</v>
+        <v>0.092</v>
       </c>
       <c r="J56" t="n">
-        <v>0.0145</v>
+        <v>0.0144</v>
       </c>
     </row>
     <row r="57">
@@ -2707,16 +2707,16 @@
         <v>0.00286</v>
       </c>
       <c r="F57" t="n">
-        <v>0.797</v>
+        <v>0.798</v>
       </c>
       <c r="G57" t="n">
-        <v>0.874</v>
+        <v>0.875</v>
       </c>
       <c r="H57" t="n">
         <v>0.132</v>
       </c>
       <c r="I57" t="n">
-        <v>0.0919</v>
+        <v>0.092</v>
       </c>
       <c r="J57" t="n">
         <v>0.0129</v>
@@ -2744,22 +2744,22 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.193</v>
+        <v>0.195</v>
       </c>
       <c r="F58" t="n">
-        <v>0.797</v>
+        <v>0.798</v>
       </c>
       <c r="G58" t="n">
-        <v>0.83</v>
+        <v>0.832</v>
       </c>
       <c r="H58" t="n">
         <v>0.132</v>
       </c>
       <c r="I58" t="n">
-        <v>0.149</v>
+        <v>0.15</v>
       </c>
       <c r="J58" t="n">
-        <v>0.24</v>
+        <v>0.242</v>
       </c>
     </row>
     <row r="59">
@@ -2787,16 +2787,16 @@
         <v>0.0577</v>
       </c>
       <c r="F59" t="n">
-        <v>0.797</v>
+        <v>0.798</v>
       </c>
       <c r="G59" t="n">
-        <v>0.83</v>
+        <v>0.832</v>
       </c>
       <c r="H59" t="n">
         <v>0.132</v>
       </c>
       <c r="I59" t="n">
-        <v>0.149</v>
+        <v>0.15</v>
       </c>
       <c r="J59" t="n">
         <v>0.0944</v>
@@ -2824,13 +2824,13 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.529</v>
+        <v>0.512</v>
       </c>
       <c r="F60" t="n">
-        <v>0.797</v>
+        <v>0.798</v>
       </c>
       <c r="G60" t="n">
-        <v>0.781</v>
+        <v>0.782</v>
       </c>
       <c r="H60" t="n">
         <v>0.132</v>
@@ -2839,7 +2839,7 @@
         <v>0.188</v>
       </c>
       <c r="J60" t="n">
-        <v>0.577</v>
+        <v>0.5590000000000001</v>
       </c>
     </row>
     <row r="61">
@@ -2864,13 +2864,13 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.98</v>
       </c>
       <c r="F61" t="n">
-        <v>0.797</v>
+        <v>0.798</v>
       </c>
       <c r="G61" t="n">
-        <v>0.781</v>
+        <v>0.782</v>
       </c>
       <c r="H61" t="n">
         <v>0.132</v>
@@ -2879,7 +2879,7 @@
         <v>0.188</v>
       </c>
       <c r="J61" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="62">
@@ -2904,22 +2904,22 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.0151</v>
+        <v>0.0141</v>
       </c>
       <c r="F62" t="n">
-        <v>0.756</v>
+        <v>0.758</v>
       </c>
       <c r="G62" t="n">
-        <v>0.789</v>
+        <v>0.791</v>
       </c>
       <c r="H62" t="n">
-        <v>0.169</v>
+        <v>0.17</v>
       </c>
       <c r="I62" t="n">
         <v>0.137</v>
       </c>
       <c r="J62" t="n">
-        <v>0.032</v>
+        <v>0.0301</v>
       </c>
     </row>
     <row r="63">
@@ -2947,13 +2947,13 @@
         <v>0.0076</v>
       </c>
       <c r="F63" t="n">
-        <v>0.756</v>
+        <v>0.758</v>
       </c>
       <c r="G63" t="n">
-        <v>0.789</v>
+        <v>0.791</v>
       </c>
       <c r="H63" t="n">
-        <v>0.169</v>
+        <v>0.17</v>
       </c>
       <c r="I63" t="n">
         <v>0.137</v>
@@ -2984,22 +2984,22 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.117</v>
+        <v>0.116</v>
       </c>
       <c r="F64" t="n">
-        <v>0.756</v>
+        <v>0.758</v>
       </c>
       <c r="G64" t="n">
-        <v>0.717</v>
+        <v>0.719</v>
       </c>
       <c r="H64" t="n">
-        <v>0.169</v>
+        <v>0.17</v>
       </c>
       <c r="I64" t="n">
         <v>0.186</v>
       </c>
       <c r="J64" t="n">
-        <v>0.162</v>
+        <v>0.161</v>
       </c>
     </row>
     <row r="65">
@@ -3027,13 +3027,13 @@
         <v>0.175</v>
       </c>
       <c r="F65" t="n">
-        <v>0.756</v>
+        <v>0.758</v>
       </c>
       <c r="G65" t="n">
-        <v>0.717</v>
+        <v>0.719</v>
       </c>
       <c r="H65" t="n">
-        <v>0.169</v>
+        <v>0.17</v>
       </c>
       <c r="I65" t="n">
         <v>0.186</v>
@@ -3064,22 +3064,22 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.00765</v>
+        <v>0.00742</v>
       </c>
       <c r="F66" t="n">
-        <v>0.756</v>
+        <v>0.758</v>
       </c>
       <c r="G66" t="n">
-        <v>0.819</v>
+        <v>0.821</v>
       </c>
       <c r="H66" t="n">
-        <v>0.169</v>
+        <v>0.17</v>
       </c>
       <c r="I66" t="n">
-        <v>0.144</v>
+        <v>0.145</v>
       </c>
       <c r="J66" t="n">
-        <v>0.025</v>
+        <v>0.0243</v>
       </c>
     </row>
     <row r="67">
@@ -3107,16 +3107,16 @@
         <v>0.00629</v>
       </c>
       <c r="F67" t="n">
-        <v>0.756</v>
+        <v>0.758</v>
       </c>
       <c r="G67" t="n">
-        <v>0.819</v>
+        <v>0.821</v>
       </c>
       <c r="H67" t="n">
-        <v>0.169</v>
+        <v>0.17</v>
       </c>
       <c r="I67" t="n">
-        <v>0.144</v>
+        <v>0.145</v>
       </c>
       <c r="J67" t="n">
         <v>0.0192</v>
@@ -3144,16 +3144,16 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.0897</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="F68" t="n">
-        <v>0.709</v>
+        <v>0.71</v>
       </c>
       <c r="G68" t="n">
-        <v>0.68</v>
+        <v>0.681</v>
       </c>
       <c r="H68" t="n">
-        <v>0.153</v>
+        <v>0.152</v>
       </c>
       <c r="I68" t="n">
         <v>0.149</v>
@@ -3187,13 +3187,13 @@
         <v>0.105</v>
       </c>
       <c r="F69" t="n">
-        <v>0.709</v>
+        <v>0.71</v>
       </c>
       <c r="G69" t="n">
-        <v>0.68</v>
+        <v>0.681</v>
       </c>
       <c r="H69" t="n">
-        <v>0.153</v>
+        <v>0.152</v>
       </c>
       <c r="I69" t="n">
         <v>0.149</v>
@@ -3224,22 +3224,22 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.00277</v>
+        <v>0.00275</v>
       </c>
       <c r="F70" t="n">
-        <v>0.709</v>
+        <v>0.71</v>
       </c>
       <c r="G70" t="n">
-        <v>0.596</v>
+        <v>0.597</v>
       </c>
       <c r="H70" t="n">
-        <v>0.153</v>
+        <v>0.152</v>
       </c>
       <c r="I70" t="n">
-        <v>0.137</v>
+        <v>0.138</v>
       </c>
       <c r="J70" t="n">
-        <v>0.0142</v>
+        <v>0.0141</v>
       </c>
     </row>
     <row r="71">
@@ -3267,19 +3267,19 @@
         <v>0.00121</v>
       </c>
       <c r="F71" t="n">
-        <v>0.709</v>
+        <v>0.71</v>
       </c>
       <c r="G71" t="n">
-        <v>0.596</v>
+        <v>0.597</v>
       </c>
       <c r="H71" t="n">
-        <v>0.153</v>
+        <v>0.152</v>
       </c>
       <c r="I71" t="n">
-        <v>0.137</v>
+        <v>0.138</v>
       </c>
       <c r="J71" t="n">
-        <v>0.00957</v>
+        <v>0.00967</v>
       </c>
     </row>
     <row r="72">
@@ -3307,19 +3307,19 @@
         <v>0.24</v>
       </c>
       <c r="F72" t="n">
-        <v>0.709</v>
+        <v>0.71</v>
       </c>
       <c r="G72" t="n">
-        <v>0.734</v>
+        <v>0.735</v>
       </c>
       <c r="H72" t="n">
-        <v>0.153</v>
+        <v>0.152</v>
       </c>
       <c r="I72" t="n">
-        <v>0.175</v>
+        <v>0.176</v>
       </c>
       <c r="J72" t="n">
-        <v>0.281</v>
+        <v>0.282</v>
       </c>
     </row>
     <row r="73">
@@ -3347,16 +3347,16 @@
         <v>0.211</v>
       </c>
       <c r="F73" t="n">
-        <v>0.709</v>
+        <v>0.71</v>
       </c>
       <c r="G73" t="n">
-        <v>0.734</v>
+        <v>0.735</v>
       </c>
       <c r="H73" t="n">
-        <v>0.153</v>
+        <v>0.152</v>
       </c>
       <c r="I73" t="n">
-        <v>0.175</v>
+        <v>0.176</v>
       </c>
       <c r="J73" t="n">
         <v>0.265</v>
@@ -3596,10 +3596,10 @@
         <v>5</v>
       </c>
       <c r="F6" t="n">
-        <v>0.82</v>
+        <v>0.827</v>
       </c>
       <c r="G6" t="n">
-        <v>0.827</v>
+        <v>0.833</v>
       </c>
       <c r="H6" t="n">
         <v>1</v>
@@ -3633,16 +3633,16 @@
         <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>0.793</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>0.907</v>
+        <v>0.92</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00911</v>
+        <v>0.0102</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0473</v>
+        <v>0.0459</v>
       </c>
     </row>
     <row r="8">
@@ -3744,16 +3744,16 @@
         <v>9</v>
       </c>
       <c r="F10" t="n">
-        <v>0.66</v>
+        <v>0.667</v>
       </c>
       <c r="G10" t="n">
-        <v>0.74</v>
+        <v>0.753</v>
       </c>
       <c r="H10" t="n">
-        <v>0.166</v>
+        <v>0.127</v>
       </c>
       <c r="I10" t="n">
-        <v>0.373</v>
+        <v>0.286</v>
       </c>
     </row>
     <row r="11">
@@ -4225,7 +4225,7 @@
         <v>6</v>
       </c>
       <c r="F23" t="n">
-        <v>0.969</v>
+        <v>0.97</v>
       </c>
       <c r="G23" t="n">
         <v>0.9429999999999999</v>
@@ -4339,10 +4339,10 @@
         <v>0.987</v>
       </c>
       <c r="G26" t="n">
-        <v>0.948</v>
+        <v>0.949</v>
       </c>
       <c r="H26" t="n">
-        <v>0.229</v>
+        <v>0.231</v>
       </c>
       <c r="I26" t="n">
         <v>0.858</v>
@@ -4780,10 +4780,10 @@
         <v>5</v>
       </c>
       <c r="F38" t="n">
-        <v>0.762</v>
+        <v>0.77</v>
       </c>
       <c r="G38" t="n">
-        <v>0.772</v>
+        <v>0.78</v>
       </c>
       <c r="H38" t="n">
         <v>1</v>
@@ -4817,16 +4817,16 @@
         <v>6</v>
       </c>
       <c r="F39" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.711</v>
       </c>
       <c r="G39" t="n">
-        <v>0.902</v>
+        <v>0.922</v>
       </c>
       <c r="H39" t="n">
-        <v>0.000433</v>
+        <v>0.000399</v>
       </c>
       <c r="I39" t="n">
-        <v>0.000974</v>
+        <v>0.000898</v>
       </c>
     </row>
     <row r="40">
@@ -4928,16 +4928,16 @@
         <v>9</v>
       </c>
       <c r="F42" t="n">
-        <v>0.603</v>
+        <v>0.608</v>
       </c>
       <c r="G42" t="n">
-        <v>0.73</v>
+        <v>0.744</v>
       </c>
       <c r="H42" t="n">
-        <v>0.0447</v>
+        <v>0.0303</v>
       </c>
       <c r="I42" t="n">
-        <v>0.134</v>
+        <v>0.09089999999999999</v>
       </c>
     </row>
     <row r="43">
@@ -5372,16 +5372,16 @@
         <v>5</v>
       </c>
       <c r="F54" t="n">
-        <v>0.851</v>
+        <v>0.856</v>
       </c>
       <c r="G54" t="n">
-        <v>0.857</v>
+        <v>0.862</v>
       </c>
       <c r="H54" t="n">
-        <v>0.883</v>
+        <v>0.881</v>
       </c>
       <c r="I54" t="n">
-        <v>0.993</v>
+        <v>0.991</v>
       </c>
     </row>
     <row r="55">
@@ -5409,16 +5409,16 @@
         <v>6</v>
       </c>
       <c r="F55" t="n">
-        <v>0.803</v>
+        <v>0.821</v>
       </c>
       <c r="G55" t="n">
-        <v>0.922</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="H55" t="n">
-        <v>0.00202</v>
+        <v>0.00212</v>
       </c>
       <c r="I55" t="n">
-        <v>0.009090000000000001</v>
+        <v>0.00954</v>
       </c>
     </row>
     <row r="56">
@@ -5520,16 +5520,16 @@
         <v>9</v>
       </c>
       <c r="F58" t="n">
-        <v>0.749</v>
+        <v>0.752</v>
       </c>
       <c r="G58" t="n">
-        <v>0.825</v>
+        <v>0.834</v>
       </c>
       <c r="H58" t="n">
-        <v>0.058</v>
+        <v>0.0411</v>
       </c>
       <c r="I58" t="n">
-        <v>0.131</v>
+        <v>0.0925</v>
       </c>
     </row>
     <row r="59">
@@ -5964,10 +5964,10 @@
         <v>5</v>
       </c>
       <c r="F70" t="n">
-        <v>0.82</v>
+        <v>0.827</v>
       </c>
       <c r="G70" t="n">
-        <v>0.827</v>
+        <v>0.833</v>
       </c>
       <c r="H70" t="n">
         <v>1</v>
@@ -6001,16 +6001,16 @@
         <v>6</v>
       </c>
       <c r="F71" t="n">
-        <v>0.793</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="G71" t="n">
-        <v>0.867</v>
+        <v>0.88</v>
       </c>
       <c r="H71" t="n">
-        <v>0.124</v>
+        <v>0.149</v>
       </c>
       <c r="I71" t="n">
-        <v>0.279</v>
+        <v>0.335</v>
       </c>
     </row>
     <row r="72">
@@ -6112,16 +6112,16 @@
         <v>9</v>
       </c>
       <c r="F74" t="n">
-        <v>0.66</v>
+        <v>0.667</v>
       </c>
       <c r="G74" t="n">
-        <v>0.773</v>
+        <v>0.787</v>
       </c>
       <c r="H74" t="n">
-        <v>0.04</v>
+        <v>0.0273</v>
       </c>
       <c r="I74" t="n">
-        <v>0.18</v>
+        <v>0.123</v>
       </c>
     </row>
     <row r="75">
@@ -6593,16 +6593,16 @@
         <v>6</v>
       </c>
       <c r="F87" t="n">
-        <v>0.969</v>
+        <v>0.97</v>
       </c>
       <c r="G87" t="n">
         <v>0.883</v>
       </c>
       <c r="H87" t="n">
-        <v>0.07530000000000001</v>
+        <v>0.075</v>
       </c>
       <c r="I87" t="n">
-        <v>0.12</v>
+        <v>0.121</v>
       </c>
     </row>
     <row r="88">
@@ -6710,7 +6710,7 @@
         <v>0.96</v>
       </c>
       <c r="H90" t="n">
-        <v>0.389</v>
+        <v>0.391</v>
       </c>
       <c r="I90" t="n">
         <v>0.858</v>
@@ -7148,16 +7148,16 @@
         <v>5</v>
       </c>
       <c r="F102" t="n">
-        <v>0.762</v>
+        <v>0.77</v>
       </c>
       <c r="G102" t="n">
-        <v>0.792</v>
+        <v>0.8</v>
       </c>
       <c r="H102" t="n">
-        <v>0.735</v>
+        <v>0.731</v>
       </c>
       <c r="I102" t="n">
-        <v>0.945</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="103">
@@ -7185,16 +7185,16 @@
         <v>6</v>
       </c>
       <c r="F103" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.711</v>
       </c>
       <c r="G103" t="n">
-        <v>0.902</v>
+        <v>0.922</v>
       </c>
       <c r="H103" t="n">
-        <v>0.000433</v>
+        <v>0.000399</v>
       </c>
       <c r="I103" t="n">
-        <v>0.000974</v>
+        <v>0.000898</v>
       </c>
     </row>
     <row r="104">
@@ -7296,16 +7296,16 @@
         <v>9</v>
       </c>
       <c r="F106" t="n">
-        <v>0.603</v>
+        <v>0.608</v>
       </c>
       <c r="G106" t="n">
-        <v>0.762</v>
+        <v>0.776</v>
       </c>
       <c r="H106" t="n">
-        <v>0.00991</v>
+        <v>0.00596</v>
       </c>
       <c r="I106" t="n">
-        <v>0.0446</v>
+        <v>0.0268</v>
       </c>
     </row>
     <row r="107">
@@ -7740,16 +7740,16 @@
         <v>5</v>
       </c>
       <c r="F118" t="n">
-        <v>0.851</v>
+        <v>0.856</v>
       </c>
       <c r="G118" t="n">
-        <v>0.86</v>
+        <v>0.865</v>
       </c>
       <c r="H118" t="n">
-        <v>0.882</v>
+        <v>0.88</v>
       </c>
       <c r="I118" t="n">
-        <v>0.993</v>
+        <v>0.991</v>
       </c>
     </row>
     <row r="119">
@@ -7777,16 +7777,16 @@
         <v>6</v>
       </c>
       <c r="F119" t="n">
-        <v>0.803</v>
+        <v>0.821</v>
       </c>
       <c r="G119" t="n">
-        <v>0.892</v>
+        <v>0.902</v>
       </c>
       <c r="H119" t="n">
-        <v>0.0225</v>
+        <v>0.0379</v>
       </c>
       <c r="I119" t="n">
-        <v>0.0506</v>
+        <v>0.0853</v>
       </c>
     </row>
     <row r="120">
@@ -7888,16 +7888,16 @@
         <v>9</v>
       </c>
       <c r="F122" t="n">
-        <v>0.749</v>
+        <v>0.752</v>
       </c>
       <c r="G122" t="n">
-        <v>0.85</v>
+        <v>0.858</v>
       </c>
       <c r="H122" t="n">
-        <v>0.0107</v>
+        <v>0.00665</v>
       </c>
       <c r="I122" t="n">
-        <v>0.0481</v>
+        <v>0.0299</v>
       </c>
     </row>
     <row r="123">
@@ -8332,10 +8332,10 @@
         <v>5</v>
       </c>
       <c r="F134" t="n">
-        <v>0.82</v>
+        <v>0.827</v>
       </c>
       <c r="G134" t="n">
-        <v>0.827</v>
+        <v>0.833</v>
       </c>
       <c r="H134" t="n">
         <v>1</v>
@@ -8369,16 +8369,16 @@
         <v>6</v>
       </c>
       <c r="F135" t="n">
-        <v>0.793</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="G135" t="n">
-        <v>0.84</v>
+        <v>0.853</v>
       </c>
       <c r="H135" t="n">
-        <v>0.371</v>
+        <v>0.439</v>
       </c>
       <c r="I135" t="n">
-        <v>0.424</v>
+        <v>0.502</v>
       </c>
     </row>
     <row r="136">
@@ -8480,16 +8480,16 @@
         <v>9</v>
       </c>
       <c r="F138" t="n">
-        <v>0.66</v>
+        <v>0.667</v>
       </c>
       <c r="G138" t="n">
-        <v>0.707</v>
+        <v>0.713</v>
       </c>
       <c r="H138" t="n">
-        <v>0.457</v>
+        <v>0.454</v>
       </c>
       <c r="I138" t="n">
-        <v>0.536</v>
+        <v>0.534</v>
       </c>
     </row>
     <row r="139">
@@ -8961,16 +8961,16 @@
         <v>6</v>
       </c>
       <c r="F151" t="n">
-        <v>0.969</v>
+        <v>0.97</v>
       </c>
       <c r="G151" t="n">
         <v>0.833</v>
       </c>
       <c r="H151" t="n">
-        <v>0.00604</v>
+        <v>0.00578</v>
       </c>
       <c r="I151" t="n">
-        <v>0.0181</v>
+        <v>0.0173</v>
       </c>
     </row>
     <row r="152">
@@ -9516,16 +9516,16 @@
         <v>5</v>
       </c>
       <c r="F166" t="n">
-        <v>0.762</v>
+        <v>0.77</v>
       </c>
       <c r="G166" t="n">
-        <v>0.802</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H166" t="n">
-        <v>0.609</v>
+        <v>0.603</v>
       </c>
       <c r="I166" t="n">
-        <v>0.913</v>
+        <v>0.904</v>
       </c>
     </row>
     <row r="167">
@@ -9553,16 +9553,16 @@
         <v>6</v>
       </c>
       <c r="F167" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.711</v>
       </c>
       <c r="G167" t="n">
-        <v>0.924</v>
+        <v>0.944</v>
       </c>
       <c r="H167" t="n">
-        <v>6.35e-05</v>
+        <v>4.59e-05</v>
       </c>
       <c r="I167" t="n">
-        <v>0.000286</v>
+        <v>0.000207</v>
       </c>
     </row>
     <row r="168">
@@ -9664,16 +9664,16 @@
         <v>9</v>
       </c>
       <c r="F170" t="n">
-        <v>0.603</v>
+        <v>0.608</v>
       </c>
       <c r="G170" t="n">
-        <v>0.675</v>
+        <v>0.68</v>
       </c>
       <c r="H170" t="n">
-        <v>0.294</v>
+        <v>0.291</v>
       </c>
       <c r="I170" t="n">
-        <v>0.425</v>
+        <v>0.423</v>
       </c>
     </row>
     <row r="171">
@@ -10108,16 +10108,16 @@
         <v>5</v>
       </c>
       <c r="F182" t="n">
-        <v>0.851</v>
+        <v>0.856</v>
       </c>
       <c r="G182" t="n">
-        <v>0.862</v>
+        <v>0.866</v>
       </c>
       <c r="H182" t="n">
-        <v>0.769</v>
+        <v>0.88</v>
       </c>
       <c r="I182" t="n">
-        <v>0.993</v>
+        <v>0.991</v>
       </c>
     </row>
     <row r="183">
@@ -10145,16 +10145,16 @@
         <v>6</v>
       </c>
       <c r="F183" t="n">
-        <v>0.803</v>
+        <v>0.821</v>
       </c>
       <c r="G183" t="n">
-        <v>0.876</v>
+        <v>0.885</v>
       </c>
       <c r="H183" t="n">
-        <v>0.07580000000000001</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="I183" t="n">
-        <v>0.136</v>
+        <v>0.167</v>
       </c>
     </row>
     <row r="184">
@@ -10256,16 +10256,16 @@
         <v>9</v>
       </c>
       <c r="F186" t="n">
-        <v>0.749</v>
+        <v>0.752</v>
       </c>
       <c r="G186" t="n">
-        <v>0.794</v>
+        <v>0.798</v>
       </c>
       <c r="H186" t="n">
-        <v>0.294</v>
+        <v>0.29</v>
       </c>
       <c r="I186" t="n">
-        <v>0.331</v>
+        <v>0.326</v>
       </c>
     </row>
     <row r="187">
@@ -10700,13 +10700,13 @@
         <v>5</v>
       </c>
       <c r="F198" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="G198" t="n">
-        <v>0.793</v>
+        <v>0.8</v>
       </c>
       <c r="H198" t="n">
-        <v>0.885</v>
+        <v>0.884</v>
       </c>
       <c r="I198" t="n">
         <v>1</v>
@@ -10737,16 +10737,16 @@
         <v>6</v>
       </c>
       <c r="F199" t="n">
-        <v>0.787</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="G199" t="n">
-        <v>0.853</v>
+        <v>0.867</v>
       </c>
       <c r="H199" t="n">
-        <v>0.176</v>
+        <v>0.211</v>
       </c>
       <c r="I199" t="n">
-        <v>0.317</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="200">
@@ -10848,16 +10848,16 @@
         <v>9</v>
       </c>
       <c r="F202" t="n">
-        <v>0.66</v>
+        <v>0.667</v>
       </c>
       <c r="G202" t="n">
-        <v>0.7</v>
+        <v>0.707</v>
       </c>
       <c r="H202" t="n">
-        <v>0.536</v>
+        <v>0.534</v>
       </c>
       <c r="I202" t="n">
-        <v>0.536</v>
+        <v>0.534</v>
       </c>
     </row>
     <row r="203">
@@ -10925,13 +10925,13 @@
         <v>0.773</v>
       </c>
       <c r="G204" t="n">
-        <v>0.793</v>
+        <v>0.8</v>
       </c>
       <c r="H204" t="n">
-        <v>0.779</v>
+        <v>0.673</v>
       </c>
       <c r="I204" t="n">
-        <v>0.779</v>
+        <v>0.673</v>
       </c>
     </row>
     <row r="205">
@@ -11329,16 +11329,16 @@
         <v>6</v>
       </c>
       <c r="F215" t="n">
-        <v>0.875</v>
+        <v>0.877</v>
       </c>
       <c r="G215" t="n">
         <v>0.961</v>
       </c>
       <c r="H215" t="n">
-        <v>0.08019999999999999</v>
+        <v>0.081</v>
       </c>
       <c r="I215" t="n">
-        <v>0.12</v>
+        <v>0.121</v>
       </c>
     </row>
     <row r="216">
@@ -11517,13 +11517,13 @@
         <v>0.863</v>
       </c>
       <c r="G220" t="n">
-        <v>0.969</v>
+        <v>0.97</v>
       </c>
       <c r="H220" t="n">
-        <v>0.038</v>
+        <v>0.0378</v>
       </c>
       <c r="I220" t="n">
-        <v>0.171</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="221">
@@ -11884,16 +11884,16 @@
         <v>5</v>
       </c>
       <c r="F230" t="n">
-        <v>0.743</v>
+        <v>0.75</v>
       </c>
       <c r="G230" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="H230" t="n">
-        <v>0.532</v>
+        <v>0.527</v>
       </c>
       <c r="I230" t="n">
-        <v>0.913</v>
+        <v>0.904</v>
       </c>
     </row>
     <row r="231">
@@ -11921,16 +11921,16 @@
         <v>6</v>
       </c>
       <c r="F231" t="n">
-        <v>0.761</v>
+        <v>0.789</v>
       </c>
       <c r="G231" t="n">
-        <v>0.793</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="H231" t="n">
-        <v>0.723</v>
+        <v>0.852</v>
       </c>
       <c r="I231" t="n">
-        <v>0.736</v>
+        <v>0.852</v>
       </c>
     </row>
     <row r="232">
@@ -12032,16 +12032,16 @@
         <v>9</v>
       </c>
       <c r="F234" t="n">
-        <v>0.619</v>
+        <v>0.624</v>
       </c>
       <c r="G234" t="n">
-        <v>0.651</v>
+        <v>0.656</v>
       </c>
       <c r="H234" t="n">
-        <v>0.695</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="I234" t="n">
-        <v>0.695</v>
+        <v>0.6929999999999999</v>
       </c>
     </row>
     <row r="235">
@@ -12109,13 +12109,13 @@
         <v>0.75</v>
       </c>
       <c r="G236" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.696</v>
       </c>
       <c r="H236" t="n">
-        <v>0.413</v>
+        <v>0.51</v>
       </c>
       <c r="I236" t="n">
-        <v>0.531</v>
+        <v>0.656</v>
       </c>
     </row>
     <row r="237">
@@ -12476,16 +12476,16 @@
         <v>5</v>
       </c>
       <c r="F246" t="n">
-        <v>0.838</v>
+        <v>0.843</v>
       </c>
       <c r="G246" t="n">
-        <v>0.819</v>
+        <v>0.824</v>
       </c>
       <c r="H246" t="n">
-        <v>0.672</v>
+        <v>0.668</v>
       </c>
       <c r="I246" t="n">
-        <v>0.993</v>
+        <v>0.991</v>
       </c>
     </row>
     <row r="247">
@@ -12513,16 +12513,16 @@
         <v>6</v>
       </c>
       <c r="F247" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="G247" t="n">
-        <v>0.869</v>
+        <v>0.88</v>
       </c>
       <c r="H247" t="n">
-        <v>0.183</v>
+        <v>0.219</v>
       </c>
       <c r="I247" t="n">
-        <v>0.235</v>
+        <v>0.282</v>
       </c>
     </row>
     <row r="248">
@@ -12624,16 +12624,16 @@
         <v>9</v>
       </c>
       <c r="F250" t="n">
-        <v>0.754</v>
+        <v>0.757</v>
       </c>
       <c r="G250" t="n">
-        <v>0.785</v>
+        <v>0.788</v>
       </c>
       <c r="H250" t="n">
-        <v>0.486</v>
+        <v>0.483</v>
       </c>
       <c r="I250" t="n">
-        <v>0.486</v>
+        <v>0.483</v>
       </c>
     </row>
     <row r="251">
@@ -12701,13 +12701,13 @@
         <v>0.802</v>
       </c>
       <c r="G252" t="n">
-        <v>0.803</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H252" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="I252" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="253">
@@ -13068,13 +13068,13 @@
         <v>5</v>
       </c>
       <c r="F262" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="G262" t="n">
-        <v>0.78</v>
+        <v>0.787</v>
       </c>
       <c r="H262" t="n">
-        <v>0.669</v>
+        <v>0.665</v>
       </c>
       <c r="I262" t="n">
         <v>1</v>
@@ -13105,16 +13105,16 @@
         <v>6</v>
       </c>
       <c r="F263" t="n">
-        <v>0.787</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="G263" t="n">
-        <v>0.833</v>
+        <v>0.847</v>
       </c>
       <c r="H263" t="n">
-        <v>0.377</v>
+        <v>0.446</v>
       </c>
       <c r="I263" t="n">
-        <v>0.424</v>
+        <v>0.502</v>
       </c>
     </row>
     <row r="264">
@@ -13216,16 +13216,16 @@
         <v>9</v>
       </c>
       <c r="F266" t="n">
-        <v>0.66</v>
+        <v>0.667</v>
       </c>
       <c r="G266" t="n">
-        <v>0.6</v>
+        <v>0.613</v>
       </c>
       <c r="H266" t="n">
-        <v>0.339</v>
+        <v>0.4</v>
       </c>
       <c r="I266" t="n">
-        <v>0.528</v>
+        <v>0.534</v>
       </c>
     </row>
     <row r="267">
@@ -13697,16 +13697,16 @@
         <v>6</v>
       </c>
       <c r="F279" t="n">
-        <v>0.875</v>
+        <v>0.877</v>
       </c>
       <c r="G279" t="n">
         <v>1</v>
       </c>
       <c r="H279" t="n">
-        <v>0.002</v>
+        <v>0.00209</v>
       </c>
       <c r="I279" t="n">
-        <v>0.018</v>
+        <v>0.0173</v>
       </c>
     </row>
     <row r="280">
@@ -13811,10 +13811,10 @@
         <v>0.963</v>
       </c>
       <c r="G282" t="n">
-        <v>0.985</v>
+        <v>0.986</v>
       </c>
       <c r="H282" t="n">
-        <v>0.626</v>
+        <v>0.625</v>
       </c>
       <c r="I282" t="n">
         <v>0.858</v>
@@ -14252,16 +14252,16 @@
         <v>5</v>
       </c>
       <c r="F294" t="n">
-        <v>0.743</v>
+        <v>0.75</v>
       </c>
       <c r="G294" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H294" t="n">
-        <v>0.437</v>
+        <v>0.431</v>
       </c>
       <c r="I294" t="n">
-        <v>0.913</v>
+        <v>0.904</v>
       </c>
     </row>
     <row r="295">
@@ -14289,16 +14289,16 @@
         <v>6</v>
       </c>
       <c r="F295" t="n">
-        <v>0.761</v>
+        <v>0.789</v>
       </c>
       <c r="G295" t="n">
-        <v>0.728</v>
+        <v>0.744</v>
       </c>
       <c r="H295" t="n">
-        <v>0.736</v>
+        <v>0.597</v>
       </c>
       <c r="I295" t="n">
-        <v>0.736</v>
+        <v>0.672</v>
       </c>
     </row>
     <row r="296">
@@ -14400,16 +14400,16 @@
         <v>9</v>
       </c>
       <c r="F298" t="n">
-        <v>0.619</v>
+        <v>0.624</v>
       </c>
       <c r="G298" t="n">
-        <v>0.532</v>
+        <v>0.544</v>
       </c>
       <c r="H298" t="n">
-        <v>0.202</v>
+        <v>0.248</v>
       </c>
       <c r="I298" t="n">
-        <v>0.364</v>
+        <v>0.423</v>
       </c>
     </row>
     <row r="299">
@@ -14844,16 +14844,16 @@
         <v>5</v>
       </c>
       <c r="F310" t="n">
-        <v>0.838</v>
+        <v>0.843</v>
       </c>
       <c r="G310" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="H310" t="n">
-        <v>0.485</v>
+        <v>0.48</v>
       </c>
       <c r="I310" t="n">
-        <v>0.993</v>
+        <v>0.991</v>
       </c>
     </row>
     <row r="311">
@@ -14881,16 +14881,16 @@
         <v>6</v>
       </c>
       <c r="F311" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="G311" t="n">
-        <v>0.843</v>
+        <v>0.854</v>
       </c>
       <c r="H311" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="I311" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="312">
@@ -14992,13 +14992,13 @@
         <v>9</v>
       </c>
       <c r="F314" t="n">
-        <v>0.754</v>
+        <v>0.757</v>
       </c>
       <c r="G314" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.701</v>
       </c>
       <c r="H314" t="n">
-        <v>0.181</v>
+        <v>0.217</v>
       </c>
       <c r="I314" t="n">
         <v>0.326</v>
@@ -15436,13 +15436,13 @@
         <v>5</v>
       </c>
       <c r="F326" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="G326" t="n">
-        <v>0.84</v>
+        <v>0.847</v>
       </c>
       <c r="H326" t="n">
-        <v>0.545</v>
+        <v>0.539</v>
       </c>
       <c r="I326" t="n">
         <v>1</v>
@@ -15473,16 +15473,16 @@
         <v>6</v>
       </c>
       <c r="F327" t="n">
-        <v>0.787</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="G327" t="n">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
       <c r="H327" t="n">
-        <v>0.0105</v>
+        <v>0.0066</v>
       </c>
       <c r="I327" t="n">
-        <v>0.0473</v>
+        <v>0.0459</v>
       </c>
     </row>
     <row r="328">
@@ -15584,16 +15584,16 @@
         <v>9</v>
       </c>
       <c r="F330" t="n">
-        <v>0.66</v>
+        <v>0.667</v>
       </c>
       <c r="G330" t="n">
-        <v>0.747</v>
+        <v>0.76</v>
       </c>
       <c r="H330" t="n">
-        <v>0.129</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="I330" t="n">
-        <v>0.373</v>
+        <v>0.286</v>
       </c>
     </row>
     <row r="331">
@@ -15667,7 +15667,7 @@
         <v>0.571</v>
       </c>
       <c r="I332" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.673</v>
       </c>
     </row>
     <row r="333">
@@ -16065,16 +16065,16 @@
         <v>6</v>
       </c>
       <c r="F343" t="n">
-        <v>0.875</v>
+        <v>0.877</v>
       </c>
       <c r="G343" t="n">
-        <v>0.975</v>
+        <v>0.976</v>
       </c>
       <c r="H343" t="n">
-        <v>0.0175</v>
+        <v>0.0176</v>
       </c>
       <c r="I343" t="n">
-        <v>0.0394</v>
+        <v>0.0396</v>
       </c>
     </row>
     <row r="344">
@@ -16179,7 +16179,7 @@
         <v>0.963</v>
       </c>
       <c r="G346" t="n">
-        <v>0.958</v>
+        <v>0.959</v>
       </c>
       <c r="H346" t="n">
         <v>1</v>
@@ -16620,16 +16620,16 @@
         <v>5</v>
       </c>
       <c r="F358" t="n">
-        <v>0.743</v>
+        <v>0.75</v>
       </c>
       <c r="G358" t="n">
-        <v>0.792</v>
+        <v>0.8</v>
       </c>
       <c r="H358" t="n">
-        <v>0.506</v>
+        <v>0.498</v>
       </c>
       <c r="I358" t="n">
-        <v>0.913</v>
+        <v>0.904</v>
       </c>
     </row>
     <row r="359">
@@ -16657,16 +16657,16 @@
         <v>6</v>
       </c>
       <c r="F359" t="n">
-        <v>0.761</v>
+        <v>0.789</v>
       </c>
       <c r="G359" t="n">
-        <v>0.859</v>
+        <v>0.889</v>
       </c>
       <c r="H359" t="n">
-        <v>0.132</v>
+        <v>0.104</v>
       </c>
       <c r="I359" t="n">
-        <v>0.198</v>
+        <v>0.156</v>
       </c>
     </row>
     <row r="360">
@@ -16768,16 +16768,16 @@
         <v>9</v>
       </c>
       <c r="F362" t="n">
-        <v>0.619</v>
+        <v>0.624</v>
       </c>
       <c r="G362" t="n">
-        <v>0.73</v>
+        <v>0.744</v>
       </c>
       <c r="H362" t="n">
-        <v>0.08019999999999999</v>
+        <v>0.0565</v>
       </c>
       <c r="I362" t="n">
-        <v>0.18</v>
+        <v>0.127</v>
       </c>
     </row>
     <row r="363">
@@ -17212,16 +17212,16 @@
         <v>5</v>
       </c>
       <c r="F374" t="n">
-        <v>0.838</v>
+        <v>0.843</v>
       </c>
       <c r="G374" t="n">
-        <v>0.87</v>
+        <v>0.874</v>
       </c>
       <c r="H374" t="n">
-        <v>0.458</v>
+        <v>0.451</v>
       </c>
       <c r="I374" t="n">
-        <v>0.993</v>
+        <v>0.991</v>
       </c>
     </row>
     <row r="375">
@@ -17249,16 +17249,16 @@
         <v>6</v>
       </c>
       <c r="F375" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="G375" t="n">
-        <v>0.913</v>
+        <v>0.93</v>
       </c>
       <c r="H375" t="n">
-        <v>0.00769</v>
+        <v>0.00464</v>
       </c>
       <c r="I375" t="n">
-        <v>0.0231</v>
+        <v>0.0139</v>
       </c>
     </row>
     <row r="376">
@@ -17360,16 +17360,16 @@
         <v>9</v>
       </c>
       <c r="F378" t="n">
-        <v>0.754</v>
+        <v>0.757</v>
       </c>
       <c r="G378" t="n">
-        <v>0.829</v>
+        <v>0.838</v>
       </c>
       <c r="H378" t="n">
-        <v>0.0576</v>
+        <v>0.0407</v>
       </c>
       <c r="I378" t="n">
-        <v>0.131</v>
+        <v>0.0925</v>
       </c>
     </row>
     <row r="379">
@@ -17804,10 +17804,10 @@
         <v>5</v>
       </c>
       <c r="F390" t="n">
-        <v>0.727</v>
+        <v>0.733</v>
       </c>
       <c r="G390" t="n">
-        <v>0.727</v>
+        <v>0.733</v>
       </c>
       <c r="H390" t="n">
         <v>1</v>
@@ -17841,16 +17841,16 @@
         <v>6</v>
       </c>
       <c r="F391" t="n">
-        <v>0.68</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="G391" t="n">
-        <v>0.733</v>
+        <v>0.747</v>
       </c>
       <c r="H391" t="n">
-        <v>0.375</v>
+        <v>0.368</v>
       </c>
       <c r="I391" t="n">
-        <v>0.424</v>
+        <v>0.502</v>
       </c>
     </row>
     <row r="392">
@@ -17952,16 +17952,16 @@
         <v>9</v>
       </c>
       <c r="F394" t="n">
-        <v>0.593</v>
+        <v>0.6</v>
       </c>
       <c r="G394" t="n">
-        <v>0.547</v>
+        <v>0.553</v>
       </c>
       <c r="H394" t="n">
-        <v>0.484</v>
+        <v>0.483</v>
       </c>
       <c r="I394" t="n">
-        <v>0.536</v>
+        <v>0.534</v>
       </c>
     </row>
     <row r="395">
@@ -18035,7 +18035,7 @@
         <v>0.608</v>
       </c>
       <c r="I396" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.673</v>
       </c>
     </row>
     <row r="397">
@@ -18988,10 +18988,10 @@
         <v>5</v>
       </c>
       <c r="F422" t="n">
-        <v>0.634</v>
+        <v>0.64</v>
       </c>
       <c r="G422" t="n">
-        <v>0.624</v>
+        <v>0.63</v>
       </c>
       <c r="H422" t="n">
         <v>1</v>
@@ -19025,16 +19025,16 @@
         <v>6</v>
       </c>
       <c r="F423" t="n">
-        <v>0.478</v>
+        <v>0.489</v>
       </c>
       <c r="G423" t="n">
-        <v>0.609</v>
+        <v>0.622</v>
       </c>
       <c r="H423" t="n">
-        <v>0.103</v>
+        <v>0.0987</v>
       </c>
       <c r="I423" t="n">
-        <v>0.185</v>
+        <v>0.156</v>
       </c>
     </row>
     <row r="424">
@@ -19136,16 +19136,16 @@
         <v>9</v>
       </c>
       <c r="F426" t="n">
-        <v>0.532</v>
+        <v>0.536</v>
       </c>
       <c r="G426" t="n">
-        <v>0.468</v>
+        <v>0.472</v>
       </c>
       <c r="H426" t="n">
-        <v>0.378</v>
+        <v>0.376</v>
       </c>
       <c r="I426" t="n">
-        <v>0.425</v>
+        <v>0.423</v>
       </c>
     </row>
     <row r="427">
@@ -19580,10 +19580,10 @@
         <v>5</v>
       </c>
       <c r="F438" t="n">
-        <v>0.757</v>
+        <v>0.762</v>
       </c>
       <c r="G438" t="n">
-        <v>0.754</v>
+        <v>0.759</v>
       </c>
       <c r="H438" t="n">
         <v>1</v>
@@ -19617,16 +19617,16 @@
         <v>6</v>
       </c>
       <c r="F439" t="n">
-        <v>0.647</v>
+        <v>0.657</v>
       </c>
       <c r="G439" t="n">
-        <v>0.737</v>
+        <v>0.747</v>
       </c>
       <c r="H439" t="n">
-        <v>0.124</v>
+        <v>0.118</v>
       </c>
       <c r="I439" t="n">
-        <v>0.186</v>
+        <v>0.177</v>
       </c>
     </row>
     <row r="440">
@@ -19728,16 +19728,16 @@
         <v>9</v>
       </c>
       <c r="F442" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="G442" t="n">
-        <v>0.634</v>
+        <v>0.638</v>
       </c>
       <c r="H442" t="n">
-        <v>0.281</v>
+        <v>0.279</v>
       </c>
       <c r="I442" t="n">
-        <v>0.331</v>
+        <v>0.326</v>
       </c>
     </row>
     <row r="443">
@@ -20172,16 +20172,16 @@
         <v>5</v>
       </c>
       <c r="F454" t="n">
-        <v>0.727</v>
+        <v>0.733</v>
       </c>
       <c r="G454" t="n">
-        <v>0.62</v>
+        <v>0.627</v>
       </c>
       <c r="H454" t="n">
-        <v>0.0645</v>
+        <v>0.0631</v>
       </c>
       <c r="I454" t="n">
-        <v>0.581</v>
+        <v>0.5679999999999999</v>
       </c>
     </row>
     <row r="455">
@@ -20209,16 +20209,16 @@
         <v>6</v>
       </c>
       <c r="F455" t="n">
-        <v>0.68</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="G455" t="n">
-        <v>0.7</v>
+        <v>0.713</v>
       </c>
       <c r="H455" t="n">
-        <v>0.803</v>
+        <v>0.801</v>
       </c>
       <c r="I455" t="n">
-        <v>0.803</v>
+        <v>0.801</v>
       </c>
     </row>
     <row r="456">
@@ -20320,16 +20320,16 @@
         <v>9</v>
       </c>
       <c r="F458" t="n">
-        <v>0.593</v>
+        <v>0.6</v>
       </c>
       <c r="G458" t="n">
-        <v>0.533</v>
+        <v>0.54</v>
       </c>
       <c r="H458" t="n">
-        <v>0.352</v>
+        <v>0.351</v>
       </c>
       <c r="I458" t="n">
-        <v>0.528</v>
+        <v>0.534</v>
       </c>
     </row>
     <row r="459">
@@ -21356,16 +21356,16 @@
         <v>5</v>
       </c>
       <c r="F486" t="n">
-        <v>0.634</v>
+        <v>0.64</v>
       </c>
       <c r="G486" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.57</v>
       </c>
       <c r="H486" t="n">
-        <v>0.389</v>
+        <v>0.386</v>
       </c>
       <c r="I486" t="n">
-        <v>0.913</v>
+        <v>0.904</v>
       </c>
     </row>
     <row r="487">
@@ -21393,16 +21393,16 @@
         <v>6</v>
       </c>
       <c r="F487" t="n">
-        <v>0.478</v>
+        <v>0.489</v>
       </c>
       <c r="G487" t="n">
-        <v>0.554</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="H487" t="n">
-        <v>0.376</v>
+        <v>0.37</v>
       </c>
       <c r="I487" t="n">
-        <v>0.483</v>
+        <v>0.476</v>
       </c>
     </row>
     <row r="488">
@@ -21504,16 +21504,16 @@
         <v>9</v>
       </c>
       <c r="F490" t="n">
-        <v>0.532</v>
+        <v>0.536</v>
       </c>
       <c r="G490" t="n">
-        <v>0.468</v>
+        <v>0.472</v>
       </c>
       <c r="H490" t="n">
-        <v>0.378</v>
+        <v>0.376</v>
       </c>
       <c r="I490" t="n">
-        <v>0.425</v>
+        <v>0.423</v>
       </c>
     </row>
     <row r="491">
@@ -21948,16 +21948,16 @@
         <v>5</v>
       </c>
       <c r="F502" t="n">
-        <v>0.757</v>
+        <v>0.762</v>
       </c>
       <c r="G502" t="n">
-        <v>0.667</v>
+        <v>0.671</v>
       </c>
       <c r="H502" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.0708</v>
       </c>
       <c r="I502" t="n">
-        <v>0.535</v>
+        <v>0.522</v>
       </c>
     </row>
     <row r="503">
@@ -21985,16 +21985,16 @@
         <v>6</v>
       </c>
       <c r="F503" t="n">
-        <v>0.647</v>
+        <v>0.657</v>
       </c>
       <c r="G503" t="n">
-        <v>0.694</v>
+        <v>0.703</v>
       </c>
       <c r="H503" t="n">
-        <v>0.448</v>
+        <v>0.441</v>
       </c>
       <c r="I503" t="n">
-        <v>0.504</v>
+        <v>0.496</v>
       </c>
     </row>
     <row r="504">
@@ -22096,16 +22096,16 @@
         <v>9</v>
       </c>
       <c r="F506" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="G506" t="n">
-        <v>0.628</v>
+        <v>0.631</v>
       </c>
       <c r="H506" t="n">
-        <v>0.237</v>
+        <v>0.235</v>
       </c>
       <c r="I506" t="n">
-        <v>0.331</v>
+        <v>0.326</v>
       </c>
     </row>
     <row r="507">
@@ -22540,13 +22540,13 @@
         <v>5</v>
       </c>
       <c r="F518" t="n">
-        <v>0.727</v>
+        <v>0.733</v>
       </c>
       <c r="G518" t="n">
-        <v>0.773</v>
+        <v>0.78</v>
       </c>
       <c r="H518" t="n">
-        <v>0.424</v>
+        <v>0.42</v>
       </c>
       <c r="I518" t="n">
         <v>1</v>
@@ -22577,16 +22577,16 @@
         <v>6</v>
       </c>
       <c r="F519" t="n">
-        <v>0.68</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="G519" t="n">
-        <v>0.787</v>
+        <v>0.8</v>
       </c>
       <c r="H519" t="n">
-        <v>0.0498</v>
+        <v>0.046</v>
       </c>
       <c r="I519" t="n">
-        <v>0.149</v>
+        <v>0.138</v>
       </c>
     </row>
     <row r="520">
@@ -22688,16 +22688,16 @@
         <v>9</v>
       </c>
       <c r="F522" t="n">
-        <v>0.593</v>
+        <v>0.6</v>
       </c>
       <c r="G522" t="n">
-        <v>0.78</v>
+        <v>0.787</v>
       </c>
       <c r="H522" t="n">
-        <v>0.000733</v>
+        <v>0.000679</v>
       </c>
       <c r="I522" t="n">
-        <v>0.0066</v>
+        <v>0.00611</v>
       </c>
     </row>
     <row r="523">
@@ -23178,7 +23178,7 @@
         <v>0.00441</v>
       </c>
       <c r="I535" t="n">
-        <v>0.0181</v>
+        <v>0.0173</v>
       </c>
     </row>
     <row r="536">
@@ -23363,7 +23363,7 @@
         <v>0.0201</v>
       </c>
       <c r="I540" t="n">
-        <v>0.171</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="541">
@@ -23724,16 +23724,16 @@
         <v>5</v>
       </c>
       <c r="F550" t="n">
-        <v>0.634</v>
+        <v>0.64</v>
       </c>
       <c r="G550" t="n">
-        <v>0.802</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H550" t="n">
-        <v>0.012</v>
+        <v>0.0109</v>
       </c>
       <c r="I550" t="n">
-        <v>0.108</v>
+        <v>0.09810000000000001</v>
       </c>
     </row>
     <row r="551">
@@ -23761,16 +23761,16 @@
         <v>6</v>
       </c>
       <c r="F551" t="n">
-        <v>0.478</v>
+        <v>0.489</v>
       </c>
       <c r="G551" t="n">
-        <v>0.793</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="H551" t="n">
-        <v>1.44e-05</v>
+        <v>9.4e-06</v>
       </c>
       <c r="I551" t="n">
-        <v>0.00013</v>
+        <v>8.46e-05</v>
       </c>
     </row>
     <row r="552">
@@ -23872,16 +23872,16 @@
         <v>9</v>
       </c>
       <c r="F554" t="n">
-        <v>0.532</v>
+        <v>0.536</v>
       </c>
       <c r="G554" t="n">
-        <v>0.786</v>
+        <v>0.792</v>
       </c>
       <c r="H554" t="n">
-        <v>3.3e-05</v>
+        <v>2.84e-05</v>
       </c>
       <c r="I554" t="n">
-        <v>0.000297</v>
+        <v>0.000256</v>
       </c>
     </row>
     <row r="555">
@@ -24316,16 +24316,16 @@
         <v>5</v>
       </c>
       <c r="F566" t="n">
-        <v>0.757</v>
+        <v>0.762</v>
       </c>
       <c r="G566" t="n">
-        <v>0.827</v>
+        <v>0.831</v>
       </c>
       <c r="H566" t="n">
-        <v>0.119</v>
+        <v>0.116</v>
       </c>
       <c r="I566" t="n">
-        <v>0.535</v>
+        <v>0.522</v>
       </c>
     </row>
     <row r="567">
@@ -24353,16 +24353,16 @@
         <v>6</v>
       </c>
       <c r="F567" t="n">
-        <v>0.647</v>
+        <v>0.657</v>
       </c>
       <c r="G567" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="H567" t="n">
-        <v>0.0006400000000000001</v>
+        <v>0.00053</v>
       </c>
       <c r="I567" t="n">
-        <v>0.00576</v>
+        <v>0.00477</v>
       </c>
     </row>
     <row r="568">
@@ -24464,16 +24464,16 @@
         <v>9</v>
       </c>
       <c r="F570" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="G570" t="n">
-        <v>0.857</v>
+        <v>0.861</v>
       </c>
       <c r="H570" t="n">
-        <v>3.48e-05</v>
+        <v>3e-05</v>
       </c>
       <c r="I570" t="n">
-        <v>0.000313</v>
+        <v>0.00027</v>
       </c>
     </row>
     <row r="571">
@@ -24857,7 +24857,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>96.9</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -24872,17 +24872,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>90.2**</t>
+          <t>92.2**</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>92.4**</t>
+          <t>94.4**</t>
         </is>
       </c>
     </row>
@@ -24952,7 +24952,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>94.9</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -24962,17 +24962,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>60.3</t>
+          <t>60.8</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>68.0</t>
         </is>
       </c>
     </row>
@@ -25172,7 +25172,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -25182,22 +25182,22 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>97.5*</t>
+          <t>97.6*</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>88.9</t>
         </is>
       </c>
     </row>
@@ -25457,17 +25457,17 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>60.9</t>
+          <t>62.2</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>79.3**</t>
+          <t>81.1**</t>
         </is>
       </c>
     </row>
@@ -25547,17 +25547,17 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>78.6**</t>
+          <t>79.2**</t>
         </is>
       </c>
     </row>

--- a/eval/results/statistical_tests_full150.xlsx
+++ b/eval/results/statistical_tests_full150.xlsx
@@ -504,7 +504,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.0009790000000000001</v>
+        <v>0.001</v>
       </c>
       <c r="F2" t="n">
         <v>0.837</v>
@@ -513,13 +513,13 @@
         <v>0.903</v>
       </c>
       <c r="H2" t="n">
-        <v>0.115</v>
+        <v>0.116</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0697</v>
+        <v>0.0706</v>
       </c>
       <c r="J2" t="n">
-        <v>0.00705</v>
+        <v>0.0072</v>
       </c>
     </row>
     <row r="3">
@@ -553,10 +553,10 @@
         <v>0.903</v>
       </c>
       <c r="H3" t="n">
-        <v>0.115</v>
+        <v>0.116</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0697</v>
+        <v>0.0706</v>
       </c>
       <c r="J3" t="n">
         <v>0.00967</v>
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.0104</v>
+        <v>0.01</v>
       </c>
       <c r="F4" t="n">
         <v>0.837</v>
@@ -593,13 +593,13 @@
         <v>0.88</v>
       </c>
       <c r="H4" t="n">
-        <v>0.115</v>
+        <v>0.116</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0828</v>
+        <v>0.0833</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0267</v>
+        <v>0.0262</v>
       </c>
     </row>
     <row r="5">
@@ -633,10 +633,10 @@
         <v>0.88</v>
       </c>
       <c r="H5" t="n">
-        <v>0.115</v>
+        <v>0.116</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0828</v>
+        <v>0.0833</v>
       </c>
       <c r="J5" t="n">
         <v>0.0486</v>
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.364</v>
+        <v>0.347</v>
       </c>
       <c r="F6" t="n">
         <v>0.837</v>
@@ -673,13 +673,13 @@
         <v>0.845</v>
       </c>
       <c r="H6" t="n">
-        <v>0.115</v>
+        <v>0.116</v>
       </c>
       <c r="I6" t="n">
         <v>0.102</v>
       </c>
       <c r="J6" t="n">
-        <v>0.409</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="7">
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.306</v>
+        <v>0.293</v>
       </c>
       <c r="F7" t="n">
         <v>0.837</v>
@@ -713,13 +713,13 @@
         <v>0.845</v>
       </c>
       <c r="H7" t="n">
-        <v>0.115</v>
+        <v>0.116</v>
       </c>
       <c r="I7" t="n">
         <v>0.102</v>
       </c>
       <c r="J7" t="n">
-        <v>0.355</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="8">
@@ -744,10 +744,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.0142</v>
+        <v>0.0136</v>
       </c>
       <c r="F8" t="n">
-        <v>0.799</v>
+        <v>0.798</v>
       </c>
       <c r="G8" t="n">
         <v>0.853</v>
@@ -759,7 +759,7 @@
         <v>0.0919</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0301</v>
+        <v>0.0288</v>
       </c>
     </row>
     <row r="9">
@@ -787,7 +787,7 @@
         <v>0.00188</v>
       </c>
       <c r="F9" t="n">
-        <v>0.799</v>
+        <v>0.798</v>
       </c>
       <c r="G9" t="n">
         <v>0.853</v>
@@ -824,13 +824,13 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.159</v>
+        <v>0.161</v>
       </c>
       <c r="F10" t="n">
-        <v>0.799</v>
+        <v>0.798</v>
       </c>
       <c r="G10" t="n">
-        <v>0.831</v>
+        <v>0.83</v>
       </c>
       <c r="H10" t="n">
         <v>0.154</v>
@@ -864,13 +864,13 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.438</v>
+        <v>0.423</v>
       </c>
       <c r="F11" t="n">
-        <v>0.799</v>
+        <v>0.798</v>
       </c>
       <c r="G11" t="n">
-        <v>0.831</v>
+        <v>0.83</v>
       </c>
       <c r="H11" t="n">
         <v>0.154</v>
@@ -879,7 +879,7 @@
         <v>0.109</v>
       </c>
       <c r="J11" t="n">
-        <v>0.493</v>
+        <v>0.476</v>
       </c>
     </row>
     <row r="12">
@@ -904,22 +904,22 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.008540000000000001</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>0.799</v>
+        <v>0.798</v>
       </c>
       <c r="G12" t="n">
-        <v>0.873</v>
+        <v>0.872</v>
       </c>
       <c r="H12" t="n">
         <v>0.154</v>
       </c>
       <c r="I12" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.0791</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0256</v>
+        <v>0.0262</v>
       </c>
     </row>
     <row r="13">
@@ -944,19 +944,19 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.008920000000000001</v>
+        <v>0.008869999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>0.799</v>
+        <v>0.798</v>
       </c>
       <c r="G13" t="n">
-        <v>0.873</v>
+        <v>0.872</v>
       </c>
       <c r="H13" t="n">
         <v>0.154</v>
       </c>
       <c r="I13" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.0791</v>
       </c>
       <c r="J13" t="n">
         <v>0.0216</v>
@@ -1384,7 +1384,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.0253</v>
+        <v>0.0254</v>
       </c>
       <c r="F24" t="n">
         <v>0.864</v>
@@ -1399,7 +1399,7 @@
         <v>0.191</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0479</v>
+        <v>0.0481</v>
       </c>
     </row>
     <row r="25">
@@ -1464,7 +1464,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.0009</v>
+        <v>0.000892</v>
       </c>
       <c r="F26" t="n">
         <v>0.793</v>
@@ -1479,7 +1479,7 @@
         <v>0.0954</v>
       </c>
       <c r="J26" t="n">
-        <v>0.00705</v>
+        <v>0.0072</v>
       </c>
     </row>
     <row r="27">
@@ -1544,7 +1544,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.00721</v>
+        <v>0.00718</v>
       </c>
       <c r="F28" t="n">
         <v>0.793</v>
@@ -1559,7 +1559,7 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="J28" t="n">
-        <v>0.0243</v>
+        <v>0.0249</v>
       </c>
     </row>
     <row r="29">
@@ -1719,7 +1719,7 @@
         <v>0.172</v>
       </c>
       <c r="J32" t="n">
-        <v>0.0479</v>
+        <v>0.0481</v>
       </c>
     </row>
     <row r="33">
@@ -1799,7 +1799,7 @@
         <v>0.226</v>
       </c>
       <c r="J34" t="n">
-        <v>0.0922</v>
+        <v>0.0925</v>
       </c>
     </row>
     <row r="35">
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.00993</v>
+        <v>0.0102</v>
       </c>
       <c r="F38" t="n">
         <v>0.765</v>
@@ -1959,7 +1959,7 @@
         <v>0.137</v>
       </c>
       <c r="J38" t="n">
-        <v>0.0267</v>
+        <v>0.0262</v>
       </c>
     </row>
     <row r="39">
@@ -2039,7 +2039,7 @@
         <v>0.185</v>
       </c>
       <c r="J40" t="n">
-        <v>0.157</v>
+        <v>0.163</v>
       </c>
     </row>
     <row r="41">
@@ -2064,7 +2064,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.112</v>
+        <v>0.09950000000000001</v>
       </c>
       <c r="F41" t="n">
         <v>0.765</v>
@@ -2079,7 +2079,7 @@
         <v>0.185</v>
       </c>
       <c r="J41" t="n">
-        <v>0.161</v>
+        <v>0.149</v>
       </c>
     </row>
     <row r="42">
@@ -2104,7 +2104,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.243</v>
+        <v>0.24</v>
       </c>
       <c r="F42" t="n">
         <v>0.765</v>
@@ -2119,7 +2119,7 @@
         <v>0.224</v>
       </c>
       <c r="J42" t="n">
-        <v>0.282</v>
+        <v>0.279</v>
       </c>
     </row>
     <row r="43">
@@ -2184,10 +2184,10 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.109</v>
+        <v>0.115</v>
       </c>
       <c r="F44" t="n">
-        <v>0.758</v>
+        <v>0.757</v>
       </c>
       <c r="G44" t="n">
         <v>0.706</v>
@@ -2199,7 +2199,7 @@
         <v>0.164</v>
       </c>
       <c r="J44" t="n">
-        <v>0.157</v>
+        <v>0.163</v>
       </c>
     </row>
     <row r="45">
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.14</v>
+        <v>0.156</v>
       </c>
       <c r="F45" t="n">
-        <v>0.758</v>
+        <v>0.757</v>
       </c>
       <c r="G45" t="n">
         <v>0.706</v>
@@ -2239,7 +2239,7 @@
         <v>0.164</v>
       </c>
       <c r="J45" t="n">
-        <v>0.194</v>
+        <v>0.216</v>
       </c>
     </row>
     <row r="46">
@@ -2264,10 +2264,10 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.0129</v>
+        <v>0.0131</v>
       </c>
       <c r="F46" t="n">
-        <v>0.758</v>
+        <v>0.757</v>
       </c>
       <c r="G46" t="n">
         <v>0.617</v>
@@ -2279,7 +2279,7 @@
         <v>0.212</v>
       </c>
       <c r="J46" t="n">
-        <v>0.0301</v>
+        <v>0.0288</v>
       </c>
     </row>
     <row r="47">
@@ -2307,7 +2307,7 @@
         <v>0.00898</v>
       </c>
       <c r="F47" t="n">
-        <v>0.758</v>
+        <v>0.757</v>
       </c>
       <c r="G47" t="n">
         <v>0.617</v>
@@ -2344,13 +2344,13 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.0538</v>
+        <v>0.0551</v>
       </c>
       <c r="F48" t="n">
-        <v>0.758</v>
+        <v>0.757</v>
       </c>
       <c r="G48" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="H48" t="n">
         <v>0.185</v>
@@ -2359,7 +2359,7 @@
         <v>0.162</v>
       </c>
       <c r="J48" t="n">
-        <v>0.0922</v>
+        <v>0.0945</v>
       </c>
     </row>
     <row r="49">
@@ -2387,10 +2387,10 @@
         <v>0.0555</v>
       </c>
       <c r="F49" t="n">
-        <v>0.758</v>
+        <v>0.757</v>
       </c>
       <c r="G49" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="H49" t="n">
         <v>0.185</v>
@@ -2439,7 +2439,7 @@
         <v>0.147</v>
       </c>
       <c r="J50" t="n">
-        <v>0.00705</v>
+        <v>0.0072</v>
       </c>
     </row>
     <row r="51">
@@ -2664,7 +2664,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.00321</v>
+        <v>0.00322</v>
       </c>
       <c r="F56" t="n">
         <v>0.798</v>
@@ -2676,10 +2676,10 @@
         <v>0.132</v>
       </c>
       <c r="I56" t="n">
-        <v>0.092</v>
+        <v>0.0921</v>
       </c>
       <c r="J56" t="n">
-        <v>0.0144</v>
+        <v>0.0145</v>
       </c>
     </row>
     <row r="57">
@@ -2716,7 +2716,7 @@
         <v>0.132</v>
       </c>
       <c r="I57" t="n">
-        <v>0.092</v>
+        <v>0.0921</v>
       </c>
       <c r="J57" t="n">
         <v>0.0129</v>
@@ -2744,7 +2744,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.195</v>
+        <v>0.193</v>
       </c>
       <c r="F58" t="n">
         <v>0.798</v>
@@ -2759,7 +2759,7 @@
         <v>0.15</v>
       </c>
       <c r="J58" t="n">
-        <v>0.242</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="59">
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.512</v>
+        <v>0.526</v>
       </c>
       <c r="F60" t="n">
         <v>0.798</v>
@@ -2839,7 +2839,7 @@
         <v>0.188</v>
       </c>
       <c r="J60" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.574</v>
       </c>
     </row>
     <row r="61">
@@ -2864,7 +2864,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.98</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F61" t="n">
         <v>0.798</v>
@@ -2879,7 +2879,7 @@
         <v>0.188</v>
       </c>
       <c r="J61" t="n">
-        <v>0.98</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="62">
@@ -2904,22 +2904,22 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.0141</v>
+        <v>0.0134</v>
       </c>
       <c r="F62" t="n">
-        <v>0.758</v>
+        <v>0.757</v>
       </c>
       <c r="G62" t="n">
         <v>0.791</v>
       </c>
       <c r="H62" t="n">
-        <v>0.17</v>
+        <v>0.169</v>
       </c>
       <c r="I62" t="n">
         <v>0.137</v>
       </c>
       <c r="J62" t="n">
-        <v>0.0301</v>
+        <v>0.0288</v>
       </c>
     </row>
     <row r="63">
@@ -2947,13 +2947,13 @@
         <v>0.0076</v>
       </c>
       <c r="F63" t="n">
-        <v>0.758</v>
+        <v>0.757</v>
       </c>
       <c r="G63" t="n">
         <v>0.791</v>
       </c>
       <c r="H63" t="n">
-        <v>0.17</v>
+        <v>0.169</v>
       </c>
       <c r="I63" t="n">
         <v>0.137</v>
@@ -2984,22 +2984,22 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.116</v>
+        <v>0.118</v>
       </c>
       <c r="F64" t="n">
-        <v>0.758</v>
+        <v>0.757</v>
       </c>
       <c r="G64" t="n">
-        <v>0.719</v>
+        <v>0.718</v>
       </c>
       <c r="H64" t="n">
-        <v>0.17</v>
+        <v>0.169</v>
       </c>
       <c r="I64" t="n">
         <v>0.186</v>
       </c>
       <c r="J64" t="n">
-        <v>0.161</v>
+        <v>0.163</v>
       </c>
     </row>
     <row r="65">
@@ -3027,13 +3027,13 @@
         <v>0.175</v>
       </c>
       <c r="F65" t="n">
-        <v>0.758</v>
+        <v>0.757</v>
       </c>
       <c r="G65" t="n">
-        <v>0.719</v>
+        <v>0.718</v>
       </c>
       <c r="H65" t="n">
-        <v>0.17</v>
+        <v>0.169</v>
       </c>
       <c r="I65" t="n">
         <v>0.186</v>
@@ -3064,22 +3064,22 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.00742</v>
+        <v>0.00761</v>
       </c>
       <c r="F66" t="n">
-        <v>0.758</v>
+        <v>0.757</v>
       </c>
       <c r="G66" t="n">
-        <v>0.821</v>
+        <v>0.82</v>
       </c>
       <c r="H66" t="n">
-        <v>0.17</v>
+        <v>0.169</v>
       </c>
       <c r="I66" t="n">
         <v>0.145</v>
       </c>
       <c r="J66" t="n">
-        <v>0.0243</v>
+        <v>0.0249</v>
       </c>
     </row>
     <row r="67">
@@ -3107,13 +3107,13 @@
         <v>0.00629</v>
       </c>
       <c r="F67" t="n">
-        <v>0.758</v>
+        <v>0.757</v>
       </c>
       <c r="G67" t="n">
-        <v>0.821</v>
+        <v>0.82</v>
       </c>
       <c r="H67" t="n">
-        <v>0.17</v>
+        <v>0.169</v>
       </c>
       <c r="I67" t="n">
         <v>0.145</v>
@@ -3199,7 +3199,7 @@
         <v>0.149</v>
       </c>
       <c r="J69" t="n">
-        <v>0.158</v>
+        <v>0.151</v>
       </c>
     </row>
     <row r="70">
@@ -3319,7 +3319,7 @@
         <v>0.176</v>
       </c>
       <c r="J72" t="n">
-        <v>0.282</v>
+        <v>0.279</v>
       </c>
     </row>
     <row r="73">
@@ -3633,16 +3633,16 @@
         <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="G7" t="n">
         <v>0.92</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0102</v>
+        <v>0.0066</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0459</v>
+        <v>0.0352</v>
       </c>
     </row>
     <row r="8">
@@ -3747,13 +3747,13 @@
         <v>0.667</v>
       </c>
       <c r="G10" t="n">
-        <v>0.753</v>
+        <v>0.747</v>
       </c>
       <c r="H10" t="n">
-        <v>0.127</v>
+        <v>0.163</v>
       </c>
       <c r="I10" t="n">
-        <v>0.286</v>
+        <v>0.367</v>
       </c>
     </row>
     <row r="11">
@@ -4225,7 +4225,7 @@
         <v>6</v>
       </c>
       <c r="F23" t="n">
-        <v>0.97</v>
+        <v>0.969</v>
       </c>
       <c r="G23" t="n">
         <v>0.9429999999999999</v>
@@ -4339,10 +4339,10 @@
         <v>0.987</v>
       </c>
       <c r="G26" t="n">
-        <v>0.949</v>
+        <v>0.948</v>
       </c>
       <c r="H26" t="n">
-        <v>0.231</v>
+        <v>0.229</v>
       </c>
       <c r="I26" t="n">
         <v>0.858</v>
@@ -4817,16 +4817,16 @@
         <v>6</v>
       </c>
       <c r="F39" t="n">
-        <v>0.711</v>
+        <v>0.7</v>
       </c>
       <c r="G39" t="n">
         <v>0.922</v>
       </c>
       <c r="H39" t="n">
-        <v>0.000399</v>
+        <v>0.000217</v>
       </c>
       <c r="I39" t="n">
-        <v>0.000898</v>
+        <v>0.000488</v>
       </c>
     </row>
     <row r="40">
@@ -4931,13 +4931,13 @@
         <v>0.608</v>
       </c>
       <c r="G42" t="n">
-        <v>0.744</v>
+        <v>0.736</v>
       </c>
       <c r="H42" t="n">
-        <v>0.0303</v>
+        <v>0.043</v>
       </c>
       <c r="I42" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.129</v>
       </c>
     </row>
     <row r="43">
@@ -5409,16 +5409,16 @@
         <v>6</v>
       </c>
       <c r="F55" t="n">
-        <v>0.821</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="G55" t="n">
         <v>0.9330000000000001</v>
       </c>
       <c r="H55" t="n">
-        <v>0.00212</v>
+        <v>0.00128</v>
       </c>
       <c r="I55" t="n">
-        <v>0.00954</v>
+        <v>0.00576</v>
       </c>
     </row>
     <row r="56">
@@ -5523,13 +5523,13 @@
         <v>0.752</v>
       </c>
       <c r="G58" t="n">
-        <v>0.834</v>
+        <v>0.829</v>
       </c>
       <c r="H58" t="n">
-        <v>0.0411</v>
+        <v>0.056</v>
       </c>
       <c r="I58" t="n">
-        <v>0.0925</v>
+        <v>0.126</v>
       </c>
     </row>
     <row r="59">
@@ -6001,16 +6001,16 @@
         <v>6</v>
       </c>
       <c r="F71" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="G71" t="n">
         <v>0.88</v>
       </c>
       <c r="H71" t="n">
-        <v>0.149</v>
+        <v>0.112</v>
       </c>
       <c r="I71" t="n">
-        <v>0.335</v>
+        <v>0.252</v>
       </c>
     </row>
     <row r="72">
@@ -6115,13 +6115,13 @@
         <v>0.667</v>
       </c>
       <c r="G74" t="n">
-        <v>0.787</v>
+        <v>0.78</v>
       </c>
       <c r="H74" t="n">
-        <v>0.0273</v>
+        <v>0.0386</v>
       </c>
       <c r="I74" t="n">
-        <v>0.123</v>
+        <v>0.174</v>
       </c>
     </row>
     <row r="75">
@@ -6593,16 +6593,16 @@
         <v>6</v>
       </c>
       <c r="F87" t="n">
-        <v>0.97</v>
+        <v>0.969</v>
       </c>
       <c r="G87" t="n">
         <v>0.883</v>
       </c>
       <c r="H87" t="n">
-        <v>0.075</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="I87" t="n">
-        <v>0.121</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="88">
@@ -6710,7 +6710,7 @@
         <v>0.96</v>
       </c>
       <c r="H90" t="n">
-        <v>0.391</v>
+        <v>0.389</v>
       </c>
       <c r="I90" t="n">
         <v>0.858</v>
@@ -7185,16 +7185,16 @@
         <v>6</v>
       </c>
       <c r="F103" t="n">
-        <v>0.711</v>
+        <v>0.7</v>
       </c>
       <c r="G103" t="n">
         <v>0.922</v>
       </c>
       <c r="H103" t="n">
-        <v>0.000399</v>
+        <v>0.000217</v>
       </c>
       <c r="I103" t="n">
-        <v>0.000898</v>
+        <v>0.000488</v>
       </c>
     </row>
     <row r="104">
@@ -7299,13 +7299,13 @@
         <v>0.608</v>
       </c>
       <c r="G106" t="n">
-        <v>0.776</v>
+        <v>0.768</v>
       </c>
       <c r="H106" t="n">
-        <v>0.00596</v>
+        <v>0.00927</v>
       </c>
       <c r="I106" t="n">
-        <v>0.0268</v>
+        <v>0.0417</v>
       </c>
     </row>
     <row r="107">
@@ -7777,16 +7777,16 @@
         <v>6</v>
       </c>
       <c r="F119" t="n">
-        <v>0.821</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="G119" t="n">
         <v>0.902</v>
       </c>
       <c r="H119" t="n">
-        <v>0.0379</v>
+        <v>0.0264</v>
       </c>
       <c r="I119" t="n">
-        <v>0.0853</v>
+        <v>0.0594</v>
       </c>
     </row>
     <row r="120">
@@ -7891,13 +7891,13 @@
         <v>0.752</v>
       </c>
       <c r="G122" t="n">
-        <v>0.858</v>
+        <v>0.853</v>
       </c>
       <c r="H122" t="n">
-        <v>0.00665</v>
+        <v>0.01</v>
       </c>
       <c r="I122" t="n">
-        <v>0.0299</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="123">
@@ -8369,16 +8369,16 @@
         <v>6</v>
       </c>
       <c r="F135" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="G135" t="n">
         <v>0.853</v>
       </c>
       <c r="H135" t="n">
-        <v>0.439</v>
+        <v>0.357</v>
       </c>
       <c r="I135" t="n">
-        <v>0.502</v>
+        <v>0.414</v>
       </c>
     </row>
     <row r="136">
@@ -8961,16 +8961,16 @@
         <v>6</v>
       </c>
       <c r="F151" t="n">
-        <v>0.97</v>
+        <v>0.969</v>
       </c>
       <c r="G151" t="n">
         <v>0.833</v>
       </c>
       <c r="H151" t="n">
-        <v>0.00578</v>
+        <v>0.00604</v>
       </c>
       <c r="I151" t="n">
-        <v>0.0173</v>
+        <v>0.0181</v>
       </c>
     </row>
     <row r="152">
@@ -9553,16 +9553,16 @@
         <v>6</v>
       </c>
       <c r="F167" t="n">
-        <v>0.711</v>
+        <v>0.7</v>
       </c>
       <c r="G167" t="n">
         <v>0.944</v>
       </c>
       <c r="H167" t="n">
-        <v>4.59e-05</v>
+        <v>2.32e-05</v>
       </c>
       <c r="I167" t="n">
-        <v>0.000207</v>
+        <v>0.000104</v>
       </c>
     </row>
     <row r="168">
@@ -10145,16 +10145,16 @@
         <v>6</v>
       </c>
       <c r="F183" t="n">
-        <v>0.821</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="G183" t="n">
         <v>0.885</v>
       </c>
       <c r="H183" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.0675</v>
       </c>
       <c r="I183" t="n">
-        <v>0.167</v>
+        <v>0.122</v>
       </c>
     </row>
     <row r="184">
@@ -10737,16 +10737,16 @@
         <v>6</v>
       </c>
       <c r="F199" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="G199" t="n">
         <v>0.867</v>
       </c>
       <c r="H199" t="n">
-        <v>0.211</v>
+        <v>0.163</v>
       </c>
       <c r="I199" t="n">
-        <v>0.38</v>
+        <v>0.293</v>
       </c>
     </row>
     <row r="200">
@@ -11329,16 +11329,16 @@
         <v>6</v>
       </c>
       <c r="F215" t="n">
-        <v>0.877</v>
+        <v>0.875</v>
       </c>
       <c r="G215" t="n">
         <v>0.961</v>
       </c>
       <c r="H215" t="n">
-        <v>0.081</v>
+        <v>0.08019999999999999</v>
       </c>
       <c r="I215" t="n">
-        <v>0.121</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="216">
@@ -11921,16 +11921,16 @@
         <v>6</v>
       </c>
       <c r="F231" t="n">
-        <v>0.789</v>
+        <v>0.778</v>
       </c>
       <c r="G231" t="n">
         <v>0.8110000000000001</v>
       </c>
       <c r="H231" t="n">
-        <v>0.852</v>
+        <v>0.713</v>
       </c>
       <c r="I231" t="n">
-        <v>0.852</v>
+        <v>0.727</v>
       </c>
     </row>
     <row r="232">
@@ -12513,16 +12513,16 @@
         <v>6</v>
       </c>
       <c r="F247" t="n">
-        <v>0.83</v>
+        <v>0.824</v>
       </c>
       <c r="G247" t="n">
         <v>0.88</v>
       </c>
       <c r="H247" t="n">
-        <v>0.219</v>
+        <v>0.169</v>
       </c>
       <c r="I247" t="n">
-        <v>0.282</v>
+        <v>0.217</v>
       </c>
     </row>
     <row r="248">
@@ -13105,16 +13105,16 @@
         <v>6</v>
       </c>
       <c r="F263" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="G263" t="n">
         <v>0.847</v>
       </c>
       <c r="H263" t="n">
-        <v>0.446</v>
+        <v>0.364</v>
       </c>
       <c r="I263" t="n">
-        <v>0.502</v>
+        <v>0.414</v>
       </c>
     </row>
     <row r="264">
@@ -13219,13 +13219,13 @@
         <v>0.667</v>
       </c>
       <c r="G266" t="n">
-        <v>0.613</v>
+        <v>0.607</v>
       </c>
       <c r="H266" t="n">
-        <v>0.4</v>
+        <v>0.337</v>
       </c>
       <c r="I266" t="n">
-        <v>0.534</v>
+        <v>0.526</v>
       </c>
     </row>
     <row r="267">
@@ -13697,16 +13697,16 @@
         <v>6</v>
       </c>
       <c r="F279" t="n">
-        <v>0.877</v>
+        <v>0.875</v>
       </c>
       <c r="G279" t="n">
         <v>1</v>
       </c>
       <c r="H279" t="n">
-        <v>0.00209</v>
+        <v>0.002</v>
       </c>
       <c r="I279" t="n">
-        <v>0.0173</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="280">
@@ -13811,10 +13811,10 @@
         <v>0.963</v>
       </c>
       <c r="G282" t="n">
-        <v>0.986</v>
+        <v>0.985</v>
       </c>
       <c r="H282" t="n">
-        <v>0.625</v>
+        <v>0.626</v>
       </c>
       <c r="I282" t="n">
         <v>0.858</v>
@@ -14289,16 +14289,16 @@
         <v>6</v>
       </c>
       <c r="F295" t="n">
-        <v>0.789</v>
+        <v>0.778</v>
       </c>
       <c r="G295" t="n">
         <v>0.744</v>
       </c>
       <c r="H295" t="n">
-        <v>0.597</v>
+        <v>0.727</v>
       </c>
       <c r="I295" t="n">
-        <v>0.672</v>
+        <v>0.727</v>
       </c>
     </row>
     <row r="296">
@@ -14403,13 +14403,13 @@
         <v>0.624</v>
       </c>
       <c r="G298" t="n">
-        <v>0.544</v>
+        <v>0.536</v>
       </c>
       <c r="H298" t="n">
-        <v>0.248</v>
+        <v>0.2</v>
       </c>
       <c r="I298" t="n">
-        <v>0.423</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="299">
@@ -14881,16 +14881,16 @@
         <v>6</v>
       </c>
       <c r="F311" t="n">
-        <v>0.83</v>
+        <v>0.824</v>
       </c>
       <c r="G311" t="n">
         <v>0.854</v>
       </c>
       <c r="H311" t="n">
-        <v>0.65</v>
+        <v>0.548</v>
       </c>
       <c r="I311" t="n">
-        <v>0.65</v>
+        <v>0.548</v>
       </c>
     </row>
     <row r="312">
@@ -14995,13 +14995,13 @@
         <v>0.757</v>
       </c>
       <c r="G314" t="n">
-        <v>0.701</v>
+        <v>0.694</v>
       </c>
       <c r="H314" t="n">
-        <v>0.217</v>
+        <v>0.178</v>
       </c>
       <c r="I314" t="n">
-        <v>0.326</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="315">
@@ -15473,16 +15473,16 @@
         <v>6</v>
       </c>
       <c r="F327" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="G327" t="n">
-        <v>0.92</v>
+        <v>0.913</v>
       </c>
       <c r="H327" t="n">
-        <v>0.0066</v>
+        <v>0.007820000000000001</v>
       </c>
       <c r="I327" t="n">
-        <v>0.0459</v>
+        <v>0.0352</v>
       </c>
     </row>
     <row r="328">
@@ -15587,13 +15587,13 @@
         <v>0.667</v>
       </c>
       <c r="G330" t="n">
-        <v>0.76</v>
+        <v>0.753</v>
       </c>
       <c r="H330" t="n">
-        <v>0.09669999999999999</v>
+        <v>0.127</v>
       </c>
       <c r="I330" t="n">
-        <v>0.286</v>
+        <v>0.367</v>
       </c>
     </row>
     <row r="331">
@@ -16065,16 +16065,16 @@
         <v>6</v>
       </c>
       <c r="F343" t="n">
-        <v>0.877</v>
+        <v>0.875</v>
       </c>
       <c r="G343" t="n">
-        <v>0.976</v>
+        <v>0.975</v>
       </c>
       <c r="H343" t="n">
-        <v>0.0176</v>
+        <v>0.0175</v>
       </c>
       <c r="I343" t="n">
-        <v>0.0396</v>
+        <v>0.0394</v>
       </c>
     </row>
     <row r="344">
@@ -16179,7 +16179,7 @@
         <v>0.963</v>
       </c>
       <c r="G346" t="n">
-        <v>0.959</v>
+        <v>0.958</v>
       </c>
       <c r="H346" t="n">
         <v>1</v>
@@ -16657,16 +16657,16 @@
         <v>6</v>
       </c>
       <c r="F359" t="n">
-        <v>0.789</v>
+        <v>0.778</v>
       </c>
       <c r="G359" t="n">
-        <v>0.889</v>
+        <v>0.878</v>
       </c>
       <c r="H359" t="n">
-        <v>0.104</v>
+        <v>0.113</v>
       </c>
       <c r="I359" t="n">
-        <v>0.156</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="360">
@@ -16771,13 +16771,13 @@
         <v>0.624</v>
       </c>
       <c r="G362" t="n">
-        <v>0.744</v>
+        <v>0.736</v>
       </c>
       <c r="H362" t="n">
-        <v>0.0565</v>
+        <v>0.0776</v>
       </c>
       <c r="I362" t="n">
-        <v>0.127</v>
+        <v>0.175</v>
       </c>
     </row>
     <row r="363">
@@ -17249,16 +17249,16 @@
         <v>6</v>
       </c>
       <c r="F375" t="n">
-        <v>0.83</v>
+        <v>0.824</v>
       </c>
       <c r="G375" t="n">
-        <v>0.93</v>
+        <v>0.924</v>
       </c>
       <c r="H375" t="n">
-        <v>0.00464</v>
+        <v>0.00556</v>
       </c>
       <c r="I375" t="n">
-        <v>0.0139</v>
+        <v>0.0167</v>
       </c>
     </row>
     <row r="376">
@@ -17363,13 +17363,13 @@
         <v>0.757</v>
       </c>
       <c r="G378" t="n">
-        <v>0.838</v>
+        <v>0.833</v>
       </c>
       <c r="H378" t="n">
-        <v>0.0407</v>
+        <v>0.0556</v>
       </c>
       <c r="I378" t="n">
-        <v>0.0925</v>
+        <v>0.126</v>
       </c>
     </row>
     <row r="379">
@@ -17850,7 +17850,7 @@
         <v>0.368</v>
       </c>
       <c r="I391" t="n">
-        <v>0.502</v>
+        <v>0.414</v>
       </c>
     </row>
     <row r="392">
@@ -19034,7 +19034,7 @@
         <v>0.0987</v>
       </c>
       <c r="I423" t="n">
-        <v>0.156</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="424">
@@ -20329,7 +20329,7 @@
         <v>0.351</v>
       </c>
       <c r="I458" t="n">
-        <v>0.534</v>
+        <v>0.526</v>
       </c>
     </row>
     <row r="459">
@@ -23178,7 +23178,7 @@
         <v>0.00441</v>
       </c>
       <c r="I535" t="n">
-        <v>0.0173</v>
+        <v>0.0181</v>
       </c>
     </row>
     <row r="536">
@@ -24857,7 +24857,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>96.9</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -24872,7 +24872,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -24952,7 +24952,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>94.9</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -24967,7 +24967,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -25172,7 +25172,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -25182,12 +25182,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>97.6*</t>
+          <t>97.5*</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -25197,7 +25197,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>87.8</t>
         </is>
       </c>
     </row>

--- a/eval/results/statistical_tests_full150.xlsx
+++ b/eval/results/statistical_tests_full150.xlsx
@@ -24746,7 +24746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24938,41 +24938,41 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>98.7</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>92.6</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>60.8</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>81.5**</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>75.0</t>
         </is>
       </c>
     </row>
@@ -24983,41 +24983,41 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>92.6</t>
+          <t>85.9**</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>70.1</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>81.5**</t>
+          <t>82.1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>61.2</t>
         </is>
       </c>
     </row>
@@ -25028,86 +25028,86 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>63.5</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>85.9**</t>
+          <t>78.0*</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>70.1</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>82.1</t>
+          <t>68.4*</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>29.8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GPT-4o</t>
+          <t>Llama3.1-70B</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>78.0*</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>68.4*</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>93.1**</t>
         </is>
       </c>
     </row>
@@ -25118,41 +25118,41 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>96.1</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>97.5*</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>93.1**</t>
+          <t>87.8</t>
         </is>
       </c>
     </row>
@@ -25163,41 +25163,41 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>96.1</t>
+          <t>98.1**</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>97.5*</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>84.9</t>
         </is>
       </c>
     </row>
@@ -25208,41 +25208,41 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>98.1**</t>
+          <t>77.1**</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>78.3**</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>78.1</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>55.2</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>84.9</t>
+          <t>70.1</t>
         </is>
       </c>
     </row>
@@ -25253,86 +25253,86 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>36.5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>77.1**</t>
+          <t>69.7**</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>78.3**</t>
+          <t>68.3**</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>66.7</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>55.2</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>70.1</t>
+          <t>49.1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Llama3.1-70B</t>
+          <t>Llama3.1-8B</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report HIV sequences from patient samples?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>69.7**</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>68.3**</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>100.0**</t>
         </is>
       </c>
     </row>
@@ -25343,41 +25343,41 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from patient samples?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>93.1</t>
+          <t>59.1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>87.5*</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>100.0**</t>
+          <t>100.0</t>
         </is>
       </c>
     </row>
@@ -25388,41 +25388,41 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>59.1</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>87.5*</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>84.9</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>62.2</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>81.1**</t>
         </is>
       </c>
     </row>
@@ -25433,41 +25433,41 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>96.4</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>84.9</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>62.2</t>
+          <t>62.4</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>81.1**</t>
+          <t>97.6**</t>
         </is>
       </c>
     </row>
@@ -25478,41 +25478,41 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>97.1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>96.4</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>62.4</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>97.6**</t>
+          <t>79.2**</t>
         </is>
       </c>
     </row>
@@ -25523,41 +25523,41 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>97.1</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>69.1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>79.2**</t>
+          <t>91.8**</t>
         </is>
       </c>
     </row>
@@ -25568,84 +25568,39 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>92.3</t>
+          <t>88.9</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.1</t>
+          <t>65.1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
-        <is>
-          <t>91.8**</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Llama3.1-8B</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>14</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>76.1</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>88.9</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>65.1</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>65.8</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
         <is>
           <t>97.3**</t>
         </is>

--- a/eval/results/statistical_tests_full150.xlsx
+++ b/eval/results/statistical_tests_full150.xlsx
@@ -507,16 +507,16 @@
         <v>0.001</v>
       </c>
       <c r="F2" t="n">
-        <v>0.837</v>
+        <v>0.838</v>
       </c>
       <c r="G2" t="n">
         <v>0.903</v>
       </c>
       <c r="H2" t="n">
-        <v>0.116</v>
+        <v>0.114</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0706</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="J2" t="n">
         <v>0.0072</v>
@@ -547,16 +547,16 @@
         <v>0.00146</v>
       </c>
       <c r="F3" t="n">
-        <v>0.837</v>
+        <v>0.838</v>
       </c>
       <c r="G3" t="n">
         <v>0.903</v>
       </c>
       <c r="H3" t="n">
-        <v>0.116</v>
+        <v>0.114</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0706</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="J3" t="n">
         <v>0.00967</v>
@@ -584,22 +584,22 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.01</v>
+        <v>0.0112</v>
       </c>
       <c r="F4" t="n">
-        <v>0.837</v>
+        <v>0.838</v>
       </c>
       <c r="G4" t="n">
         <v>0.88</v>
       </c>
       <c r="H4" t="n">
-        <v>0.116</v>
+        <v>0.114</v>
       </c>
       <c r="I4" t="n">
         <v>0.0833</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0262</v>
+        <v>0.0288</v>
       </c>
     </row>
     <row r="5">
@@ -624,22 +624,22 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.0243</v>
+        <v>0.0259</v>
       </c>
       <c r="F5" t="n">
-        <v>0.837</v>
+        <v>0.838</v>
       </c>
       <c r="G5" t="n">
         <v>0.88</v>
       </c>
       <c r="H5" t="n">
-        <v>0.116</v>
+        <v>0.114</v>
       </c>
       <c r="I5" t="n">
         <v>0.0833</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0486</v>
+        <v>0.0518</v>
       </c>
     </row>
     <row r="6">
@@ -664,22 +664,22 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.347</v>
+        <v>0.412</v>
       </c>
       <c r="F6" t="n">
-        <v>0.837</v>
+        <v>0.838</v>
       </c>
       <c r="G6" t="n">
         <v>0.845</v>
       </c>
       <c r="H6" t="n">
-        <v>0.116</v>
+        <v>0.114</v>
       </c>
       <c r="I6" t="n">
         <v>0.102</v>
       </c>
       <c r="J6" t="n">
-        <v>0.39</v>
+        <v>0.463</v>
       </c>
     </row>
     <row r="7">
@@ -704,22 +704,22 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.293</v>
+        <v>0.362</v>
       </c>
       <c r="F7" t="n">
-        <v>0.837</v>
+        <v>0.838</v>
       </c>
       <c r="G7" t="n">
         <v>0.845</v>
       </c>
       <c r="H7" t="n">
-        <v>0.116</v>
+        <v>0.114</v>
       </c>
       <c r="I7" t="n">
         <v>0.102</v>
       </c>
       <c r="J7" t="n">
-        <v>0.34</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="8">
@@ -744,10 +744,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.0136</v>
+        <v>0.0151</v>
       </c>
       <c r="F8" t="n">
-        <v>0.798</v>
+        <v>0.799</v>
       </c>
       <c r="G8" t="n">
         <v>0.853</v>
@@ -759,7 +759,7 @@
         <v>0.0919</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0288</v>
+        <v>0.0326</v>
       </c>
     </row>
     <row r="9">
@@ -787,7 +787,7 @@
         <v>0.00188</v>
       </c>
       <c r="F9" t="n">
-        <v>0.798</v>
+        <v>0.799</v>
       </c>
       <c r="G9" t="n">
         <v>0.853</v>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.161</v>
+        <v>0.176</v>
       </c>
       <c r="F10" t="n">
-        <v>0.798</v>
+        <v>0.799</v>
       </c>
       <c r="G10" t="n">
         <v>0.83</v>
@@ -839,7 +839,7 @@
         <v>0.109</v>
       </c>
       <c r="J10" t="n">
-        <v>0.211</v>
+        <v>0.226</v>
       </c>
     </row>
     <row r="11">
@@ -867,7 +867,7 @@
         <v>0.423</v>
       </c>
       <c r="F11" t="n">
-        <v>0.798</v>
+        <v>0.799</v>
       </c>
       <c r="G11" t="n">
         <v>0.83</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0094</v>
       </c>
       <c r="F12" t="n">
-        <v>0.798</v>
+        <v>0.799</v>
       </c>
       <c r="G12" t="n">
         <v>0.872</v>
@@ -919,7 +919,7 @@
         <v>0.0791</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0262</v>
+        <v>0.0282</v>
       </c>
     </row>
     <row r="13">
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.008869999999999999</v>
+        <v>0.008920000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>0.798</v>
+        <v>0.799</v>
       </c>
       <c r="G13" t="n">
         <v>0.872</v>
@@ -984,22 +984,22 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.661</v>
+        <v>0.705</v>
       </c>
       <c r="F14" t="n">
-        <v>0.78</v>
+        <v>0.781</v>
       </c>
       <c r="G14" t="n">
         <v>0.787</v>
       </c>
       <c r="H14" t="n">
-        <v>0.13</v>
+        <v>0.129</v>
       </c>
       <c r="I14" t="n">
         <v>0.115</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7</v>
+        <v>0.746</v>
       </c>
     </row>
     <row r="15">
@@ -1024,22 +1024,22 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.753</v>
+        <v>0.801</v>
       </c>
       <c r="F15" t="n">
-        <v>0.78</v>
+        <v>0.781</v>
       </c>
       <c r="G15" t="n">
         <v>0.787</v>
       </c>
       <c r="H15" t="n">
-        <v>0.13</v>
+        <v>0.129</v>
       </c>
       <c r="I15" t="n">
         <v>0.115</v>
       </c>
       <c r="J15" t="n">
-        <v>0.797</v>
+        <v>0.843</v>
       </c>
     </row>
     <row r="16">
@@ -1064,22 +1064,22 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.00558</v>
+        <v>0.00515</v>
       </c>
       <c r="F16" t="n">
-        <v>0.78</v>
+        <v>0.781</v>
       </c>
       <c r="G16" t="n">
         <v>0.707</v>
       </c>
       <c r="H16" t="n">
-        <v>0.13</v>
+        <v>0.129</v>
       </c>
       <c r="I16" t="n">
         <v>0.106</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0223</v>
+        <v>0.0206</v>
       </c>
     </row>
     <row r="17">
@@ -1107,19 +1107,19 @@
         <v>0.0106</v>
       </c>
       <c r="F17" t="n">
-        <v>0.78</v>
+        <v>0.781</v>
       </c>
       <c r="G17" t="n">
         <v>0.707</v>
       </c>
       <c r="H17" t="n">
-        <v>0.13</v>
+        <v>0.129</v>
       </c>
       <c r="I17" t="n">
         <v>0.106</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0233</v>
+        <v>0.0238</v>
       </c>
     </row>
     <row r="18">
@@ -1144,22 +1144,22 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.914</v>
+        <v>0.93</v>
       </c>
       <c r="F18" t="n">
-        <v>0.78</v>
+        <v>0.781</v>
       </c>
       <c r="G18" t="n">
-        <v>0.782</v>
+        <v>0.783</v>
       </c>
       <c r="H18" t="n">
-        <v>0.13</v>
+        <v>0.129</v>
       </c>
       <c r="I18" t="n">
         <v>0.11</v>
       </c>
       <c r="J18" t="n">
-        <v>0.914</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="19">
@@ -1187,13 +1187,13 @@
         <v>0.82</v>
       </c>
       <c r="F19" t="n">
-        <v>0.78</v>
+        <v>0.781</v>
       </c>
       <c r="G19" t="n">
-        <v>0.782</v>
+        <v>0.783</v>
       </c>
       <c r="H19" t="n">
-        <v>0.13</v>
+        <v>0.129</v>
       </c>
       <c r="I19" t="n">
         <v>0.11</v>
@@ -1224,7 +1224,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.09039999999999999</v>
+        <v>0.0911</v>
       </c>
       <c r="F20" t="n">
         <v>0.864</v>
@@ -1239,7 +1239,7 @@
         <v>0.0584</v>
       </c>
       <c r="J20" t="n">
-        <v>0.141</v>
+        <v>0.143</v>
       </c>
     </row>
     <row r="21">
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="F22" t="n">
         <v>0.864</v>
@@ -1319,7 +1319,7 @@
         <v>0.11</v>
       </c>
       <c r="J22" t="n">
-        <v>0.832</v>
+        <v>0.823</v>
       </c>
     </row>
     <row r="23">
@@ -1384,7 +1384,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.0254</v>
+        <v>0.0242</v>
       </c>
       <c r="F24" t="n">
         <v>0.864</v>
@@ -1399,7 +1399,7 @@
         <v>0.191</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0481</v>
+        <v>0.046</v>
       </c>
     </row>
     <row r="25">
@@ -1464,7 +1464,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.000892</v>
+        <v>0.000899</v>
       </c>
       <c r="F26" t="n">
         <v>0.793</v>
@@ -1544,7 +1544,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.00718</v>
+        <v>0.00721</v>
       </c>
       <c r="F28" t="n">
         <v>0.793</v>
@@ -1559,7 +1559,7 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="J28" t="n">
-        <v>0.0249</v>
+        <v>0.026</v>
       </c>
     </row>
     <row r="29">
@@ -1624,7 +1624,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.164</v>
+        <v>0.165</v>
       </c>
       <c r="F30" t="n">
         <v>0.793</v>
@@ -1639,7 +1639,7 @@
         <v>0.164</v>
       </c>
       <c r="J30" t="n">
-        <v>0.211</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="31">
@@ -1704,7 +1704,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.0242</v>
+        <v>0.0243</v>
       </c>
       <c r="F32" t="n">
         <v>0.778</v>
@@ -1719,7 +1719,7 @@
         <v>0.172</v>
       </c>
       <c r="J32" t="n">
-        <v>0.0481</v>
+        <v>0.046</v>
       </c>
     </row>
     <row r="33">
@@ -1784,7 +1784,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.0514</v>
+        <v>0.0513</v>
       </c>
       <c r="F34" t="n">
         <v>0.778</v>
@@ -1799,7 +1799,7 @@
         <v>0.226</v>
       </c>
       <c r="J34" t="n">
-        <v>0.0925</v>
+        <v>0.09229999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1864,7 +1864,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5.79e-05</v>
+        <v>5.82e-05</v>
       </c>
       <c r="F36" t="n">
         <v>0.778</v>
@@ -1879,7 +1879,7 @@
         <v>0.205</v>
       </c>
       <c r="J36" t="n">
-        <v>0.00104</v>
+        <v>0.00105</v>
       </c>
     </row>
     <row r="37">
@@ -1944,22 +1944,22 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.0102</v>
+        <v>0.011</v>
       </c>
       <c r="F38" t="n">
-        <v>0.765</v>
+        <v>0.767</v>
       </c>
       <c r="G38" t="n">
         <v>0.845</v>
       </c>
       <c r="H38" t="n">
-        <v>0.165</v>
+        <v>0.164</v>
       </c>
       <c r="I38" t="n">
         <v>0.137</v>
       </c>
       <c r="J38" t="n">
-        <v>0.0262</v>
+        <v>0.0288</v>
       </c>
     </row>
     <row r="39">
@@ -1984,22 +1984,22 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.011</v>
+        <v>0.0132</v>
       </c>
       <c r="F39" t="n">
-        <v>0.765</v>
+        <v>0.767</v>
       </c>
       <c r="G39" t="n">
         <v>0.845</v>
       </c>
       <c r="H39" t="n">
-        <v>0.165</v>
+        <v>0.164</v>
       </c>
       <c r="I39" t="n">
         <v>0.137</v>
       </c>
       <c r="J39" t="n">
-        <v>0.0233</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="40">
@@ -2024,22 +2024,22 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.109</v>
+        <v>0.124</v>
       </c>
       <c r="F40" t="n">
-        <v>0.765</v>
+        <v>0.767</v>
       </c>
       <c r="G40" t="n">
         <v>0.8179999999999999</v>
       </c>
       <c r="H40" t="n">
-        <v>0.165</v>
+        <v>0.164</v>
       </c>
       <c r="I40" t="n">
         <v>0.185</v>
       </c>
       <c r="J40" t="n">
-        <v>0.163</v>
+        <v>0.172</v>
       </c>
     </row>
     <row r="41">
@@ -2064,22 +2064,22 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.09950000000000001</v>
+        <v>0.112</v>
       </c>
       <c r="F41" t="n">
-        <v>0.765</v>
+        <v>0.767</v>
       </c>
       <c r="G41" t="n">
         <v>0.8179999999999999</v>
       </c>
       <c r="H41" t="n">
-        <v>0.165</v>
+        <v>0.164</v>
       </c>
       <c r="I41" t="n">
         <v>0.185</v>
       </c>
       <c r="J41" t="n">
-        <v>0.149</v>
+        <v>0.161</v>
       </c>
     </row>
     <row r="42">
@@ -2104,22 +2104,22 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.24</v>
+        <v>0.273</v>
       </c>
       <c r="F42" t="n">
-        <v>0.765</v>
+        <v>0.767</v>
       </c>
       <c r="G42" t="n">
         <v>0.8</v>
       </c>
       <c r="H42" t="n">
-        <v>0.165</v>
+        <v>0.164</v>
       </c>
       <c r="I42" t="n">
         <v>0.224</v>
       </c>
       <c r="J42" t="n">
-        <v>0.279</v>
+        <v>0.317</v>
       </c>
     </row>
     <row r="43">
@@ -2144,22 +2144,22 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.221</v>
+        <v>0.198</v>
       </c>
       <c r="F43" t="n">
-        <v>0.765</v>
+        <v>0.767</v>
       </c>
       <c r="G43" t="n">
         <v>0.8</v>
       </c>
       <c r="H43" t="n">
-        <v>0.165</v>
+        <v>0.164</v>
       </c>
       <c r="I43" t="n">
         <v>0.224</v>
       </c>
       <c r="J43" t="n">
-        <v>0.265</v>
+        <v>0.255</v>
       </c>
     </row>
     <row r="44">
@@ -2184,22 +2184,22 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.115</v>
+        <v>0.107</v>
       </c>
       <c r="F44" t="n">
-        <v>0.757</v>
+        <v>0.758</v>
       </c>
       <c r="G44" t="n">
         <v>0.706</v>
       </c>
       <c r="H44" t="n">
-        <v>0.185</v>
+        <v>0.184</v>
       </c>
       <c r="I44" t="n">
         <v>0.164</v>
       </c>
       <c r="J44" t="n">
-        <v>0.163</v>
+        <v>0.161</v>
       </c>
     </row>
     <row r="45">
@@ -2224,22 +2224,22 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.156</v>
+        <v>0.14</v>
       </c>
       <c r="F45" t="n">
-        <v>0.757</v>
+        <v>0.758</v>
       </c>
       <c r="G45" t="n">
         <v>0.706</v>
       </c>
       <c r="H45" t="n">
-        <v>0.185</v>
+        <v>0.184</v>
       </c>
       <c r="I45" t="n">
         <v>0.164</v>
       </c>
       <c r="J45" t="n">
-        <v>0.216</v>
+        <v>0.194</v>
       </c>
     </row>
     <row r="46">
@@ -2264,22 +2264,22 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.0131</v>
+        <v>0.0124</v>
       </c>
       <c r="F46" t="n">
-        <v>0.757</v>
+        <v>0.758</v>
       </c>
       <c r="G46" t="n">
         <v>0.617</v>
       </c>
       <c r="H46" t="n">
-        <v>0.185</v>
+        <v>0.184</v>
       </c>
       <c r="I46" t="n">
         <v>0.212</v>
       </c>
       <c r="J46" t="n">
-        <v>0.0288</v>
+        <v>0.0298</v>
       </c>
     </row>
     <row r="47">
@@ -2307,13 +2307,13 @@
         <v>0.00898</v>
       </c>
       <c r="F47" t="n">
-        <v>0.757</v>
+        <v>0.758</v>
       </c>
       <c r="G47" t="n">
         <v>0.617</v>
       </c>
       <c r="H47" t="n">
-        <v>0.185</v>
+        <v>0.184</v>
       </c>
       <c r="I47" t="n">
         <v>0.212</v>
@@ -2344,22 +2344,22 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.0551</v>
+        <v>0.058</v>
       </c>
       <c r="F48" t="n">
-        <v>0.757</v>
+        <v>0.758</v>
       </c>
       <c r="G48" t="n">
         <v>0.8169999999999999</v>
       </c>
       <c r="H48" t="n">
-        <v>0.185</v>
+        <v>0.184</v>
       </c>
       <c r="I48" t="n">
         <v>0.162</v>
       </c>
       <c r="J48" t="n">
-        <v>0.0945</v>
+        <v>0.0994</v>
       </c>
     </row>
     <row r="49">
@@ -2387,19 +2387,19 @@
         <v>0.0555</v>
       </c>
       <c r="F49" t="n">
-        <v>0.757</v>
+        <v>0.758</v>
       </c>
       <c r="G49" t="n">
         <v>0.8169999999999999</v>
       </c>
       <c r="H49" t="n">
-        <v>0.185</v>
+        <v>0.184</v>
       </c>
       <c r="I49" t="n">
         <v>0.162</v>
       </c>
       <c r="J49" t="n">
-        <v>0.0944</v>
+        <v>0.0951</v>
       </c>
     </row>
     <row r="50">
@@ -2424,22 +2424,22 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.000634</v>
+        <v>0.000566</v>
       </c>
       <c r="F50" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="G50" t="n">
         <v>0.58</v>
       </c>
       <c r="H50" t="n">
-        <v>0.179</v>
+        <v>0.178</v>
       </c>
       <c r="I50" t="n">
         <v>0.147</v>
       </c>
       <c r="J50" t="n">
-        <v>0.0072</v>
+        <v>0.00679</v>
       </c>
     </row>
     <row r="51">
@@ -2467,13 +2467,13 @@
         <v>0.00377</v>
       </c>
       <c r="F51" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="G51" t="n">
         <v>0.58</v>
       </c>
       <c r="H51" t="n">
-        <v>0.179</v>
+        <v>0.178</v>
       </c>
       <c r="I51" t="n">
         <v>0.147</v>
@@ -2504,22 +2504,22 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.0026</v>
+        <v>0.00237</v>
       </c>
       <c r="F52" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="G52" t="n">
         <v>0.589</v>
       </c>
       <c r="H52" t="n">
-        <v>0.179</v>
+        <v>0.178</v>
       </c>
       <c r="I52" t="n">
         <v>0.163</v>
       </c>
       <c r="J52" t="n">
-        <v>0.0141</v>
+        <v>0.0132</v>
       </c>
     </row>
     <row r="53">
@@ -2544,22 +2544,22 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.00641</v>
+        <v>0.00539</v>
       </c>
       <c r="F53" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="G53" t="n">
         <v>0.589</v>
       </c>
       <c r="H53" t="n">
-        <v>0.179</v>
+        <v>0.178</v>
       </c>
       <c r="I53" t="n">
         <v>0.163</v>
       </c>
       <c r="J53" t="n">
-        <v>0.0192</v>
+        <v>0.0176</v>
       </c>
     </row>
     <row r="54">
@@ -2584,22 +2584,22 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3.17e-05</v>
+        <v>2.77e-05</v>
       </c>
       <c r="F54" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="G54" t="n">
-        <v>0.842</v>
+        <v>0.843</v>
       </c>
       <c r="H54" t="n">
-        <v>0.179</v>
+        <v>0.178</v>
       </c>
       <c r="I54" t="n">
         <v>0.173</v>
       </c>
       <c r="J54" t="n">
-        <v>0.00104</v>
+        <v>0.0009970000000000001</v>
       </c>
     </row>
     <row r="55">
@@ -2627,13 +2627,13 @@
         <v>6.1e-05</v>
       </c>
       <c r="F55" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="G55" t="n">
-        <v>0.842</v>
+        <v>0.843</v>
       </c>
       <c r="H55" t="n">
-        <v>0.179</v>
+        <v>0.178</v>
       </c>
       <c r="I55" t="n">
         <v>0.173</v>
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.00322</v>
+        <v>0.00336</v>
       </c>
       <c r="F56" t="n">
-        <v>0.798</v>
+        <v>0.799</v>
       </c>
       <c r="G56" t="n">
         <v>0.875</v>
@@ -2679,7 +2679,7 @@
         <v>0.0921</v>
       </c>
       <c r="J56" t="n">
-        <v>0.0145</v>
+        <v>0.0151</v>
       </c>
     </row>
     <row r="57">
@@ -2707,7 +2707,7 @@
         <v>0.00286</v>
       </c>
       <c r="F57" t="n">
-        <v>0.798</v>
+        <v>0.799</v>
       </c>
       <c r="G57" t="n">
         <v>0.875</v>
@@ -2744,10 +2744,10 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.193</v>
+        <v>0.211</v>
       </c>
       <c r="F58" t="n">
-        <v>0.798</v>
+        <v>0.799</v>
       </c>
       <c r="G58" t="n">
         <v>0.832</v>
@@ -2759,7 +2759,7 @@
         <v>0.15</v>
       </c>
       <c r="J58" t="n">
-        <v>0.24</v>
+        <v>0.262</v>
       </c>
     </row>
     <row r="59">
@@ -2784,10 +2784,10 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.0577</v>
+        <v>0.0654</v>
       </c>
       <c r="F59" t="n">
-        <v>0.798</v>
+        <v>0.799</v>
       </c>
       <c r="G59" t="n">
         <v>0.832</v>
@@ -2799,7 +2799,7 @@
         <v>0.15</v>
       </c>
       <c r="J59" t="n">
-        <v>0.0944</v>
+        <v>0.107</v>
       </c>
     </row>
     <row r="60">
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.526</v>
+        <v>0.487</v>
       </c>
       <c r="F60" t="n">
-        <v>0.798</v>
+        <v>0.799</v>
       </c>
       <c r="G60" t="n">
         <v>0.782</v>
@@ -2839,7 +2839,7 @@
         <v>0.188</v>
       </c>
       <c r="J60" t="n">
-        <v>0.574</v>
+        <v>0.531</v>
       </c>
     </row>
     <row r="61">
@@ -2867,7 +2867,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="F61" t="n">
-        <v>0.798</v>
+        <v>0.799</v>
       </c>
       <c r="G61" t="n">
         <v>0.782</v>
@@ -2904,10 +2904,10 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.0134</v>
+        <v>0.0154</v>
       </c>
       <c r="F62" t="n">
-        <v>0.757</v>
+        <v>0.758</v>
       </c>
       <c r="G62" t="n">
         <v>0.791</v>
@@ -2919,7 +2919,7 @@
         <v>0.137</v>
       </c>
       <c r="J62" t="n">
-        <v>0.0288</v>
+        <v>0.0326</v>
       </c>
     </row>
     <row r="63">
@@ -2947,7 +2947,7 @@
         <v>0.0076</v>
       </c>
       <c r="F63" t="n">
-        <v>0.757</v>
+        <v>0.758</v>
       </c>
       <c r="G63" t="n">
         <v>0.791</v>
@@ -2984,10 +2984,10 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.118</v>
+        <v>0.112</v>
       </c>
       <c r="F64" t="n">
-        <v>0.757</v>
+        <v>0.758</v>
       </c>
       <c r="G64" t="n">
         <v>0.718</v>
@@ -2999,7 +2999,7 @@
         <v>0.186</v>
       </c>
       <c r="J64" t="n">
-        <v>0.163</v>
+        <v>0.161</v>
       </c>
     </row>
     <row r="65">
@@ -3024,10 +3024,10 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.175</v>
+        <v>0.159</v>
       </c>
       <c r="F65" t="n">
-        <v>0.757</v>
+        <v>0.758</v>
       </c>
       <c r="G65" t="n">
         <v>0.718</v>
@@ -3039,7 +3039,7 @@
         <v>0.186</v>
       </c>
       <c r="J65" t="n">
-        <v>0.233</v>
+        <v>0.212</v>
       </c>
     </row>
     <row r="66">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.00761</v>
+        <v>0.008160000000000001</v>
       </c>
       <c r="F66" t="n">
-        <v>0.757</v>
+        <v>0.758</v>
       </c>
       <c r="G66" t="n">
         <v>0.82</v>
@@ -3079,7 +3079,7 @@
         <v>0.145</v>
       </c>
       <c r="J66" t="n">
-        <v>0.0249</v>
+        <v>0.0267</v>
       </c>
     </row>
     <row r="67">
@@ -3107,7 +3107,7 @@
         <v>0.00629</v>
       </c>
       <c r="F67" t="n">
-        <v>0.757</v>
+        <v>0.758</v>
       </c>
       <c r="G67" t="n">
         <v>0.82</v>
@@ -3119,7 +3119,7 @@
         <v>0.145</v>
       </c>
       <c r="J67" t="n">
-        <v>0.0192</v>
+        <v>0.0189</v>
       </c>
     </row>
     <row r="68">
@@ -3144,10 +3144,10 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.08989999999999999</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="F68" t="n">
-        <v>0.71</v>
+        <v>0.711</v>
       </c>
       <c r="G68" t="n">
         <v>0.681</v>
@@ -3159,7 +3159,7 @@
         <v>0.149</v>
       </c>
       <c r="J68" t="n">
-        <v>0.141</v>
+        <v>0.137</v>
       </c>
     </row>
     <row r="69">
@@ -3187,7 +3187,7 @@
         <v>0.105</v>
       </c>
       <c r="F69" t="n">
-        <v>0.71</v>
+        <v>0.711</v>
       </c>
       <c r="G69" t="n">
         <v>0.681</v>
@@ -3199,7 +3199,7 @@
         <v>0.149</v>
       </c>
       <c r="J69" t="n">
-        <v>0.151</v>
+        <v>0.158</v>
       </c>
     </row>
     <row r="70">
@@ -3224,10 +3224,10 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.00275</v>
+        <v>0.00256</v>
       </c>
       <c r="F70" t="n">
-        <v>0.71</v>
+        <v>0.711</v>
       </c>
       <c r="G70" t="n">
         <v>0.597</v>
@@ -3239,7 +3239,7 @@
         <v>0.138</v>
       </c>
       <c r="J70" t="n">
-        <v>0.0141</v>
+        <v>0.0132</v>
       </c>
     </row>
     <row r="71">
@@ -3267,7 +3267,7 @@
         <v>0.00121</v>
       </c>
       <c r="F71" t="n">
-        <v>0.71</v>
+        <v>0.711</v>
       </c>
       <c r="G71" t="n">
         <v>0.597</v>
@@ -3304,13 +3304,13 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.24</v>
+        <v>0.238</v>
       </c>
       <c r="F72" t="n">
-        <v>0.71</v>
+        <v>0.711</v>
       </c>
       <c r="G72" t="n">
-        <v>0.735</v>
+        <v>0.736</v>
       </c>
       <c r="H72" t="n">
         <v>0.152</v>
@@ -3319,7 +3319,7 @@
         <v>0.176</v>
       </c>
       <c r="J72" t="n">
-        <v>0.279</v>
+        <v>0.286</v>
       </c>
     </row>
     <row r="73">
@@ -3347,10 +3347,10 @@
         <v>0.211</v>
       </c>
       <c r="F73" t="n">
-        <v>0.71</v>
+        <v>0.711</v>
       </c>
       <c r="G73" t="n">
-        <v>0.735</v>
+        <v>0.736</v>
       </c>
       <c r="H73" t="n">
         <v>0.152</v>
@@ -3359,7 +3359,7 @@
         <v>0.176</v>
       </c>
       <c r="J73" t="n">
-        <v>0.265</v>
+        <v>0.262</v>
       </c>
     </row>
   </sheetData>
@@ -3744,16 +3744,16 @@
         <v>9</v>
       </c>
       <c r="F10" t="n">
-        <v>0.667</v>
+        <v>0.673</v>
       </c>
       <c r="G10" t="n">
         <v>0.747</v>
       </c>
       <c r="H10" t="n">
-        <v>0.163</v>
+        <v>0.203</v>
       </c>
       <c r="I10" t="n">
-        <v>0.367</v>
+        <v>0.364</v>
       </c>
     </row>
     <row r="11">
@@ -3781,16 +3781,16 @@
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>0.853</v>
+        <v>0.86</v>
       </c>
       <c r="G11" t="n">
-        <v>0.873</v>
+        <v>0.88</v>
       </c>
       <c r="H11" t="n">
-        <v>0.737</v>
+        <v>0.732</v>
       </c>
       <c r="I11" t="n">
-        <v>0.879</v>
+        <v>0.854</v>
       </c>
     </row>
     <row r="12">
@@ -3966,16 +3966,16 @@
         <v>15</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="G16" t="n">
         <v>0.86</v>
       </c>
       <c r="H16" t="n">
-        <v>0.000507</v>
+        <v>0.000797</v>
       </c>
       <c r="I16" t="n">
-        <v>0.00152</v>
+        <v>0.00239</v>
       </c>
     </row>
     <row r="17">
@@ -4342,10 +4342,10 @@
         <v>0.948</v>
       </c>
       <c r="H26" t="n">
-        <v>0.229</v>
+        <v>0.227</v>
       </c>
       <c r="I26" t="n">
-        <v>0.858</v>
+        <v>0.854</v>
       </c>
     </row>
     <row r="27">
@@ -4373,10 +4373,10 @@
         <v>10</v>
       </c>
       <c r="F27" t="n">
-        <v>0.928</v>
+        <v>0.929</v>
       </c>
       <c r="G27" t="n">
-        <v>0.931</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="H27" t="n">
         <v>1</v>
@@ -4558,16 +4558,16 @@
         <v>15</v>
       </c>
       <c r="F32" t="n">
-        <v>0.635</v>
+        <v>0.64</v>
       </c>
       <c r="G32" t="n">
         <v>0.859</v>
       </c>
       <c r="H32" t="n">
-        <v>0.00339</v>
+        <v>0.00361</v>
       </c>
       <c r="I32" t="n">
-        <v>0.00763</v>
+        <v>0.00812</v>
       </c>
     </row>
     <row r="33">
@@ -4928,16 +4928,16 @@
         <v>9</v>
       </c>
       <c r="F42" t="n">
-        <v>0.608</v>
+        <v>0.616</v>
       </c>
       <c r="G42" t="n">
         <v>0.736</v>
       </c>
       <c r="H42" t="n">
-        <v>0.043</v>
+        <v>0.0582</v>
       </c>
       <c r="I42" t="n">
-        <v>0.129</v>
+        <v>0.175</v>
       </c>
     </row>
     <row r="43">
@@ -4965,16 +4965,16 @@
         <v>10</v>
       </c>
       <c r="F43" t="n">
-        <v>0.79</v>
+        <v>0.802</v>
       </c>
       <c r="G43" t="n">
-        <v>0.827</v>
+        <v>0.84</v>
       </c>
       <c r="H43" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="I43" t="n">
-        <v>0.776</v>
+        <v>0.767</v>
       </c>
     </row>
     <row r="44">
@@ -5150,16 +5150,16 @@
         <v>15</v>
       </c>
       <c r="F48" t="n">
-        <v>0.701</v>
+        <v>0.716</v>
       </c>
       <c r="G48" t="n">
         <v>0.821</v>
       </c>
       <c r="H48" t="n">
-        <v>0.155</v>
+        <v>0.219</v>
       </c>
       <c r="I48" t="n">
-        <v>0.279</v>
+        <v>0.329</v>
       </c>
     </row>
     <row r="49">
@@ -5520,16 +5520,16 @@
         <v>9</v>
       </c>
       <c r="F58" t="n">
-        <v>0.752</v>
+        <v>0.759</v>
       </c>
       <c r="G58" t="n">
         <v>0.829</v>
       </c>
       <c r="H58" t="n">
-        <v>0.056</v>
+        <v>0.0917</v>
       </c>
       <c r="I58" t="n">
-        <v>0.126</v>
+        <v>0.207</v>
       </c>
     </row>
     <row r="59">
@@ -5557,16 +5557,16 @@
         <v>10</v>
       </c>
       <c r="F59" t="n">
-        <v>0.853</v>
+        <v>0.861</v>
       </c>
       <c r="G59" t="n">
-        <v>0.876</v>
+        <v>0.883</v>
       </c>
       <c r="H59" t="n">
-        <v>0.616</v>
+        <v>0.609</v>
       </c>
       <c r="I59" t="n">
-        <v>0.728</v>
+        <v>0.6850000000000001</v>
       </c>
     </row>
     <row r="60">
@@ -5742,16 +5742,16 @@
         <v>15</v>
       </c>
       <c r="F64" t="n">
-        <v>0.667</v>
+        <v>0.676</v>
       </c>
       <c r="G64" t="n">
         <v>0.84</v>
       </c>
       <c r="H64" t="n">
-        <v>0.0012</v>
+        <v>0.00191</v>
       </c>
       <c r="I64" t="n">
-        <v>0.0108</v>
+        <v>0.0124</v>
       </c>
     </row>
     <row r="65">
@@ -6112,16 +6112,16 @@
         <v>9</v>
       </c>
       <c r="F74" t="n">
-        <v>0.667</v>
+        <v>0.673</v>
       </c>
       <c r="G74" t="n">
         <v>0.78</v>
       </c>
       <c r="H74" t="n">
-        <v>0.0386</v>
+        <v>0.0516</v>
       </c>
       <c r="I74" t="n">
-        <v>0.174</v>
+        <v>0.232</v>
       </c>
     </row>
     <row r="75">
@@ -6149,16 +6149,16 @@
         <v>10</v>
       </c>
       <c r="F75" t="n">
-        <v>0.853</v>
+        <v>0.86</v>
       </c>
       <c r="G75" t="n">
         <v>0.893</v>
       </c>
       <c r="H75" t="n">
-        <v>0.386</v>
+        <v>0.483</v>
       </c>
       <c r="I75" t="n">
-        <v>0.695</v>
+        <v>0.854</v>
       </c>
     </row>
     <row r="76">
@@ -6334,16 +6334,16 @@
         <v>15</v>
       </c>
       <c r="F80" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="G80" t="n">
         <v>0.753</v>
       </c>
       <c r="H80" t="n">
-        <v>0.247</v>
+        <v>0.302</v>
       </c>
       <c r="I80" t="n">
-        <v>0.37</v>
+        <v>0.453</v>
       </c>
     </row>
     <row r="81">
@@ -6710,10 +6710,10 @@
         <v>0.96</v>
       </c>
       <c r="H90" t="n">
-        <v>0.389</v>
+        <v>0.387</v>
       </c>
       <c r="I90" t="n">
-        <v>0.858</v>
+        <v>0.854</v>
       </c>
     </row>
     <row r="91">
@@ -6741,7 +6741,7 @@
         <v>10</v>
       </c>
       <c r="F91" t="n">
-        <v>0.928</v>
+        <v>0.929</v>
       </c>
       <c r="G91" t="n">
         <v>0.9330000000000001</v>
@@ -6926,16 +6926,16 @@
         <v>15</v>
       </c>
       <c r="F96" t="n">
-        <v>0.635</v>
+        <v>0.64</v>
       </c>
       <c r="G96" t="n">
         <v>0.768</v>
       </c>
       <c r="H96" t="n">
-        <v>0.126</v>
+        <v>0.129</v>
       </c>
       <c r="I96" t="n">
-        <v>0.189</v>
+        <v>0.194</v>
       </c>
     </row>
     <row r="97">
@@ -7296,16 +7296,16 @@
         <v>9</v>
       </c>
       <c r="F106" t="n">
-        <v>0.608</v>
+        <v>0.616</v>
       </c>
       <c r="G106" t="n">
         <v>0.768</v>
       </c>
       <c r="H106" t="n">
-        <v>0.00927</v>
+        <v>0.0134</v>
       </c>
       <c r="I106" t="n">
-        <v>0.0417</v>
+        <v>0.0603</v>
       </c>
     </row>
     <row r="107">
@@ -7333,16 +7333,16 @@
         <v>10</v>
       </c>
       <c r="F107" t="n">
-        <v>0.79</v>
+        <v>0.802</v>
       </c>
       <c r="G107" t="n">
         <v>0.864</v>
       </c>
       <c r="H107" t="n">
-        <v>0.299</v>
+        <v>0.399</v>
       </c>
       <c r="I107" t="n">
-        <v>0.538</v>
+        <v>0.599</v>
       </c>
     </row>
     <row r="108">
@@ -7518,16 +7518,16 @@
         <v>15</v>
       </c>
       <c r="F112" t="n">
-        <v>0.701</v>
+        <v>0.716</v>
       </c>
       <c r="G112" t="n">
         <v>0.642</v>
       </c>
       <c r="H112" t="n">
-        <v>0.581</v>
+        <v>0.459</v>
       </c>
       <c r="I112" t="n">
-        <v>0.581</v>
+        <v>0.459</v>
       </c>
     </row>
     <row r="113">
@@ -7888,16 +7888,16 @@
         <v>9</v>
       </c>
       <c r="F122" t="n">
-        <v>0.752</v>
+        <v>0.759</v>
       </c>
       <c r="G122" t="n">
         <v>0.853</v>
       </c>
       <c r="H122" t="n">
-        <v>0.01</v>
+        <v>0.0141</v>
       </c>
       <c r="I122" t="n">
-        <v>0.045</v>
+        <v>0.0634</v>
       </c>
     </row>
     <row r="123">
@@ -7925,16 +7925,16 @@
         <v>10</v>
       </c>
       <c r="F123" t="n">
-        <v>0.853</v>
+        <v>0.861</v>
       </c>
       <c r="G123" t="n">
         <v>0.897</v>
       </c>
       <c r="H123" t="n">
-        <v>0.299</v>
+        <v>0.382</v>
       </c>
       <c r="I123" t="n">
-        <v>0.538</v>
+        <v>0.6850000000000001</v>
       </c>
     </row>
     <row r="124">
@@ -8110,13 +8110,13 @@
         <v>15</v>
       </c>
       <c r="F128" t="n">
-        <v>0.667</v>
+        <v>0.676</v>
       </c>
       <c r="G128" t="n">
         <v>0.699</v>
       </c>
       <c r="H128" t="n">
-        <v>0.598</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="I128" t="n">
         <v>0.793</v>
@@ -8480,16 +8480,16 @@
         <v>9</v>
       </c>
       <c r="F138" t="n">
-        <v>0.667</v>
+        <v>0.673</v>
       </c>
       <c r="G138" t="n">
         <v>0.713</v>
       </c>
       <c r="H138" t="n">
-        <v>0.454</v>
+        <v>0.531</v>
       </c>
       <c r="I138" t="n">
-        <v>0.534</v>
+        <v>0.597</v>
       </c>
     </row>
     <row r="139">
@@ -8517,16 +8517,16 @@
         <v>10</v>
       </c>
       <c r="F139" t="n">
-        <v>0.853</v>
+        <v>0.86</v>
       </c>
       <c r="G139" t="n">
         <v>0.867</v>
       </c>
       <c r="H139" t="n">
-        <v>0.868</v>
+        <v>1</v>
       </c>
       <c r="I139" t="n">
-        <v>0.879</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140">
@@ -8702,16 +8702,16 @@
         <v>15</v>
       </c>
       <c r="F144" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="G144" t="n">
         <v>0.713</v>
       </c>
       <c r="H144" t="n">
-        <v>0.706</v>
+        <v>0.801</v>
       </c>
       <c r="I144" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.901</v>
       </c>
     </row>
     <row r="145">
@@ -9078,10 +9078,10 @@
         <v>0.966</v>
       </c>
       <c r="H154" t="n">
-        <v>0.624</v>
+        <v>0.623</v>
       </c>
       <c r="I154" t="n">
-        <v>0.858</v>
+        <v>0.854</v>
       </c>
     </row>
     <row r="155">
@@ -9109,13 +9109,13 @@
         <v>10</v>
       </c>
       <c r="F155" t="n">
-        <v>0.928</v>
+        <v>0.929</v>
       </c>
       <c r="G155" t="n">
         <v>0.955</v>
       </c>
       <c r="H155" t="n">
-        <v>0.718</v>
+        <v>0.719</v>
       </c>
       <c r="I155" t="n">
         <v>1</v>
@@ -9294,13 +9294,13 @@
         <v>15</v>
       </c>
       <c r="F160" t="n">
-        <v>0.635</v>
+        <v>0.64</v>
       </c>
       <c r="G160" t="n">
         <v>0.707</v>
       </c>
       <c r="H160" t="n">
-        <v>0.458</v>
+        <v>0.461</v>
       </c>
       <c r="I160" t="n">
         <v>0.523</v>
@@ -9664,16 +9664,16 @@
         <v>9</v>
       </c>
       <c r="F170" t="n">
-        <v>0.608</v>
+        <v>0.616</v>
       </c>
       <c r="G170" t="n">
         <v>0.68</v>
       </c>
       <c r="H170" t="n">
-        <v>0.291</v>
+        <v>0.354</v>
       </c>
       <c r="I170" t="n">
-        <v>0.423</v>
+        <v>0.398</v>
       </c>
     </row>
     <row r="171">
@@ -9701,7 +9701,7 @@
         <v>10</v>
       </c>
       <c r="F171" t="n">
-        <v>0.79</v>
+        <v>0.802</v>
       </c>
       <c r="G171" t="n">
         <v>0.79</v>
@@ -9886,16 +9886,16 @@
         <v>15</v>
       </c>
       <c r="F176" t="n">
-        <v>0.701</v>
+        <v>0.716</v>
       </c>
       <c r="G176" t="n">
         <v>0.612</v>
       </c>
       <c r="H176" t="n">
-        <v>0.363</v>
+        <v>0.272</v>
       </c>
       <c r="I176" t="n">
-        <v>0.408</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="177">
@@ -10256,16 +10256,16 @@
         <v>9</v>
       </c>
       <c r="F186" t="n">
-        <v>0.752</v>
+        <v>0.759</v>
       </c>
       <c r="G186" t="n">
         <v>0.798</v>
       </c>
       <c r="H186" t="n">
-        <v>0.29</v>
+        <v>0.347</v>
       </c>
       <c r="I186" t="n">
-        <v>0.326</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="187">
@@ -10293,16 +10293,16 @@
         <v>10</v>
       </c>
       <c r="F187" t="n">
-        <v>0.853</v>
+        <v>0.861</v>
       </c>
       <c r="G187" t="n">
         <v>0.865</v>
       </c>
       <c r="H187" t="n">
-        <v>0.868</v>
+        <v>1</v>
       </c>
       <c r="I187" t="n">
-        <v>0.868</v>
+        <v>1</v>
       </c>
     </row>
     <row r="188">
@@ -10478,16 +10478,16 @@
         <v>15</v>
       </c>
       <c r="F192" t="n">
-        <v>0.667</v>
+        <v>0.676</v>
       </c>
       <c r="G192" t="n">
         <v>0.656</v>
       </c>
       <c r="H192" t="n">
-        <v>0.897</v>
+        <v>0.795</v>
       </c>
       <c r="I192" t="n">
-        <v>0.897</v>
+        <v>0.795</v>
       </c>
     </row>
     <row r="193">
@@ -10848,16 +10848,16 @@
         <v>9</v>
       </c>
       <c r="F202" t="n">
-        <v>0.667</v>
+        <v>0.68</v>
       </c>
       <c r="G202" t="n">
         <v>0.707</v>
       </c>
       <c r="H202" t="n">
-        <v>0.534</v>
+        <v>0.707</v>
       </c>
       <c r="I202" t="n">
-        <v>0.534</v>
+        <v>0.707</v>
       </c>
     </row>
     <row r="203">
@@ -11440,16 +11440,16 @@
         <v>9</v>
       </c>
       <c r="F218" t="n">
-        <v>0.963</v>
+        <v>0.964</v>
       </c>
       <c r="G218" t="n">
         <v>0.988</v>
       </c>
       <c r="H218" t="n">
-        <v>0.364</v>
+        <v>0.62</v>
       </c>
       <c r="I218" t="n">
-        <v>0.858</v>
+        <v>0.854</v>
       </c>
     </row>
     <row r="219">
@@ -12032,16 +12032,16 @@
         <v>9</v>
       </c>
       <c r="F234" t="n">
-        <v>0.624</v>
+        <v>0.64</v>
       </c>
       <c r="G234" t="n">
         <v>0.656</v>
       </c>
       <c r="H234" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.895</v>
       </c>
       <c r="I234" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.895</v>
       </c>
     </row>
     <row r="235">
@@ -12624,16 +12624,16 @@
         <v>9</v>
       </c>
       <c r="F250" t="n">
-        <v>0.757</v>
+        <v>0.769</v>
       </c>
       <c r="G250" t="n">
         <v>0.788</v>
       </c>
       <c r="H250" t="n">
-        <v>0.483</v>
+        <v>0.723</v>
       </c>
       <c r="I250" t="n">
-        <v>0.483</v>
+        <v>0.723</v>
       </c>
     </row>
     <row r="251">
@@ -13216,16 +13216,16 @@
         <v>9</v>
       </c>
       <c r="F266" t="n">
-        <v>0.667</v>
+        <v>0.68</v>
       </c>
       <c r="G266" t="n">
         <v>0.607</v>
       </c>
       <c r="H266" t="n">
-        <v>0.337</v>
+        <v>0.228</v>
       </c>
       <c r="I266" t="n">
-        <v>0.526</v>
+        <v>0.364</v>
       </c>
     </row>
     <row r="267">
@@ -13262,7 +13262,7 @@
         <v>0.665</v>
       </c>
       <c r="I267" t="n">
-        <v>0.879</v>
+        <v>0.854</v>
       </c>
     </row>
     <row r="268">
@@ -13808,16 +13808,16 @@
         <v>9</v>
       </c>
       <c r="F282" t="n">
-        <v>0.963</v>
+        <v>0.964</v>
       </c>
       <c r="G282" t="n">
         <v>0.985</v>
       </c>
       <c r="H282" t="n">
-        <v>0.626</v>
+        <v>0.628</v>
       </c>
       <c r="I282" t="n">
-        <v>0.858</v>
+        <v>0.854</v>
       </c>
     </row>
     <row r="283">
@@ -14400,16 +14400,16 @@
         <v>9</v>
       </c>
       <c r="F298" t="n">
-        <v>0.624</v>
+        <v>0.64</v>
       </c>
       <c r="G298" t="n">
         <v>0.536</v>
       </c>
       <c r="H298" t="n">
-        <v>0.2</v>
+        <v>0.123</v>
       </c>
       <c r="I298" t="n">
-        <v>0.36</v>
+        <v>0.239</v>
       </c>
     </row>
     <row r="299">
@@ -14446,7 +14446,7 @@
         <v>0.623</v>
       </c>
       <c r="I299" t="n">
-        <v>0.776</v>
+        <v>0.767</v>
       </c>
     </row>
     <row r="300">
@@ -14992,16 +14992,16 @@
         <v>9</v>
       </c>
       <c r="F314" t="n">
-        <v>0.757</v>
+        <v>0.769</v>
       </c>
       <c r="G314" t="n">
         <v>0.694</v>
       </c>
       <c r="H314" t="n">
-        <v>0.178</v>
+        <v>0.0919</v>
       </c>
       <c r="I314" t="n">
-        <v>0.32</v>
+        <v>0.207</v>
       </c>
     </row>
     <row r="315">
@@ -15038,7 +15038,7 @@
         <v>0.5580000000000001</v>
       </c>
       <c r="I315" t="n">
-        <v>0.728</v>
+        <v>0.6850000000000001</v>
       </c>
     </row>
     <row r="316">
@@ -15584,16 +15584,16 @@
         <v>9</v>
       </c>
       <c r="F330" t="n">
-        <v>0.667</v>
+        <v>0.68</v>
       </c>
       <c r="G330" t="n">
         <v>0.753</v>
       </c>
       <c r="H330" t="n">
-        <v>0.127</v>
+        <v>0.2</v>
       </c>
       <c r="I330" t="n">
-        <v>0.367</v>
+        <v>0.364</v>
       </c>
     </row>
     <row r="331">
@@ -16176,7 +16176,7 @@
         <v>9</v>
       </c>
       <c r="F346" t="n">
-        <v>0.963</v>
+        <v>0.964</v>
       </c>
       <c r="G346" t="n">
         <v>0.958</v>
@@ -16768,16 +16768,16 @@
         <v>9</v>
       </c>
       <c r="F362" t="n">
-        <v>0.624</v>
+        <v>0.64</v>
       </c>
       <c r="G362" t="n">
         <v>0.736</v>
       </c>
       <c r="H362" t="n">
-        <v>0.0776</v>
+        <v>0.133</v>
       </c>
       <c r="I362" t="n">
-        <v>0.175</v>
+        <v>0.239</v>
       </c>
     </row>
     <row r="363">
@@ -17360,16 +17360,16 @@
         <v>9</v>
       </c>
       <c r="F378" t="n">
-        <v>0.757</v>
+        <v>0.769</v>
       </c>
       <c r="G378" t="n">
         <v>0.833</v>
       </c>
       <c r="H378" t="n">
-        <v>0.0556</v>
+        <v>0.115</v>
       </c>
       <c r="I378" t="n">
-        <v>0.126</v>
+        <v>0.207</v>
       </c>
     </row>
     <row r="379">
@@ -17952,16 +17952,16 @@
         <v>9</v>
       </c>
       <c r="F394" t="n">
-        <v>0.6</v>
+        <v>0.613</v>
       </c>
       <c r="G394" t="n">
         <v>0.553</v>
       </c>
       <c r="H394" t="n">
-        <v>0.483</v>
+        <v>0.349</v>
       </c>
       <c r="I394" t="n">
-        <v>0.534</v>
+        <v>0.449</v>
       </c>
     </row>
     <row r="395">
@@ -18544,7 +18544,7 @@
         <v>9</v>
       </c>
       <c r="F410" t="n">
-        <v>0.971</v>
+        <v>0.972</v>
       </c>
       <c r="G410" t="n">
         <v>0.983</v>
@@ -19136,16 +19136,16 @@
         <v>9</v>
       </c>
       <c r="F426" t="n">
-        <v>0.536</v>
+        <v>0.552</v>
       </c>
       <c r="G426" t="n">
         <v>0.472</v>
       </c>
       <c r="H426" t="n">
-        <v>0.376</v>
+        <v>0.255</v>
       </c>
       <c r="I426" t="n">
-        <v>0.423</v>
+        <v>0.328</v>
       </c>
     </row>
     <row r="427">
@@ -19367,7 +19367,7 @@
         <v>0.211</v>
       </c>
       <c r="I432" t="n">
-        <v>0.317</v>
+        <v>0.329</v>
       </c>
     </row>
     <row r="433">
@@ -19728,16 +19728,16 @@
         <v>9</v>
       </c>
       <c r="F442" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.704</v>
       </c>
       <c r="G442" t="n">
         <v>0.638</v>
       </c>
       <c r="H442" t="n">
-        <v>0.279</v>
+        <v>0.191</v>
       </c>
       <c r="I442" t="n">
-        <v>0.326</v>
+        <v>0.246</v>
       </c>
     </row>
     <row r="443">
@@ -20320,16 +20320,16 @@
         <v>9</v>
       </c>
       <c r="F458" t="n">
-        <v>0.6</v>
+        <v>0.613</v>
       </c>
       <c r="G458" t="n">
         <v>0.54</v>
       </c>
       <c r="H458" t="n">
-        <v>0.351</v>
+        <v>0.243</v>
       </c>
       <c r="I458" t="n">
-        <v>0.526</v>
+        <v>0.364</v>
       </c>
     </row>
     <row r="459">
@@ -20551,7 +20551,7 @@
         <v>0.72</v>
       </c>
       <c r="I464" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.901</v>
       </c>
     </row>
     <row r="465">
@@ -20912,16 +20912,16 @@
         <v>9</v>
       </c>
       <c r="F474" t="n">
-        <v>0.971</v>
+        <v>0.972</v>
       </c>
       <c r="G474" t="n">
         <v>0.952</v>
       </c>
       <c r="H474" t="n">
-        <v>0.667</v>
+        <v>0.664</v>
       </c>
       <c r="I474" t="n">
-        <v>0.858</v>
+        <v>0.854</v>
       </c>
     </row>
     <row r="475">
@@ -21504,16 +21504,16 @@
         <v>9</v>
       </c>
       <c r="F490" t="n">
-        <v>0.536</v>
+        <v>0.552</v>
       </c>
       <c r="G490" t="n">
         <v>0.472</v>
       </c>
       <c r="H490" t="n">
-        <v>0.376</v>
+        <v>0.255</v>
       </c>
       <c r="I490" t="n">
-        <v>0.423</v>
+        <v>0.328</v>
       </c>
     </row>
     <row r="491">
@@ -22096,16 +22096,16 @@
         <v>9</v>
       </c>
       <c r="F506" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.704</v>
       </c>
       <c r="G506" t="n">
         <v>0.631</v>
       </c>
       <c r="H506" t="n">
-        <v>0.235</v>
+        <v>0.158</v>
       </c>
       <c r="I506" t="n">
-        <v>0.326</v>
+        <v>0.237</v>
       </c>
     </row>
     <row r="507">
@@ -22688,16 +22688,16 @@
         <v>9</v>
       </c>
       <c r="F522" t="n">
-        <v>0.6</v>
+        <v>0.613</v>
       </c>
       <c r="G522" t="n">
         <v>0.787</v>
       </c>
       <c r="H522" t="n">
-        <v>0.000679</v>
+        <v>0.00156</v>
       </c>
       <c r="I522" t="n">
-        <v>0.00611</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="523">
@@ -22728,13 +22728,13 @@
         <v>0.82</v>
       </c>
       <c r="G523" t="n">
-        <v>0.833</v>
+        <v>0.84</v>
       </c>
       <c r="H523" t="n">
-        <v>0.879</v>
+        <v>0.759</v>
       </c>
       <c r="I523" t="n">
-        <v>0.879</v>
+        <v>0.854</v>
       </c>
     </row>
     <row r="524">
@@ -23280,16 +23280,16 @@
         <v>9</v>
       </c>
       <c r="F538" t="n">
-        <v>0.971</v>
+        <v>0.972</v>
       </c>
       <c r="G538" t="n">
         <v>0.9429999999999999</v>
       </c>
       <c r="H538" t="n">
-        <v>0.481</v>
+        <v>0.477</v>
       </c>
       <c r="I538" t="n">
-        <v>0.858</v>
+        <v>0.854</v>
       </c>
     </row>
     <row r="539">
@@ -23320,10 +23320,10 @@
         <v>0.95</v>
       </c>
       <c r="G539" t="n">
-        <v>0.9</v>
+        <v>0.901</v>
       </c>
       <c r="H539" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="I539" t="n">
         <v>1</v>
@@ -23872,16 +23872,16 @@
         <v>9</v>
       </c>
       <c r="F554" t="n">
-        <v>0.536</v>
+        <v>0.552</v>
       </c>
       <c r="G554" t="n">
         <v>0.792</v>
       </c>
       <c r="H554" t="n">
-        <v>2.84e-05</v>
+        <v>8.27e-05</v>
       </c>
       <c r="I554" t="n">
-        <v>0.000256</v>
+        <v>0.000744</v>
       </c>
     </row>
     <row r="555">
@@ -23912,13 +23912,13 @@
         <v>0.704</v>
       </c>
       <c r="G555" t="n">
-        <v>0.778</v>
+        <v>0.79</v>
       </c>
       <c r="H555" t="n">
-        <v>0.37</v>
+        <v>0.278</v>
       </c>
       <c r="I555" t="n">
-        <v>0.555</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="556">
@@ -24103,7 +24103,7 @@
         <v>0.33</v>
       </c>
       <c r="I560" t="n">
-        <v>0.408</v>
+        <v>0.371</v>
       </c>
     </row>
     <row r="561">
@@ -24464,16 +24464,16 @@
         <v>9</v>
       </c>
       <c r="F570" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.704</v>
       </c>
       <c r="G570" t="n">
         <v>0.861</v>
       </c>
       <c r="H570" t="n">
-        <v>3e-05</v>
+        <v>0.000122</v>
       </c>
       <c r="I570" t="n">
-        <v>0.00027</v>
+        <v>0.0011</v>
       </c>
     </row>
     <row r="571">
@@ -24504,13 +24504,13 @@
         <v>0.8090000000000001</v>
       </c>
       <c r="G571" t="n">
-        <v>0.834</v>
+        <v>0.842</v>
       </c>
       <c r="H571" t="n">
-        <v>0.647</v>
+        <v>0.538</v>
       </c>
       <c r="I571" t="n">
-        <v>0.728</v>
+        <v>0.6850000000000001</v>
       </c>
     </row>
     <row r="572">
@@ -24992,7 +24992,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>63.5</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -25007,7 +25007,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>70.1</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -25487,7 +25487,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>97.1</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -25502,7 +25502,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>55.2</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
